--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="254">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -334,6 +334,21 @@
     <t xml:space="preserve">to-12-coolray-1-main.png</t>
   </si>
   <si>
+    <t xml:space="preserve">TO-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kia Picanto 1.0 / 1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G3LA 1.0 / G4LA 1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТО-кит Kia Picanto 1.0/1.2: масло и фильтры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to-13-picanto-1-main.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">GRM-01</t>
   </si>
   <si>
@@ -578,6 +593,30 @@
   </si>
   <si>
     <t xml:space="preserve">Поставьте 1, если объём заливки с фильтром больше 4 л (проверьте по VIN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyundai/Kia Super Extra Gasoline 5W-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 2 051,00 ₽ — впишите в колонку поставщика, у которого брали. Проверьте допуск: для Picanto рекомендуют API SM / ILSAC GF-4 и выше.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 154,70 ₽ — впишите в колонку поставщика, у которого брали.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 533,00 ₽ — впишите в колонку поставщика, у которого брали.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIG FILTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 387,00 ₽ — впишите в колонку поставщика, у которого брали.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена по стандартному составу ТО-кита; подберите по VIN (обычно 30–60 ₽).</t>
   </si>
   <si>
     <t xml:space="preserve">Комплект цепи ГРМ (цепь, натяжитель, успокоители)</t>
@@ -1394,7 +1433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2118,13 +2157,13 @@
         <v>91</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>32</v>
@@ -2133,10 +2172,10 @@
         <v>33</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I14" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)+Параметры!$B$3)</f>
@@ -2144,7 +2183,7 @@
       </c>
       <c r="J14" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A14,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" s="11" t="str">
         <f aca="false">IF(I14="","",CEILING(I14*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2169,16 +2208,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>32</v>
@@ -2187,10 +2226,10 @@
         <v>33</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I15" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)+Параметры!$B$3)</f>
@@ -2223,16 +2262,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>32</v>
@@ -2241,10 +2280,10 @@
         <v>33</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I16" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)+Параметры!$B$3)</f>
@@ -2277,16 +2316,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>32</v>
@@ -2295,10 +2334,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I17" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)+Параметры!$B$3)</f>
@@ -2331,28 +2370,28 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I18" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)+Параметры!$B$3)</f>
@@ -2385,28 +2424,28 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I19" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)+Параметры!$B$3)</f>
@@ -2414,7 +2453,7 @@
       </c>
       <c r="J19" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A19,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="11" t="str">
         <f aca="false">IF(I19="","",CEILING(I19*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2439,28 +2478,28 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I20" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)+Параметры!$B$3)</f>
@@ -2468,7 +2507,7 @@
       </c>
       <c r="J20" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A20,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" s="11" t="str">
         <f aca="false">IF(I20="","",CEILING(I20*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2493,28 +2532,28 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I21" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)+Параметры!$B$3)</f>
@@ -2547,28 +2586,28 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I22" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)+Параметры!$B$3)</f>
@@ -2601,22 +2640,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>123</v>
@@ -2658,25 +2697,25 @@
         <v>125</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I24" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)+Параметры!$B$3)</f>
@@ -2684,7 +2723,7 @@
       </c>
       <c r="J24" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A24,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="11" t="str">
         <f aca="false">IF(I24="","",CEILING(I24*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2707,19 +2746,73 @@
         <v>36</v>
       </c>
     </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="9" t="str">
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)+Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="J25" s="10" t="n">
+        <f aca="false">COUNTIFS(Состав!$A:$A,A25,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="K25" s="11" t="str">
+        <f aca="false">IF(I25="","",CEILING(I25*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="7" t="str">
+        <f aca="false">IF(OR(K25="",L25=""),"",IF(K25&lt;=L25,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="N25" s="9" t="str">
+        <f aca="false">IF(K25="","",K25-I25-K25*Параметры!$B$6-Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O25" s="13" t="str">
+        <f aca="false">IF(N25="","",N25/K25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J24">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"дороже рынка"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P24" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P25" type="list">
       <formula1>"не выложен,выложен,есть продажи,снят"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2750,79 +2843,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B2" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2841,7 +2934,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S120"/>
+  <dimension ref="A1:S125"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2865,75 +2958,75 @@
         <v>14</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G2" s="19" t="n">
         <v>460</v>
@@ -2965,7 +3058,7 @@
         <v>430</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2977,7 +3070,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -3006,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3018,7 +3111,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -3057,7 +3150,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -3096,7 +3189,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -3135,7 +3228,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -3174,7 +3267,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -3203,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3215,7 +3308,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -3254,7 +3347,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -3293,7 +3386,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -3332,7 +3425,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -3371,7 +3464,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -3400,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3412,7 +3505,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -3451,7 +3544,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -3490,7 +3583,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -3529,7 +3622,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -3568,7 +3661,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -3597,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3609,7 +3702,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -3648,7 +3741,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -3687,7 +3780,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -3726,7 +3819,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -3765,7 +3858,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -3794,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3806,7 +3899,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -3845,7 +3938,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -3884,7 +3977,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -3923,7 +4016,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -3962,7 +4055,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -3991,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4003,7 +4096,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -4042,7 +4135,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -4081,7 +4174,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -4120,7 +4213,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -4159,7 +4252,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -4188,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4200,7 +4293,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -4229,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4241,7 +4334,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -4280,7 +4373,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -4319,7 +4412,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -4358,7 +4451,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -4397,7 +4490,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -4426,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4438,7 +4531,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -4467,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4479,7 +4572,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -4518,7 +4611,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -4557,7 +4650,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -4596,7 +4689,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -4635,7 +4728,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -4664,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4676,7 +4769,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -4705,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4717,7 +4810,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -4756,7 +4849,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -4795,7 +4888,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -4834,7 +4927,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -4873,7 +4966,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -4902,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4914,7 +5007,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -4943,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4955,7 +5048,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -4994,7 +5087,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -5033,7 +5126,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -5072,7 +5165,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -5111,7 +5204,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -5140,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5152,7 +5245,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -5181,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5193,7 +5286,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -5232,7 +5325,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -5271,7 +5364,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -5310,7 +5403,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -5349,7 +5442,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -5378,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5390,7 +5483,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -5419,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5431,7 +5524,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -5470,7 +5563,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -5509,7 +5602,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -5548,7 +5641,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -5578,21 +5671,23 @@
       </c>
       <c r="S68" s="8"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
         <v>91</v>
       </c>
       <c r="B69" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A69,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="14"/>
+      <c r="E69" s="14" t="s">
+        <v>178</v>
+      </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
@@ -5616,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5625,15 +5720,17 @@
       </c>
       <c r="B70" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A70,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="14"/>
+      <c r="E70" s="14" t="s">
+        <v>180</v>
+      </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12"/>
@@ -5656,7 +5753,9 @@
         <f aca="false">IF(P70="",0,P70*D70)</f>
         <v>0</v>
       </c>
-      <c r="S70" s="8"/>
+      <c r="S70" s="8" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
@@ -5664,15 +5763,17 @@
       </c>
       <c r="B71" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A71,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="14"/>
+      <c r="E71" s="14" t="s">
+        <v>180</v>
+      </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
@@ -5695,7 +5796,9 @@
         <f aca="false">IF(P71="",0,P71*D71)</f>
         <v>0</v>
       </c>
-      <c r="S71" s="8"/>
+      <c r="S71" s="8" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
@@ -5703,15 +5806,17 @@
       </c>
       <c r="B72" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A72,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>183</v>
+      </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12"/>
@@ -5735,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,13 +5849,13 @@
       </c>
       <c r="B73" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A73,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="14"/>
       <c r="F73" s="14"/>
@@ -5776,19 +5881,19 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B74" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A74,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
@@ -5817,19 +5922,19 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B75" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A75,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
@@ -5861,14 +5966,14 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B76" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A76,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
@@ -5900,14 +6005,14 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B77" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A77,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>0</v>
@@ -5936,19 +6041,19 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B78" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A78,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>0</v>
@@ -5977,19 +6082,19 @@
         <v>0</v>
       </c>
       <c r="S78" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B79" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A79,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -6018,19 +6123,19 @@
         <v>0</v>
       </c>
       <c r="S79" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B80" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A80,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>1</v>
@@ -6062,14 +6167,14 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B81" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A81,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>1</v>
@@ -6101,14 +6206,14 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B82" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A82,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>0</v>
@@ -6137,19 +6242,19 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B83" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A83,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>0</v>
@@ -6178,19 +6283,19 @@
         <v>0</v>
       </c>
       <c r="S83" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B84" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A84,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -6219,19 +6324,19 @@
         <v>0</v>
       </c>
       <c r="S84" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B85" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A85,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>1</v>
@@ -6263,14 +6368,14 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B86" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A86,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>1</v>
@@ -6302,14 +6407,14 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B87" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A87,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>0</v>
@@ -6338,19 +6443,19 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B88" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A88,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>0</v>
@@ -6379,19 +6484,19 @@
         <v>0</v>
       </c>
       <c r="S88" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B89" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A89,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -6420,19 +6525,19 @@
         <v>0</v>
       </c>
       <c r="S89" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B90" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A90,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>1</v>
@@ -6464,14 +6569,14 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B91" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A91,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>1</v>
@@ -6503,14 +6608,14 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B92" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A92,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>0</v>
@@ -6539,19 +6644,19 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B93" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A93,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>0</v>
@@ -6580,19 +6685,19 @@
         <v>0</v>
       </c>
       <c r="S93" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B94" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A94,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -6620,21 +6725,23 @@
         <f aca="false">IF(P94="",0,P94*D94)</f>
         <v>0</v>
       </c>
-      <c r="S94" s="8"/>
+      <c r="S94" s="8" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B95" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A95,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="14"/>
       <c r="F95" s="14"/>
@@ -6659,23 +6766,21 @@
         <f aca="false">IF(P95="",0,P95*D95)</f>
         <v>0</v>
       </c>
-      <c r="S95" s="8" t="s">
-        <v>178</v>
-      </c>
+      <c r="S95" s="8"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B96" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A96,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="14"/>
       <c r="F96" s="14"/>
@@ -6700,23 +6805,21 @@
         <f aca="false">IF(P96="",0,P96*D96)</f>
         <v>0</v>
       </c>
-      <c r="S96" s="8" t="s">
-        <v>180</v>
-      </c>
+      <c r="S96" s="8"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B97" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A97,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="D97" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="14"/>
       <c r="F97" s="14"/>
@@ -6742,22 +6845,22 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B98" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A98,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="D98" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="14"/>
       <c r="F98" s="14"/>
@@ -6782,18 +6885,20 @@
         <f aca="false">IF(P98="",0,P98*D98)</f>
         <v>0</v>
       </c>
-      <c r="S98" s="8"/>
+      <c r="S98" s="8" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B99" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A99,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -6825,14 +6930,14 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B100" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A100,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -6861,19 +6966,19 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B101" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A101,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -6902,19 +7007,19 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B102" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A102,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -6943,19 +7048,19 @@
         <v>0</v>
       </c>
       <c r="S102" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B103" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A103,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>1</v>
@@ -6987,14 +7092,14 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B104" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A104,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>1</v>
@@ -7026,14 +7131,14 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B105" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A105,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>0</v>
@@ -7062,19 +7167,19 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B106" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A106,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>0</v>
@@ -7103,19 +7208,19 @@
         <v>0</v>
       </c>
       <c r="S106" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B107" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A107,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -7144,19 +7249,19 @@
         <v>0</v>
       </c>
       <c r="S107" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B108" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A108,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>1</v>
@@ -7188,14 +7293,14 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B109" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A109,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>1</v>
@@ -7227,14 +7332,14 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B110" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A110,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>0</v>
@@ -7263,19 +7368,19 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B111" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A111,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>0</v>
@@ -7304,19 +7409,19 @@
         <v>0</v>
       </c>
       <c r="S111" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B112" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A112,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -7345,19 +7450,19 @@
         <v>0</v>
       </c>
       <c r="S112" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B113" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A113,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>1</v>
@@ -7389,14 +7494,14 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B114" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A114,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>1</v>
@@ -7428,14 +7533,14 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B115" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A115,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>0</v>
@@ -7464,19 +7569,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B116" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A116,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>0</v>
@@ -7505,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="S116" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7514,10 +7619,10 @@
       </c>
       <c r="B117" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A117,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -7545,7 +7650,9 @@
         <f aca="false">IF(P117="",0,P117*D117)</f>
         <v>0</v>
       </c>
-      <c r="S117" s="8"/>
+      <c r="S117" s="8" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
@@ -7553,10 +7660,10 @@
       </c>
       <c r="B118" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A118,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>1</v>
@@ -7584,9 +7691,7 @@
         <f aca="false">IF(P118="",0,P118*D118)</f>
         <v>0</v>
       </c>
-      <c r="S118" s="8" t="s">
-        <v>183</v>
-      </c>
+      <c r="S118" s="8"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
@@ -7594,13 +7699,13 @@
       </c>
       <c r="B119" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A119,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D119" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="14"/>
       <c r="F119" s="14"/>
@@ -7625,9 +7730,7 @@
         <f aca="false">IF(P119="",0,P119*D119)</f>
         <v>0</v>
       </c>
-      <c r="S119" s="8" t="s">
-        <v>178</v>
-      </c>
+      <c r="S119" s="8"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
@@ -7635,10 +7738,10 @@
       </c>
       <c r="B120" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A120,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>0</v>
@@ -7667,7 +7770,210 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>180</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A121,Киты!$A:$A,0)),"")</f>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D121" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="14"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="9" t="str">
+        <f aca="false">IF(COUNT(G121:O121)=0,"",MIN(G121:O121))</f>
+        <v/>
+      </c>
+      <c r="Q121" s="7" t="str">
+        <f aca="false">IF(P121="","",INDEX($G$1:$O$1,MATCH(P121,G121:O121,0)))</f>
+        <v/>
+      </c>
+      <c r="R121" s="9" t="n">
+        <f aca="false">IF(P121="",0,P121*D121)</f>
+        <v>0</v>
+      </c>
+      <c r="S121" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A122,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="14"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="9" t="str">
+        <f aca="false">IF(COUNT(G122:O122)=0,"",MIN(G122:O122))</f>
+        <v/>
+      </c>
+      <c r="Q122" s="7" t="str">
+        <f aca="false">IF(P122="","",INDEX($G$1:$O$1,MATCH(P122,G122:O122,0)))</f>
+        <v/>
+      </c>
+      <c r="R122" s="9" t="n">
+        <f aca="false">IF(P122="",0,P122*D122)</f>
+        <v>0</v>
+      </c>
+      <c r="S122" s="8"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A123,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="14"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="9" t="str">
+        <f aca="false">IF(COUNT(G123:O123)=0,"",MIN(G123:O123))</f>
+        <v/>
+      </c>
+      <c r="Q123" s="7" t="str">
+        <f aca="false">IF(P123="","",INDEX($G$1:$O$1,MATCH(P123,G123:O123,0)))</f>
+        <v/>
+      </c>
+      <c r="R123" s="9" t="n">
+        <f aca="false">IF(P123="",0,P123*D123)</f>
+        <v>0</v>
+      </c>
+      <c r="S123" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A124,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="14"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="9" t="str">
+        <f aca="false">IF(COUNT(G124:O124)=0,"",MIN(G124:O124))</f>
+        <v/>
+      </c>
+      <c r="Q124" s="7" t="str">
+        <f aca="false">IF(P124="","",INDEX($G$1:$O$1,MATCH(P124,G124:O124,0)))</f>
+        <v/>
+      </c>
+      <c r="R124" s="9" t="n">
+        <f aca="false">IF(P124="",0,P124*D124)</f>
+        <v>0</v>
+      </c>
+      <c r="S124" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A125,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="14"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="12"/>
+      <c r="L125" s="12"/>
+      <c r="M125" s="12"/>
+      <c r="N125" s="12"/>
+      <c r="O125" s="12"/>
+      <c r="P125" s="9" t="str">
+        <f aca="false">IF(COUNT(G125:O125)=0,"",MIN(G125:O125))</f>
+        <v/>
+      </c>
+      <c r="Q125" s="7" t="str">
+        <f aca="false">IF(P125="","",INDEX($G$1:$O$1,MATCH(P125,G125:O125,0)))</f>
+        <v/>
+      </c>
+      <c r="R125" s="9" t="n">
+        <f aca="false">IF(P125="",0,P125*D125)</f>
+        <v>0</v>
+      </c>
+      <c r="S125" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -7704,80 +8010,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -7791,10 +8097,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -7808,10 +8114,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -7825,10 +8131,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -7842,10 +8148,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -7859,10 +8165,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
@@ -7876,10 +8182,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -7893,10 +8199,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
@@ -7910,10 +8216,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -7964,7 +8270,7 @@
         <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>15</v>
@@ -7973,197 +8279,197 @@
         <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="253">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -595,28 +595,25 @@
     <t xml:space="preserve">Поставьте 1, если объём заливки с фильтром больше 4 л (проверьте по VIN)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hyundai/Kia Super Extra Gasoline 5W-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ваша закупка: 2 051,00 ₽ — впишите в колонку поставщика, у которого брали. Проверьте допуск: для Picanto рекомендуют API SM / ILSAC GF-4 и выше.</t>
+    <t xml:space="preserve">Hyundai/Kia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 2 051,00 ₽ — впишите в колонку поставщика, у которого брали. Проверьте допуск: для Picanto рекомендуют API SM / ILSAC GF-4 и выше</t>
   </si>
   <si>
     <t xml:space="preserve">AMD</t>
   </si>
   <si>
-    <t xml:space="preserve">Ваша закупка: 154,70 ₽ — впишите в колонку поставщика, у которого брали.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ваша закупка: 533,00 ₽ — впишите в колонку поставщика, у которого брали.</t>
+    <t xml:space="preserve">Ваша закупка: 154,70 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 533,00 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">BIG FILTER</t>
   </si>
   <si>
-    <t xml:space="preserve">Ваша закупка: 387,00 ₽ — впишите в колонку поставщика, у которого брали.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Добавлена по стандартному составу ТО-кита; подберите по VIN (обычно 30–60 ₽).</t>
+    <t xml:space="preserve">Ваша закупка: 387,00 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">Комплект цепи ГРМ (цепь, натяжитель, успокоители)</t>
@@ -2183,7 +2180,7 @@
       </c>
       <c r="J14" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A14,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K14" s="11" t="str">
         <f aca="false">IF(I14="","",CEILING(I14*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2934,7 +2931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S125"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5845,14 +5842,14 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B73" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A73,Киты!$A:$A,0)),"")</f>
-        <v>Kia Picanto 1.0 / 1.2</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
@@ -5881,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5893,7 +5890,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
@@ -5921,9 +5918,7 @@
         <f aca="false">IF(P74="",0,P74*D74)</f>
         <v>0</v>
       </c>
-      <c r="S74" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
@@ -5976,7 +5971,7 @@
         <v>189</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
@@ -6001,7 +5996,9 @@
         <f aca="false">IF(P76="",0,P76*D76)</f>
         <v>0</v>
       </c>
-      <c r="S76" s="8"/>
+      <c r="S76" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
@@ -6012,7 +6009,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>0</v>
@@ -6041,22 +6038,22 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B78" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A78,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D78" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="14"/>
       <c r="F78" s="14"/>
@@ -6082,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6094,7 +6091,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -6122,9 +6119,7 @@
         <f aca="false">IF(P79="",0,P79*D79)</f>
         <v>0</v>
       </c>
-      <c r="S79" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S79" s="8"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
@@ -6177,7 +6172,7 @@
         <v>189</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="14"/>
       <c r="F81" s="14"/>
@@ -6202,7 +6197,9 @@
         <f aca="false">IF(P81="",0,P81*D81)</f>
         <v>0</v>
       </c>
-      <c r="S81" s="8"/>
+      <c r="S81" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
@@ -6213,7 +6210,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>0</v>
@@ -6242,22 +6239,22 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B83" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A83,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
@@ -6283,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6295,7 +6292,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -6323,9 +6320,7 @@
         <f aca="false">IF(P84="",0,P84*D84)</f>
         <v>0</v>
       </c>
-      <c r="S84" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
@@ -6378,7 +6373,7 @@
         <v>189</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
@@ -6403,7 +6398,9 @@
         <f aca="false">IF(P86="",0,P86*D86)</f>
         <v>0</v>
       </c>
-      <c r="S86" s="8"/>
+      <c r="S86" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
@@ -6414,7 +6411,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>0</v>
@@ -6443,22 +6440,22 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B88" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A88,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
@@ -6484,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6496,7 +6493,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -6524,9 +6521,7 @@
         <f aca="false">IF(P89="",0,P89*D89)</f>
         <v>0</v>
       </c>
-      <c r="S89" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S89" s="8"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
@@ -6579,7 +6574,7 @@
         <v>189</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
@@ -6604,7 +6599,9 @@
         <f aca="false">IF(P91="",0,P91*D91)</f>
         <v>0</v>
       </c>
-      <c r="S91" s="8"/>
+      <c r="S91" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
@@ -6615,7 +6612,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>0</v>
@@ -6644,22 +6641,22 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B93" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A93,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
@@ -6685,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6697,7 +6694,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -6725,9 +6722,7 @@
         <f aca="false">IF(P94="",0,P94*D94)</f>
         <v>0</v>
       </c>
-      <c r="S94" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S94" s="8"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
@@ -6780,7 +6775,7 @@
         <v>189</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="14"/>
       <c r="F96" s="14"/>
@@ -6805,7 +6800,9 @@
         <f aca="false">IF(P96="",0,P96*D96)</f>
         <v>0</v>
       </c>
-      <c r="S96" s="8"/>
+      <c r="S96" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
@@ -6816,7 +6813,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>0</v>
@@ -6845,22 +6842,22 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B98" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A98,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D98" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="14"/>
       <c r="F98" s="14"/>
@@ -6885,9 +6882,7 @@
         <f aca="false">IF(P98="",0,P98*D98)</f>
         <v>0</v>
       </c>
-      <c r="S98" s="8" t="s">
-        <v>193</v>
-      </c>
+      <c r="S98" s="8"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
@@ -6898,10 +6893,10 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="14"/>
       <c r="F99" s="14"/>
@@ -6926,7 +6921,9 @@
         <f aca="false">IF(P99="",0,P99*D99)</f>
         <v>0</v>
       </c>
-      <c r="S99" s="8"/>
+      <c r="S99" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
@@ -6937,7 +6934,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -6966,22 +6963,22 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B101" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A101,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="14"/>
       <c r="F101" s="14"/>
@@ -7007,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,7 +7016,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -7047,9 +7044,7 @@
         <f aca="false">IF(P102="",0,P102*D102)</f>
         <v>0</v>
       </c>
-      <c r="S102" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S102" s="8"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
@@ -7102,7 +7097,7 @@
         <v>189</v>
       </c>
       <c r="D104" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="14"/>
       <c r="F104" s="14"/>
@@ -7127,7 +7122,9 @@
         <f aca="false">IF(P104="",0,P104*D104)</f>
         <v>0</v>
       </c>
-      <c r="S104" s="8"/>
+      <c r="S104" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
@@ -7138,7 +7135,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>0</v>
@@ -7167,22 +7164,22 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B106" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A106,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D106" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="14"/>
       <c r="F106" s="14"/>
@@ -7208,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7220,7 +7217,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -7248,9 +7245,7 @@
         <f aca="false">IF(P107="",0,P107*D107)</f>
         <v>0</v>
       </c>
-      <c r="S107" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S107" s="8"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
@@ -7303,7 +7298,7 @@
         <v>189</v>
       </c>
       <c r="D109" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14"/>
@@ -7328,7 +7323,9 @@
         <f aca="false">IF(P109="",0,P109*D109)</f>
         <v>0</v>
       </c>
-      <c r="S109" s="8"/>
+      <c r="S109" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
@@ -7339,7 +7336,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>0</v>
@@ -7368,22 +7365,22 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B111" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A111,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D111" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" s="14"/>
       <c r="F111" s="14"/>
@@ -7409,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7421,7 +7418,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -7449,9 +7446,7 @@
         <f aca="false">IF(P112="",0,P112*D112)</f>
         <v>0</v>
       </c>
-      <c r="S112" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S112" s="8"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
@@ -7504,7 +7499,7 @@
         <v>189</v>
       </c>
       <c r="D114" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="14"/>
       <c r="F114" s="14"/>
@@ -7529,7 +7524,9 @@
         <f aca="false">IF(P114="",0,P114*D114)</f>
         <v>0</v>
       </c>
-      <c r="S114" s="8"/>
+      <c r="S114" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
@@ -7540,7 +7537,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>0</v>
@@ -7569,22 +7566,22 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B116" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A116,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D116" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="14"/>
       <c r="F116" s="14"/>
@@ -7610,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="S116" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7622,7 +7619,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -7650,9 +7647,7 @@
         <f aca="false">IF(P117="",0,P117*D117)</f>
         <v>0</v>
       </c>
-      <c r="S117" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="S117" s="8"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
@@ -7705,7 +7700,7 @@
         <v>189</v>
       </c>
       <c r="D119" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" s="14"/>
       <c r="F119" s="14"/>
@@ -7730,7 +7725,9 @@
         <f aca="false">IF(P119="",0,P119*D119)</f>
         <v>0</v>
       </c>
-      <c r="S119" s="8"/>
+      <c r="S119" s="8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
@@ -7741,7 +7738,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>0</v>
@@ -7770,22 +7767,22 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B121" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A121,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D121" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="14"/>
       <c r="F121" s="14"/>
@@ -7810,9 +7807,7 @@
         <f aca="false">IF(P121="",0,P121*D121)</f>
         <v>0</v>
       </c>
-      <c r="S121" s="8" t="s">
-        <v>193</v>
-      </c>
+      <c r="S121" s="8"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
@@ -7851,7 +7846,9 @@
         <f aca="false">IF(P122="",0,P122*D122)</f>
         <v>0</v>
       </c>
-      <c r="S122" s="8"/>
+      <c r="S122" s="8" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
@@ -7862,10 +7859,10 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D123" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" s="14"/>
       <c r="F123" s="14"/>
@@ -7891,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7903,7 +7900,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -7932,48 +7929,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125" s="7" t="str">
-        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A125,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
-      </c>
-      <c r="C125" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="D125" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="14"/>
-      <c r="F125" s="14"/>
-      <c r="G125" s="12"/>
-      <c r="H125" s="12"/>
-      <c r="I125" s="12"/>
-      <c r="J125" s="12"/>
-      <c r="K125" s="12"/>
-      <c r="L125" s="12"/>
-      <c r="M125" s="12"/>
-      <c r="N125" s="12"/>
-      <c r="O125" s="12"/>
-      <c r="P125" s="9" t="str">
-        <f aca="false">IF(COUNT(G125:O125)=0,"",MIN(G125:O125))</f>
-        <v/>
-      </c>
-      <c r="Q125" s="7" t="str">
-        <f aca="false">IF(P125="","",INDEX($G$1:$O$1,MATCH(P125,G125:O125,0)))</f>
-        <v/>
-      </c>
-      <c r="R125" s="9" t="n">
-        <f aca="false">IF(P125="",0,P125*D125)</f>
-        <v>0</v>
-      </c>
-      <c r="S125" s="8" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -8010,34 +7966,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>164</v>
@@ -8048,31 +8004,31 @@
         <v>165</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="E2" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>212</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>213</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>166</v>
@@ -8083,7 +8039,7 @@
         <v>152</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -8100,7 +8056,7 @@
         <v>153</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -8117,7 +8073,7 @@
         <v>154</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -8134,7 +8090,7 @@
         <v>155</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -8151,7 +8107,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -8168,7 +8124,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
@@ -8185,7 +8141,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -8202,7 +8158,7 @@
         <v>159</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
@@ -8219,7 +8175,7 @@
         <v>160</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -8270,7 +8226,7 @@
         <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>15</v>
@@ -8279,197 +8235,197 @@
         <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>221</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>226</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>231</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>235</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>244</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>247</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>248</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>250</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>251</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="265">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -349,6 +349,24 @@
     <t xml:space="preserve">to-13-picanto-1-main.png</t>
   </si>
   <si>
+    <t xml:space="preserve">TO-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW Jetta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">уточнить по VIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТО-кит VW Jetta: масло и фильтры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to-14-jetta-1-main.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">GRM-01</t>
   </si>
   <si>
@@ -614,6 +632,24 @@
   </si>
   <si>
     <t xml:space="preserve">Ваша закупка: 387,00 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEBOIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 3 525,84 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 308,10 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 311,00 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 317,00 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">Комплект цепи ГРМ (цепь, натяжитель, успокоители)</t>
@@ -1430,7 +1466,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2208,25 +2244,25 @@
         <v>96</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I15" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)+Параметры!$B$3)</f>
@@ -2234,7 +2270,7 @@
       </c>
       <c r="J15" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A15,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="11" t="str">
         <f aca="false">IF(I15="","",CEILING(I15*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2259,16 +2295,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>32</v>
@@ -2277,10 +2313,10 @@
         <v>33</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I16" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)+Параметры!$B$3)</f>
@@ -2313,16 +2349,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>32</v>
@@ -2331,10 +2367,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I17" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)+Параметры!$B$3)</f>
@@ -2367,16 +2403,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>32</v>
@@ -2385,10 +2421,10 @@
         <v>33</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I18" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)+Параметры!$B$3)</f>
@@ -2421,28 +2457,28 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I19" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)+Параметры!$B$3)</f>
@@ -2475,28 +2511,28 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I20" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)+Параметры!$B$3)</f>
@@ -2504,7 +2540,7 @@
       </c>
       <c r="J20" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A20,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="11" t="str">
         <f aca="false">IF(I20="","",CEILING(I20*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2529,28 +2565,28 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I21" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)+Параметры!$B$3)</f>
@@ -2558,7 +2594,7 @@
       </c>
       <c r="J21" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A21,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" s="11" t="str">
         <f aca="false">IF(I21="","",CEILING(I21*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2583,28 +2619,28 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I22" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)+Параметры!$B$3)</f>
@@ -2637,28 +2673,28 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I23" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)+Параметры!$B$3)</f>
@@ -2691,28 +2727,28 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I24" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)+Параметры!$B$3)</f>
@@ -2745,28 +2781,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I25" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)+Параметры!$B$3)</f>
@@ -2774,7 +2810,7 @@
       </c>
       <c r="J25" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A25,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="11" t="str">
         <f aca="false">IF(I25="","",CEILING(I25*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
@@ -2797,19 +2833,73 @@
         <v>36</v>
       </c>
     </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="9" t="str">
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)+Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="J26" s="10" t="n">
+        <f aca="false">COUNTIFS(Состав!$A:$A,A26,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="K26" s="11" t="str">
+        <f aca="false">IF(I26="","",CEILING(I26*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" s="7" t="str">
+        <f aca="false">IF(OR(K26="",L26=""),"",IF(K26&lt;=L26,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="N26" s="9" t="str">
+        <f aca="false">IF(K26="","",K26-I26-K26*Параметры!$B$6-Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O26" s="13" t="str">
+        <f aca="false">IF(N26="","",N26/K26)</f>
+        <v/>
+      </c>
+      <c r="P26" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"дороже рынка"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P25" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P26" type="list">
       <formula1>"не выложен,выложен,есть продажи,снят"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2840,79 +2930,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B2" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2931,7 +3021,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2955,75 +3045,75 @@
         <v>14</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G2" s="19" t="n">
         <v>460</v>
@@ -3055,7 +3145,7 @@
         <v>430</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3067,7 +3157,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -3096,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3108,7 +3198,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -3147,7 +3237,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -3186,7 +3276,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -3225,7 +3315,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -3264,7 +3354,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -3293,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,7 +3395,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -3344,7 +3434,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -3383,7 +3473,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -3422,7 +3512,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -3461,7 +3551,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -3490,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3502,7 +3592,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -3541,7 +3631,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -3580,7 +3670,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -3619,7 +3709,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -3658,7 +3748,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -3687,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3699,7 +3789,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -3738,7 +3828,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -3777,7 +3867,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -3816,7 +3906,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -3855,7 +3945,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -3884,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3896,7 +3986,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -3935,7 +4025,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -3974,7 +4064,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -4013,7 +4103,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -4052,7 +4142,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -4081,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4093,7 +4183,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -4132,7 +4222,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -4171,7 +4261,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -4210,7 +4300,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -4249,7 +4339,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -4278,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4290,7 +4380,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -4319,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4331,7 +4421,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -4370,7 +4460,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -4409,7 +4499,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -4448,7 +4538,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -4487,7 +4577,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -4516,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4528,7 +4618,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -4557,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4569,7 +4659,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -4608,7 +4698,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -4647,7 +4737,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -4686,7 +4776,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -4725,7 +4815,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -4754,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4766,7 +4856,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -4795,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4807,7 +4897,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -4846,7 +4936,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -4885,7 +4975,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -4924,7 +5014,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -4963,7 +5053,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -4992,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5004,7 +5094,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -5033,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5045,7 +5135,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -5084,7 +5174,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -5123,7 +5213,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -5162,7 +5252,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -5201,7 +5291,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -5230,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5242,7 +5332,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -5271,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5283,7 +5373,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -5322,7 +5412,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -5361,7 +5451,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -5400,7 +5490,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -5439,7 +5529,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -5468,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5480,7 +5570,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -5509,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5521,7 +5611,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -5560,7 +5650,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -5599,7 +5689,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -5638,7 +5728,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -5677,13 +5767,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -5708,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5720,13 +5810,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -5751,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5763,13 +5853,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -5794,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5806,13 +5896,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -5837,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5846,15 +5936,17 @@
       </c>
       <c r="B73" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A73,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="14"/>
+      <c r="E73" s="14" t="s">
+        <v>191</v>
+      </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
@@ -5878,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5887,15 +5979,17 @@
       </c>
       <c r="B74" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A74,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="14"/>
+      <c r="E74" s="14" t="s">
+        <v>186</v>
+      </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12"/>
@@ -5918,7 +6012,9 @@
         <f aca="false">IF(P74="",0,P74*D74)</f>
         <v>0</v>
       </c>
-      <c r="S74" s="8"/>
+      <c r="S74" s="8" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
@@ -5926,15 +6022,17 @@
       </c>
       <c r="B75" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A75,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E75" s="14"/>
+      <c r="E75" s="14" t="s">
+        <v>194</v>
+      </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
@@ -5957,7 +6055,9 @@
         <f aca="false">IF(P75="",0,P75*D75)</f>
         <v>0</v>
       </c>
-      <c r="S75" s="8"/>
+      <c r="S75" s="8" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
@@ -5965,15 +6065,17 @@
       </c>
       <c r="B76" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A76,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2010–2017</v>
+        <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>194</v>
+      </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12"/>
@@ -5997,22 +6099,22 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B77" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A77,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
@@ -6038,19 +6140,19 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B78" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A78,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -6078,20 +6180,18 @@
         <f aca="false">IF(P78="",0,P78*D78)</f>
         <v>0</v>
       </c>
-      <c r="S78" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S78" s="8"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B79" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A79,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -6123,17 +6223,17 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B80" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A80,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D80" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
@@ -6158,18 +6258,20 @@
         <f aca="false">IF(P80="",0,P80*D80)</f>
         <v>0</v>
       </c>
-      <c r="S80" s="8"/>
+      <c r="S80" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B81" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A81,Киты!$A:$A,0)),"")</f>
-        <v>Hyundai Solaris 2017–2022</v>
+        <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -6198,22 +6300,22 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B82" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A82,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="14"/>
       <c r="F82" s="14"/>
@@ -6239,19 +6341,19 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B83" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A83,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -6279,20 +6381,18 @@
         <f aca="false">IF(P83="",0,P83*D83)</f>
         <v>0</v>
       </c>
-      <c r="S83" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S83" s="8"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B84" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A84,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -6324,17 +6424,17 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B85" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A85,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
@@ -6359,18 +6459,20 @@
         <f aca="false">IF(P85="",0,P85*D85)</f>
         <v>0</v>
       </c>
-      <c r="S85" s="8"/>
+      <c r="S85" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B86" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A86,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2011–2017</v>
+        <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -6399,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B87" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A87,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D87" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="14"/>
       <c r="F87" s="14"/>
@@ -6440,19 +6542,19 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B88" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A88,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -6480,20 +6582,18 @@
         <f aca="false">IF(P88="",0,P88*D88)</f>
         <v>0</v>
       </c>
-      <c r="S88" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S88" s="8"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B89" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A89,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -6525,17 +6625,17 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B90" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A90,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
@@ -6560,18 +6660,20 @@
         <f aca="false">IF(P90="",0,P90*D90)</f>
         <v>0</v>
       </c>
-      <c r="S90" s="8"/>
+      <c r="S90" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B91" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A91,Киты!$A:$A,0)),"")</f>
-        <v>Kia Rio 2017–2021</v>
+        <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -6600,22 +6702,22 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B92" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A92,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D92" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
@@ -6641,19 +6743,19 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B93" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A93,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -6681,20 +6783,18 @@
         <f aca="false">IF(P93="",0,P93*D93)</f>
         <v>0</v>
       </c>
-      <c r="S93" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S93" s="8"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B94" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A94,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -6726,17 +6826,17 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B95" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A95,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" s="14"/>
       <c r="F95" s="14"/>
@@ -6761,18 +6861,20 @@
         <f aca="false">IF(P95="",0,P95*D95)</f>
         <v>0</v>
       </c>
-      <c r="S95" s="8"/>
+      <c r="S95" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B96" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A96,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CFNA</v>
+        <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -6801,22 +6903,22 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B97" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A97,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D97" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="14"/>
       <c r="F97" s="14"/>
@@ -6842,19 +6944,19 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B98" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A98,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -6886,17 +6988,17 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B99" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A99,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="14"/>
       <c r="F99" s="14"/>
@@ -6921,20 +7023,18 @@
         <f aca="false">IF(P99="",0,P99*D99)</f>
         <v>0</v>
       </c>
-      <c r="S99" s="8" t="s">
-        <v>190</v>
-      </c>
+      <c r="S99" s="8"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B100" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A100,Киты!$A:$A,0)),"")</f>
-        <v>VW Polo 1.6 CWVA</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -6963,22 +7063,22 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B101" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A101,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="14"/>
       <c r="F101" s="14"/>
@@ -7004,19 +7104,19 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B102" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A102,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -7048,17 +7148,17 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B103" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A103,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D103" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" s="14"/>
       <c r="F103" s="14"/>
@@ -7083,18 +7183,20 @@
         <f aca="false">IF(P103="",0,P103*D103)</f>
         <v>0</v>
       </c>
-      <c r="S103" s="8"/>
+      <c r="S103" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B104" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A104,Киты!$A:$A,0)),"")</f>
-        <v>Haval Jolion 1.5T</v>
+        <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -7123,22 +7225,22 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B105" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A105,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D105" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="14"/>
       <c r="F105" s="14"/>
@@ -7164,19 +7266,19 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B106" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A106,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -7204,20 +7306,18 @@
         <f aca="false">IF(P106="",0,P106*D106)</f>
         <v>0</v>
       </c>
-      <c r="S106" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S106" s="8"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B107" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A107,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -7249,17 +7349,17 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B108" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A108,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D108" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="14"/>
       <c r="F108" s="14"/>
@@ -7284,18 +7384,20 @@
         <f aca="false">IF(P108="",0,P108*D108)</f>
         <v>0</v>
       </c>
-      <c r="S108" s="8"/>
+      <c r="S108" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B109" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A109,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 1.5T</v>
+        <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -7324,22 +7426,22 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B110" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A110,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D110" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="14"/>
       <c r="F110" s="14"/>
@@ -7365,19 +7467,19 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B111" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A111,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -7405,20 +7507,18 @@
         <f aca="false">IF(P111="",0,P111*D111)</f>
         <v>0</v>
       </c>
-      <c r="S111" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S111" s="8"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B112" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A112,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -7450,17 +7550,17 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B113" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A113,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D113" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="14"/>
       <c r="F113" s="14"/>
@@ -7485,18 +7585,20 @@
         <f aca="false">IF(P113="",0,P113*D113)</f>
         <v>0</v>
       </c>
-      <c r="S113" s="8"/>
+      <c r="S113" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B114" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A114,Киты!$A:$A,0)),"")</f>
-        <v>Haval F7 / F7x 2.0T</v>
+        <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -7525,22 +7627,22 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B115" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A115,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D115" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="14"/>
@@ -7566,19 +7668,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B116" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A116,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -7606,20 +7708,18 @@
         <f aca="false">IF(P116="",0,P116*D116)</f>
         <v>0</v>
       </c>
-      <c r="S116" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="S116" s="8"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B117" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A117,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -7651,17 +7751,17 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B118" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A118,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D118" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" s="14"/>
       <c r="F118" s="14"/>
@@ -7686,18 +7786,20 @@
         <f aca="false">IF(P118="",0,P118*D118)</f>
         <v>0</v>
       </c>
-      <c r="S118" s="8"/>
+      <c r="S118" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B119" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A119,Киты!$A:$A,0)),"")</f>
-        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
+        <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -7726,22 +7828,22 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B120" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A120,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D120" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" s="14"/>
       <c r="F120" s="14"/>
@@ -7767,19 +7869,19 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B121" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A121,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -7811,14 +7913,14 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B122" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A122,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -7846,20 +7948,18 @@
         <f aca="false">IF(P122="",0,P122*D122)</f>
         <v>0</v>
       </c>
-      <c r="S122" s="8" t="s">
-        <v>195</v>
-      </c>
+      <c r="S122" s="8"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B123" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A123,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -7888,19 +7988,19 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B124" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A124,Киты!$A:$A,0)),"")</f>
-        <v>Geely Coolray 1.5T</v>
+        <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -7929,7 +8029,169 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>192</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B125" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A125,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="14"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="12"/>
+      <c r="L125" s="12"/>
+      <c r="M125" s="12"/>
+      <c r="N125" s="12"/>
+      <c r="O125" s="12"/>
+      <c r="P125" s="9" t="str">
+        <f aca="false">IF(COUNT(G125:O125)=0,"",MIN(G125:O125))</f>
+        <v/>
+      </c>
+      <c r="Q125" s="7" t="str">
+        <f aca="false">IF(P125="","",INDEX($G$1:$O$1,MATCH(P125,G125:O125,0)))</f>
+        <v/>
+      </c>
+      <c r="R125" s="9" t="n">
+        <f aca="false">IF(P125="",0,P125*D125)</f>
+        <v>0</v>
+      </c>
+      <c r="S125" s="8"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B126" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A126,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="14"/>
+      <c r="F126" s="14"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+      <c r="L126" s="12"/>
+      <c r="M126" s="12"/>
+      <c r="N126" s="12"/>
+      <c r="O126" s="12"/>
+      <c r="P126" s="9" t="str">
+        <f aca="false">IF(COUNT(G126:O126)=0,"",MIN(G126:O126))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="7" t="str">
+        <f aca="false">IF(P126="","",INDEX($G$1:$O$1,MATCH(P126,G126:O126,0)))</f>
+        <v/>
+      </c>
+      <c r="R126" s="9" t="n">
+        <f aca="false">IF(P126="",0,P126*D126)</f>
+        <v>0</v>
+      </c>
+      <c r="S126" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A127,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D127" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="14"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="12"/>
+      <c r="I127" s="12"/>
+      <c r="J127" s="12"/>
+      <c r="K127" s="12"/>
+      <c r="L127" s="12"/>
+      <c r="M127" s="12"/>
+      <c r="N127" s="12"/>
+      <c r="O127" s="12"/>
+      <c r="P127" s="9" t="str">
+        <f aca="false">IF(COUNT(G127:O127)=0,"",MIN(G127:O127))</f>
+        <v/>
+      </c>
+      <c r="Q127" s="7" t="str">
+        <f aca="false">IF(P127="","",INDEX($G$1:$O$1,MATCH(P127,G127:O127,0)))</f>
+        <v/>
+      </c>
+      <c r="R127" s="9" t="n">
+        <f aca="false">IF(P127="",0,P127*D127)</f>
+        <v>0</v>
+      </c>
+      <c r="S127" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A128,Киты!$A:$A,0)),"")</f>
+        <v>Geely Coolray 1.5T</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="14"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="12"/>
+      <c r="I128" s="12"/>
+      <c r="J128" s="12"/>
+      <c r="K128" s="12"/>
+      <c r="L128" s="12"/>
+      <c r="M128" s="12"/>
+      <c r="N128" s="12"/>
+      <c r="O128" s="12"/>
+      <c r="P128" s="9" t="str">
+        <f aca="false">IF(COUNT(G128:O128)=0,"",MIN(G128:O128))</f>
+        <v/>
+      </c>
+      <c r="Q128" s="7" t="str">
+        <f aca="false">IF(P128="","",INDEX($G$1:$O$1,MATCH(P128,G128:O128,0)))</f>
+        <v/>
+      </c>
+      <c r="R128" s="9" t="n">
+        <f aca="false">IF(P128="",0,P128*D128)</f>
+        <v>0</v>
+      </c>
+      <c r="S128" s="8" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -7966,80 +8228,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -8053,10 +8315,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -8070,10 +8332,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -8087,10 +8349,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -8104,10 +8366,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -8121,10 +8383,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
@@ -8138,10 +8400,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -8155,10 +8417,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
@@ -8172,10 +8434,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -8226,7 +8488,7 @@
         <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>15</v>
@@ -8235,197 +8497,197 @@
         <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>239</v>
-      </c>
       <c r="G9" s="8" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -637,7 +637,7 @@
     <t xml:space="preserve">TEBOIL</t>
   </si>
   <si>
-    <t xml:space="preserve">Ваша закупка: 3 525,84 ₽ — впишите в колонку поставщика, у которого брали</t>
+    <t xml:space="preserve">Ваша закупка: 2 668,39 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">Ваша закупка: 308,10 ₽ — впишите в колонку поставщика, у которого брали</t>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -42,7 +42,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="U1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -50,7 +50,19 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Прибыль до налога: цена − закупка − комиссия Авито − просмотры (см. «Параметры»).</t>
+          <t xml:space="preserve">До налога: цена − закупка − комиссия Авито − показы − резерв − постоянные расходы.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">До налога: цена − закупка − комиссия банка − показы − резерв − постоянные расходы − СДЭК за ваш счёт.</t>
         </r>
       </text>
     </comment>
@@ -59,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="297">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -76,10 +88,13 @@
     <t xml:space="preserve">    Лучшая цена, поставщик и сумма посчитаются сами. Кол-во 0 = позиция не входит (например, помпа); поставьте 1, если нужна.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. «Киты» — сами посчитаются закупка, цена на Авито и прибыль. Впишите минимальную цену конкурентов — появится сравнение.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. «Параметры» — наценка, упаковка, комиссия Авито. Поменяете там — пересчитается всё.</t>
+    <t xml:space="preserve">3. «Киты» — сами посчитаются закупка, цена на Авито и прибыль до налога в двух вариантах: оплата через Авито Доставку и прямым переводом.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. «Параметры» — наценка, комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
   </si>
   <si>
     <t xml:space="preserve">5. «Моторы» — справка: где цепь, где ремень, что входит в ГРМ-кит, источники.</t>
@@ -121,12 +136,18 @@
     <t xml:space="preserve">Главное фото (avito/png/…)</t>
   </si>
   <si>
+    <t xml:space="preserve">Детали, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Позиций без цены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Упаковка, ₽</t>
+  </si>
+  <si>
     <t xml:space="preserve">Закупка, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Позиций без цены</t>
-  </si>
-  <si>
     <t xml:space="preserve">Цена на Авито, ₽</t>
   </si>
   <si>
@@ -136,10 +157,28 @@
     <t xml:space="preserve">Сравнение с рынком</t>
   </si>
   <si>
-    <t xml:space="preserve">Прибыль с кита, ₽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа</t>
+    <t xml:space="preserve">Комиссия Авито, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Комиссия банка, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Показы, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резерв на товар, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянные расходы, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль: Авито Доставка, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль: перевод, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маржа (Авито Доставка)</t>
   </si>
   <si>
     <t xml:space="preserve">Статус</t>
@@ -490,7 +529,7 @@
     <t xml:space="preserve">Наценка к закупке</t>
   </si>
   <si>
-    <t xml:space="preserve">Цена кита = закупка × (1 + наценка), вверх до шага округления, минус «вычесть». Ваше решение, можно менять.</t>
+    <t xml:space="preserve">Цена кита = (детали + упаковка) × (1 + наценка), вверх до шага округления, минус «вычесть». Ваше решение.</t>
   </si>
   <si>
     <t xml:space="preserve">Упаковка на 1 кит, ₽</t>
@@ -514,13 +553,82 @@
     <t xml:space="preserve">Комиссия Авито Доставки</t>
   </si>
   <si>
-    <t xml:space="preserve">≈6,5% для профессиональных продавцов по данным селлерских сервисов (SelSup, 2026). Сверьте ставку в кабинете Авито.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расход на просмотры на 1 заказ, ₽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка: ≈150 просмотров × 1,2 ₽. После запуска замените на своё значение из статистики Авито.</t>
+    <t xml:space="preserve">Только для заказов через Авито Доставку. ≈6,5% по данным селлерских сервисов (SelSup, 2026) — сверьте в кабинете Авито.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Показы объявления на 1 заказ, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка: ≈150 показов × 1,2 ₽. Клиент пришёл с Авито при любой оплате, поэтому вычитается всегда. После запуска: расход на показы за месяц ÷ число заказов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резерв на товар (возвраты, брак, довоз), % от деталей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваше решение: 5% от стоимости деталей. Через 2–3 месяца сверьте с фактом и поправьте.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резерв включать в цену? (1 — да, 0 — нет)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 — резерв вычитается из прибыли, цена не меняется. 1 — резерв добавляется к закупке, и цена кита растёт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Комиссия банка при оплате переводом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Для прямых переводов. Оплата по QR/СБП для бизнеса обычно 0,4–0,7%; обычный перевод на счёт ИП часто бесплатный — уточните у банка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СДЭК за ваш счёт при оплате переводом, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, если доставку оплачивает покупатель. Если отправляете бесплатно — впишите среднюю стоимость отправки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взносы ИП, ₽ в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57 390 ₽ за 2026 год ÷ 12 (фиксированные взносы ИП).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Онлайн-касса, ₽ в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При оплате переводом покупателю по закону нужен чек (54-ФЗ). Оценка облачной кассы — уточните у своего банка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подписка Авито Pro, ₽ в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, пока не подключена. Впишите ≈3 000, когда подключите (обложка, автозагрузка).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание счёта, ₽ в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 на бесплатном тарифе.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прочее (связь, печать, расходники), ₽ в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">План заказов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На сколько заказов делятся постоянные расходы. Больше заказов — меньше расходов на один кит.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянные расходы на 1 кит, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Считается сам: сумма постоянных расходов в месяц ÷ план заказов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог в расчёт не входит: прибыль на листе «Киты» — до налога.</t>
   </si>
   <si>
     <t xml:space="preserve">Позиция</t>
@@ -860,11 +968,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;;\-#,##0&quot; ₽&quot;;\-"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1016,7 +1125,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1081,6 +1190,14 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1118,7 +1235,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -1131,6 +1248,15 @@
         <name val="Arial"/>
         <charset val="1"/>
         <family val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
         <color rgb="FFC00000"/>
       </font>
     </dxf>
@@ -1378,7 +1504,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1428,12 +1554,12 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -1448,6 +1574,11 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1466,7 +1597,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1478,1413 +1609,2243 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I2" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A2)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A2)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A2)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A2))</f>
         <v/>
       </c>
       <c r="J2" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A2,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K2" s="11" t="str">
-        <f aca="false">IF(I2="","",CEILING(I2*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="7" t="str">
-        <f aca="false">IF(OR(K2="",L2=""),"",IF(K2&lt;=L2,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N2" s="9" t="str">
-        <f aca="false">IF(K2="","",K2-I2-K2*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O2" s="13" t="str">
-        <f aca="false">IF(N2="","",N2/K2)</f>
-        <v/>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>36</v>
+      <c r="K2" s="9" t="str">
+        <f aca="false">IF(I2="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L2" s="9" t="str">
+        <f aca="false">IF(I2="","",I2+K2)</f>
+        <v/>
+      </c>
+      <c r="M2" s="11" t="str">
+        <f aca="false">IF(I2="","",CEILING((I2*(1+Параметры!$B$8*Параметры!$B$9)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="7" t="str">
+        <f aca="false">IF(OR(M2="",N2=""),"",IF(M2&lt;=N2,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P2" s="9" t="str">
+        <f aca="false">IF(M2="","",M2*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q2" s="9" t="str">
+        <f aca="false">IF(M2="","",M2*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R2" s="9" t="str">
+        <f aca="false">IF(M2="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S2" s="9" t="str">
+        <f aca="false">IF(I2="","",I2*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T2" s="9" t="str">
+        <f aca="false">IF(M2="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U2" s="11" t="str">
+        <f aca="false">IF(M2="","",M2-L2-P2-R2-S2-T2)</f>
+        <v/>
+      </c>
+      <c r="V2" s="11" t="str">
+        <f aca="false">IF(M2="","",M2-L2-Q2-R2-S2-T2-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W2" s="13" t="str">
+        <f aca="false">IF(U2="","",U2/M2)</f>
+        <v/>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A3)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A3)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A3)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A3))</f>
         <v/>
       </c>
       <c r="J3" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A3,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K3" s="11" t="str">
-        <f aca="false">IF(I3="","",CEILING(I3*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="7" t="str">
-        <f aca="false">IF(OR(K3="",L3=""),"",IF(K3&lt;=L3,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N3" s="9" t="str">
-        <f aca="false">IF(K3="","",K3-I3-K3*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O3" s="13" t="str">
-        <f aca="false">IF(N3="","",N3/K3)</f>
-        <v/>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>36</v>
+      <c r="K3" s="9" t="str">
+        <f aca="false">IF(I3="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="9" t="str">
+        <f aca="false">IF(I3="","",I3+K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="11" t="str">
+        <f aca="false">IF(I3="","",CEILING((I3*(1+Параметры!$B$8*Параметры!$B$9)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="7" t="str">
+        <f aca="false">IF(OR(M3="",N3=""),"",IF(M3&lt;=N3,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P3" s="9" t="str">
+        <f aca="false">IF(M3="","",M3*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q3" s="9" t="str">
+        <f aca="false">IF(M3="","",M3*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R3" s="9" t="str">
+        <f aca="false">IF(M3="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S3" s="9" t="str">
+        <f aca="false">IF(I3="","",I3*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T3" s="9" t="str">
+        <f aca="false">IF(M3="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U3" s="11" t="str">
+        <f aca="false">IF(M3="","",M3-L3-P3-R3-S3-T3)</f>
+        <v/>
+      </c>
+      <c r="V3" s="11" t="str">
+        <f aca="false">IF(M3="","",M3-L3-Q3-R3-S3-T3-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W3" s="13" t="str">
+        <f aca="false">IF(U3="","",U3/M3)</f>
+        <v/>
+      </c>
+      <c r="X3" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I4" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A4)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A4)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A4)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A4))</f>
         <v/>
       </c>
       <c r="J4" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A4,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K4" s="11" t="str">
-        <f aca="false">IF(I4="","",CEILING(I4*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="7" t="str">
-        <f aca="false">IF(OR(K4="",L4=""),"",IF(K4&lt;=L4,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N4" s="9" t="str">
-        <f aca="false">IF(K4="","",K4-I4-K4*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O4" s="13" t="str">
-        <f aca="false">IF(N4="","",N4/K4)</f>
-        <v/>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>36</v>
+      <c r="K4" s="9" t="str">
+        <f aca="false">IF(I4="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L4" s="9" t="str">
+        <f aca="false">IF(I4="","",I4+K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="11" t="str">
+        <f aca="false">IF(I4="","",CEILING((I4*(1+Параметры!$B$8*Параметры!$B$9)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="O4" s="7" t="str">
+        <f aca="false">IF(OR(M4="",N4=""),"",IF(M4&lt;=N4,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P4" s="9" t="str">
+        <f aca="false">IF(M4="","",M4*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="9" t="str">
+        <f aca="false">IF(M4="","",M4*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R4" s="9" t="str">
+        <f aca="false">IF(M4="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S4" s="9" t="str">
+        <f aca="false">IF(I4="","",I4*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T4" s="9" t="str">
+        <f aca="false">IF(M4="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U4" s="11" t="str">
+        <f aca="false">IF(M4="","",M4-L4-P4-R4-S4-T4)</f>
+        <v/>
+      </c>
+      <c r="V4" s="11" t="str">
+        <f aca="false">IF(M4="","",M4-L4-Q4-R4-S4-T4-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W4" s="13" t="str">
+        <f aca="false">IF(U4="","",U4/M4)</f>
+        <v/>
+      </c>
+      <c r="X4" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I5" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A5)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A5)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A5)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A5))</f>
         <v/>
       </c>
       <c r="J5" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A5,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K5" s="11" t="str">
-        <f aca="false">IF(I5="","",CEILING(I5*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="7" t="str">
-        <f aca="false">IF(OR(K5="",L5=""),"",IF(K5&lt;=L5,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N5" s="9" t="str">
-        <f aca="false">IF(K5="","",K5-I5-K5*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O5" s="13" t="str">
-        <f aca="false">IF(N5="","",N5/K5)</f>
-        <v/>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>36</v>
+      <c r="K5" s="9" t="str">
+        <f aca="false">IF(I5="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L5" s="9" t="str">
+        <f aca="false">IF(I5="","",I5+K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="11" t="str">
+        <f aca="false">IF(I5="","",CEILING((I5*(1+Параметры!$B$8*Параметры!$B$9)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="12"/>
+      <c r="O5" s="7" t="str">
+        <f aca="false">IF(OR(M5="",N5=""),"",IF(M5&lt;=N5,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P5" s="9" t="str">
+        <f aca="false">IF(M5="","",M5*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="9" t="str">
+        <f aca="false">IF(M5="","",M5*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R5" s="9" t="str">
+        <f aca="false">IF(M5="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S5" s="9" t="str">
+        <f aca="false">IF(I5="","",I5*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T5" s="9" t="str">
+        <f aca="false">IF(M5="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U5" s="11" t="str">
+        <f aca="false">IF(M5="","",M5-L5-P5-R5-S5-T5)</f>
+        <v/>
+      </c>
+      <c r="V5" s="11" t="str">
+        <f aca="false">IF(M5="","",M5-L5-Q5-R5-S5-T5-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W5" s="13" t="str">
+        <f aca="false">IF(U5="","",U5/M5)</f>
+        <v/>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I6" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A6)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A6)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A6)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A6))</f>
         <v/>
       </c>
       <c r="J6" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A6,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K6" s="11" t="str">
-        <f aca="false">IF(I6="","",CEILING(I6*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="7" t="str">
-        <f aca="false">IF(OR(K6="",L6=""),"",IF(K6&lt;=L6,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N6" s="9" t="str">
-        <f aca="false">IF(K6="","",K6-I6-K6*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O6" s="13" t="str">
-        <f aca="false">IF(N6="","",N6/K6)</f>
-        <v/>
-      </c>
-      <c r="P6" s="14" t="s">
-        <v>36</v>
+      <c r="K6" s="9" t="str">
+        <f aca="false">IF(I6="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L6" s="9" t="str">
+        <f aca="false">IF(I6="","",I6+K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="11" t="str">
+        <f aca="false">IF(I6="","",CEILING((I6*(1+Параметры!$B$8*Параметры!$B$9)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="7" t="str">
+        <f aca="false">IF(OR(M6="",N6=""),"",IF(M6&lt;=N6,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P6" s="9" t="str">
+        <f aca="false">IF(M6="","",M6*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="9" t="str">
+        <f aca="false">IF(M6="","",M6*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R6" s="9" t="str">
+        <f aca="false">IF(M6="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S6" s="9" t="str">
+        <f aca="false">IF(I6="","",I6*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T6" s="9" t="str">
+        <f aca="false">IF(M6="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U6" s="11" t="str">
+        <f aca="false">IF(M6="","",M6-L6-P6-R6-S6-T6)</f>
+        <v/>
+      </c>
+      <c r="V6" s="11" t="str">
+        <f aca="false">IF(M6="","",M6-L6-Q6-R6-S6-T6-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W6" s="13" t="str">
+        <f aca="false">IF(U6="","",U6/M6)</f>
+        <v/>
+      </c>
+      <c r="X6" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I7" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A7)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A7)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A7)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A7))</f>
         <v/>
       </c>
       <c r="J7" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A7,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K7" s="11" t="str">
-        <f aca="false">IF(I7="","",CEILING(I7*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="7" t="str">
-        <f aca="false">IF(OR(K7="",L7=""),"",IF(K7&lt;=L7,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N7" s="9" t="str">
-        <f aca="false">IF(K7="","",K7-I7-K7*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="13" t="str">
-        <f aca="false">IF(N7="","",N7/K7)</f>
-        <v/>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>36</v>
+      <c r="K7" s="9" t="str">
+        <f aca="false">IF(I7="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L7" s="9" t="str">
+        <f aca="false">IF(I7="","",I7+K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="11" t="str">
+        <f aca="false">IF(I7="","",CEILING((I7*(1+Параметры!$B$8*Параметры!$B$9)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="7" t="str">
+        <f aca="false">IF(OR(M7="",N7=""),"",IF(M7&lt;=N7,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P7" s="9" t="str">
+        <f aca="false">IF(M7="","",M7*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="9" t="str">
+        <f aca="false">IF(M7="","",M7*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R7" s="9" t="str">
+        <f aca="false">IF(M7="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="9" t="str">
+        <f aca="false">IF(I7="","",I7*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T7" s="9" t="str">
+        <f aca="false">IF(M7="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U7" s="11" t="str">
+        <f aca="false">IF(M7="","",M7-L7-P7-R7-S7-T7)</f>
+        <v/>
+      </c>
+      <c r="V7" s="11" t="str">
+        <f aca="false">IF(M7="","",M7-L7-Q7-R7-S7-T7-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W7" s="13" t="str">
+        <f aca="false">IF(U7="","",U7/M7)</f>
+        <v/>
+      </c>
+      <c r="X7" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I8" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A8)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A8)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A8)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A8))</f>
         <v/>
       </c>
       <c r="J8" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A8,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K8" s="11" t="str">
-        <f aca="false">IF(I8="","",CEILING(I8*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="7" t="str">
-        <f aca="false">IF(OR(K8="",L8=""),"",IF(K8&lt;=L8,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N8" s="9" t="str">
-        <f aca="false">IF(K8="","",K8-I8-K8*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O8" s="13" t="str">
-        <f aca="false">IF(N8="","",N8/K8)</f>
-        <v/>
-      </c>
-      <c r="P8" s="14" t="s">
-        <v>36</v>
+      <c r="K8" s="9" t="str">
+        <f aca="false">IF(I8="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L8" s="9" t="str">
+        <f aca="false">IF(I8="","",I8+K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="11" t="str">
+        <f aca="false">IF(I8="","",CEILING((I8*(1+Параметры!$B$8*Параметры!$B$9)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="7" t="str">
+        <f aca="false">IF(OR(M8="",N8=""),"",IF(M8&lt;=N8,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P8" s="9" t="str">
+        <f aca="false">IF(M8="","",M8*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="9" t="str">
+        <f aca="false">IF(M8="","",M8*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R8" s="9" t="str">
+        <f aca="false">IF(M8="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S8" s="9" t="str">
+        <f aca="false">IF(I8="","",I8*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="9" t="str">
+        <f aca="false">IF(M8="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U8" s="11" t="str">
+        <f aca="false">IF(M8="","",M8-L8-P8-R8-S8-T8)</f>
+        <v/>
+      </c>
+      <c r="V8" s="11" t="str">
+        <f aca="false">IF(M8="","",M8-L8-Q8-R8-S8-T8-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W8" s="13" t="str">
+        <f aca="false">IF(U8="","",U8/M8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I9" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A9)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A9)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A9)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A9))</f>
         <v/>
       </c>
       <c r="J9" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A9,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K9" s="11" t="str">
-        <f aca="false">IF(I9="","",CEILING(I9*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="7" t="str">
-        <f aca="false">IF(OR(K9="",L9=""),"",IF(K9&lt;=L9,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N9" s="9" t="str">
-        <f aca="false">IF(K9="","",K9-I9-K9*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O9" s="13" t="str">
-        <f aca="false">IF(N9="","",N9/K9)</f>
-        <v/>
-      </c>
-      <c r="P9" s="14" t="s">
-        <v>36</v>
+      <c r="K9" s="9" t="str">
+        <f aca="false">IF(I9="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L9" s="9" t="str">
+        <f aca="false">IF(I9="","",I9+K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="11" t="str">
+        <f aca="false">IF(I9="","",CEILING((I9*(1+Параметры!$B$8*Параметры!$B$9)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="7" t="str">
+        <f aca="false">IF(OR(M9="",N9=""),"",IF(M9&lt;=N9,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="9" t="str">
+        <f aca="false">IF(M9="","",M9*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="9" t="str">
+        <f aca="false">IF(M9="","",M9*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R9" s="9" t="str">
+        <f aca="false">IF(M9="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S9" s="9" t="str">
+        <f aca="false">IF(I9="","",I9*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T9" s="9" t="str">
+        <f aca="false">IF(M9="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U9" s="11" t="str">
+        <f aca="false">IF(M9="","",M9-L9-P9-R9-S9-T9)</f>
+        <v/>
+      </c>
+      <c r="V9" s="11" t="str">
+        <f aca="false">IF(M9="","",M9-L9-Q9-R9-S9-T9-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W9" s="13" t="str">
+        <f aca="false">IF(U9="","",U9/M9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I10" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A10)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A10)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A10)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A10))</f>
         <v/>
       </c>
       <c r="J10" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A10,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K10" s="11" t="str">
-        <f aca="false">IF(I10="","",CEILING(I10*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="7" t="str">
-        <f aca="false">IF(OR(K10="",L10=""),"",IF(K10&lt;=L10,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N10" s="9" t="str">
-        <f aca="false">IF(K10="","",K10-I10-K10*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O10" s="13" t="str">
-        <f aca="false">IF(N10="","",N10/K10)</f>
-        <v/>
-      </c>
-      <c r="P10" s="14" t="s">
-        <v>36</v>
+      <c r="K10" s="9" t="str">
+        <f aca="false">IF(I10="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L10" s="9" t="str">
+        <f aca="false">IF(I10="","",I10+K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="11" t="str">
+        <f aca="false">IF(I10="","",CEILING((I10*(1+Параметры!$B$8*Параметры!$B$9)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="7" t="str">
+        <f aca="false">IF(OR(M10="",N10=""),"",IF(M10&lt;=N10,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="9" t="str">
+        <f aca="false">IF(M10="","",M10*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="9" t="str">
+        <f aca="false">IF(M10="","",M10*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="9" t="str">
+        <f aca="false">IF(M10="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S10" s="9" t="str">
+        <f aca="false">IF(I10="","",I10*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T10" s="9" t="str">
+        <f aca="false">IF(M10="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U10" s="11" t="str">
+        <f aca="false">IF(M10="","",M10-L10-P10-R10-S10-T10)</f>
+        <v/>
+      </c>
+      <c r="V10" s="11" t="str">
+        <f aca="false">IF(M10="","",M10-L10-Q10-R10-S10-T10-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W10" s="13" t="str">
+        <f aca="false">IF(U10="","",U10/M10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I11" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A11)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A11)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A11)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A11))</f>
         <v/>
       </c>
       <c r="J11" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A11,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K11" s="11" t="str">
-        <f aca="false">IF(I11="","",CEILING(I11*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="7" t="str">
-        <f aca="false">IF(OR(K11="",L11=""),"",IF(K11&lt;=L11,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N11" s="9" t="str">
-        <f aca="false">IF(K11="","",K11-I11-K11*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O11" s="13" t="str">
-        <f aca="false">IF(N11="","",N11/K11)</f>
-        <v/>
-      </c>
-      <c r="P11" s="14" t="s">
-        <v>36</v>
+      <c r="K11" s="9" t="str">
+        <f aca="false">IF(I11="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L11" s="9" t="str">
+        <f aca="false">IF(I11="","",I11+K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="11" t="str">
+        <f aca="false">IF(I11="","",CEILING((I11*(1+Параметры!$B$8*Параметры!$B$9)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="7" t="str">
+        <f aca="false">IF(OR(M11="",N11=""),"",IF(M11&lt;=N11,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="9" t="str">
+        <f aca="false">IF(M11="","",M11*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="9" t="str">
+        <f aca="false">IF(M11="","",M11*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R11" s="9" t="str">
+        <f aca="false">IF(M11="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S11" s="9" t="str">
+        <f aca="false">IF(I11="","",I11*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T11" s="9" t="str">
+        <f aca="false">IF(M11="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U11" s="11" t="str">
+        <f aca="false">IF(M11="","",M11-L11-P11-R11-S11-T11)</f>
+        <v/>
+      </c>
+      <c r="V11" s="11" t="str">
+        <f aca="false">IF(M11="","",M11-L11-Q11-R11-S11-T11-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W11" s="13" t="str">
+        <f aca="false">IF(U11="","",U11/M11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I12" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A12)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A12)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A12)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A12))</f>
         <v/>
       </c>
       <c r="J12" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A12,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K12" s="11" t="str">
-        <f aca="false">IF(I12="","",CEILING(I12*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="7" t="str">
-        <f aca="false">IF(OR(K12="",L12=""),"",IF(K12&lt;=L12,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N12" s="9" t="str">
-        <f aca="false">IF(K12="","",K12-I12-K12*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O12" s="13" t="str">
-        <f aca="false">IF(N12="","",N12/K12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="14" t="s">
-        <v>36</v>
+      <c r="K12" s="9" t="str">
+        <f aca="false">IF(I12="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L12" s="9" t="str">
+        <f aca="false">IF(I12="","",I12+K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="11" t="str">
+        <f aca="false">IF(I12="","",CEILING((I12*(1+Параметры!$B$8*Параметры!$B$9)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="7" t="str">
+        <f aca="false">IF(OR(M12="",N12=""),"",IF(M12&lt;=N12,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="9" t="str">
+        <f aca="false">IF(M12="","",M12*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="9" t="str">
+        <f aca="false">IF(M12="","",M12*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R12" s="9" t="str">
+        <f aca="false">IF(M12="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S12" s="9" t="str">
+        <f aca="false">IF(I12="","",I12*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T12" s="9" t="str">
+        <f aca="false">IF(M12="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U12" s="11" t="str">
+        <f aca="false">IF(M12="","",M12-L12-P12-R12-S12-T12)</f>
+        <v/>
+      </c>
+      <c r="V12" s="11" t="str">
+        <f aca="false">IF(M12="","",M12-L12-Q12-R12-S12-T12-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W12" s="13" t="str">
+        <f aca="false">IF(U12="","",U12/M12)</f>
+        <v/>
+      </c>
+      <c r="X12" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I13" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A13)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A13)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A13)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A13))</f>
         <v/>
       </c>
       <c r="J13" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A13,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="K13" s="11" t="str">
-        <f aca="false">IF(I13="","",CEILING(I13*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="7" t="str">
-        <f aca="false">IF(OR(K13="",L13=""),"",IF(K13&lt;=L13,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N13" s="9" t="str">
-        <f aca="false">IF(K13="","",K13-I13-K13*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O13" s="13" t="str">
-        <f aca="false">IF(N13="","",N13/K13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>36</v>
+      <c r="K13" s="9" t="str">
+        <f aca="false">IF(I13="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L13" s="9" t="str">
+        <f aca="false">IF(I13="","",I13+K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="11" t="str">
+        <f aca="false">IF(I13="","",CEILING((I13*(1+Параметры!$B$8*Параметры!$B$9)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="7" t="str">
+        <f aca="false">IF(OR(M13="",N13=""),"",IF(M13&lt;=N13,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="9" t="str">
+        <f aca="false">IF(M13="","",M13*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="9" t="str">
+        <f aca="false">IF(M13="","",M13*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R13" s="9" t="str">
+        <f aca="false">IF(M13="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S13" s="9" t="str">
+        <f aca="false">IF(I13="","",I13*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T13" s="9" t="str">
+        <f aca="false">IF(M13="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U13" s="11" t="str">
+        <f aca="false">IF(M13="","",M13-L13-P13-R13-S13-T13)</f>
+        <v/>
+      </c>
+      <c r="V13" s="11" t="str">
+        <f aca="false">IF(M13="","",M13-L13-Q13-R13-S13-T13-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W13" s="13" t="str">
+        <f aca="false">IF(U13="","",U13/M13)</f>
+        <v/>
+      </c>
+      <c r="X13" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I14" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A14))</f>
         <v/>
       </c>
       <c r="J14" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A14,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>4</v>
       </c>
-      <c r="K14" s="11" t="str">
-        <f aca="false">IF(I14="","",CEILING(I14*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="7" t="str">
-        <f aca="false">IF(OR(K14="",L14=""),"",IF(K14&lt;=L14,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N14" s="9" t="str">
-        <f aca="false">IF(K14="","",K14-I14-K14*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O14" s="13" t="str">
-        <f aca="false">IF(N14="","",N14/K14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="14" t="s">
-        <v>36</v>
+      <c r="K14" s="9" t="str">
+        <f aca="false">IF(I14="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L14" s="9" t="str">
+        <f aca="false">IF(I14="","",I14+K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="11" t="str">
+        <f aca="false">IF(I14="","",CEILING((I14*(1+Параметры!$B$8*Параметры!$B$9)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="7" t="str">
+        <f aca="false">IF(OR(M14="",N14=""),"",IF(M14&lt;=N14,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="9" t="str">
+        <f aca="false">IF(M14="","",M14*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="9" t="str">
+        <f aca="false">IF(M14="","",M14*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R14" s="9" t="str">
+        <f aca="false">IF(M14="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S14" s="9" t="str">
+        <f aca="false">IF(I14="","",I14*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T14" s="9" t="str">
+        <f aca="false">IF(M14="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U14" s="11" t="str">
+        <f aca="false">IF(M14="","",M14-L14-P14-R14-S14-T14)</f>
+        <v/>
+      </c>
+      <c r="V14" s="11" t="str">
+        <f aca="false">IF(M14="","",M14-L14-Q14-R14-S14-T14-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W14" s="13" t="str">
+        <f aca="false">IF(U14="","",U14/M14)</f>
+        <v/>
+      </c>
+      <c r="X14" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I15" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A15))</f>
         <v/>
       </c>
       <c r="J15" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A15,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>4</v>
       </c>
-      <c r="K15" s="11" t="str">
-        <f aca="false">IF(I15="","",CEILING(I15*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="7" t="str">
-        <f aca="false">IF(OR(K15="",L15=""),"",IF(K15&lt;=L15,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N15" s="9" t="str">
-        <f aca="false">IF(K15="","",K15-I15-K15*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O15" s="13" t="str">
-        <f aca="false">IF(N15="","",N15/K15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="14" t="s">
-        <v>36</v>
+      <c r="K15" s="9" t="str">
+        <f aca="false">IF(I15="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L15" s="9" t="str">
+        <f aca="false">IF(I15="","",I15+K15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="11" t="str">
+        <f aca="false">IF(I15="","",CEILING((I15*(1+Параметры!$B$8*Параметры!$B$9)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="7" t="str">
+        <f aca="false">IF(OR(M15="",N15=""),"",IF(M15&lt;=N15,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="9" t="str">
+        <f aca="false">IF(M15="","",M15*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="9" t="str">
+        <f aca="false">IF(M15="","",M15*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R15" s="9" t="str">
+        <f aca="false">IF(M15="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S15" s="9" t="str">
+        <f aca="false">IF(I15="","",I15*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T15" s="9" t="str">
+        <f aca="false">IF(M15="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U15" s="11" t="str">
+        <f aca="false">IF(M15="","",M15-L15-P15-R15-S15-T15)</f>
+        <v/>
+      </c>
+      <c r="V15" s="11" t="str">
+        <f aca="false">IF(M15="","",M15-L15-Q15-R15-S15-T15-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W15" s="13" t="str">
+        <f aca="false">IF(U15="","",U15/M15)</f>
+        <v/>
+      </c>
+      <c r="X15" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I16" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A16))</f>
         <v/>
       </c>
       <c r="J16" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A16,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K16" s="11" t="str">
-        <f aca="false">IF(I16="","",CEILING(I16*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="7" t="str">
-        <f aca="false">IF(OR(K16="",L16=""),"",IF(K16&lt;=L16,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N16" s="9" t="str">
-        <f aca="false">IF(K16="","",K16-I16-K16*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O16" s="13" t="str">
-        <f aca="false">IF(N16="","",N16/K16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="14" t="s">
-        <v>36</v>
+      <c r="K16" s="9" t="str">
+        <f aca="false">IF(I16="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L16" s="9" t="str">
+        <f aca="false">IF(I16="","",I16+K16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11" t="str">
+        <f aca="false">IF(I16="","",CEILING((I16*(1+Параметры!$B$8*Параметры!$B$9)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="O16" s="7" t="str">
+        <f aca="false">IF(OR(M16="",N16=""),"",IF(M16&lt;=N16,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="9" t="str">
+        <f aca="false">IF(M16="","",M16*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="9" t="str">
+        <f aca="false">IF(M16="","",M16*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R16" s="9" t="str">
+        <f aca="false">IF(M16="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S16" s="9" t="str">
+        <f aca="false">IF(I16="","",I16*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T16" s="9" t="str">
+        <f aca="false">IF(M16="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U16" s="11" t="str">
+        <f aca="false">IF(M16="","",M16-L16-P16-R16-S16-T16)</f>
+        <v/>
+      </c>
+      <c r="V16" s="11" t="str">
+        <f aca="false">IF(M16="","",M16-L16-Q16-R16-S16-T16-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W16" s="13" t="str">
+        <f aca="false">IF(U16="","",U16/M16)</f>
+        <v/>
+      </c>
+      <c r="X16" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I17" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A17))</f>
         <v/>
       </c>
       <c r="J17" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A17,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K17" s="11" t="str">
-        <f aca="false">IF(I17="","",CEILING(I17*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="7" t="str">
-        <f aca="false">IF(OR(K17="",L17=""),"",IF(K17&lt;=L17,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N17" s="9" t="str">
-        <f aca="false">IF(K17="","",K17-I17-K17*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O17" s="13" t="str">
-        <f aca="false">IF(N17="","",N17/K17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="14" t="s">
-        <v>36</v>
+      <c r="K17" s="9" t="str">
+        <f aca="false">IF(I17="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L17" s="9" t="str">
+        <f aca="false">IF(I17="","",I17+K17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="11" t="str">
+        <f aca="false">IF(I17="","",CEILING((I17*(1+Параметры!$B$8*Параметры!$B$9)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="7" t="str">
+        <f aca="false">IF(OR(M17="",N17=""),"",IF(M17&lt;=N17,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P17" s="9" t="str">
+        <f aca="false">IF(M17="","",M17*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="9" t="str">
+        <f aca="false">IF(M17="","",M17*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R17" s="9" t="str">
+        <f aca="false">IF(M17="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S17" s="9" t="str">
+        <f aca="false">IF(I17="","",I17*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T17" s="9" t="str">
+        <f aca="false">IF(M17="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U17" s="11" t="str">
+        <f aca="false">IF(M17="","",M17-L17-P17-R17-S17-T17)</f>
+        <v/>
+      </c>
+      <c r="V17" s="11" t="str">
+        <f aca="false">IF(M17="","",M17-L17-Q17-R17-S17-T17-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W17" s="13" t="str">
+        <f aca="false">IF(U17="","",U17/M17)</f>
+        <v/>
+      </c>
+      <c r="X17" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I18" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A18))</f>
         <v/>
       </c>
       <c r="J18" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A18,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K18" s="11" t="str">
-        <f aca="false">IF(I18="","",CEILING(I18*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="7" t="str">
-        <f aca="false">IF(OR(K18="",L18=""),"",IF(K18&lt;=L18,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N18" s="9" t="str">
-        <f aca="false">IF(K18="","",K18-I18-K18*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O18" s="13" t="str">
-        <f aca="false">IF(N18="","",N18/K18)</f>
-        <v/>
-      </c>
-      <c r="P18" s="14" t="s">
-        <v>36</v>
+      <c r="K18" s="9" t="str">
+        <f aca="false">IF(I18="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L18" s="9" t="str">
+        <f aca="false">IF(I18="","",I18+K18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="11" t="str">
+        <f aca="false">IF(I18="","",CEILING((I18*(1+Параметры!$B$8*Параметры!$B$9)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N18" s="12"/>
+      <c r="O18" s="7" t="str">
+        <f aca="false">IF(OR(M18="",N18=""),"",IF(M18&lt;=N18,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P18" s="9" t="str">
+        <f aca="false">IF(M18="","",M18*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="9" t="str">
+        <f aca="false">IF(M18="","",M18*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R18" s="9" t="str">
+        <f aca="false">IF(M18="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S18" s="9" t="str">
+        <f aca="false">IF(I18="","",I18*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T18" s="9" t="str">
+        <f aca="false">IF(M18="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="11" t="str">
+        <f aca="false">IF(M18="","",M18-L18-P18-R18-S18-T18)</f>
+        <v/>
+      </c>
+      <c r="V18" s="11" t="str">
+        <f aca="false">IF(M18="","",M18-L18-Q18-R18-S18-T18-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W18" s="13" t="str">
+        <f aca="false">IF(U18="","",U18/M18)</f>
+        <v/>
+      </c>
+      <c r="X18" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="C19" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I19" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A19))</f>
         <v/>
       </c>
       <c r="J19" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A19,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K19" s="11" t="str">
-        <f aca="false">IF(I19="","",CEILING(I19*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="7" t="str">
-        <f aca="false">IF(OR(K19="",L19=""),"",IF(K19&lt;=L19,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N19" s="9" t="str">
-        <f aca="false">IF(K19="","",K19-I19-K19*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O19" s="13" t="str">
-        <f aca="false">IF(N19="","",N19/K19)</f>
-        <v/>
-      </c>
-      <c r="P19" s="14" t="s">
-        <v>36</v>
+      <c r="K19" s="9" t="str">
+        <f aca="false">IF(I19="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L19" s="9" t="str">
+        <f aca="false">IF(I19="","",I19+K19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="11" t="str">
+        <f aca="false">IF(I19="","",CEILING((I19*(1+Параметры!$B$8*Параметры!$B$9)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N19" s="12"/>
+      <c r="O19" s="7" t="str">
+        <f aca="false">IF(OR(M19="",N19=""),"",IF(M19&lt;=N19,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="9" t="str">
+        <f aca="false">IF(M19="","",M19*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="9" t="str">
+        <f aca="false">IF(M19="","",M19*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R19" s="9" t="str">
+        <f aca="false">IF(M19="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S19" s="9" t="str">
+        <f aca="false">IF(I19="","",I19*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T19" s="9" t="str">
+        <f aca="false">IF(M19="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U19" s="11" t="str">
+        <f aca="false">IF(M19="","",M19-L19-P19-R19-S19-T19)</f>
+        <v/>
+      </c>
+      <c r="V19" s="11" t="str">
+        <f aca="false">IF(M19="","",M19-L19-Q19-R19-S19-T19-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W19" s="13" t="str">
+        <f aca="false">IF(U19="","",U19/M19)</f>
+        <v/>
+      </c>
+      <c r="X19" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I20" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A20))</f>
         <v/>
       </c>
       <c r="J20" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A20,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K20" s="11" t="str">
-        <f aca="false">IF(I20="","",CEILING(I20*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="7" t="str">
-        <f aca="false">IF(OR(K20="",L20=""),"",IF(K20&lt;=L20,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N20" s="9" t="str">
-        <f aca="false">IF(K20="","",K20-I20-K20*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O20" s="13" t="str">
-        <f aca="false">IF(N20="","",N20/K20)</f>
-        <v/>
-      </c>
-      <c r="P20" s="14" t="s">
-        <v>36</v>
+      <c r="K20" s="9" t="str">
+        <f aca="false">IF(I20="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L20" s="9" t="str">
+        <f aca="false">IF(I20="","",I20+K20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="11" t="str">
+        <f aca="false">IF(I20="","",CEILING((I20*(1+Параметры!$B$8*Параметры!$B$9)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N20" s="12"/>
+      <c r="O20" s="7" t="str">
+        <f aca="false">IF(OR(M20="",N20=""),"",IF(M20&lt;=N20,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P20" s="9" t="str">
+        <f aca="false">IF(M20="","",M20*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="9" t="str">
+        <f aca="false">IF(M20="","",M20*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R20" s="9" t="str">
+        <f aca="false">IF(M20="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S20" s="9" t="str">
+        <f aca="false">IF(I20="","",I20*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T20" s="9" t="str">
+        <f aca="false">IF(M20="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U20" s="11" t="str">
+        <f aca="false">IF(M20="","",M20-L20-P20-R20-S20-T20)</f>
+        <v/>
+      </c>
+      <c r="V20" s="11" t="str">
+        <f aca="false">IF(M20="","",M20-L20-Q20-R20-S20-T20-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W20" s="13" t="str">
+        <f aca="false">IF(U20="","",U20/M20)</f>
+        <v/>
+      </c>
+      <c r="X20" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I21" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A21))</f>
         <v/>
       </c>
       <c r="J21" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A21,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>1</v>
       </c>
-      <c r="K21" s="11" t="str">
-        <f aca="false">IF(I21="","",CEILING(I21*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="7" t="str">
-        <f aca="false">IF(OR(K21="",L21=""),"",IF(K21&lt;=L21,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N21" s="9" t="str">
-        <f aca="false">IF(K21="","",K21-I21-K21*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O21" s="13" t="str">
-        <f aca="false">IF(N21="","",N21/K21)</f>
-        <v/>
-      </c>
-      <c r="P21" s="14" t="s">
-        <v>36</v>
+      <c r="K21" s="9" t="str">
+        <f aca="false">IF(I21="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L21" s="9" t="str">
+        <f aca="false">IF(I21="","",I21+K21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="11" t="str">
+        <f aca="false">IF(I21="","",CEILING((I21*(1+Параметры!$B$8*Параметры!$B$9)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N21" s="12"/>
+      <c r="O21" s="7" t="str">
+        <f aca="false">IF(OR(M21="",N21=""),"",IF(M21&lt;=N21,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P21" s="9" t="str">
+        <f aca="false">IF(M21="","",M21*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="9" t="str">
+        <f aca="false">IF(M21="","",M21*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R21" s="9" t="str">
+        <f aca="false">IF(M21="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S21" s="9" t="str">
+        <f aca="false">IF(I21="","",I21*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T21" s="9" t="str">
+        <f aca="false">IF(M21="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U21" s="11" t="str">
+        <f aca="false">IF(M21="","",M21-L21-P21-R21-S21-T21)</f>
+        <v/>
+      </c>
+      <c r="V21" s="11" t="str">
+        <f aca="false">IF(M21="","",M21-L21-Q21-R21-S21-T21-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W21" s="13" t="str">
+        <f aca="false">IF(U21="","",U21/M21)</f>
+        <v/>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I22" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A22))</f>
         <v/>
       </c>
       <c r="J22" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A22,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K22" s="11" t="str">
-        <f aca="false">IF(I22="","",CEILING(I22*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="7" t="str">
-        <f aca="false">IF(OR(K22="",L22=""),"",IF(K22&lt;=L22,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N22" s="9" t="str">
-        <f aca="false">IF(K22="","",K22-I22-K22*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O22" s="13" t="str">
-        <f aca="false">IF(N22="","",N22/K22)</f>
-        <v/>
-      </c>
-      <c r="P22" s="14" t="s">
-        <v>36</v>
+      <c r="K22" s="9" t="str">
+        <f aca="false">IF(I22="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L22" s="9" t="str">
+        <f aca="false">IF(I22="","",I22+K22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="11" t="str">
+        <f aca="false">IF(I22="","",CEILING((I22*(1+Параметры!$B$8*Параметры!$B$9)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N22" s="12"/>
+      <c r="O22" s="7" t="str">
+        <f aca="false">IF(OR(M22="",N22=""),"",IF(M22&lt;=N22,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P22" s="9" t="str">
+        <f aca="false">IF(M22="","",M22*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="9" t="str">
+        <f aca="false">IF(M22="","",M22*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R22" s="9" t="str">
+        <f aca="false">IF(M22="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S22" s="9" t="str">
+        <f aca="false">IF(I22="","",I22*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T22" s="9" t="str">
+        <f aca="false">IF(M22="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U22" s="11" t="str">
+        <f aca="false">IF(M22="","",M22-L22-P22-R22-S22-T22)</f>
+        <v/>
+      </c>
+      <c r="V22" s="11" t="str">
+        <f aca="false">IF(M22="","",M22-L22-Q22-R22-S22-T22-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W22" s="13" t="str">
+        <f aca="false">IF(U22="","",U22/M22)</f>
+        <v/>
+      </c>
+      <c r="X22" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I23" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A23))</f>
         <v/>
       </c>
       <c r="J23" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A23,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K23" s="11" t="str">
-        <f aca="false">IF(I23="","",CEILING(I23*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="7" t="str">
-        <f aca="false">IF(OR(K23="",L23=""),"",IF(K23&lt;=L23,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N23" s="9" t="str">
-        <f aca="false">IF(K23="","",K23-I23-K23*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O23" s="13" t="str">
-        <f aca="false">IF(N23="","",N23/K23)</f>
-        <v/>
-      </c>
-      <c r="P23" s="14" t="s">
-        <v>36</v>
+      <c r="K23" s="9" t="str">
+        <f aca="false">IF(I23="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="9" t="str">
+        <f aca="false">IF(I23="","",I23+K23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="11" t="str">
+        <f aca="false">IF(I23="","",CEILING((I23*(1+Параметры!$B$8*Параметры!$B$9)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12"/>
+      <c r="O23" s="7" t="str">
+        <f aca="false">IF(OR(M23="",N23=""),"",IF(M23&lt;=N23,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P23" s="9" t="str">
+        <f aca="false">IF(M23="","",M23*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="9" t="str">
+        <f aca="false">IF(M23="","",M23*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R23" s="9" t="str">
+        <f aca="false">IF(M23="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S23" s="9" t="str">
+        <f aca="false">IF(I23="","",I23*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T23" s="9" t="str">
+        <f aca="false">IF(M23="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U23" s="11" t="str">
+        <f aca="false">IF(M23="","",M23-L23-P23-R23-S23-T23)</f>
+        <v/>
+      </c>
+      <c r="V23" s="11" t="str">
+        <f aca="false">IF(M23="","",M23-L23-Q23-R23-S23-T23-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W23" s="13" t="str">
+        <f aca="false">IF(U23="","",U23/M23)</f>
+        <v/>
+      </c>
+      <c r="X23" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I24" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A24))</f>
         <v/>
       </c>
       <c r="J24" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A24,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K24" s="11" t="str">
-        <f aca="false">IF(I24="","",CEILING(I24*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="7" t="str">
-        <f aca="false">IF(OR(K24="",L24=""),"",IF(K24&lt;=L24,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N24" s="9" t="str">
-        <f aca="false">IF(K24="","",K24-I24-K24*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O24" s="13" t="str">
-        <f aca="false">IF(N24="","",N24/K24)</f>
-        <v/>
-      </c>
-      <c r="P24" s="14" t="s">
-        <v>36</v>
+      <c r="K24" s="9" t="str">
+        <f aca="false">IF(I24="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="9" t="str">
+        <f aca="false">IF(I24="","",I24+K24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="11" t="str">
+        <f aca="false">IF(I24="","",CEILING((I24*(1+Параметры!$B$8*Параметры!$B$9)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N24" s="12"/>
+      <c r="O24" s="7" t="str">
+        <f aca="false">IF(OR(M24="",N24=""),"",IF(M24&lt;=N24,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P24" s="9" t="str">
+        <f aca="false">IF(M24="","",M24*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="9" t="str">
+        <f aca="false">IF(M24="","",M24*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R24" s="9" t="str">
+        <f aca="false">IF(M24="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S24" s="9" t="str">
+        <f aca="false">IF(I24="","",I24*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T24" s="9" t="str">
+        <f aca="false">IF(M24="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U24" s="11" t="str">
+        <f aca="false">IF(M24="","",M24-L24-P24-R24-S24-T24)</f>
+        <v/>
+      </c>
+      <c r="V24" s="11" t="str">
+        <f aca="false">IF(M24="","",M24-L24-Q24-R24-S24-T24-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W24" s="13" t="str">
+        <f aca="false">IF(U24="","",U24/M24)</f>
+        <v/>
+      </c>
+      <c r="X24" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I25" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A25))</f>
         <v/>
       </c>
       <c r="J25" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A25,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="K25" s="11" t="str">
-        <f aca="false">IF(I25="","",CEILING(I25*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="7" t="str">
-        <f aca="false">IF(OR(K25="",L25=""),"",IF(K25&lt;=L25,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N25" s="9" t="str">
-        <f aca="false">IF(K25="","",K25-I25-K25*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O25" s="13" t="str">
-        <f aca="false">IF(N25="","",N25/K25)</f>
-        <v/>
-      </c>
-      <c r="P25" s="14" t="s">
-        <v>36</v>
+      <c r="K25" s="9" t="str">
+        <f aca="false">IF(I25="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="9" t="str">
+        <f aca="false">IF(I25="","",I25+K25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="11" t="str">
+        <f aca="false">IF(I25="","",CEILING((I25*(1+Параметры!$B$8*Параметры!$B$9)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N25" s="12"/>
+      <c r="O25" s="7" t="str">
+        <f aca="false">IF(OR(M25="",N25=""),"",IF(M25&lt;=N25,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P25" s="9" t="str">
+        <f aca="false">IF(M25="","",M25*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="9" t="str">
+        <f aca="false">IF(M25="","",M25*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R25" s="9" t="str">
+        <f aca="false">IF(M25="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S25" s="9" t="str">
+        <f aca="false">IF(I25="","",I25*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T25" s="9" t="str">
+        <f aca="false">IF(M25="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U25" s="11" t="str">
+        <f aca="false">IF(M25="","",M25-L25-P25-R25-S25-T25)</f>
+        <v/>
+      </c>
+      <c r="V25" s="11" t="str">
+        <f aca="false">IF(M25="","",M25-L25-Q25-R25-S25-T25-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W25" s="13" t="str">
+        <f aca="false">IF(U25="","",U25/M25)</f>
+        <v/>
+      </c>
+      <c r="X25" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I26" s="9" t="str">
-        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)+Параметры!$B$3)</f>
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A26))</f>
         <v/>
       </c>
       <c r="J26" s="10" t="n">
         <f aca="false">COUNTIFS(Состав!$A:$A,A26,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
         <v>2</v>
       </c>
-      <c r="K26" s="11" t="str">
-        <f aca="false">IF(I26="","",CEILING(I26*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="7" t="str">
-        <f aca="false">IF(OR(K26="",L26=""),"",IF(K26&lt;=L26,"не дороже рынка","дороже рынка"))</f>
-        <v/>
-      </c>
-      <c r="N26" s="9" t="str">
-        <f aca="false">IF(K26="","",K26-I26-K26*Параметры!$B$6-Параметры!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O26" s="13" t="str">
-        <f aca="false">IF(N26="","",N26/K26)</f>
-        <v/>
-      </c>
-      <c r="P26" s="14" t="s">
-        <v>36</v>
+      <c r="K26" s="9" t="str">
+        <f aca="false">IF(I26="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="9" t="str">
+        <f aca="false">IF(I26="","",I26+K26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="11" t="str">
+        <f aca="false">IF(I26="","",CEILING((I26*(1+Параметры!$B$8*Параметры!$B$9)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <v/>
+      </c>
+      <c r="N26" s="12"/>
+      <c r="O26" s="7" t="str">
+        <f aca="false">IF(OR(M26="",N26=""),"",IF(M26&lt;=N26,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P26" s="9" t="str">
+        <f aca="false">IF(M26="","",M26*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="9" t="str">
+        <f aca="false">IF(M26="","",M26*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R26" s="9" t="str">
+        <f aca="false">IF(M26="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S26" s="9" t="str">
+        <f aca="false">IF(I26="","",I26*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T26" s="9" t="str">
+        <f aca="false">IF(M26="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U26" s="11" t="str">
+        <f aca="false">IF(M26="","",M26-L26-P26-R26-S26-T26)</f>
+        <v/>
+      </c>
+      <c r="V26" s="11" t="str">
+        <f aca="false">IF(M26="","",M26-L26-Q26-R26-S26-T26-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W26" s="13" t="str">
+        <f aca="false">IF(U26="","",U26/M26)</f>
+        <v/>
+      </c>
+      <c r="X26" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2893,13 +3854,23 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"дороже рынка"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U26">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V26">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P26" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="X2:X26" type="list">
       <formula1>"не выложен,выложен,есть продажи,снят"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2920,89 +3891,216 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="96"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B2" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>4783</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="11" t="n">
+        <f aca="false">($B$12+$B$13+$B$14+$B$15+$B$16)/MAX(1,$B$17)</f>
+        <v>339.15</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3039,125 +4137,125 @@
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="G2" s="19" t="n">
+      <c r="A2" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="21" t="n">
         <v>460</v>
       </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19" t="n">
+      <c r="H2" s="21"/>
+      <c r="I2" s="21" t="n">
         <v>445</v>
       </c>
-      <c r="J2" s="19" t="n">
+      <c r="J2" s="21" t="n">
         <v>430</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19" t="n">
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21" t="n">
         <v>470</v>
       </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="20" t="n">
+      <c r="O2" s="21"/>
+      <c r="P2" s="22" t="n">
         <f aca="false">IF(COUNT(G2:O2)=0,"",MIN(G2:O2))</f>
         <v>430</v>
       </c>
-      <c r="Q2" s="17" t="str">
+      <c r="Q2" s="19" t="str">
         <f aca="false">IF(P2="","",INDEX($G$1:$O$1,MATCH(P2,G2:O2,0)))</f>
         <v>Росско</v>
       </c>
-      <c r="R2" s="20" t="n">
+      <c r="R2" s="22" t="n">
         <f aca="false">IF(P2="",0,P2*D2)</f>
         <v>430</v>
       </c>
-      <c r="S2" s="21" t="s">
-        <v>176</v>
+      <c r="S2" s="23" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B3" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A3,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -3186,19 +4284,19 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B4" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A4,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -3230,14 +4328,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B5" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A5,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -3269,14 +4367,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B6" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A6,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -3308,14 +4406,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A7,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -3347,14 +4445,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B8" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A8,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -3383,19 +4481,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A9,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -3427,14 +4525,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B10" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A10,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -3466,14 +4564,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B11" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A11,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -3505,14 +4603,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B12" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A12,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -3544,14 +4642,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A13,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -3580,19 +4678,19 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B14" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A14,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -3624,14 +4722,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A15,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -3663,14 +4761,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A16,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -3702,14 +4800,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B17" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A17,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -3741,14 +4839,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B18" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A18,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -3777,19 +4875,19 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B19" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A19,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -3821,14 +4919,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B20" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A20,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -3860,14 +4958,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B21" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A21,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -3899,14 +4997,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B22" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A22,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -3938,14 +5036,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B23" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A23,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -3974,19 +5072,19 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B24" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A24,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -4018,14 +5116,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B25" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A25,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -4057,14 +5155,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B26" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A26,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -4096,14 +5194,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B27" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A27,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -4135,14 +5233,14 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B28" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A28,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -4171,19 +5269,19 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B29" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A29,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -4215,14 +5313,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B30" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A30,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -4254,14 +5352,14 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B31" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A31,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -4293,14 +5391,14 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B32" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A32,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -4332,14 +5430,14 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B33" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A33,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -4368,19 +5466,19 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B34" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A34,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -4409,19 +5507,19 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B35" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A35,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -4453,14 +5551,14 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B36" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A36,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -4492,14 +5590,14 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B37" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A37,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -4531,14 +5629,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B38" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A38,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -4570,14 +5668,14 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B39" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A39,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -4606,19 +5704,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B40" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A40,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -4647,19 +5745,19 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B41" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A41,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -4691,14 +5789,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B42" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A42,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -4730,14 +5828,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B43" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A43,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -4769,14 +5867,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B44" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A44,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -4808,14 +5906,14 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B45" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A45,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -4844,19 +5942,19 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B46" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A46,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -4885,19 +5983,19 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B47" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A47,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -4929,14 +6027,14 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B48" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A48,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -4968,14 +6066,14 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B49" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A49,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -5007,14 +6105,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B50" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A50,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -5046,14 +6144,14 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B51" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A51,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -5082,19 +6180,19 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B52" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A52,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -5123,19 +6221,19 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B53" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A53,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -5167,14 +6265,14 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B54" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A54,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -5206,14 +6304,14 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B55" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A55,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -5245,14 +6343,14 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B56" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A56,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -5284,14 +6382,14 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B57" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A57,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -5320,19 +6418,19 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B58" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A58,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -5361,19 +6459,19 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B59" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A59,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -5405,14 +6503,14 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B60" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A60,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -5444,14 +6542,14 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B61" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A61,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -5483,14 +6581,14 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B62" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A62,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -5522,14 +6620,14 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B63" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A63,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -5558,19 +6656,19 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B64" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A64,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -5599,19 +6697,19 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B65" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A65,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -5643,14 +6741,14 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B66" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A66,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -5682,14 +6780,14 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B67" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A67,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -5721,14 +6819,14 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B68" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A68,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -5760,20 +6858,20 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B69" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A69,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -5798,25 +6896,25 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B70" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A70,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -5841,25 +6939,25 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B71" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A71,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -5884,25 +6982,25 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B72" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A72,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -5927,25 +7025,25 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B73" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A73,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -5970,25 +7068,25 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B74" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A74,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -6013,25 +7111,25 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B75" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A75,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -6056,25 +7154,25 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B76" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A76,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -6099,19 +7197,19 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B77" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A77,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -6140,19 +7238,19 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B78" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A78,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -6184,14 +7282,14 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B79" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A79,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -6223,14 +7321,14 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B80" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A80,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -6259,19 +7357,19 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B81" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A81,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -6300,19 +7398,19 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B82" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A82,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -6341,19 +7439,19 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B83" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A83,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -6385,14 +7483,14 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B84" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A84,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -6424,14 +7522,14 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B85" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A85,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -6460,19 +7558,19 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B86" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A86,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -6501,19 +7599,19 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B87" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A87,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -6542,19 +7640,19 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B88" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A88,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -6586,14 +7684,14 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B89" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A89,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -6625,14 +7723,14 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B90" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A90,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -6661,19 +7759,19 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B91" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A91,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -6702,19 +7800,19 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B92" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A92,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -6743,19 +7841,19 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B93" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A93,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -6787,14 +7885,14 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B94" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A94,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -6826,14 +7924,14 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B95" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A95,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -6862,19 +7960,19 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B96" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A96,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -6903,19 +8001,19 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B97" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A97,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -6944,19 +8042,19 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B98" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A98,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -6988,14 +8086,14 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B99" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A99,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -7027,14 +8125,14 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B100" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A100,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -7063,19 +8161,19 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B101" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A101,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -7104,19 +8202,19 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B102" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A102,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -7148,14 +8246,14 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B103" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A103,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -7184,19 +8282,19 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B104" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A104,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -7225,19 +8323,19 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B105" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A105,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -7266,19 +8364,19 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B106" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A106,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -7310,14 +8408,14 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B107" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A107,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -7349,14 +8447,14 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B108" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A108,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -7385,19 +8483,19 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B109" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A109,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -7426,19 +8524,19 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B110" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A110,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -7467,19 +8565,19 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B111" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A111,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -7511,14 +8609,14 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B112" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A112,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -7550,14 +8648,14 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B113" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A113,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -7586,19 +8684,19 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B114" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A114,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -7627,19 +8725,19 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B115" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A115,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -7668,19 +8766,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B116" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A116,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -7712,14 +8810,14 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B117" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A117,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -7751,14 +8849,14 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B118" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A118,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -7787,19 +8885,19 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B119" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A119,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -7828,19 +8926,19 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B120" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A120,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -7869,19 +8967,19 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B121" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A121,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -7913,14 +9011,14 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B122" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A122,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -7952,14 +9050,14 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B123" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A123,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -7988,19 +9086,19 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B124" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A124,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -8029,19 +9127,19 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B125" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A125,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
@@ -8073,14 +9171,14 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B126" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A126,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -8109,19 +9207,19 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B127" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A127,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -8150,19 +9248,19 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B128" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A128,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -8191,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -8228,226 +9326,226 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>172</v>
+      <c r="A2" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
+        <v>249</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8485,209 +9583,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -10,10 +10,11 @@
   <sheets>
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Киты" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Параметры" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Состав" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Поставщики" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Моторы" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Прогноз" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Параметры" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Состав" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Поставщики" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Моторы" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -71,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="319">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -97,7 +98,10 @@
     <t xml:space="preserve">4. «Параметры» — наценка, комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. «Моторы» — справка: где цепь, где ремень, что входит в ГРМ-кит, источники.</t>
+    <t xml:space="preserve">5. «Прогноз» — выручка и прибыль за месяц при разном числе заказов, точка безубыточности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. «Моторы» — справка: где цепь, где ремень, что входит в ГРМ-кит, источники.</t>
   </si>
   <si>
     <t xml:space="preserve">Обозначения:</t>
@@ -515,6 +519,69 @@
   </si>
   <si>
     <t xml:space="preserve">grm-12-coolray-1-main.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прогноз на месяц (до налога)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средний чек кита, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднее по собранным китам Picanto (4 190) и Jetta (4 790). Замените, когда соберёте больше китов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средняя стоимость деталей, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднее по Picanto (3 126) и Jetta (3 604).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля оплат через Авито Доставку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Остальные — прямым переводом. Ваша оценка; уточните по факту.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Справка: средний чек по листу «Киты»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Справка: средние детали по листу «Киты»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянные расходы в месяц, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сумма постоянных расходов с листа «Параметры».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль с 1 заказа до постоянных расходов, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точка безубыточности, заказов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Детали и упаковка, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СДЭК за ваш счёт, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянные, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль до налога, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль на 1 заказ, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог не учтён. Число заказов в колонке A можно менять. При росте продаж впишите в «Параметры» подписку Авито Pro, если подключите.</t>
   </si>
   <si>
     <t xml:space="preserve">Параметр</t>
@@ -968,14 +1035,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;;\-#,##0&quot; ₽&quot;;\-"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1040,6 +1108,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -1125,7 +1201,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1186,19 +1262,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1504,7 +1588,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1559,15 +1643,15 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1579,6 +1663,11 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1626,102 +1715,102 @@
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I2" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A2)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A2))</f>
@@ -1781,33 +1870,33 @@
         <v/>
       </c>
       <c r="X2" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I3" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A3)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A3))</f>
@@ -1867,33 +1956,33 @@
         <v/>
       </c>
       <c r="X3" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I4" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A4)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A4))</f>
@@ -1953,33 +2042,33 @@
         <v/>
       </c>
       <c r="X4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I5" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A5)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A5))</f>
@@ -2039,33 +2128,33 @@
         <v/>
       </c>
       <c r="X5" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A6)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A6))</f>
@@ -2125,33 +2214,33 @@
         <v/>
       </c>
       <c r="X6" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I7" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A7)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A7))</f>
@@ -2211,33 +2300,33 @@
         <v/>
       </c>
       <c r="X7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I8" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A8)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A8))</f>
@@ -2297,33 +2386,33 @@
         <v/>
       </c>
       <c r="X8" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A9)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A9))</f>
@@ -2383,33 +2472,33 @@
         <v/>
       </c>
       <c r="X9" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A10)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A10))</f>
@@ -2469,33 +2558,33 @@
         <v/>
       </c>
       <c r="X10" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I11" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A11)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A11))</f>
@@ -2555,33 +2644,33 @@
         <v/>
       </c>
       <c r="X11" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I12" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A12)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A12))</f>
@@ -2641,33 +2730,33 @@
         <v/>
       </c>
       <c r="X12" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I13" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A13)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A13))</f>
@@ -2727,33 +2816,33 @@
         <v/>
       </c>
       <c r="X13" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I14" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A14))</f>
@@ -2813,33 +2902,33 @@
         <v/>
       </c>
       <c r="X14" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I15" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A15))</f>
@@ -2899,33 +2988,33 @@
         <v/>
       </c>
       <c r="X15" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I16" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A16))</f>
@@ -2985,33 +3074,33 @@
         <v/>
       </c>
       <c r="X16" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I17" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A17))</f>
@@ -3071,33 +3160,33 @@
         <v/>
       </c>
       <c r="X17" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I18" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A18))</f>
@@ -3157,33 +3246,33 @@
         <v/>
       </c>
       <c r="X18" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I19" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A19))</f>
@@ -3243,33 +3332,33 @@
         <v/>
       </c>
       <c r="X19" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I20" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A20))</f>
@@ -3329,33 +3418,33 @@
         <v/>
       </c>
       <c r="X20" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I21" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A21))</f>
@@ -3415,33 +3504,33 @@
         <v/>
       </c>
       <c r="X21" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I22" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A22))</f>
@@ -3501,33 +3590,33 @@
         <v/>
       </c>
       <c r="X22" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I23" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A23))</f>
@@ -3587,33 +3676,33 @@
         <v/>
       </c>
       <c r="X23" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I24" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A24))</f>
@@ -3673,33 +3762,33 @@
         <v/>
       </c>
       <c r="X24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I25" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A25))</f>
@@ -3759,33 +3848,33 @@
         <v/>
       </c>
       <c r="X25" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I26" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A26))</f>
@@ -3845,7 +3934,7 @@
         <v/>
       </c>
       <c r="X26" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3891,6 +3980,424 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>4490</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>3365</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIF(Киты!$M:$M,"&gt;0"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIF(Киты!$I:$I,"&gt;0"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <f aca="false">(Параметры!$B$12+Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16)</f>
+        <v>6783</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <f aca="false">B3-(B4+Параметры!$B$3)-B5*B3*Параметры!$B$6-(1-B5)*(B3*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-B4*Параметры!$B$8</f>
+        <v>565.11</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <f aca="false">IF(B9&lt;=0,"не окупается",ROUNDUP(B8/B9,0))</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <f aca="false">A13*$B$3</f>
+        <v>44900</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <f aca="false">A13*($B$4+Параметры!$B$3)</f>
+        <v>34150</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <f aca="false">A13*$B$5*$B$3*Параметры!$B$6</f>
+        <v>1459.25</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <f aca="false">A13*(1-$B$5)*$B$3*Параметры!$B$10</f>
+        <v>157.15</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <f aca="false">A13*Параметры!$B$7</f>
+        <v>1800</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <f aca="false">A13*$B$4*Параметры!$B$8</f>
+        <v>1682.5</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <f aca="false">A13*(1-$B$5)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <f aca="false">$B$8</f>
+        <v>6783</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <f aca="false">B13-SUM(C13:I13)</f>
+        <v>-1131.9</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <f aca="false">IF(A13=0,"",J13/A13)</f>
+        <v>-113.19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <f aca="false">A14*$B$3</f>
+        <v>89800</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <f aca="false">A14*($B$4+Параметры!$B$3)</f>
+        <v>68300</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <f aca="false">A14*$B$5*$B$3*Параметры!$B$6</f>
+        <v>2918.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <f aca="false">A14*(1-$B$5)*$B$3*Параметры!$B$10</f>
+        <v>314.3</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <f aca="false">A14*Параметры!$B$7</f>
+        <v>3600</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <f aca="false">A14*$B$4*Параметры!$B$8</f>
+        <v>3365</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <f aca="false">A14*(1-$B$5)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <f aca="false">$B$8</f>
+        <v>6783</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <f aca="false">B14-SUM(C14:I14)</f>
+        <v>4519.2</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <f aca="false">IF(A14=0,"",J14/A14)</f>
+        <v>225.96</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <f aca="false">A15*$B$3</f>
+        <v>134700</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <f aca="false">A15*($B$4+Параметры!$B$3)</f>
+        <v>102450</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <f aca="false">A15*$B$5*$B$3*Параметры!$B$6</f>
+        <v>4377.75</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <f aca="false">A15*(1-$B$5)*$B$3*Параметры!$B$10</f>
+        <v>471.45</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <f aca="false">A15*Параметры!$B$7</f>
+        <v>5400</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <f aca="false">A15*$B$4*Параметры!$B$8</f>
+        <v>5047.5</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <f aca="false">A15*(1-$B$5)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <f aca="false">$B$8</f>
+        <v>6783</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <f aca="false">B15-SUM(C15:I15)</f>
+        <v>10170.3</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <f aca="false">IF(A15=0,"",J15/A15)</f>
+        <v>339.01</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <f aca="false">A16*$B$3</f>
+        <v>224500</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <f aca="false">A16*($B$4+Параметры!$B$3)</f>
+        <v>170750</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">A16*$B$5*$B$3*Параметры!$B$6</f>
+        <v>7296.25</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <f aca="false">A16*(1-$B$5)*$B$3*Параметры!$B$10</f>
+        <v>785.75</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <f aca="false">A16*Параметры!$B$7</f>
+        <v>9000</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <f aca="false">A16*$B$4*Параметры!$B$8</f>
+        <v>8412.5</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <f aca="false">A16*(1-$B$5)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <f aca="false">$B$8</f>
+        <v>6783</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <f aca="false">B16-SUM(C16:I16)</f>
+        <v>21472.5</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <f aca="false">IF(A16=0,"",J16/A16)</f>
+        <v>429.45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <f aca="false">A17*$B$3</f>
+        <v>449000</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <f aca="false">A17*($B$4+Параметры!$B$3)</f>
+        <v>341500</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <f aca="false">A17*$B$5*$B$3*Параметры!$B$6</f>
+        <v>14592.5</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">A17*(1-$B$5)*$B$3*Параметры!$B$10</f>
+        <v>1571.5</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <f aca="false">A17*Параметры!$B$7</f>
+        <v>18000</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <f aca="false">A17*$B$4*Параметры!$B$8</f>
+        <v>16825</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <f aca="false">A17*(1-$B$5)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <f aca="false">$B$8</f>
+        <v>6783</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <f aca="false">B17-SUM(C17:I17)</f>
+        <v>49728</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <f aca="false">IF(A17=0,"",J17/A17)</f>
+        <v>497.28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="C8:J8"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J13:J17">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3901,206 +4408,206 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="15" t="n">
+        <v>173</v>
+      </c>
+      <c r="B2" s="18" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="15" t="n">
+        <v>181</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="15" t="n">
+        <v>185</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="15" t="n">
+        <v>189</v>
+      </c>
+      <c r="B10" s="18" t="n">
         <v>0.007</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>4783</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>1500</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>500</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="16" t="n">
+        <v>203</v>
+      </c>
+      <c r="B17" s="19" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">($B$12+$B$13+$B$14+$B$15+$B$16)/MAX(1,$B$17)</f>
         <v>339.15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -4114,7 +4621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4137,125 +4644,125 @@
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" s="20" t="n">
+      <c r="A2" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="21" t="n">
+      <c r="E2" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" s="23" t="n">
         <v>460</v>
       </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21" t="n">
+      <c r="H2" s="23"/>
+      <c r="I2" s="23" t="n">
         <v>445</v>
       </c>
-      <c r="J2" s="21" t="n">
+      <c r="J2" s="23" t="n">
         <v>430</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21" t="n">
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="22" t="n">
+      <c r="O2" s="23"/>
+      <c r="P2" s="24" t="n">
         <f aca="false">IF(COUNT(G2:O2)=0,"",MIN(G2:O2))</f>
         <v>430</v>
       </c>
-      <c r="Q2" s="19" t="str">
+      <c r="Q2" s="21" t="str">
         <f aca="false">IF(P2="","",INDEX($G$1:$O$1,MATCH(P2,G2:O2,0)))</f>
         <v>Росско</v>
       </c>
-      <c r="R2" s="22" t="n">
+      <c r="R2" s="24" t="n">
         <f aca="false">IF(P2="",0,P2*D2)</f>
         <v>430</v>
       </c>
-      <c r="S2" s="23" t="s">
-        <v>208</v>
+      <c r="S2" s="25" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A3,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -4284,19 +4791,19 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A4,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -4328,14 +4835,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A5,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -4367,14 +4874,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A6,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -4406,14 +4913,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A7,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -4445,14 +4952,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A8,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -4481,19 +4988,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A9,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -4525,14 +5032,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A10,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -4564,14 +5071,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A11,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -4603,14 +5110,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A12,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -4642,14 +5149,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A13,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -4678,19 +5185,19 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A14,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -4722,14 +5229,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A15,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -4761,14 +5268,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A16,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -4800,14 +5307,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A17,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -4839,14 +5346,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A18,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -4875,19 +5382,19 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A19,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -4919,14 +5426,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A20,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -4958,14 +5465,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A21,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -4997,14 +5504,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A22,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -5036,14 +5543,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A23,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -5072,19 +5579,19 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A24,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -5116,14 +5623,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A25,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -5155,14 +5662,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A26,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -5194,14 +5701,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A27,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -5233,14 +5740,14 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A28,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -5269,19 +5776,19 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A29,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -5313,14 +5820,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A30,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -5352,14 +5859,14 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A31,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -5391,14 +5898,14 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A32,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -5430,14 +5937,14 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A33,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -5466,19 +5973,19 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A34,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -5507,19 +6014,19 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A35,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -5551,14 +6058,14 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A36,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -5590,14 +6097,14 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A37,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -5629,14 +6136,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B38" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A38,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -5668,14 +6175,14 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B39" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A39,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -5704,19 +6211,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A40,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -5745,19 +6252,19 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B41" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A41,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -5789,14 +6296,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B42" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A42,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -5828,14 +6335,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B43" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A43,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -5867,14 +6374,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B44" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A44,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -5906,14 +6413,14 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B45" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A45,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -5942,19 +6449,19 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B46" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A46,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -5983,19 +6490,19 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B47" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A47,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -6027,14 +6534,14 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B48" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A48,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -6066,14 +6573,14 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B49" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A49,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -6105,14 +6612,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B50" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A50,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -6144,14 +6651,14 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B51" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A51,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -6180,19 +6687,19 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B52" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A52,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -6221,19 +6728,19 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B53" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A53,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -6265,14 +6772,14 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B54" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A54,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -6304,14 +6811,14 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B55" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A55,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -6343,14 +6850,14 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B56" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A56,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -6382,14 +6889,14 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B57" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A57,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -6418,19 +6925,19 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B58" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A58,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -6459,19 +6966,19 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B59" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A59,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -6503,14 +7010,14 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B60" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A60,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -6542,14 +7049,14 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B61" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A61,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -6581,14 +7088,14 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B62" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A62,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -6620,14 +7127,14 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B63" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A63,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -6656,19 +7163,19 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B64" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A64,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -6697,19 +7204,19 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B65" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A65,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -6741,14 +7248,14 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B66" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A66,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -6780,14 +7287,14 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B67" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A67,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -6819,14 +7326,14 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B68" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A68,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -6858,20 +7365,20 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B69" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A69,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -6896,25 +7403,25 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B70" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A70,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -6939,25 +7446,25 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B71" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A71,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -6982,25 +7489,25 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B72" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A72,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -7025,25 +7532,25 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B73" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A73,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -7068,25 +7575,25 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B74" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A74,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -7111,25 +7618,25 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B75" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A75,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -7154,25 +7661,25 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B76" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A76,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -7197,19 +7704,19 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B77" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A77,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -7238,19 +7745,19 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B78" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A78,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -7282,14 +7789,14 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B79" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A79,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -7321,14 +7828,14 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B80" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A80,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -7357,19 +7864,19 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B81" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A81,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -7398,19 +7905,19 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B82" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A82,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -7439,19 +7946,19 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B83" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A83,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -7483,14 +7990,14 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B84" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A84,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -7522,14 +8029,14 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B85" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A85,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -7558,19 +8065,19 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B86" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A86,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -7599,19 +8106,19 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B87" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A87,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -7640,19 +8147,19 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B88" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A88,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -7684,14 +8191,14 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B89" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A89,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -7723,14 +8230,14 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B90" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A90,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -7759,19 +8266,19 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B91" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A91,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -7800,19 +8307,19 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B92" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A92,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -7841,19 +8348,19 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B93" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A93,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -7885,14 +8392,14 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B94" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A94,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -7924,14 +8431,14 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B95" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A95,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -7960,19 +8467,19 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B96" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A96,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -8001,19 +8508,19 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B97" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A97,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -8042,19 +8549,19 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B98" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A98,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -8086,14 +8593,14 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B99" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A99,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -8125,14 +8632,14 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B100" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A100,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -8161,19 +8668,19 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B101" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A101,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -8202,19 +8709,19 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B102" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A102,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -8246,14 +8753,14 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B103" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A103,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -8282,19 +8789,19 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B104" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A104,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -8323,19 +8830,19 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B105" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A105,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -8364,19 +8871,19 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B106" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A106,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -8408,14 +8915,14 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B107" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A107,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -8447,14 +8954,14 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B108" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A108,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -8483,19 +8990,19 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B109" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A109,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -8524,19 +9031,19 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B110" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A110,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -8565,19 +9072,19 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B111" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A111,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -8609,14 +9116,14 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B112" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A112,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -8648,14 +9155,14 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B113" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A113,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -8684,19 +9191,19 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B114" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A114,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -8725,19 +9232,19 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B115" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A115,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -8766,19 +9273,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B116" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A116,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -8810,14 +9317,14 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B117" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A117,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -8849,14 +9356,14 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B118" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A118,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -8885,19 +9392,19 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B119" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A119,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -8926,19 +9433,19 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B120" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A120,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -8967,19 +9474,19 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B121" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A121,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -9011,14 +9518,14 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B122" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A122,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -9050,14 +9557,14 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B123" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A123,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -9086,19 +9593,19 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B124" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A124,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -9127,19 +9634,19 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B125" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A125,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
@@ -9171,14 +9678,14 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B126" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A126,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -9207,19 +9714,19 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B127" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A127,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -9248,19 +9755,19 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B128" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A128,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -9289,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -9303,7 +9810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9326,226 +9833,226 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="E2" s="18" t="n">
+      <c r="A2" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>204</v>
+      <c r="F2" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
+        <v>279</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
+        <v>271</v>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -9564,7 +10071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9583,209 +10090,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>265</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="323">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">GRM-12</t>
   </si>
   <si>
-    <t xml:space="preserve">ГРМ-кит Geely Coolray 1.5T: 2 ремня и ролик</t>
+    <t xml:space="preserve">ГРМ-кит Geely Coolray 1.5T: 2 ремня и 2 ролика</t>
   </si>
   <si>
     <t xml:space="preserve">grm-12-coolray-1-main.png</t>
@@ -854,10 +854,22 @@
     <t xml:space="preserve">Комплект ремня ГРМ (ремень, натяжной ролик)</t>
   </si>
   <si>
+    <t xml:space="preserve">Комплект ГРМ XIAOLU XIBTK007: ремень и 2 ролика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIAOLU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIBTK007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 8 582,00 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ремень привода помпы</t>
   </si>
   <si>
-    <t xml:space="preserve">По регламенту меняется вместе с ремнём ГРМ</t>
+    <t xml:space="preserve">Ваша закупка: 990,23 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">Поставщик</t>
@@ -9646,13 +9658,17 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E125" s="14"/>
-      <c r="F125" s="14"/>
+      <c r="E125" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>262</v>
+      </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
@@ -9674,7 +9690,9 @@
         <f aca="false">IF(P125="",0,P125*D125)</f>
         <v>0</v>
       </c>
-      <c r="S125" s="8"/>
+      <c r="S125" s="8" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
@@ -9685,7 +9703,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -9714,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9833,34 +9851,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>224</v>
@@ -9871,31 +9889,31 @@
         <v>225</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>226</v>
@@ -9906,7 +9924,7 @@
         <v>212</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -9923,7 +9941,7 @@
         <v>213</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -9940,7 +9958,7 @@
         <v>214</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -9957,7 +9975,7 @@
         <v>215</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -9974,7 +9992,7 @@
         <v>216</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
@@ -9991,7 +10009,7 @@
         <v>217</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -10008,7 +10026,7 @@
         <v>218</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
@@ -10025,7 +10043,7 @@
         <v>219</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -10042,7 +10060,7 @@
         <v>220</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -10093,7 +10111,7 @@
         <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>17</v>
@@ -10102,197 +10120,197 @@
         <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -43,6 +43,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Считается по наценке с листа «Параметры». Если в колонке Y «Своя цена по рынку» есть число — берётся оно.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="U1" authorId="0">
       <text>
         <r>
@@ -67,12 +79,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Для китов, где цену ставим по рынку, а не по наценке: впишите цену, по которой конечный покупатель берёт то же самое на маркетплейсах. Пусто — цена по наценке.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Цена по рынку (сентябрь 2026): Gates K0120529 отдельно — 7 290–10 526 ₽ в рознице, ремень помпы — 740–1 679 ₽. У нас оба ремня и ролики в одной коробке дешевле, чем по отдельности на Яндекс Маркете.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="324">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -92,7 +128,7 @@
     <t xml:space="preserve">3. «Киты» — сами посчитаются закупка, цена на Авито и прибыль до налога в двух вариантах: оплата через Авито Доставку и прямым переводом.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком.</t>
+    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком. Колонка Y «Своя цена по рынку» — если цену кита ставим по рынку, а не по наценке.</t>
   </si>
   <si>
     <t xml:space="preserve">4. «Параметры» — наценка, комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
@@ -188,6 +224,9 @@
     <t xml:space="preserve">Статус</t>
   </si>
   <si>
+    <t xml:space="preserve">Своя цена по рынку, ₽</t>
+  </si>
+  <si>
     <t xml:space="preserve">TO-01</t>
   </si>
   <si>
@@ -515,7 +554,7 @@
     <t xml:space="preserve">GRM-12</t>
   </si>
   <si>
-    <t xml:space="preserve">ГРМ-кит Geely Coolray 1.5T: 2 ремня и 2 ролика</t>
+    <t xml:space="preserve">ГРМ-кит Gates Geely Coolray 1.5T: ремни и ролики</t>
   </si>
   <si>
     <t xml:space="preserve">grm-12-coolray-1-main.png</t>
@@ -854,16 +893,16 @@
     <t xml:space="preserve">Комплект ремня ГРМ (ремень, натяжной ролик)</t>
   </si>
   <si>
-    <t xml:space="preserve">Комплект ГРМ XIAOLU XIBTK007: ремень и 2 ролика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIAOLU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIBTK007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ваша закупка: 8 582,00 ₽ — впишите в колонку поставщика, у которого брали</t>
+    <t xml:space="preserve">Комплект ГРМ Gates K0120529: ремень и 2 ролика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K0120529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 6 066,00 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">Ремень привода помпы</t>
@@ -1698,7 +1737,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1722,7 +1761,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1798,31 +1837,34 @@
       <c r="X1" s="5" t="s">
         <v>37</v>
       </c>
+      <c r="Y1" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I2" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A2)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A2))</f>
@@ -1841,7 +1883,7 @@
         <v/>
       </c>
       <c r="M2" s="11" t="str">
-        <f aca="false">IF(I2="","",CEILING((I2*(1+Параметры!$B$8*Параметры!$B$9)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I2="","",IF(Y2&lt;&gt;"",Y2,CEILING((I2*(1+Параметры!$B$8*Параметры!$B$9)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N2" s="12"/>
@@ -1882,33 +1924,34 @@
         <v/>
       </c>
       <c r="X2" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I3" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A3)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A3))</f>
@@ -1927,7 +1970,7 @@
         <v/>
       </c>
       <c r="M3" s="11" t="str">
-        <f aca="false">IF(I3="","",CEILING((I3*(1+Параметры!$B$8*Параметры!$B$9)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I3="","",IF(Y3&lt;&gt;"",Y3,CEILING((I3*(1+Параметры!$B$8*Параметры!$B$9)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N3" s="12"/>
@@ -1968,33 +2011,34 @@
         <v/>
       </c>
       <c r="X3" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I4" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A4)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A4))</f>
@@ -2013,7 +2057,7 @@
         <v/>
       </c>
       <c r="M4" s="11" t="str">
-        <f aca="false">IF(I4="","",CEILING((I4*(1+Параметры!$B$8*Параметры!$B$9)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I4="","",IF(Y4&lt;&gt;"",Y4,CEILING((I4*(1+Параметры!$B$8*Параметры!$B$9)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N4" s="12"/>
@@ -2054,33 +2098,34 @@
         <v/>
       </c>
       <c r="X4" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I5" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A5)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A5))</f>
@@ -2099,7 +2144,7 @@
         <v/>
       </c>
       <c r="M5" s="11" t="str">
-        <f aca="false">IF(I5="","",CEILING((I5*(1+Параметры!$B$8*Параметры!$B$9)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I5="","",IF(Y5&lt;&gt;"",Y5,CEILING((I5*(1+Параметры!$B$8*Параметры!$B$9)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N5" s="12"/>
@@ -2140,33 +2185,34 @@
         <v/>
       </c>
       <c r="X5" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I6" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A6)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A6))</f>
@@ -2185,7 +2231,7 @@
         <v/>
       </c>
       <c r="M6" s="11" t="str">
-        <f aca="false">IF(I6="","",CEILING((I6*(1+Параметры!$B$8*Параметры!$B$9)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I6="","",IF(Y6&lt;&gt;"",Y6,CEILING((I6*(1+Параметры!$B$8*Параметры!$B$9)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N6" s="12"/>
@@ -2226,33 +2272,34 @@
         <v/>
       </c>
       <c r="X6" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A7)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A7))</f>
@@ -2271,7 +2318,7 @@
         <v/>
       </c>
       <c r="M7" s="11" t="str">
-        <f aca="false">IF(I7="","",CEILING((I7*(1+Параметры!$B$8*Параметры!$B$9)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I7="","",IF(Y7&lt;&gt;"",Y7,CEILING((I7*(1+Параметры!$B$8*Параметры!$B$9)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N7" s="12"/>
@@ -2312,33 +2359,34 @@
         <v/>
       </c>
       <c r="X7" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A8)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A8))</f>
@@ -2357,7 +2405,7 @@
         <v/>
       </c>
       <c r="M8" s="11" t="str">
-        <f aca="false">IF(I8="","",CEILING((I8*(1+Параметры!$B$8*Параметры!$B$9)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I8="","",IF(Y8&lt;&gt;"",Y8,CEILING((I8*(1+Параметры!$B$8*Параметры!$B$9)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N8" s="12"/>
@@ -2398,33 +2446,34 @@
         <v/>
       </c>
       <c r="X8" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I9" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A9)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A9))</f>
@@ -2443,7 +2492,7 @@
         <v/>
       </c>
       <c r="M9" s="11" t="str">
-        <f aca="false">IF(I9="","",CEILING((I9*(1+Параметры!$B$8*Параметры!$B$9)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I9="","",IF(Y9&lt;&gt;"",Y9,CEILING((I9*(1+Параметры!$B$8*Параметры!$B$9)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N9" s="12"/>
@@ -2484,33 +2533,34 @@
         <v/>
       </c>
       <c r="X9" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A10)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A10))</f>
@@ -2529,7 +2579,7 @@
         <v/>
       </c>
       <c r="M10" s="11" t="str">
-        <f aca="false">IF(I10="","",CEILING((I10*(1+Параметры!$B$8*Параметры!$B$9)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I10="","",IF(Y10&lt;&gt;"",Y10,CEILING((I10*(1+Параметры!$B$8*Параметры!$B$9)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N10" s="12"/>
@@ -2570,33 +2620,34 @@
         <v/>
       </c>
       <c r="X10" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I11" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A11)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A11))</f>
@@ -2615,7 +2666,7 @@
         <v/>
       </c>
       <c r="M11" s="11" t="str">
-        <f aca="false">IF(I11="","",CEILING((I11*(1+Параметры!$B$8*Параметры!$B$9)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I11="","",IF(Y11&lt;&gt;"",Y11,CEILING((I11*(1+Параметры!$B$8*Параметры!$B$9)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N11" s="12"/>
@@ -2656,33 +2707,34 @@
         <v/>
       </c>
       <c r="X11" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I12" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A12)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A12))</f>
@@ -2701,7 +2753,7 @@
         <v/>
       </c>
       <c r="M12" s="11" t="str">
-        <f aca="false">IF(I12="","",CEILING((I12*(1+Параметры!$B$8*Параметры!$B$9)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I12="","",IF(Y12&lt;&gt;"",Y12,CEILING((I12*(1+Параметры!$B$8*Параметры!$B$9)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N12" s="12"/>
@@ -2742,33 +2794,34 @@
         <v/>
       </c>
       <c r="X12" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I13" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A13)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A13))</f>
@@ -2787,7 +2840,7 @@
         <v/>
       </c>
       <c r="M13" s="11" t="str">
-        <f aca="false">IF(I13="","",CEILING((I13*(1+Параметры!$B$8*Параметры!$B$9)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I13="","",IF(Y13&lt;&gt;"",Y13,CEILING((I13*(1+Параметры!$B$8*Параметры!$B$9)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N13" s="12"/>
@@ -2828,33 +2881,34 @@
         <v/>
       </c>
       <c r="X13" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I14" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A14)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A14))</f>
@@ -2873,7 +2927,7 @@
         <v/>
       </c>
       <c r="M14" s="11" t="str">
-        <f aca="false">IF(I14="","",CEILING((I14*(1+Параметры!$B$8*Параметры!$B$9)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I14="","",IF(Y14&lt;&gt;"",Y14,CEILING((I14*(1+Параметры!$B$8*Параметры!$B$9)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N14" s="12"/>
@@ -2914,33 +2968,34 @@
         <v/>
       </c>
       <c r="X14" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I15" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A15)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A15))</f>
@@ -2959,7 +3014,7 @@
         <v/>
       </c>
       <c r="M15" s="11" t="str">
-        <f aca="false">IF(I15="","",CEILING((I15*(1+Параметры!$B$8*Параметры!$B$9)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I15="","",IF(Y15&lt;&gt;"",Y15,CEILING((I15*(1+Параметры!$B$8*Параметры!$B$9)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N15" s="12"/>
@@ -3000,33 +3055,34 @@
         <v/>
       </c>
       <c r="X15" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I16" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A16)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A16))</f>
@@ -3045,7 +3101,7 @@
         <v/>
       </c>
       <c r="M16" s="11" t="str">
-        <f aca="false">IF(I16="","",CEILING((I16*(1+Параметры!$B$8*Параметры!$B$9)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I16="","",IF(Y16&lt;&gt;"",Y16,CEILING((I16*(1+Параметры!$B$8*Параметры!$B$9)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N16" s="12"/>
@@ -3086,33 +3142,34 @@
         <v/>
       </c>
       <c r="X16" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I17" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A17)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A17))</f>
@@ -3131,7 +3188,7 @@
         <v/>
       </c>
       <c r="M17" s="11" t="str">
-        <f aca="false">IF(I17="","",CEILING((I17*(1+Параметры!$B$8*Параметры!$B$9)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I17="","",IF(Y17&lt;&gt;"",Y17,CEILING((I17*(1+Параметры!$B$8*Параметры!$B$9)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N17" s="12"/>
@@ -3172,33 +3229,34 @@
         <v/>
       </c>
       <c r="X17" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I18" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A18)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A18))</f>
@@ -3217,7 +3275,7 @@
         <v/>
       </c>
       <c r="M18" s="11" t="str">
-        <f aca="false">IF(I18="","",CEILING((I18*(1+Параметры!$B$8*Параметры!$B$9)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I18="","",IF(Y18&lt;&gt;"",Y18,CEILING((I18*(1+Параметры!$B$8*Параметры!$B$9)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N18" s="12"/>
@@ -3258,33 +3316,34 @@
         <v/>
       </c>
       <c r="X18" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I19" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A19)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A19))</f>
@@ -3303,7 +3362,7 @@
         <v/>
       </c>
       <c r="M19" s="11" t="str">
-        <f aca="false">IF(I19="","",CEILING((I19*(1+Параметры!$B$8*Параметры!$B$9)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I19="","",IF(Y19&lt;&gt;"",Y19,CEILING((I19*(1+Параметры!$B$8*Параметры!$B$9)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N19" s="12"/>
@@ -3344,33 +3403,34 @@
         <v/>
       </c>
       <c r="X19" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I20" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A20)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A20))</f>
@@ -3389,7 +3449,7 @@
         <v/>
       </c>
       <c r="M20" s="11" t="str">
-        <f aca="false">IF(I20="","",CEILING((I20*(1+Параметры!$B$8*Параметры!$B$9)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I20="","",IF(Y20&lt;&gt;"",Y20,CEILING((I20*(1+Параметры!$B$8*Параметры!$B$9)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N20" s="12"/>
@@ -3430,33 +3490,34 @@
         <v/>
       </c>
       <c r="X20" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I21" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A21)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A21))</f>
@@ -3475,7 +3536,7 @@
         <v/>
       </c>
       <c r="M21" s="11" t="str">
-        <f aca="false">IF(I21="","",CEILING((I21*(1+Параметры!$B$8*Параметры!$B$9)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I21="","",IF(Y21&lt;&gt;"",Y21,CEILING((I21*(1+Параметры!$B$8*Параметры!$B$9)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N21" s="12"/>
@@ -3516,33 +3577,34 @@
         <v/>
       </c>
       <c r="X21" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I22" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A22)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A22))</f>
@@ -3561,7 +3623,7 @@
         <v/>
       </c>
       <c r="M22" s="11" t="str">
-        <f aca="false">IF(I22="","",CEILING((I22*(1+Параметры!$B$8*Параметры!$B$9)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I22="","",IF(Y22&lt;&gt;"",Y22,CEILING((I22*(1+Параметры!$B$8*Параметры!$B$9)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N22" s="12"/>
@@ -3602,33 +3664,34 @@
         <v/>
       </c>
       <c r="X22" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I23" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A23)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A23))</f>
@@ -3647,7 +3710,7 @@
         <v/>
       </c>
       <c r="M23" s="11" t="str">
-        <f aca="false">IF(I23="","",CEILING((I23*(1+Параметры!$B$8*Параметры!$B$9)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I23="","",IF(Y23&lt;&gt;"",Y23,CEILING((I23*(1+Параметры!$B$8*Параметры!$B$9)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N23" s="12"/>
@@ -3688,33 +3751,34 @@
         <v/>
       </c>
       <c r="X23" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I24" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A24)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A24))</f>
@@ -3733,7 +3797,7 @@
         <v/>
       </c>
       <c r="M24" s="11" t="str">
-        <f aca="false">IF(I24="","",CEILING((I24*(1+Параметры!$B$8*Параметры!$B$9)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I24="","",IF(Y24&lt;&gt;"",Y24,CEILING((I24*(1+Параметры!$B$8*Параметры!$B$9)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N24" s="12"/>
@@ -3774,33 +3838,34 @@
         <v/>
       </c>
       <c r="X24" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I25" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A25)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A25))</f>
@@ -3819,7 +3884,7 @@
         <v/>
       </c>
       <c r="M25" s="11" t="str">
-        <f aca="false">IF(I25="","",CEILING((I25*(1+Параметры!$B$8*Параметры!$B$9)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I25="","",IF(Y25&lt;&gt;"",Y25,CEILING((I25*(1+Параметры!$B$8*Параметры!$B$9)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N25" s="12"/>
@@ -3860,33 +3925,34 @@
         <v/>
       </c>
       <c r="X25" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Y25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I26" s="9" t="str">
         <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A26)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A26))</f>
@@ -3905,7 +3971,7 @@
         <v/>
       </c>
       <c r="M26" s="11" t="str">
-        <f aca="false">IF(I26="","",CEILING((I26*(1+Параметры!$B$8*Параметры!$B$9)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I26="","",IF(Y26&lt;&gt;"",Y26,CEILING((I26*(1+Параметры!$B$8*Параметры!$B$9)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N26" s="12"/>
@@ -3946,7 +4012,10 @@
         <v/>
       </c>
       <c r="X26" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="Y26" s="12" t="n">
+        <v>9990</v>
       </c>
     </row>
   </sheetData>
@@ -4006,18 +4075,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>4490</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -4029,13 +4098,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3365</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -4047,13 +4116,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -4065,7 +4134,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIF(Киты!$M:$M,"&gt;0"),"")</f>
@@ -4074,7 +4143,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B7" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIF(Киты!$I:$I,"&gt;0"),"")</f>
@@ -4083,14 +4152,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">(Параметры!$B$12+Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16)</f>
         <v>6783</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -4102,7 +4171,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">B3-(B4+Параметры!$B$3)-B5*B3*Параметры!$B$6-(1-B5)*(B3*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-B4*Параметры!$B$8</f>
@@ -4111,7 +4180,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">IF(B9&lt;=0,"не окупается",ROUNDUP(B8/B9,0))</f>
@@ -4120,13 +4189,13 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>29</v>
@@ -4141,16 +4210,16 @@
         <v>32</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4380,7 +4449,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4420,206 +4489,206 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0.007</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>4783</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>1500</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>500</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">($B$12+$B$13+$B$14+$B$15+$B$16)/MAX(1,$B$17)</f>
         <v>339.15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4662,75 +4731,75 @@
         <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G2" s="23" t="n">
         <v>460</v>
@@ -4762,19 +4831,19 @@
         <v>430</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A3,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -4803,19 +4872,19 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A4,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -4847,14 +4916,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A5,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -4886,14 +4955,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A6,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -4925,14 +4994,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A7,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -4964,14 +5033,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A8,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -5000,19 +5069,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A9,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -5044,14 +5113,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A10,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -5083,14 +5152,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A11,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -5122,14 +5191,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A12,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -5161,14 +5230,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A13,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -5197,19 +5266,19 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A14,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -5241,14 +5310,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A15,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -5280,14 +5349,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A16,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -5319,14 +5388,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A17,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -5358,14 +5427,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A18,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -5394,19 +5463,19 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A19,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -5438,14 +5507,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A20,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -5477,14 +5546,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A21,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -5516,14 +5585,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A22,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -5555,14 +5624,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A23,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -5591,19 +5660,19 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A24,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -5635,14 +5704,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A25,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -5674,14 +5743,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A26,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -5713,14 +5782,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A27,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -5752,14 +5821,14 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A28,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -5788,19 +5857,19 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A29,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -5832,14 +5901,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A30,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -5871,14 +5940,14 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B31" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A31,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -5910,14 +5979,14 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B32" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A32,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -5949,14 +6018,14 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A33,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -5985,19 +6054,19 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A34,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -6026,19 +6095,19 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B35" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A35,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -6070,14 +6139,14 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B36" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A36,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -6109,14 +6178,14 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A37,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -6148,14 +6217,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A38,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -6187,14 +6256,14 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A39,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -6223,19 +6292,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B40" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A40,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -6264,19 +6333,19 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A41,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -6308,14 +6377,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B42" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A42,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -6347,14 +6416,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B43" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A43,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -6386,14 +6455,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B44" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A44,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -6425,14 +6494,14 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B45" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A45,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -6461,19 +6530,19 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B46" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A46,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -6502,19 +6571,19 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B47" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A47,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -6546,14 +6615,14 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B48" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A48,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -6585,14 +6654,14 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B49" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A49,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -6624,14 +6693,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B50" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A50,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -6663,14 +6732,14 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B51" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A51,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -6699,19 +6768,19 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B52" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A52,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -6740,19 +6809,19 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B53" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A53,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -6784,14 +6853,14 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B54" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A54,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -6823,14 +6892,14 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B55" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A55,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -6862,14 +6931,14 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B56" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A56,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -6901,14 +6970,14 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B57" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A57,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -6937,19 +7006,19 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B58" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A58,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -6978,19 +7047,19 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B59" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A59,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -7022,14 +7091,14 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B60" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A60,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -7061,14 +7130,14 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B61" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A61,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -7100,14 +7169,14 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B62" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A62,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -7139,14 +7208,14 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B63" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A63,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -7175,19 +7244,19 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B64" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A64,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -7216,19 +7285,19 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B65" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A65,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -7260,14 +7329,14 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B66" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A66,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -7299,14 +7368,14 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B67" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A67,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -7338,14 +7407,14 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B68" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A68,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -7377,20 +7446,20 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B69" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A69,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -7415,25 +7484,25 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B70" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A70,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -7458,25 +7527,25 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B71" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A71,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -7501,25 +7570,25 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B72" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A72,Киты!$A:$A,0)),"")</f>
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -7544,25 +7613,25 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B73" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A73,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -7587,25 +7656,25 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B74" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A74,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -7630,25 +7699,25 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B75" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A75,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -7673,25 +7742,25 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B76" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A76,Киты!$A:$A,0)),"")</f>
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -7716,19 +7785,19 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B77" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A77,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -7757,19 +7826,19 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B78" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A78,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -7801,14 +7870,14 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B79" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A79,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -7840,14 +7909,14 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B80" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A80,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -7876,19 +7945,19 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B81" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A81,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -7917,19 +7986,19 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B82" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A82,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -7958,19 +8027,19 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B83" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A83,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -8002,14 +8071,14 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B84" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A84,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -8041,14 +8110,14 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B85" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A85,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -8077,19 +8146,19 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B86" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A86,Киты!$A:$A,0)),"")</f>
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -8118,19 +8187,19 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B87" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A87,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -8159,19 +8228,19 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B88" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A88,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -8203,14 +8272,14 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B89" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A89,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -8242,14 +8311,14 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B90" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A90,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -8278,19 +8347,19 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B91" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A91,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -8319,19 +8388,19 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B92" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A92,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -8360,19 +8429,19 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B93" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A93,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -8404,14 +8473,14 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B94" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A94,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -8443,14 +8512,14 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B95" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A95,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -8479,19 +8548,19 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B96" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A96,Киты!$A:$A,0)),"")</f>
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -8520,19 +8589,19 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B97" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A97,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -8561,19 +8630,19 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B98" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A98,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -8605,14 +8674,14 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B99" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A99,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -8644,14 +8713,14 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B100" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A100,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -8680,19 +8749,19 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B101" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A101,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -8721,19 +8790,19 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B102" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A102,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -8765,14 +8834,14 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B103" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A103,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -8801,19 +8870,19 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B104" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A104,Киты!$A:$A,0)),"")</f>
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -8842,19 +8911,19 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B105" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A105,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -8883,19 +8952,19 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B106" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A106,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -8927,14 +8996,14 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B107" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A107,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -8966,14 +9035,14 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B108" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A108,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -9002,19 +9071,19 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B109" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A109,Киты!$A:$A,0)),"")</f>
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -9043,19 +9112,19 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B110" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A110,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -9084,19 +9153,19 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B111" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A111,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -9128,14 +9197,14 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B112" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A112,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -9167,14 +9236,14 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B113" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A113,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -9203,19 +9272,19 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B114" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A114,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -9244,19 +9313,19 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B115" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A115,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -9285,19 +9354,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B116" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A116,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -9329,14 +9398,14 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B117" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A117,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -9368,14 +9437,14 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B118" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A118,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -9404,19 +9473,19 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B119" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A119,Киты!$A:$A,0)),"")</f>
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -9445,19 +9514,19 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B120" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A120,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -9486,19 +9555,19 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B121" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A121,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -9530,14 +9599,14 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B122" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A122,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -9569,14 +9638,14 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B123" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A123,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -9605,19 +9674,19 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B124" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A124,Киты!$A:$A,0)),"")</f>
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -9646,28 +9715,28 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B125" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A125,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
@@ -9691,19 +9760,19 @@
         <v>0</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B126" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A126,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -9732,19 +9801,19 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B127" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A127,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -9773,19 +9842,19 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B128" s="7" t="str">
         <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A128,Киты!$A:$A,0)),"")</f>
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -9814,7 +9883,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -9851,80 +9920,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -9938,10 +10007,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -9955,10 +10024,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -9972,10 +10041,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -9989,10 +10058,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
@@ -10006,10 +10075,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -10023,10 +10092,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
@@ -10040,10 +10109,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -10057,10 +10126,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -10111,7 +10180,7 @@
         <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>17</v>
@@ -10120,197 +10189,197 @@
         <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>298</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>301</v>
-      </c>
       <c r="G5" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="333">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">4. «Параметры» — наценка, комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. «Прогноз» — выручка и прибыль за месяц при разном числе заказов, точка безубыточности.</t>
+    <t xml:space="preserve">5. «Прогноз» — выручка и прибыль за месяц: ТО-киты и ГРМ-киты отдельно и вместе, точка безубыточности.</t>
   </si>
   <si>
     <t xml:space="preserve">6. «Моторы» — справка: где цепь, где ремень, что входит в ГРМ-кит, источники.</t>
@@ -560,25 +560,34 @@
     <t xml:space="preserve">grm-12-coolray-1-main.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Прогноз на месяц (до налога)</t>
+    <t xml:space="preserve">Прогноз на месяц (до налога): ТО-киты и ГРМ-киты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТО-кит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГРМ-кит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пояснение</t>
   </si>
   <si>
     <t xml:space="preserve">Средний чек кита, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Среднее по собранным китам Picanto (4 190) и Jetta (4 790). Замените, когда соберёте больше китов.</t>
+    <t xml:space="preserve">ТО: среднее по Picanto (4 190) и Jetta (4 790). ГРМ: пока собран один — Coolray на Gates (9 990). Когда соберёте больше китов, возьмите средние из справки ниже.</t>
   </si>
   <si>
     <t xml:space="preserve">Средняя стоимость деталей, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Среднее по Picanto (3 126) и Jetta (3 604).</t>
+    <t xml:space="preserve">ТО: среднее по Picanto и Jetta. ГРМ: Coolray — Gates K0120529 6 066 + ремень помпы 990,23.</t>
   </si>
   <si>
     <t xml:space="preserve">Доля оплат через Авито Доставку</t>
   </si>
   <si>
-    <t xml:space="preserve">Остальные — прямым переводом. Ваша оценка; уточните по факту.</t>
+    <t xml:space="preserve">Общая для ТО и ГРМ. Остальные — прямым переводом. Ваша оценка; уточните по факту.</t>
   </si>
   <si>
     <t xml:space="preserve">Справка: средний чек по листу «Киты»</t>
@@ -590,7 +599,7 @@
     <t xml:space="preserve">Постоянные расходы в месяц, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Сумма постоянных расходов с листа «Параметры».</t>
+    <t xml:space="preserve">Сумма постоянных расходов с листа «Параметры». Платятся один раз в месяц на весь магазин.</t>
   </si>
   <si>
     <t xml:space="preserve">Прибыль с 1 заказа до постоянных расходов, ₽</t>
@@ -599,7 +608,16 @@
     <t xml:space="preserve">Точка безубыточности, заказов в месяц</t>
   </si>
   <si>
-    <t xml:space="preserve">Заказов в месяц</t>
+    <t xml:space="preserve">Сколько китов одного вида нужно продать, чтобы покрыть постоянные расходы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сценарий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТО-китов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГРМ-китов в месяц</t>
   </si>
   <si>
     <t xml:space="preserve">Выручка, ₽</t>
@@ -620,7 +638,16 @@
     <t xml:space="preserve">Прибыль на 1 заказ, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Налог не учтён. Число заказов в колонке A можно менять. При росте продаж впишите в «Параметры» подписку Авито Pro, если подключите.</t>
+    <t xml:space="preserve">Только ГРМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Только ТО — для сравнения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТО + ГРМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог не учтён. Число китов в колонках B и C можно менять. При росте продаж впишите в «Параметры» подписку Авито Pro, если подключите.</t>
   </si>
   <si>
     <t xml:space="preserve">Параметр</t>
@@ -4061,16 +4088,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4078,388 +4105,738 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="C3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="12" t="n">
         <v>4490</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="12" t="n">
-        <v>3365</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" s="8"/>
+      <c r="C4" s="12" t="n">
+        <v>9990</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="B5" s="12" t="n">
+        <v>3365</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>7056.23</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="9" t="str">
-        <f aca="false">IFERROR(AVERAGEIF(Киты!$M:$M,"&gt;0"),"")</f>
-        <v/>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B7" s="9" t="str">
-        <f aca="false">IFERROR(AVERAGEIF(Киты!$I:$I,"&gt;0"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"ТО",Киты!$M:$M,"&gt;0"),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"ГРМ",Киты!$M:$M,"&gt;0"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="9" t="n">
+        <v>161</v>
+      </c>
+      <c r="B8" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"ТО",Киты!$I:$I,"&gt;0"),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"ГРМ",Киты!$I:$I,"&gt;0"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="9" t="n">
         <f aca="false">(Параметры!$B$12+Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16)</f>
         <v>6783</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <f aca="false">B3-(B4+Параметры!$B$3)-B5*B3*Параметры!$B$6-(1-B5)*(B3*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-B4*Параметры!$B$8</f>
+      <c r="D9" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <f aca="false">B4-(B5+Параметры!$B$3)-$B$6*B4*Параметры!$B$6-(1-$B$6)*(B4*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-B5*Параметры!$B$8</f>
         <v>565.11</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <f aca="false">IF(B9&lt;=0,"не окупается",ROUNDUP(B8/B9,0))</f>
+      <c r="C10" s="11" t="n">
+        <f aca="false">C4-(C5+Параметры!$B$3)-$B$6*C4*Параметры!$B$6-(1-$B$6)*(C4*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-C5*Параметры!$B$8</f>
+        <v>1991.3185</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <f aca="false">IF(B10&lt;=0,"не окупается",ROUNDUP($B$9/B10,0))</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C11" s="6" t="n">
+        <f aca="false">IF(C10&lt;=0,"не окупается",ROUNDUP($B$9/C10,0))</f>
+        <v>4</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="n">
+      <c r="J13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <f aca="false">B14*$B$4+C14*$C$4</f>
+        <v>49950</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <f aca="false">B14*($B$5+Параметры!$B$3)+C14*($C$5+Параметры!$B$3)</f>
+        <v>35531.15</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <f aca="false">$B$6*D14*Параметры!$B$6</f>
+        <v>1623.375</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <f aca="false">(1-$B$6)*D14*Параметры!$B$10</f>
+        <v>174.825</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <f aca="false">(B14+C14)*Параметры!$B$7</f>
+        <v>900</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <f aca="false">(B14*$B$5+C14*$C$5)*Параметры!$B$8</f>
+        <v>1764.0575</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <f aca="false">(B14+C14)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <f aca="false">$B$9</f>
+        <v>6783</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <f aca="false">D14-SUM(E14:K14)</f>
+        <v>3173.59250000001</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <f aca="false">IF(B14+C14=0,"",L14/(B14+C14))</f>
+        <v>634.718500000001</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">A13*$B$3</f>
-        <v>44900</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <f aca="false">A13*($B$4+Параметры!$B$3)</f>
-        <v>34150</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">A13*$B$5*$B$3*Параметры!$B$6</f>
-        <v>1459.25</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">A13*(1-$B$5)*$B$3*Параметры!$B$10</f>
-        <v>157.15</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <f aca="false">A13*Параметры!$B$7</f>
+      <c r="D15" s="9" t="n">
+        <f aca="false">B15*$B$4+C15*$C$4</f>
+        <v>99900</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <f aca="false">B15*($B$5+Параметры!$B$3)+C15*($C$5+Параметры!$B$3)</f>
+        <v>71062.3</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <f aca="false">$B$6*D15*Параметры!$B$6</f>
+        <v>3246.75</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <f aca="false">(1-$B$6)*D15*Параметры!$B$10</f>
+        <v>349.65</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <f aca="false">(B15+C15)*Параметры!$B$7</f>
         <v>1800</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <f aca="false">A13*$B$4*Параметры!$B$8</f>
-        <v>1682.5</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <f aca="false">A13*(1-$B$5)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <f aca="false">$B$8</f>
+      <c r="I15" s="9" t="n">
+        <f aca="false">(B15*$B$5+C15*$C$5)*Параметры!$B$8</f>
+        <v>3528.115</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <f aca="false">(B15+C15)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="J13" s="11" t="n">
-        <f aca="false">B13-SUM(C13:I13)</f>
-        <v>-1131.9</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <f aca="false">IF(A13=0,"",J13/A13)</f>
-        <v>-113.19</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="n">
+      <c r="L15" s="11" t="n">
+        <f aca="false">D15-SUM(E15:K15)</f>
+        <v>13130.185</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <f aca="false">IF(B15+C15=0,"",L15/(B15+C15))</f>
+        <v>1313.0185</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">B16*$B$4+C16*$C$4</f>
+        <v>149850</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <f aca="false">B16*($B$5+Параметры!$B$3)+C16*($C$5+Параметры!$B$3)</f>
+        <v>106593.45</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <f aca="false">$B$6*D16*Параметры!$B$6</f>
+        <v>4870.125</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <f aca="false">(1-$B$6)*D16*Параметры!$B$10</f>
+        <v>524.475</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <f aca="false">(B16+C16)*Параметры!$B$7</f>
+        <v>2700</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <f aca="false">(B16*$B$5+C16*$C$5)*Параметры!$B$8</f>
+        <v>5292.1725</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <f aca="false">(B16+C16)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <f aca="false">$B$9</f>
+        <v>6783</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <f aca="false">D16-SUM(E16:K16)</f>
+        <v>23086.7775</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <f aca="false">IF(B16+C16=0,"",L16/(B16+C16))</f>
+        <v>1539.1185</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">A14*$B$3</f>
+      <c r="D17" s="9" t="n">
+        <f aca="false">B17*$B$4+C17*$C$4</f>
+        <v>199800</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">B17*($B$5+Параметры!$B$3)+C17*($C$5+Параметры!$B$3)</f>
+        <v>142124.6</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <f aca="false">$B$6*D17*Параметры!$B$6</f>
+        <v>6493.5</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <f aca="false">(1-$B$6)*D17*Параметры!$B$10</f>
+        <v>699.3</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <f aca="false">(B17+C17)*Параметры!$B$7</f>
+        <v>3600</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <f aca="false">(B17*$B$5+C17*$C$5)*Параметры!$B$8</f>
+        <v>7056.23</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <f aca="false">(B17+C17)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <f aca="false">$B$9</f>
+        <v>6783</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <f aca="false">D17-SUM(E17:K17)</f>
+        <v>33043.37</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <f aca="false">IF(B17+C17=0,"",L17/(B17+C17))</f>
+        <v>1652.1685</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <f aca="false">B18*$B$4+C18*$C$4</f>
+        <v>299700</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <f aca="false">B18*($B$5+Параметры!$B$3)+C18*($C$5+Параметры!$B$3)</f>
+        <v>213186.9</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <f aca="false">$B$6*D18*Параметры!$B$6</f>
+        <v>9740.25</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <f aca="false">(1-$B$6)*D18*Параметры!$B$10</f>
+        <v>1048.95</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <f aca="false">(B18+C18)*Параметры!$B$7</f>
+        <v>5400</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <f aca="false">(B18*$B$5+C18*$C$5)*Параметры!$B$8</f>
+        <v>10584.345</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <f aca="false">(B18+C18)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <f aca="false">$B$9</f>
+        <v>6783</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <f aca="false">D18-SUM(E18:K18)</f>
+        <v>52956.555</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <f aca="false">IF(B18+C18=0,"",L18/(B18+C18))</f>
+        <v>1765.2185</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <f aca="false">B19*$B$4+C19*$C$4</f>
         <v>89800</v>
       </c>
-      <c r="C14" s="9" t="n">
-        <f aca="false">A14*($B$4+Параметры!$B$3)</f>
+      <c r="E19" s="9" t="n">
+        <f aca="false">B19*($B$5+Параметры!$B$3)+C19*($C$5+Параметры!$B$3)</f>
         <v>68300</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">A14*$B$5*$B$3*Параметры!$B$6</f>
+      <c r="F19" s="9" t="n">
+        <f aca="false">$B$6*D19*Параметры!$B$6</f>
         <v>2918.5</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <f aca="false">A14*(1-$B$5)*$B$3*Параметры!$B$10</f>
+      <c r="G19" s="9" t="n">
+        <f aca="false">(1-$B$6)*D19*Параметры!$B$10</f>
         <v>314.3</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <f aca="false">A14*Параметры!$B$7</f>
+      <c r="H19" s="9" t="n">
+        <f aca="false">(B19+C19)*Параметры!$B$7</f>
         <v>3600</v>
       </c>
-      <c r="G14" s="9" t="n">
-        <f aca="false">A14*$B$4*Параметры!$B$8</f>
+      <c r="I19" s="9" t="n">
+        <f aca="false">(B19*$B$5+C19*$C$5)*Параметры!$B$8</f>
         <v>3365</v>
       </c>
-      <c r="H14" s="9" t="n">
-        <f aca="false">A14*(1-$B$5)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <f aca="false">$B$8</f>
+      <c r="J19" s="9" t="n">
+        <f aca="false">(B19+C19)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="J14" s="11" t="n">
-        <f aca="false">B14-SUM(C14:I14)</f>
+      <c r="L19" s="11" t="n">
+        <f aca="false">D19-SUM(E19:K19)</f>
         <v>4519.2</v>
       </c>
-      <c r="K14" s="9" t="n">
-        <f aca="false">IF(A14=0,"",J14/A14)</f>
+      <c r="M19" s="9" t="n">
+        <f aca="false">IF(B19+C19=0,"",L19/(B19+C19))</f>
         <v>225.96</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <f aca="false">B20*$B$4+C20*$C$4</f>
+        <v>139750</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <f aca="false">B20*($B$5+Параметры!$B$3)+C20*($C$5+Параметры!$B$3)</f>
+        <v>103831.15</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <f aca="false">$B$6*D20*Параметры!$B$6</f>
+        <v>4541.875</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <f aca="false">(1-$B$6)*D20*Параметры!$B$10</f>
+        <v>489.125</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <f aca="false">(B20+C20)*Параметры!$B$7</f>
+        <v>4500</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <f aca="false">(B20*$B$5+C20*$C$5)*Параметры!$B$8</f>
+        <v>5129.0575</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <f aca="false">(B20+C20)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <f aca="false">$B$9</f>
+        <v>6783</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <f aca="false">D20-SUM(E20:K20)</f>
+        <v>14475.7925</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <f aca="false">IF(B20+C20=0,"",L20/(B20+C20))</f>
+        <v>579.031700000001</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <f aca="false">B21*$B$4+C21*$C$4</f>
+        <v>189700</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <f aca="false">B21*($B$5+Параметры!$B$3)+C21*($C$5+Параметры!$B$3)</f>
+        <v>139362.3</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <f aca="false">$B$6*D21*Параметры!$B$6</f>
+        <v>6165.25</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <f aca="false">(1-$B$6)*D21*Параметры!$B$10</f>
+        <v>663.95</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <f aca="false">(B21+C21)*Параметры!$B$7</f>
+        <v>5400</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <f aca="false">(B21*$B$5+C21*$C$5)*Параметры!$B$8</f>
+        <v>6893.115</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <f aca="false">(B21+C21)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <f aca="false">$B$9</f>
+        <v>6783</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <f aca="false">D21-SUM(E21:K21)</f>
+        <v>24432.385</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <f aca="false">IF(B21+C21=0,"",L21/(B21+C21))</f>
+        <v>814.412833333334</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B22" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <f aca="false">A15*$B$3</f>
-        <v>134700</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <f aca="false">A15*($B$4+Параметры!$B$3)</f>
-        <v>102450</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">A15*$B$5*$B$3*Параметры!$B$6</f>
-        <v>4377.75</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <f aca="false">A15*(1-$B$5)*$B$3*Параметры!$B$10</f>
-        <v>471.45</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <f aca="false">A15*Параметры!$B$7</f>
-        <v>5400</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <f aca="false">A15*$B$4*Параметры!$B$8</f>
-        <v>5047.5</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <f aca="false">A15*(1-$B$5)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <f aca="false">$B$8</f>
+      <c r="C22" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <f aca="false">B22*$B$4+C22*$C$4</f>
+        <v>284550</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <f aca="false">B22*($B$5+Параметры!$B$3)+C22*($C$5+Параметры!$B$3)</f>
+        <v>209043.45</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <f aca="false">$B$6*D22*Параметры!$B$6</f>
+        <v>9247.875</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <f aca="false">(1-$B$6)*D22*Параметры!$B$10</f>
+        <v>995.925</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <f aca="false">(B22+C22)*Параметры!$B$7</f>
+        <v>8100</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <f aca="false">(B22*$B$5+C22*$C$5)*Параметры!$B$8</f>
+        <v>10339.6725</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <f aca="false">(B22+C22)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="J15" s="11" t="n">
-        <f aca="false">B15-SUM(C15:I15)</f>
-        <v>10170.3</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <f aca="false">IF(A15=0,"",J15/A15)</f>
-        <v>339.01</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="n">
+      <c r="L22" s="11" t="n">
+        <f aca="false">D22-SUM(E22:K22)</f>
+        <v>40040.0775</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <f aca="false">IF(B22+C22=0,"",L22/(B22+C22))</f>
+        <v>889.7795</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="B16" s="9" t="n">
-        <f aca="false">A16*$B$3</f>
-        <v>224500</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <f aca="false">A16*($B$4+Параметры!$B$3)</f>
-        <v>170750</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">A16*$B$5*$B$3*Параметры!$B$6</f>
-        <v>7296.25</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <f aca="false">A16*(1-$B$5)*$B$3*Параметры!$B$10</f>
-        <v>785.75</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <f aca="false">A16*Параметры!$B$7</f>
-        <v>9000</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <f aca="false">A16*$B$4*Параметры!$B$8</f>
-        <v>8412.5</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <f aca="false">A16*(1-$B$5)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <f aca="false">$B$8</f>
+      <c r="C23" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <f aca="false">B23*$B$4+C23*$C$4</f>
+        <v>424300</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <f aca="false">B23*($B$5+Параметры!$B$3)+C23*($C$5+Параметры!$B$3)</f>
+        <v>312874.6</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <f aca="false">$B$6*D23*Параметры!$B$6</f>
+        <v>13789.75</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <f aca="false">(1-$B$6)*D23*Параметры!$B$10</f>
+        <v>1485.05</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <f aca="false">(B23+C23)*Параметры!$B$7</f>
+        <v>12600</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <f aca="false">(B23*$B$5+C23*$C$5)*Параметры!$B$8</f>
+        <v>15468.73</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <f aca="false">(B23+C23)*(1-$B$6)*Параметры!$B$11</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="J16" s="11" t="n">
-        <f aca="false">B16-SUM(C16:I16)</f>
-        <v>21472.5</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <f aca="false">IF(A16=0,"",J16/A16)</f>
-        <v>429.45</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <f aca="false">A17*$B$3</f>
-        <v>449000</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <f aca="false">A17*($B$4+Параметры!$B$3)</f>
-        <v>341500</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">A17*$B$5*$B$3*Параметры!$B$6</f>
-        <v>14592.5</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <f aca="false">A17*(1-$B$5)*$B$3*Параметры!$B$10</f>
-        <v>1571.5</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <f aca="false">A17*Параметры!$B$7</f>
-        <v>18000</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <f aca="false">A17*$B$4*Параметры!$B$8</f>
-        <v>16825</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <f aca="false">A17*(1-$B$5)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <f aca="false">$B$8</f>
-        <v>6783</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <f aca="false">B17-SUM(C17:I17)</f>
-        <v>49728</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <f aca="false">IF(A17=0,"",J17/A17)</f>
-        <v>497.28</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>170</v>
+      <c r="L23" s="11" t="n">
+        <f aca="false">D23-SUM(E23:K23)</f>
+        <v>61298.87</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <f aca="false">IF(B23+C23=0,"",L23/(B23+C23))</f>
+        <v>875.698142857143</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C8:J8"/>
+  <mergeCells count="6">
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="D5:L5"/>
+    <mergeCell ref="D6:L6"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="D11:L11"/>
   </mergeCells>
-  <conditionalFormatting sqref="J13:J17">
+  <conditionalFormatting sqref="L14:L23">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -4489,206 +4866,206 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0.007</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>4783</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>1500</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>500</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">($B$12+$B$13+$B$14+$B$15+$B$16)/MAX(1,$B$17)</f>
         <v>339.15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -4731,75 +5108,75 @@
         <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="G2" s="23" t="n">
         <v>460</v>
@@ -4831,7 +5208,7 @@
         <v>430</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4843,7 +5220,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -4872,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4884,7 +5261,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -4923,7 +5300,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -4962,7 +5339,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -5001,7 +5378,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -5040,7 +5417,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -5069,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,7 +5458,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -5120,7 +5497,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -5159,7 +5536,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -5198,7 +5575,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -5237,7 +5614,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -5266,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5278,7 +5655,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -5317,7 +5694,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -5356,7 +5733,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -5395,7 +5772,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -5434,7 +5811,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -5463,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5475,7 +5852,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -5514,7 +5891,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -5553,7 +5930,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -5592,7 +5969,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -5631,7 +6008,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -5660,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5672,7 +6049,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -5711,7 +6088,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -5750,7 +6127,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -5789,7 +6166,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -5828,7 +6205,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -5857,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,7 +6246,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -5908,7 +6285,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -5947,7 +6324,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -5986,7 +6363,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -6025,7 +6402,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -6054,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6066,7 +6443,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -6095,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6107,7 +6484,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -6146,7 +6523,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -6185,7 +6562,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -6224,7 +6601,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -6263,7 +6640,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -6292,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6304,7 +6681,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -6333,7 +6710,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6345,7 +6722,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -6384,7 +6761,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -6423,7 +6800,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -6462,7 +6839,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -6501,7 +6878,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -6530,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6542,7 +6919,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -6571,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6583,7 +6960,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -6622,7 +6999,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -6661,7 +7038,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -6700,7 +7077,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -6739,7 +7116,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -6768,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6780,7 +7157,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -6809,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6821,7 +7198,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -6860,7 +7237,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -6899,7 +7276,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -6938,7 +7315,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -6977,7 +7354,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -7006,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7018,7 +7395,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -7047,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7059,7 +7436,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -7098,7 +7475,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -7137,7 +7514,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -7176,7 +7553,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -7215,7 +7592,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -7244,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7256,7 +7633,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -7285,7 +7662,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7297,7 +7674,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -7336,7 +7713,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -7375,7 +7752,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -7414,7 +7791,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -7453,13 +7830,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -7484,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7496,13 +7873,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -7527,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7539,13 +7916,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -7570,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7582,13 +7959,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -7613,7 +7990,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7625,13 +8002,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -7656,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7668,13 +8045,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -7699,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7711,13 +8088,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -7742,7 +8119,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7754,13 +8131,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -7785,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7797,7 +8174,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -7826,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7838,7 +8215,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -7877,7 +8254,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -7916,7 +8293,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -7945,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7957,7 +8334,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -7986,7 +8363,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7998,7 +8375,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -8027,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8039,7 +8416,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -8078,7 +8455,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -8117,7 +8494,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -8146,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8158,7 +8535,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -8187,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8199,7 +8576,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -8228,7 +8605,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8240,7 +8617,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -8279,7 +8656,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -8318,7 +8695,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -8347,7 +8724,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8359,7 +8736,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -8388,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8400,7 +8777,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -8429,7 +8806,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8441,7 +8818,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -8480,7 +8857,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -8519,7 +8896,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -8548,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8560,7 +8937,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -8589,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8601,7 +8978,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -8630,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8642,7 +9019,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -8681,7 +9058,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -8720,7 +9097,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -8749,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8761,7 +9138,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -8790,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8802,7 +9179,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -8841,7 +9218,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -8870,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8882,7 +9259,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -8911,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8923,7 +9300,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -8952,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8964,7 +9341,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -9003,7 +9380,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -9042,7 +9419,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -9071,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9083,7 +9460,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -9112,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9124,7 +9501,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -9153,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9165,7 +9542,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -9204,7 +9581,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -9243,7 +9620,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -9272,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9284,7 +9661,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -9313,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9325,7 +9702,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -9354,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9366,7 +9743,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -9405,7 +9782,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -9444,7 +9821,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -9473,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9485,7 +9862,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -9514,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9526,7 +9903,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -9555,7 +9932,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9567,7 +9944,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -9606,7 +9983,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -9645,7 +10022,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -9674,7 +10051,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9686,7 +10063,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -9715,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9727,16 +10104,16 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
@@ -9760,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9772,7 +10149,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -9801,7 +10178,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9813,7 +10190,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -9842,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9854,7 +10231,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -9883,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -9920,80 +10297,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -10007,10 +10384,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -10024,10 +10401,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -10041,10 +10418,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -10058,10 +10435,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
@@ -10075,10 +10452,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -10092,10 +10469,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
@@ -10109,10 +10486,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -10126,10 +10503,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -10180,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>17</v>
@@ -10189,197 +10566,197 @@
         <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -103,12 +103,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="Y27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMDBD262 в рознице 1 435–2 078 ₽ за штуку (обычно ≈1 770), колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020). Пара дисков + колодки + смазка по отдельности ≈ 4 700 ₽.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMDBD262 в рознице 1 435–2 078 ₽ за штуку (обычно ≈1 770), колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020). Пара дисков + колодки + смазка по отдельности ≈ 4 700 ₽.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="349">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -560,6 +584,30 @@
     <t xml:space="preserve">grm-12-coolray-1-main.png</t>
   </si>
   <si>
+    <t xml:space="preserve">TRM-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тормоза</t>
+  </si>
+  <si>
+    <t xml:space="preserve">все моторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тормоз-кит Kia Rio 4 2017–2021: диски и колодки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trm-01-rio-4-1-main.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRM-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тормоз-кит Hyundai Solaris 2017+: диски, колодки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trm-02-solaris-2017-1-main.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Прогноз на месяц (до налога): ТО-киты и ГРМ-киты</t>
   </si>
   <si>
@@ -936,6 +984,30 @@
   </si>
   <si>
     <t xml:space="preserve">Ваша закупка: 990,23 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диски тормозные передние AMD (AMDBD262) — 2 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMDBD262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 2 711,80 ₽ — впишите в колонку поставщика, у которого брали. Цена за пару: кол-во 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Колодки тормозные передние AMD (AMDBF453)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMDBF453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваша закупка: 815,10 ₽ — впишите в колонку поставщика, у которого брали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Смазка для направляющих суппорта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цены пока нет — впишите в колонку поставщика, у которого берёте</t>
   </si>
   <si>
     <t xml:space="preserve">Поставщик</t>
@@ -1764,7 +1836,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4045,29 +4117,207 @@
         <v>9990</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" s="9" t="str">
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A27)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="10" t="n">
+        <f aca="false">COUNTIFS(Состав!$A:$A,A27,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="K27" s="9" t="str">
+        <f aca="false">IF(I27="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="9" t="str">
+        <f aca="false">IF(I27="","",I27+K27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="11" t="str">
+        <f aca="false">IF(I27="","",IF(Y27&lt;&gt;"",Y27,CEILING((I27*(1+Параметры!$B$8*Параметры!$B$9)+K27)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <v/>
+      </c>
+      <c r="N27" s="12"/>
+      <c r="O27" s="7" t="str">
+        <f aca="false">IF(OR(M27="",N27=""),"",IF(M27&lt;=N27,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P27" s="9" t="str">
+        <f aca="false">IF(M27="","",M27*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="9" t="str">
+        <f aca="false">IF(M27="","",M27*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R27" s="9" t="str">
+        <f aca="false">IF(M27="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S27" s="9" t="str">
+        <f aca="false">IF(I27="","",I27*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T27" s="9" t="str">
+        <f aca="false">IF(M27="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U27" s="11" t="str">
+        <f aca="false">IF(M27="","",M27-L27-P27-R27-S27-T27)</f>
+        <v/>
+      </c>
+      <c r="V27" s="11" t="str">
+        <f aca="false">IF(M27="","",M27-L27-Q27-R27-S27-T27-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W27" s="13" t="str">
+        <f aca="false">IF(U27="","",U27/M27)</f>
+        <v/>
+      </c>
+      <c r="X27" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y27" s="12" t="n">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="9" t="str">
+        <f aca="false">IF(SUMIFS(Состав!$R:$R,Состав!$A:$A,A28)=0,"",SUMIFS(Состав!$R:$R,Состав!$A:$A,A28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="10" t="n">
+        <f aca="false">COUNTIFS(Состав!$A:$A,A28,Состав!$P:$P,"",Состав!$D:$D,"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="K28" s="9" t="str">
+        <f aca="false">IF(I28="","",Параметры!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="9" t="str">
+        <f aca="false">IF(I28="","",I28+K28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="11" t="str">
+        <f aca="false">IF(I28="","",IF(Y28&lt;&gt;"",Y28,CEILING((I28*(1+Параметры!$B$8*Параметры!$B$9)+K28)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <v/>
+      </c>
+      <c r="N28" s="12"/>
+      <c r="O28" s="7" t="str">
+        <f aca="false">IF(OR(M28="",N28=""),"",IF(M28&lt;=N28,"не дороже рынка","дороже рынка"))</f>
+        <v/>
+      </c>
+      <c r="P28" s="9" t="str">
+        <f aca="false">IF(M28="","",M28*Параметры!$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="9" t="str">
+        <f aca="false">IF(M28="","",M28*Параметры!$B$10)</f>
+        <v/>
+      </c>
+      <c r="R28" s="9" t="str">
+        <f aca="false">IF(M28="","",Параметры!$B$7)</f>
+        <v/>
+      </c>
+      <c r="S28" s="9" t="str">
+        <f aca="false">IF(I28="","",I28*Параметры!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T28" s="9" t="str">
+        <f aca="false">IF(M28="","",Параметры!$B$18)</f>
+        <v/>
+      </c>
+      <c r="U28" s="11" t="str">
+        <f aca="false">IF(M28="","",M28-L28-P28-R28-S28-T28)</f>
+        <v/>
+      </c>
+      <c r="V28" s="11" t="str">
+        <f aca="false">IF(M28="","",M28-L28-Q28-R28-S28-T28-Параметры!$B$11)</f>
+        <v/>
+      </c>
+      <c r="W28" s="13" t="str">
+        <f aca="false">IF(U28="","",U28/M28)</f>
+        <v/>
+      </c>
+      <c r="X28" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y28" s="12" t="n">
+        <v>4790</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J28">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O28">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"дороже рынка"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U26">
+  <conditionalFormatting sqref="U2:U28">
     <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V26">
+  <conditionalFormatting sqref="V2:V28">
     <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="X2:X26" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="X2:X28" type="list">
       <formula1>"не выложен,выложен,есть продажи,снят"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4102,19 +4352,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -4127,7 +4377,7 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>4490</v>
@@ -4136,7 +4386,7 @@
         <v>9990</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4149,7 +4399,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>3365</v>
@@ -4158,7 +4408,7 @@
         <v>7056.23</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -4171,13 +4421,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -4190,7 +4440,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B7" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"ТО",Киты!$M:$M,"&gt;0"),"")</f>
@@ -4203,7 +4453,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B8" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"ТО",Киты!$I:$I,"&gt;0"),"")</f>
@@ -4216,14 +4466,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">(Параметры!$B$12+Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16)</f>
         <v>6783</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -4236,7 +4486,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">B4-(B5+Параметры!$B$3)-$B$6*B4*Параметры!$B$6-(1-$B$6)*(B4*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-B5*Параметры!$B$8</f>
@@ -4249,7 +4499,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">IF(B10&lt;=0,"не окупается",ROUNDUP($B$9/B10,0))</f>
@@ -4260,7 +4510,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -4273,19 +4523,19 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>29</v>
@@ -4300,21 +4550,21 @@
         <v>32</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>0</v>
@@ -4365,7 +4615,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>0</v>
@@ -4416,7 +4666,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>0</v>
@@ -4467,7 +4717,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>0</v>
@@ -4518,7 +4768,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>0</v>
@@ -4569,7 +4819,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>20</v>
@@ -4620,7 +4870,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>20</v>
@@ -4671,7 +4921,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>20</v>
@@ -4722,7 +4972,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B22" s="16" t="n">
         <v>30</v>
@@ -4773,7 +5023,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>50</v>
@@ -4824,7 +5074,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4866,206 +5116,206 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0.065</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0.007</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>4783</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>1500</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>500</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">($B$12+$B$13+$B$14+$B$15+$B$16)/MAX(1,$B$17)</f>
         <v>339.15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -5084,7 +5334,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S134"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5108,75 +5358,75 @@
         <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G2" s="23" t="n">
         <v>460</v>
@@ -5208,7 +5458,7 @@
         <v>430</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5220,7 +5470,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -5249,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5261,7 +5511,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -5300,7 +5550,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -5339,7 +5589,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -5378,7 +5628,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -5417,7 +5667,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -5446,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5458,7 +5708,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -5497,7 +5747,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -5536,7 +5786,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -5575,7 +5825,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -5614,7 +5864,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -5643,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5655,7 +5905,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -5694,7 +5944,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -5733,7 +5983,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -5772,7 +6022,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -5811,7 +6061,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -5840,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5852,7 +6102,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -5891,7 +6141,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -5930,7 +6180,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -5969,7 +6219,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -6008,7 +6258,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -6037,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6049,7 +6299,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -6088,7 +6338,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -6127,7 +6377,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -6166,7 +6416,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -6205,7 +6455,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -6234,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6246,7 +6496,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -6285,7 +6535,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -6324,7 +6574,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -6363,7 +6613,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -6402,7 +6652,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -6431,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6443,7 +6693,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -6472,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6484,7 +6734,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -6523,7 +6773,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -6562,7 +6812,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -6601,7 +6851,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -6640,7 +6890,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -6669,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6681,7 +6931,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -6710,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6722,7 +6972,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -6761,7 +7011,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -6800,7 +7050,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -6839,7 +7089,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -6878,7 +7128,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -6907,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6919,7 +7169,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -6948,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6960,7 +7210,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -6999,7 +7249,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -7038,7 +7288,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -7077,7 +7327,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -7116,7 +7366,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -7145,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7157,7 +7407,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -7186,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7198,7 +7448,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -7237,7 +7487,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -7276,7 +7526,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -7315,7 +7565,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -7354,7 +7604,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -7383,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7395,7 +7645,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -7424,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7436,7 +7686,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -7475,7 +7725,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -7514,7 +7764,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -7553,7 +7803,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -7592,7 +7842,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -7621,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7633,7 +7883,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -7662,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7674,7 +7924,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -7713,7 +7963,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -7752,7 +8002,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -7791,7 +8041,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -7830,13 +8080,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -7861,7 +8111,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7873,13 +8123,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -7904,7 +8154,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7916,13 +8166,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -7947,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7959,13 +8209,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -7990,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8002,13 +8252,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -8033,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8045,13 +8295,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -8076,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8088,13 +8338,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -8119,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8131,13 +8381,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -8162,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8174,7 +8424,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -8203,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8215,7 +8465,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -8254,7 +8504,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -8293,7 +8543,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -8322,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8334,7 +8584,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -8363,7 +8613,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8375,7 +8625,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -8404,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8416,7 +8666,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -8455,7 +8705,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -8494,7 +8744,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -8523,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8535,7 +8785,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -8564,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8576,7 +8826,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -8605,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8617,7 +8867,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -8656,7 +8906,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -8695,7 +8945,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -8724,7 +8974,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8736,7 +8986,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -8765,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8777,7 +9027,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -8806,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8818,7 +9068,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -8857,7 +9107,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -8896,7 +9146,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -8925,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8937,7 +9187,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -8966,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8978,7 +9228,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -9007,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9019,7 +9269,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -9058,7 +9308,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -9097,7 +9347,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -9126,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9138,7 +9388,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -9167,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9179,7 +9429,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -9218,7 +9468,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -9247,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9259,7 +9509,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -9288,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9300,7 +9550,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -9329,7 +9579,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9341,7 +9591,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -9380,7 +9630,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -9419,7 +9669,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -9448,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9460,7 +9710,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -9489,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9501,7 +9751,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -9530,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9542,7 +9792,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -9581,7 +9831,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -9620,7 +9870,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -9649,7 +9899,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9661,7 +9911,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -9690,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9702,7 +9952,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -9731,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9743,7 +9993,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -9782,7 +10032,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -9821,7 +10071,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -9850,7 +10100,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9862,7 +10112,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -9891,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9903,7 +10153,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -9932,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9944,7 +10194,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -9983,7 +10233,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -10022,7 +10272,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -10051,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10063,7 +10313,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -10092,7 +10342,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10104,16 +10354,16 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
@@ -10137,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10149,7 +10399,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -10178,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10190,7 +10440,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -10219,7 +10469,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10231,7 +10481,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -10260,7 +10510,269 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B129" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A129,Киты!$A:$A,0)),"")</f>
+        <v>Kia Rio 2017–2021</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="G129" s="12"/>
+      <c r="H129" s="12"/>
+      <c r="I129" s="12"/>
+      <c r="J129" s="12"/>
+      <c r="K129" s="12"/>
+      <c r="L129" s="12"/>
+      <c r="M129" s="12"/>
+      <c r="N129" s="12"/>
+      <c r="O129" s="12"/>
+      <c r="P129" s="9" t="str">
+        <f aca="false">IF(COUNT(G129:O129)=0,"",MIN(G129:O129))</f>
+        <v/>
+      </c>
+      <c r="Q129" s="7" t="str">
+        <f aca="false">IF(P129="","",INDEX($G$1:$O$1,MATCH(P129,G129:O129,0)))</f>
+        <v/>
+      </c>
+      <c r="R129" s="9" t="n">
+        <f aca="false">IF(P129="",0,P129*D129)</f>
+        <v>0</v>
+      </c>
+      <c r="S129" s="8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B130" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A130,Киты!$A:$A,0)),"")</f>
+        <v>Kia Rio 2017–2021</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
+      <c r="K130" s="12"/>
+      <c r="L130" s="12"/>
+      <c r="M130" s="12"/>
+      <c r="N130" s="12"/>
+      <c r="O130" s="12"/>
+      <c r="P130" s="9" t="str">
+        <f aca="false">IF(COUNT(G130:O130)=0,"",MIN(G130:O130))</f>
+        <v/>
+      </c>
+      <c r="Q130" s="7" t="str">
+        <f aca="false">IF(P130="","",INDEX($G$1:$O$1,MATCH(P130,G130:O130,0)))</f>
+        <v/>
+      </c>
+      <c r="R130" s="9" t="n">
+        <f aca="false">IF(P130="",0,P130*D130)</f>
+        <v>0</v>
+      </c>
+      <c r="S130" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A131,Киты!$A:$A,0)),"")</f>
+        <v>Kia Rio 2017–2021</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D131" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="14"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="12"/>
+      <c r="K131" s="12"/>
+      <c r="L131" s="12"/>
+      <c r="M131" s="12"/>
+      <c r="N131" s="12"/>
+      <c r="O131" s="12"/>
+      <c r="P131" s="9" t="str">
+        <f aca="false">IF(COUNT(G131:O131)=0,"",MIN(G131:O131))</f>
+        <v/>
+      </c>
+      <c r="Q131" s="7" t="str">
+        <f aca="false">IF(P131="","",INDEX($G$1:$O$1,MATCH(P131,G131:O131,0)))</f>
+        <v/>
+      </c>
+      <c r="R131" s="9" t="n">
+        <f aca="false">IF(P131="",0,P131*D131)</f>
+        <v>0</v>
+      </c>
+      <c r="S131" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B132" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A132,Киты!$A:$A,0)),"")</f>
+        <v>Hyundai Solaris 2017–2022</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D132" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="12"/>
+      <c r="K132" s="12"/>
+      <c r="L132" s="12"/>
+      <c r="M132" s="12"/>
+      <c r="N132" s="12"/>
+      <c r="O132" s="12"/>
+      <c r="P132" s="9" t="str">
+        <f aca="false">IF(COUNT(G132:O132)=0,"",MIN(G132:O132))</f>
+        <v/>
+      </c>
+      <c r="Q132" s="7" t="str">
+        <f aca="false">IF(P132="","",INDEX($G$1:$O$1,MATCH(P132,G132:O132,0)))</f>
+        <v/>
+      </c>
+      <c r="R132" s="9" t="n">
+        <f aca="false">IF(P132="",0,P132*D132)</f>
+        <v>0</v>
+      </c>
+      <c r="S132" s="8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B133" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A133,Киты!$A:$A,0)),"")</f>
+        <v>Hyundai Solaris 2017–2022</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="G133" s="12"/>
+      <c r="H133" s="12"/>
+      <c r="I133" s="12"/>
+      <c r="J133" s="12"/>
+      <c r="K133" s="12"/>
+      <c r="L133" s="12"/>
+      <c r="M133" s="12"/>
+      <c r="N133" s="12"/>
+      <c r="O133" s="12"/>
+      <c r="P133" s="9" t="str">
+        <f aca="false">IF(COUNT(G133:O133)=0,"",MIN(G133:O133))</f>
+        <v/>
+      </c>
+      <c r="Q133" s="7" t="str">
+        <f aca="false">IF(P133="","",INDEX($G$1:$O$1,MATCH(P133,G133:O133,0)))</f>
+        <v/>
+      </c>
+      <c r="R133" s="9" t="n">
+        <f aca="false">IF(P133="",0,P133*D133)</f>
+        <v>0</v>
+      </c>
+      <c r="S133" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B134" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Киты!$C:$C,MATCH(A134,Киты!$A:$A,0)),"")</f>
+        <v>Hyundai Solaris 2017–2022</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="12"/>
+      <c r="I134" s="12"/>
+      <c r="J134" s="12"/>
+      <c r="K134" s="12"/>
+      <c r="L134" s="12"/>
+      <c r="M134" s="12"/>
+      <c r="N134" s="12"/>
+      <c r="O134" s="12"/>
+      <c r="P134" s="9" t="str">
+        <f aca="false">IF(COUNT(G134:O134)=0,"",MIN(G134:O134))</f>
+        <v/>
+      </c>
+      <c r="Q134" s="7" t="str">
+        <f aca="false">IF(P134="","",INDEX($G$1:$O$1,MATCH(P134,G134:O134,0)))</f>
+        <v/>
+      </c>
+      <c r="R134" s="9" t="n">
+        <f aca="false">IF(P134="",0,P134*D134)</f>
+        <v>0</v>
+      </c>
+      <c r="S134" s="8" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -10297,80 +10809,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -10384,10 +10896,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -10401,10 +10913,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -10418,10 +10930,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -10435,10 +10947,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
@@ -10452,10 +10964,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -10469,10 +10981,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
@@ -10486,10 +10998,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -10503,10 +11015,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -10557,7 +11069,7 @@
         <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>17</v>
@@ -10566,197 +11078,197 @@
         <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -111,7 +111,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMDBD262 в рознице 1 435–2 078 ₽ за штуку (обычно ≈1 770), колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020). Пара дисков + колодки + смазка по отдельности ≈ 4 700 ₽.</t>
+          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000) — у нас дешевле и одной коробкой.</t>
         </r>
       </text>
     </comment>
@@ -123,7 +123,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMDBD262 в рознице 1 435–2 078 ₽ за штуку (обычно ≈1 770), колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020). Пара дисков + колодки + смазка по отдельности ≈ 4 700 ₽.</t>
+          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000) — у нас дешевле и одной коробкой.</t>
         </r>
       </text>
     </comment>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">Смазка для направляющих суппорта</t>
   </si>
   <si>
-    <t xml:space="preserve">Цены пока нет — впишите в колонку поставщика, у которого берёте</t>
+    <t xml:space="preserve">Ваша закупка: 97,70 ₽ — впишите в колонку поставщика, у которого брали</t>
   </si>
   <si>
     <t xml:space="preserve">Поставщик</t>
@@ -4203,7 +4203,7 @@
         <v>47</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>4790</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4292,7 +4292,7 @@
         <v>47</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>4790</v>
+        <v>4990</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -51,7 +51,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Считается по наценке с листа «Параметры». Если в колонке Y «Своя цена по рынку» есть число — берётся оно.</t>
+          <t xml:space="preserve">База — по наценке с листа «Параметры» или цена по рынку из колонки Y, если она есть. Сверху — «Повышение цен» с листа «Параметры», затем округление до …90.</t>
         </r>
       </text>
     </comment>
@@ -87,7 +87,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Для китов, где цену ставим по рынку, а не по наценке: впишите цену, по которой конечный покупатель берёт то же самое на маркетплейсах. Пусто — цена по наценке.</t>
+          <t xml:space="preserve">Для китов, где цену ставим по рынку, а не по наценке: впишите цену, по которой конечный покупатель берёт то же самое на маркетплейсах. Повышение цен добавится сверху. Пусто — цена по наценке.</t>
         </r>
       </text>
     </comment>
@@ -99,7 +99,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Цена по рынку (сентябрь 2026): Gates K0120529 отдельно — 7 290–10 526 ₽ в рознице, ремень помпы — 740–1 679 ₽. У нас оба ремня и ролики в одной коробке дешевле, чем по отдельности на Яндекс Маркете.</t>
+          <t xml:space="preserve">Рыночная база (сентябрь 2026): Gates K0120529 отдельно — 7 290–10 526 ₽ в рознице, ремень помпы — 740–1 679 ₽. Итоговая цена — база плюс повышение с листа «Параметры»; даже с ним кит дешевле, чем Gates и ремень помпы по отдельности на Яндекс Маркете.</t>
         </r>
       </text>
     </comment>
@@ -111,7 +111,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000) — у нас дешевле и одной коробкой.</t>
+          <t xml:space="preserve">Рыночная база (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000). Итоговая цена — база плюс повышение с листа «Параметры».</t>
         </r>
       </text>
     </comment>
@@ -123,7 +123,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Цена по рынку (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000) — у нас дешевле и одной коробкой.</t>
+          <t xml:space="preserve">Рыночная база (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000). Итоговая цена — база плюс повышение с листа «Параметры».</t>
         </r>
       </text>
     </comment>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="357">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">3. «Киты» — сами посчитаются закупка, цена на Авито и прибыль до налога в двух вариантах: оплата через Авито Доставку и прямым переводом.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком. Колонка Y «Своя цена по рынку» — если цену кита ставим по рынку, а не по наценке.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. «Параметры» — наценка, комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. «Прогноз» — выручка и прибыль за месяц: ТО-киты и ГРМ-киты отдельно и вместе, точка безубыточности.</t>
+    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком. Колонка Y «Цена по рынку (база)» — если цену кита ставим по рынку, а не по наценке.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. «Параметры» — наценка, повышение цен (+5%), комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. «Прогноз» — выручка и прибыль за месяц: ТО, ГРМ и тормоз-киты отдельно и вместе, точка безубыточности.</t>
   </si>
   <si>
     <t xml:space="preserve">6. «Моторы» — справка: где цепь, где ремень, что входит в ГРМ-кит, источники.</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">Статус</t>
   </si>
   <si>
-    <t xml:space="preserve">Своя цена по рынку, ₽</t>
+    <t xml:space="preserve">Цена по рынку (база), ₽</t>
   </si>
   <si>
     <t xml:space="preserve">TO-01</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">trm-02-solaris-2017-1-main.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Прогноз на месяц (до налога): ТО-киты и ГРМ-киты</t>
+    <t xml:space="preserve">Прогноз на месяц (до налога): ТО, ГРМ и тормоз-киты</t>
   </si>
   <si>
     <t xml:space="preserve">ТО-кит</t>
@@ -617,25 +617,28 @@
     <t xml:space="preserve">ГРМ-кит</t>
   </si>
   <si>
+    <t xml:space="preserve">Тормоз-кит</t>
+  </si>
+  <si>
     <t xml:space="preserve">Пояснение</t>
   </si>
   <si>
     <t xml:space="preserve">Средний чек кита, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">ТО: среднее по Picanto (4 190) и Jetta (4 790). ГРМ: пока собран один — Coolray на Gates (9 990). Когда соберёте больше китов, возьмите средние из справки ниже.</t>
+    <t xml:space="preserve">Среднее по собранным китам, уже с повышением цен: ТО-кит: Kia Picanto 1.0 / 1.2 (4 390 ₽), VW Jetta (5 090 ₽); ГРМ-кит: Geely Coolray 1.5T (10 490 ₽); Тормоз-кит: Kia Rio 2017–2021 (5 290 ₽), Hyundai Solaris 2017–2022 (5 290 ₽). Замените, когда соберёте больше китов.</t>
   </si>
   <si>
     <t xml:space="preserve">Средняя стоимость деталей, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">ТО: среднее по Picanto и Jetta. ГРМ: Coolray — Gates K0120529 6 066 + ремень помпы 990,23.</t>
+    <t xml:space="preserve">Среднее по деталям тех же китов (без упаковки).</t>
   </si>
   <si>
     <t xml:space="preserve">Доля оплат через Авито Доставку</t>
   </si>
   <si>
-    <t xml:space="preserve">Общая для ТО и ГРМ. Остальные — прямым переводом. Ваша оценка; уточните по факту.</t>
+    <t xml:space="preserve">Общая для всех китов. Остальные — прямым переводом. Ваша оценка; уточните по факту.</t>
   </si>
   <si>
     <t xml:space="preserve">Справка: средний чек по листу «Киты»</t>
@@ -662,10 +665,13 @@
     <t xml:space="preserve">Сценарий</t>
   </si>
   <si>
-    <t xml:space="preserve">ТО-китов в месяц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГРМ-китов в месяц</t>
+    <t xml:space="preserve">ТО-китов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГРМ-китов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тормоз-китов</t>
   </si>
   <si>
     <t xml:space="preserve">Выручка, ₽</t>
@@ -686,16 +692,28 @@
     <t xml:space="preserve">Прибыль на 1 заказ, ₽</t>
   </si>
   <si>
+    <t xml:space="preserve">Только ТО</t>
+  </si>
+  <si>
     <t xml:space="preserve">Только ГРМ</t>
   </si>
   <si>
-    <t xml:space="preserve">Только ТО — для сравнения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТО + ГРМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Налог не учтён. Число китов в колонках B и C можно менять. При росте продаж впишите в «Параметры» подписку Авито Pro, если подключите.</t>
+    <t xml:space="preserve">Только тормоза</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рабочий месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хороший месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог не учтён. Число китов в колонках B–D можно менять. При росте продаж впишите в «Параметры» подписку Авито Pro, если подключите.</t>
   </si>
   <si>
     <t xml:space="preserve">Параметр</t>
@@ -729,6 +747,12 @@
   </si>
   <si>
     <t xml:space="preserve">Чтобы цена заканчивалась на …90 (4 700 → 4 690).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Повышение цен ко всем китам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваше решение: +5% сверху ко всем китам — и к цене по наценке, и к цене по рынку (колонка Y на листе «Киты»). Затем снова округление до …90. Поставьте 0%, чтобы убрать.</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссия Авито Доставки</t>
@@ -1982,7 +2006,7 @@
         <v/>
       </c>
       <c r="M2" s="11" t="str">
-        <f aca="false">IF(I2="","",IF(Y2&lt;&gt;"",Y2,CEILING((I2*(1+Параметры!$B$8*Параметры!$B$9)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I2="","",CEILING((IF(Y2&lt;&gt;"",Y2,CEILING((I2*(1+Параметры!$B$9*Параметры!$B$10)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N2" s="12"/>
@@ -1991,23 +2015,23 @@
         <v/>
       </c>
       <c r="P2" s="9" t="str">
-        <f aca="false">IF(M2="","",M2*Параметры!$B$6)</f>
+        <f aca="false">IF(M2="","",M2*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q2" s="9" t="str">
-        <f aca="false">IF(M2="","",M2*Параметры!$B$10)</f>
+        <f aca="false">IF(M2="","",M2*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R2" s="9" t="str">
-        <f aca="false">IF(M2="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M2="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S2" s="9" t="str">
-        <f aca="false">IF(I2="","",I2*Параметры!$B$8)</f>
+        <f aca="false">IF(I2="","",I2*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T2" s="9" t="str">
-        <f aca="false">IF(M2="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M2="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U2" s="11" t="str">
@@ -2015,7 +2039,7 @@
         <v/>
       </c>
       <c r="V2" s="11" t="str">
-        <f aca="false">IF(M2="","",M2-L2-Q2-R2-S2-T2-Параметры!$B$11)</f>
+        <f aca="false">IF(M2="","",M2-L2-Q2-R2-S2-T2-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W2" s="13" t="str">
@@ -2069,7 +2093,7 @@
         <v/>
       </c>
       <c r="M3" s="11" t="str">
-        <f aca="false">IF(I3="","",IF(Y3&lt;&gt;"",Y3,CEILING((I3*(1+Параметры!$B$8*Параметры!$B$9)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I3="","",CEILING((IF(Y3&lt;&gt;"",Y3,CEILING((I3*(1+Параметры!$B$9*Параметры!$B$10)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N3" s="12"/>
@@ -2078,23 +2102,23 @@
         <v/>
       </c>
       <c r="P3" s="9" t="str">
-        <f aca="false">IF(M3="","",M3*Параметры!$B$6)</f>
+        <f aca="false">IF(M3="","",M3*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q3" s="9" t="str">
-        <f aca="false">IF(M3="","",M3*Параметры!$B$10)</f>
+        <f aca="false">IF(M3="","",M3*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R3" s="9" t="str">
-        <f aca="false">IF(M3="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M3="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S3" s="9" t="str">
-        <f aca="false">IF(I3="","",I3*Параметры!$B$8)</f>
+        <f aca="false">IF(I3="","",I3*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T3" s="9" t="str">
-        <f aca="false">IF(M3="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M3="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U3" s="11" t="str">
@@ -2102,7 +2126,7 @@
         <v/>
       </c>
       <c r="V3" s="11" t="str">
-        <f aca="false">IF(M3="","",M3-L3-Q3-R3-S3-T3-Параметры!$B$11)</f>
+        <f aca="false">IF(M3="","",M3-L3-Q3-R3-S3-T3-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W3" s="13" t="str">
@@ -2156,7 +2180,7 @@
         <v/>
       </c>
       <c r="M4" s="11" t="str">
-        <f aca="false">IF(I4="","",IF(Y4&lt;&gt;"",Y4,CEILING((I4*(1+Параметры!$B$8*Параметры!$B$9)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I4="","",CEILING((IF(Y4&lt;&gt;"",Y4,CEILING((I4*(1+Параметры!$B$9*Параметры!$B$10)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N4" s="12"/>
@@ -2165,23 +2189,23 @@
         <v/>
       </c>
       <c r="P4" s="9" t="str">
-        <f aca="false">IF(M4="","",M4*Параметры!$B$6)</f>
+        <f aca="false">IF(M4="","",M4*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q4" s="9" t="str">
-        <f aca="false">IF(M4="","",M4*Параметры!$B$10)</f>
+        <f aca="false">IF(M4="","",M4*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R4" s="9" t="str">
-        <f aca="false">IF(M4="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M4="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S4" s="9" t="str">
-        <f aca="false">IF(I4="","",I4*Параметры!$B$8)</f>
+        <f aca="false">IF(I4="","",I4*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T4" s="9" t="str">
-        <f aca="false">IF(M4="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M4="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U4" s="11" t="str">
@@ -2189,7 +2213,7 @@
         <v/>
       </c>
       <c r="V4" s="11" t="str">
-        <f aca="false">IF(M4="","",M4-L4-Q4-R4-S4-T4-Параметры!$B$11)</f>
+        <f aca="false">IF(M4="","",M4-L4-Q4-R4-S4-T4-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W4" s="13" t="str">
@@ -2243,7 +2267,7 @@
         <v/>
       </c>
       <c r="M5" s="11" t="str">
-        <f aca="false">IF(I5="","",IF(Y5&lt;&gt;"",Y5,CEILING((I5*(1+Параметры!$B$8*Параметры!$B$9)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I5="","",CEILING((IF(Y5&lt;&gt;"",Y5,CEILING((I5*(1+Параметры!$B$9*Параметры!$B$10)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N5" s="12"/>
@@ -2252,23 +2276,23 @@
         <v/>
       </c>
       <c r="P5" s="9" t="str">
-        <f aca="false">IF(M5="","",M5*Параметры!$B$6)</f>
+        <f aca="false">IF(M5="","",M5*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q5" s="9" t="str">
-        <f aca="false">IF(M5="","",M5*Параметры!$B$10)</f>
+        <f aca="false">IF(M5="","",M5*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R5" s="9" t="str">
-        <f aca="false">IF(M5="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M5="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S5" s="9" t="str">
-        <f aca="false">IF(I5="","",I5*Параметры!$B$8)</f>
+        <f aca="false">IF(I5="","",I5*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T5" s="9" t="str">
-        <f aca="false">IF(M5="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M5="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U5" s="11" t="str">
@@ -2276,7 +2300,7 @@
         <v/>
       </c>
       <c r="V5" s="11" t="str">
-        <f aca="false">IF(M5="","",M5-L5-Q5-R5-S5-T5-Параметры!$B$11)</f>
+        <f aca="false">IF(M5="","",M5-L5-Q5-R5-S5-T5-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W5" s="13" t="str">
@@ -2330,7 +2354,7 @@
         <v/>
       </c>
       <c r="M6" s="11" t="str">
-        <f aca="false">IF(I6="","",IF(Y6&lt;&gt;"",Y6,CEILING((I6*(1+Параметры!$B$8*Параметры!$B$9)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I6="","",CEILING((IF(Y6&lt;&gt;"",Y6,CEILING((I6*(1+Параметры!$B$9*Параметры!$B$10)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N6" s="12"/>
@@ -2339,23 +2363,23 @@
         <v/>
       </c>
       <c r="P6" s="9" t="str">
-        <f aca="false">IF(M6="","",M6*Параметры!$B$6)</f>
+        <f aca="false">IF(M6="","",M6*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q6" s="9" t="str">
-        <f aca="false">IF(M6="","",M6*Параметры!$B$10)</f>
+        <f aca="false">IF(M6="","",M6*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R6" s="9" t="str">
-        <f aca="false">IF(M6="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M6="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S6" s="9" t="str">
-        <f aca="false">IF(I6="","",I6*Параметры!$B$8)</f>
+        <f aca="false">IF(I6="","",I6*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T6" s="9" t="str">
-        <f aca="false">IF(M6="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M6="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U6" s="11" t="str">
@@ -2363,7 +2387,7 @@
         <v/>
       </c>
       <c r="V6" s="11" t="str">
-        <f aca="false">IF(M6="","",M6-L6-Q6-R6-S6-T6-Параметры!$B$11)</f>
+        <f aca="false">IF(M6="","",M6-L6-Q6-R6-S6-T6-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W6" s="13" t="str">
@@ -2417,7 +2441,7 @@
         <v/>
       </c>
       <c r="M7" s="11" t="str">
-        <f aca="false">IF(I7="","",IF(Y7&lt;&gt;"",Y7,CEILING((I7*(1+Параметры!$B$8*Параметры!$B$9)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I7="","",CEILING((IF(Y7&lt;&gt;"",Y7,CEILING((I7*(1+Параметры!$B$9*Параметры!$B$10)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N7" s="12"/>
@@ -2426,23 +2450,23 @@
         <v/>
       </c>
       <c r="P7" s="9" t="str">
-        <f aca="false">IF(M7="","",M7*Параметры!$B$6)</f>
+        <f aca="false">IF(M7="","",M7*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q7" s="9" t="str">
-        <f aca="false">IF(M7="","",M7*Параметры!$B$10)</f>
+        <f aca="false">IF(M7="","",M7*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R7" s="9" t="str">
-        <f aca="false">IF(M7="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M7="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S7" s="9" t="str">
-        <f aca="false">IF(I7="","",I7*Параметры!$B$8)</f>
+        <f aca="false">IF(I7="","",I7*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T7" s="9" t="str">
-        <f aca="false">IF(M7="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M7="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U7" s="11" t="str">
@@ -2450,7 +2474,7 @@
         <v/>
       </c>
       <c r="V7" s="11" t="str">
-        <f aca="false">IF(M7="","",M7-L7-Q7-R7-S7-T7-Параметры!$B$11)</f>
+        <f aca="false">IF(M7="","",M7-L7-Q7-R7-S7-T7-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W7" s="13" t="str">
@@ -2504,7 +2528,7 @@
         <v/>
       </c>
       <c r="M8" s="11" t="str">
-        <f aca="false">IF(I8="","",IF(Y8&lt;&gt;"",Y8,CEILING((I8*(1+Параметры!$B$8*Параметры!$B$9)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I8="","",CEILING((IF(Y8&lt;&gt;"",Y8,CEILING((I8*(1+Параметры!$B$9*Параметры!$B$10)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N8" s="12"/>
@@ -2513,23 +2537,23 @@
         <v/>
       </c>
       <c r="P8" s="9" t="str">
-        <f aca="false">IF(M8="","",M8*Параметры!$B$6)</f>
+        <f aca="false">IF(M8="","",M8*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q8" s="9" t="str">
-        <f aca="false">IF(M8="","",M8*Параметры!$B$10)</f>
+        <f aca="false">IF(M8="","",M8*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R8" s="9" t="str">
-        <f aca="false">IF(M8="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M8="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S8" s="9" t="str">
-        <f aca="false">IF(I8="","",I8*Параметры!$B$8)</f>
+        <f aca="false">IF(I8="","",I8*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T8" s="9" t="str">
-        <f aca="false">IF(M8="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M8="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U8" s="11" t="str">
@@ -2537,7 +2561,7 @@
         <v/>
       </c>
       <c r="V8" s="11" t="str">
-        <f aca="false">IF(M8="","",M8-L8-Q8-R8-S8-T8-Параметры!$B$11)</f>
+        <f aca="false">IF(M8="","",M8-L8-Q8-R8-S8-T8-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W8" s="13" t="str">
@@ -2591,7 +2615,7 @@
         <v/>
       </c>
       <c r="M9" s="11" t="str">
-        <f aca="false">IF(I9="","",IF(Y9&lt;&gt;"",Y9,CEILING((I9*(1+Параметры!$B$8*Параметры!$B$9)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I9="","",CEILING((IF(Y9&lt;&gt;"",Y9,CEILING((I9*(1+Параметры!$B$9*Параметры!$B$10)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N9" s="12"/>
@@ -2600,23 +2624,23 @@
         <v/>
       </c>
       <c r="P9" s="9" t="str">
-        <f aca="false">IF(M9="","",M9*Параметры!$B$6)</f>
+        <f aca="false">IF(M9="","",M9*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q9" s="9" t="str">
-        <f aca="false">IF(M9="","",M9*Параметры!$B$10)</f>
+        <f aca="false">IF(M9="","",M9*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R9" s="9" t="str">
-        <f aca="false">IF(M9="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M9="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S9" s="9" t="str">
-        <f aca="false">IF(I9="","",I9*Параметры!$B$8)</f>
+        <f aca="false">IF(I9="","",I9*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T9" s="9" t="str">
-        <f aca="false">IF(M9="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M9="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U9" s="11" t="str">
@@ -2624,7 +2648,7 @@
         <v/>
       </c>
       <c r="V9" s="11" t="str">
-        <f aca="false">IF(M9="","",M9-L9-Q9-R9-S9-T9-Параметры!$B$11)</f>
+        <f aca="false">IF(M9="","",M9-L9-Q9-R9-S9-T9-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W9" s="13" t="str">
@@ -2678,7 +2702,7 @@
         <v/>
       </c>
       <c r="M10" s="11" t="str">
-        <f aca="false">IF(I10="","",IF(Y10&lt;&gt;"",Y10,CEILING((I10*(1+Параметры!$B$8*Параметры!$B$9)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I10="","",CEILING((IF(Y10&lt;&gt;"",Y10,CEILING((I10*(1+Параметры!$B$9*Параметры!$B$10)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N10" s="12"/>
@@ -2687,23 +2711,23 @@
         <v/>
       </c>
       <c r="P10" s="9" t="str">
-        <f aca="false">IF(M10="","",M10*Параметры!$B$6)</f>
+        <f aca="false">IF(M10="","",M10*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q10" s="9" t="str">
-        <f aca="false">IF(M10="","",M10*Параметры!$B$10)</f>
+        <f aca="false">IF(M10="","",M10*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R10" s="9" t="str">
-        <f aca="false">IF(M10="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M10="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S10" s="9" t="str">
-        <f aca="false">IF(I10="","",I10*Параметры!$B$8)</f>
+        <f aca="false">IF(I10="","",I10*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T10" s="9" t="str">
-        <f aca="false">IF(M10="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M10="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U10" s="11" t="str">
@@ -2711,7 +2735,7 @@
         <v/>
       </c>
       <c r="V10" s="11" t="str">
-        <f aca="false">IF(M10="","",M10-L10-Q10-R10-S10-T10-Параметры!$B$11)</f>
+        <f aca="false">IF(M10="","",M10-L10-Q10-R10-S10-T10-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W10" s="13" t="str">
@@ -2765,7 +2789,7 @@
         <v/>
       </c>
       <c r="M11" s="11" t="str">
-        <f aca="false">IF(I11="","",IF(Y11&lt;&gt;"",Y11,CEILING((I11*(1+Параметры!$B$8*Параметры!$B$9)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I11="","",CEILING((IF(Y11&lt;&gt;"",Y11,CEILING((I11*(1+Параметры!$B$9*Параметры!$B$10)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N11" s="12"/>
@@ -2774,23 +2798,23 @@
         <v/>
       </c>
       <c r="P11" s="9" t="str">
-        <f aca="false">IF(M11="","",M11*Параметры!$B$6)</f>
+        <f aca="false">IF(M11="","",M11*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q11" s="9" t="str">
-        <f aca="false">IF(M11="","",M11*Параметры!$B$10)</f>
+        <f aca="false">IF(M11="","",M11*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R11" s="9" t="str">
-        <f aca="false">IF(M11="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M11="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S11" s="9" t="str">
-        <f aca="false">IF(I11="","",I11*Параметры!$B$8)</f>
+        <f aca="false">IF(I11="","",I11*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T11" s="9" t="str">
-        <f aca="false">IF(M11="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M11="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U11" s="11" t="str">
@@ -2798,7 +2822,7 @@
         <v/>
       </c>
       <c r="V11" s="11" t="str">
-        <f aca="false">IF(M11="","",M11-L11-Q11-R11-S11-T11-Параметры!$B$11)</f>
+        <f aca="false">IF(M11="","",M11-L11-Q11-R11-S11-T11-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W11" s="13" t="str">
@@ -2852,7 +2876,7 @@
         <v/>
       </c>
       <c r="M12" s="11" t="str">
-        <f aca="false">IF(I12="","",IF(Y12&lt;&gt;"",Y12,CEILING((I12*(1+Параметры!$B$8*Параметры!$B$9)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I12="","",CEILING((IF(Y12&lt;&gt;"",Y12,CEILING((I12*(1+Параметры!$B$9*Параметры!$B$10)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N12" s="12"/>
@@ -2861,23 +2885,23 @@
         <v/>
       </c>
       <c r="P12" s="9" t="str">
-        <f aca="false">IF(M12="","",M12*Параметры!$B$6)</f>
+        <f aca="false">IF(M12="","",M12*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q12" s="9" t="str">
-        <f aca="false">IF(M12="","",M12*Параметры!$B$10)</f>
+        <f aca="false">IF(M12="","",M12*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R12" s="9" t="str">
-        <f aca="false">IF(M12="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M12="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S12" s="9" t="str">
-        <f aca="false">IF(I12="","",I12*Параметры!$B$8)</f>
+        <f aca="false">IF(I12="","",I12*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T12" s="9" t="str">
-        <f aca="false">IF(M12="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M12="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U12" s="11" t="str">
@@ -2885,7 +2909,7 @@
         <v/>
       </c>
       <c r="V12" s="11" t="str">
-        <f aca="false">IF(M12="","",M12-L12-Q12-R12-S12-T12-Параметры!$B$11)</f>
+        <f aca="false">IF(M12="","",M12-L12-Q12-R12-S12-T12-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W12" s="13" t="str">
@@ -2939,7 +2963,7 @@
         <v/>
       </c>
       <c r="M13" s="11" t="str">
-        <f aca="false">IF(I13="","",IF(Y13&lt;&gt;"",Y13,CEILING((I13*(1+Параметры!$B$8*Параметры!$B$9)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I13="","",CEILING((IF(Y13&lt;&gt;"",Y13,CEILING((I13*(1+Параметры!$B$9*Параметры!$B$10)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N13" s="12"/>
@@ -2948,23 +2972,23 @@
         <v/>
       </c>
       <c r="P13" s="9" t="str">
-        <f aca="false">IF(M13="","",M13*Параметры!$B$6)</f>
+        <f aca="false">IF(M13="","",M13*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q13" s="9" t="str">
-        <f aca="false">IF(M13="","",M13*Параметры!$B$10)</f>
+        <f aca="false">IF(M13="","",M13*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R13" s="9" t="str">
-        <f aca="false">IF(M13="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M13="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S13" s="9" t="str">
-        <f aca="false">IF(I13="","",I13*Параметры!$B$8)</f>
+        <f aca="false">IF(I13="","",I13*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T13" s="9" t="str">
-        <f aca="false">IF(M13="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M13="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U13" s="11" t="str">
@@ -2972,7 +2996,7 @@
         <v/>
       </c>
       <c r="V13" s="11" t="str">
-        <f aca="false">IF(M13="","",M13-L13-Q13-R13-S13-T13-Параметры!$B$11)</f>
+        <f aca="false">IF(M13="","",M13-L13-Q13-R13-S13-T13-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W13" s="13" t="str">
@@ -3026,7 +3050,7 @@
         <v/>
       </c>
       <c r="M14" s="11" t="str">
-        <f aca="false">IF(I14="","",IF(Y14&lt;&gt;"",Y14,CEILING((I14*(1+Параметры!$B$8*Параметры!$B$9)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I14="","",CEILING((IF(Y14&lt;&gt;"",Y14,CEILING((I14*(1+Параметры!$B$9*Параметры!$B$10)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N14" s="12"/>
@@ -3035,23 +3059,23 @@
         <v/>
       </c>
       <c r="P14" s="9" t="str">
-        <f aca="false">IF(M14="","",M14*Параметры!$B$6)</f>
+        <f aca="false">IF(M14="","",M14*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q14" s="9" t="str">
-        <f aca="false">IF(M14="","",M14*Параметры!$B$10)</f>
+        <f aca="false">IF(M14="","",M14*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R14" s="9" t="str">
-        <f aca="false">IF(M14="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M14="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S14" s="9" t="str">
-        <f aca="false">IF(I14="","",I14*Параметры!$B$8)</f>
+        <f aca="false">IF(I14="","",I14*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T14" s="9" t="str">
-        <f aca="false">IF(M14="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M14="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U14" s="11" t="str">
@@ -3059,7 +3083,7 @@
         <v/>
       </c>
       <c r="V14" s="11" t="str">
-        <f aca="false">IF(M14="","",M14-L14-Q14-R14-S14-T14-Параметры!$B$11)</f>
+        <f aca="false">IF(M14="","",M14-L14-Q14-R14-S14-T14-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W14" s="13" t="str">
@@ -3113,7 +3137,7 @@
         <v/>
       </c>
       <c r="M15" s="11" t="str">
-        <f aca="false">IF(I15="","",IF(Y15&lt;&gt;"",Y15,CEILING((I15*(1+Параметры!$B$8*Параметры!$B$9)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I15="","",CEILING((IF(Y15&lt;&gt;"",Y15,CEILING((I15*(1+Параметры!$B$9*Параметры!$B$10)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N15" s="12"/>
@@ -3122,23 +3146,23 @@
         <v/>
       </c>
       <c r="P15" s="9" t="str">
-        <f aca="false">IF(M15="","",M15*Параметры!$B$6)</f>
+        <f aca="false">IF(M15="","",M15*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q15" s="9" t="str">
-        <f aca="false">IF(M15="","",M15*Параметры!$B$10)</f>
+        <f aca="false">IF(M15="","",M15*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R15" s="9" t="str">
-        <f aca="false">IF(M15="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M15="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S15" s="9" t="str">
-        <f aca="false">IF(I15="","",I15*Параметры!$B$8)</f>
+        <f aca="false">IF(I15="","",I15*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T15" s="9" t="str">
-        <f aca="false">IF(M15="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M15="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U15" s="11" t="str">
@@ -3146,7 +3170,7 @@
         <v/>
       </c>
       <c r="V15" s="11" t="str">
-        <f aca="false">IF(M15="","",M15-L15-Q15-R15-S15-T15-Параметры!$B$11)</f>
+        <f aca="false">IF(M15="","",M15-L15-Q15-R15-S15-T15-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W15" s="13" t="str">
@@ -3200,7 +3224,7 @@
         <v/>
       </c>
       <c r="M16" s="11" t="str">
-        <f aca="false">IF(I16="","",IF(Y16&lt;&gt;"",Y16,CEILING((I16*(1+Параметры!$B$8*Параметры!$B$9)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I16="","",CEILING((IF(Y16&lt;&gt;"",Y16,CEILING((I16*(1+Параметры!$B$9*Параметры!$B$10)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N16" s="12"/>
@@ -3209,23 +3233,23 @@
         <v/>
       </c>
       <c r="P16" s="9" t="str">
-        <f aca="false">IF(M16="","",M16*Параметры!$B$6)</f>
+        <f aca="false">IF(M16="","",M16*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q16" s="9" t="str">
-        <f aca="false">IF(M16="","",M16*Параметры!$B$10)</f>
+        <f aca="false">IF(M16="","",M16*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R16" s="9" t="str">
-        <f aca="false">IF(M16="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M16="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S16" s="9" t="str">
-        <f aca="false">IF(I16="","",I16*Параметры!$B$8)</f>
+        <f aca="false">IF(I16="","",I16*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T16" s="9" t="str">
-        <f aca="false">IF(M16="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M16="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U16" s="11" t="str">
@@ -3233,7 +3257,7 @@
         <v/>
       </c>
       <c r="V16" s="11" t="str">
-        <f aca="false">IF(M16="","",M16-L16-Q16-R16-S16-T16-Параметры!$B$11)</f>
+        <f aca="false">IF(M16="","",M16-L16-Q16-R16-S16-T16-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W16" s="13" t="str">
@@ -3287,7 +3311,7 @@
         <v/>
       </c>
       <c r="M17" s="11" t="str">
-        <f aca="false">IF(I17="","",IF(Y17&lt;&gt;"",Y17,CEILING((I17*(1+Параметры!$B$8*Параметры!$B$9)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I17="","",CEILING((IF(Y17&lt;&gt;"",Y17,CEILING((I17*(1+Параметры!$B$9*Параметры!$B$10)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N17" s="12"/>
@@ -3296,23 +3320,23 @@
         <v/>
       </c>
       <c r="P17" s="9" t="str">
-        <f aca="false">IF(M17="","",M17*Параметры!$B$6)</f>
+        <f aca="false">IF(M17="","",M17*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q17" s="9" t="str">
-        <f aca="false">IF(M17="","",M17*Параметры!$B$10)</f>
+        <f aca="false">IF(M17="","",M17*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R17" s="9" t="str">
-        <f aca="false">IF(M17="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M17="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S17" s="9" t="str">
-        <f aca="false">IF(I17="","",I17*Параметры!$B$8)</f>
+        <f aca="false">IF(I17="","",I17*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T17" s="9" t="str">
-        <f aca="false">IF(M17="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M17="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U17" s="11" t="str">
@@ -3320,7 +3344,7 @@
         <v/>
       </c>
       <c r="V17" s="11" t="str">
-        <f aca="false">IF(M17="","",M17-L17-Q17-R17-S17-T17-Параметры!$B$11)</f>
+        <f aca="false">IF(M17="","",M17-L17-Q17-R17-S17-T17-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W17" s="13" t="str">
@@ -3374,7 +3398,7 @@
         <v/>
       </c>
       <c r="M18" s="11" t="str">
-        <f aca="false">IF(I18="","",IF(Y18&lt;&gt;"",Y18,CEILING((I18*(1+Параметры!$B$8*Параметры!$B$9)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I18="","",CEILING((IF(Y18&lt;&gt;"",Y18,CEILING((I18*(1+Параметры!$B$9*Параметры!$B$10)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N18" s="12"/>
@@ -3383,23 +3407,23 @@
         <v/>
       </c>
       <c r="P18" s="9" t="str">
-        <f aca="false">IF(M18="","",M18*Параметры!$B$6)</f>
+        <f aca="false">IF(M18="","",M18*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q18" s="9" t="str">
-        <f aca="false">IF(M18="","",M18*Параметры!$B$10)</f>
+        <f aca="false">IF(M18="","",M18*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R18" s="9" t="str">
-        <f aca="false">IF(M18="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M18="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S18" s="9" t="str">
-        <f aca="false">IF(I18="","",I18*Параметры!$B$8)</f>
+        <f aca="false">IF(I18="","",I18*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T18" s="9" t="str">
-        <f aca="false">IF(M18="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M18="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U18" s="11" t="str">
@@ -3407,7 +3431,7 @@
         <v/>
       </c>
       <c r="V18" s="11" t="str">
-        <f aca="false">IF(M18="","",M18-L18-Q18-R18-S18-T18-Параметры!$B$11)</f>
+        <f aca="false">IF(M18="","",M18-L18-Q18-R18-S18-T18-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W18" s="13" t="str">
@@ -3461,7 +3485,7 @@
         <v/>
       </c>
       <c r="M19" s="11" t="str">
-        <f aca="false">IF(I19="","",IF(Y19&lt;&gt;"",Y19,CEILING((I19*(1+Параметры!$B$8*Параметры!$B$9)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I19="","",CEILING((IF(Y19&lt;&gt;"",Y19,CEILING((I19*(1+Параметры!$B$9*Параметры!$B$10)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N19" s="12"/>
@@ -3470,23 +3494,23 @@
         <v/>
       </c>
       <c r="P19" s="9" t="str">
-        <f aca="false">IF(M19="","",M19*Параметры!$B$6)</f>
+        <f aca="false">IF(M19="","",M19*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q19" s="9" t="str">
-        <f aca="false">IF(M19="","",M19*Параметры!$B$10)</f>
+        <f aca="false">IF(M19="","",M19*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R19" s="9" t="str">
-        <f aca="false">IF(M19="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M19="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S19" s="9" t="str">
-        <f aca="false">IF(I19="","",I19*Параметры!$B$8)</f>
+        <f aca="false">IF(I19="","",I19*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T19" s="9" t="str">
-        <f aca="false">IF(M19="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M19="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U19" s="11" t="str">
@@ -3494,7 +3518,7 @@
         <v/>
       </c>
       <c r="V19" s="11" t="str">
-        <f aca="false">IF(M19="","",M19-L19-Q19-R19-S19-T19-Параметры!$B$11)</f>
+        <f aca="false">IF(M19="","",M19-L19-Q19-R19-S19-T19-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W19" s="13" t="str">
@@ -3548,7 +3572,7 @@
         <v/>
       </c>
       <c r="M20" s="11" t="str">
-        <f aca="false">IF(I20="","",IF(Y20&lt;&gt;"",Y20,CEILING((I20*(1+Параметры!$B$8*Параметры!$B$9)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I20="","",CEILING((IF(Y20&lt;&gt;"",Y20,CEILING((I20*(1+Параметры!$B$9*Параметры!$B$10)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N20" s="12"/>
@@ -3557,23 +3581,23 @@
         <v/>
       </c>
       <c r="P20" s="9" t="str">
-        <f aca="false">IF(M20="","",M20*Параметры!$B$6)</f>
+        <f aca="false">IF(M20="","",M20*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q20" s="9" t="str">
-        <f aca="false">IF(M20="","",M20*Параметры!$B$10)</f>
+        <f aca="false">IF(M20="","",M20*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R20" s="9" t="str">
-        <f aca="false">IF(M20="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M20="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S20" s="9" t="str">
-        <f aca="false">IF(I20="","",I20*Параметры!$B$8)</f>
+        <f aca="false">IF(I20="","",I20*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T20" s="9" t="str">
-        <f aca="false">IF(M20="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M20="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U20" s="11" t="str">
@@ -3581,7 +3605,7 @@
         <v/>
       </c>
       <c r="V20" s="11" t="str">
-        <f aca="false">IF(M20="","",M20-L20-Q20-R20-S20-T20-Параметры!$B$11)</f>
+        <f aca="false">IF(M20="","",M20-L20-Q20-R20-S20-T20-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W20" s="13" t="str">
@@ -3635,7 +3659,7 @@
         <v/>
       </c>
       <c r="M21" s="11" t="str">
-        <f aca="false">IF(I21="","",IF(Y21&lt;&gt;"",Y21,CEILING((I21*(1+Параметры!$B$8*Параметры!$B$9)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I21="","",CEILING((IF(Y21&lt;&gt;"",Y21,CEILING((I21*(1+Параметры!$B$9*Параметры!$B$10)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N21" s="12"/>
@@ -3644,23 +3668,23 @@
         <v/>
       </c>
       <c r="P21" s="9" t="str">
-        <f aca="false">IF(M21="","",M21*Параметры!$B$6)</f>
+        <f aca="false">IF(M21="","",M21*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q21" s="9" t="str">
-        <f aca="false">IF(M21="","",M21*Параметры!$B$10)</f>
+        <f aca="false">IF(M21="","",M21*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R21" s="9" t="str">
-        <f aca="false">IF(M21="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M21="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S21" s="9" t="str">
-        <f aca="false">IF(I21="","",I21*Параметры!$B$8)</f>
+        <f aca="false">IF(I21="","",I21*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T21" s="9" t="str">
-        <f aca="false">IF(M21="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M21="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U21" s="11" t="str">
@@ -3668,7 +3692,7 @@
         <v/>
       </c>
       <c r="V21" s="11" t="str">
-        <f aca="false">IF(M21="","",M21-L21-Q21-R21-S21-T21-Параметры!$B$11)</f>
+        <f aca="false">IF(M21="","",M21-L21-Q21-R21-S21-T21-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W21" s="13" t="str">
@@ -3722,7 +3746,7 @@
         <v/>
       </c>
       <c r="M22" s="11" t="str">
-        <f aca="false">IF(I22="","",IF(Y22&lt;&gt;"",Y22,CEILING((I22*(1+Параметры!$B$8*Параметры!$B$9)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I22="","",CEILING((IF(Y22&lt;&gt;"",Y22,CEILING((I22*(1+Параметры!$B$9*Параметры!$B$10)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N22" s="12"/>
@@ -3731,23 +3755,23 @@
         <v/>
       </c>
       <c r="P22" s="9" t="str">
-        <f aca="false">IF(M22="","",M22*Параметры!$B$6)</f>
+        <f aca="false">IF(M22="","",M22*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q22" s="9" t="str">
-        <f aca="false">IF(M22="","",M22*Параметры!$B$10)</f>
+        <f aca="false">IF(M22="","",M22*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R22" s="9" t="str">
-        <f aca="false">IF(M22="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M22="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S22" s="9" t="str">
-        <f aca="false">IF(I22="","",I22*Параметры!$B$8)</f>
+        <f aca="false">IF(I22="","",I22*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T22" s="9" t="str">
-        <f aca="false">IF(M22="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M22="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U22" s="11" t="str">
@@ -3755,7 +3779,7 @@
         <v/>
       </c>
       <c r="V22" s="11" t="str">
-        <f aca="false">IF(M22="","",M22-L22-Q22-R22-S22-T22-Параметры!$B$11)</f>
+        <f aca="false">IF(M22="","",M22-L22-Q22-R22-S22-T22-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W22" s="13" t="str">
@@ -3809,7 +3833,7 @@
         <v/>
       </c>
       <c r="M23" s="11" t="str">
-        <f aca="false">IF(I23="","",IF(Y23&lt;&gt;"",Y23,CEILING((I23*(1+Параметры!$B$8*Параметры!$B$9)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I23="","",CEILING((IF(Y23&lt;&gt;"",Y23,CEILING((I23*(1+Параметры!$B$9*Параметры!$B$10)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N23" s="12"/>
@@ -3818,23 +3842,23 @@
         <v/>
       </c>
       <c r="P23" s="9" t="str">
-        <f aca="false">IF(M23="","",M23*Параметры!$B$6)</f>
+        <f aca="false">IF(M23="","",M23*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q23" s="9" t="str">
-        <f aca="false">IF(M23="","",M23*Параметры!$B$10)</f>
+        <f aca="false">IF(M23="","",M23*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R23" s="9" t="str">
-        <f aca="false">IF(M23="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M23="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S23" s="9" t="str">
-        <f aca="false">IF(I23="","",I23*Параметры!$B$8)</f>
+        <f aca="false">IF(I23="","",I23*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T23" s="9" t="str">
-        <f aca="false">IF(M23="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M23="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U23" s="11" t="str">
@@ -3842,7 +3866,7 @@
         <v/>
       </c>
       <c r="V23" s="11" t="str">
-        <f aca="false">IF(M23="","",M23-L23-Q23-R23-S23-T23-Параметры!$B$11)</f>
+        <f aca="false">IF(M23="","",M23-L23-Q23-R23-S23-T23-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W23" s="13" t="str">
@@ -3896,7 +3920,7 @@
         <v/>
       </c>
       <c r="M24" s="11" t="str">
-        <f aca="false">IF(I24="","",IF(Y24&lt;&gt;"",Y24,CEILING((I24*(1+Параметры!$B$8*Параметры!$B$9)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I24="","",CEILING((IF(Y24&lt;&gt;"",Y24,CEILING((I24*(1+Параметры!$B$9*Параметры!$B$10)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N24" s="12"/>
@@ -3905,23 +3929,23 @@
         <v/>
       </c>
       <c r="P24" s="9" t="str">
-        <f aca="false">IF(M24="","",M24*Параметры!$B$6)</f>
+        <f aca="false">IF(M24="","",M24*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q24" s="9" t="str">
-        <f aca="false">IF(M24="","",M24*Параметры!$B$10)</f>
+        <f aca="false">IF(M24="","",M24*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R24" s="9" t="str">
-        <f aca="false">IF(M24="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M24="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S24" s="9" t="str">
-        <f aca="false">IF(I24="","",I24*Параметры!$B$8)</f>
+        <f aca="false">IF(I24="","",I24*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T24" s="9" t="str">
-        <f aca="false">IF(M24="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M24="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U24" s="11" t="str">
@@ -3929,7 +3953,7 @@
         <v/>
       </c>
       <c r="V24" s="11" t="str">
-        <f aca="false">IF(M24="","",M24-L24-Q24-R24-S24-T24-Параметры!$B$11)</f>
+        <f aca="false">IF(M24="","",M24-L24-Q24-R24-S24-T24-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W24" s="13" t="str">
@@ -3983,7 +4007,7 @@
         <v/>
       </c>
       <c r="M25" s="11" t="str">
-        <f aca="false">IF(I25="","",IF(Y25&lt;&gt;"",Y25,CEILING((I25*(1+Параметры!$B$8*Параметры!$B$9)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I25="","",CEILING((IF(Y25&lt;&gt;"",Y25,CEILING((I25*(1+Параметры!$B$9*Параметры!$B$10)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N25" s="12"/>
@@ -3992,23 +4016,23 @@
         <v/>
       </c>
       <c r="P25" s="9" t="str">
-        <f aca="false">IF(M25="","",M25*Параметры!$B$6)</f>
+        <f aca="false">IF(M25="","",M25*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q25" s="9" t="str">
-        <f aca="false">IF(M25="","",M25*Параметры!$B$10)</f>
+        <f aca="false">IF(M25="","",M25*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R25" s="9" t="str">
-        <f aca="false">IF(M25="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M25="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S25" s="9" t="str">
-        <f aca="false">IF(I25="","",I25*Параметры!$B$8)</f>
+        <f aca="false">IF(I25="","",I25*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T25" s="9" t="str">
-        <f aca="false">IF(M25="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M25="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U25" s="11" t="str">
@@ -4016,7 +4040,7 @@
         <v/>
       </c>
       <c r="V25" s="11" t="str">
-        <f aca="false">IF(M25="","",M25-L25-Q25-R25-S25-T25-Параметры!$B$11)</f>
+        <f aca="false">IF(M25="","",M25-L25-Q25-R25-S25-T25-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W25" s="13" t="str">
@@ -4070,7 +4094,7 @@
         <v/>
       </c>
       <c r="M26" s="11" t="str">
-        <f aca="false">IF(I26="","",IF(Y26&lt;&gt;"",Y26,CEILING((I26*(1+Параметры!$B$8*Параметры!$B$9)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I26="","",CEILING((IF(Y26&lt;&gt;"",Y26,CEILING((I26*(1+Параметры!$B$9*Параметры!$B$10)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N26" s="12"/>
@@ -4079,23 +4103,23 @@
         <v/>
       </c>
       <c r="P26" s="9" t="str">
-        <f aca="false">IF(M26="","",M26*Параметры!$B$6)</f>
+        <f aca="false">IF(M26="","",M26*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q26" s="9" t="str">
-        <f aca="false">IF(M26="","",M26*Параметры!$B$10)</f>
+        <f aca="false">IF(M26="","",M26*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R26" s="9" t="str">
-        <f aca="false">IF(M26="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M26="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S26" s="9" t="str">
-        <f aca="false">IF(I26="","",I26*Параметры!$B$8)</f>
+        <f aca="false">IF(I26="","",I26*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T26" s="9" t="str">
-        <f aca="false">IF(M26="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M26="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U26" s="11" t="str">
@@ -4103,7 +4127,7 @@
         <v/>
       </c>
       <c r="V26" s="11" t="str">
-        <f aca="false">IF(M26="","",M26-L26-Q26-R26-S26-T26-Параметры!$B$11)</f>
+        <f aca="false">IF(M26="","",M26-L26-Q26-R26-S26-T26-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W26" s="13" t="str">
@@ -4159,7 +4183,7 @@
         <v/>
       </c>
       <c r="M27" s="11" t="str">
-        <f aca="false">IF(I27="","",IF(Y27&lt;&gt;"",Y27,CEILING((I27*(1+Параметры!$B$8*Параметры!$B$9)+K27)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I27="","",CEILING((IF(Y27&lt;&gt;"",Y27,CEILING((I27*(1+Параметры!$B$9*Параметры!$B$10)+K27)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N27" s="12"/>
@@ -4168,23 +4192,23 @@
         <v/>
       </c>
       <c r="P27" s="9" t="str">
-        <f aca="false">IF(M27="","",M27*Параметры!$B$6)</f>
+        <f aca="false">IF(M27="","",M27*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q27" s="9" t="str">
-        <f aca="false">IF(M27="","",M27*Параметры!$B$10)</f>
+        <f aca="false">IF(M27="","",M27*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R27" s="9" t="str">
-        <f aca="false">IF(M27="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M27="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S27" s="9" t="str">
-        <f aca="false">IF(I27="","",I27*Параметры!$B$8)</f>
+        <f aca="false">IF(I27="","",I27*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T27" s="9" t="str">
-        <f aca="false">IF(M27="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M27="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U27" s="11" t="str">
@@ -4192,7 +4216,7 @@
         <v/>
       </c>
       <c r="V27" s="11" t="str">
-        <f aca="false">IF(M27="","",M27-L27-Q27-R27-S27-T27-Параметры!$B$11)</f>
+        <f aca="false">IF(M27="","",M27-L27-Q27-R27-S27-T27-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W27" s="13" t="str">
@@ -4248,7 +4272,7 @@
         <v/>
       </c>
       <c r="M28" s="11" t="str">
-        <f aca="false">IF(I28="","",IF(Y28&lt;&gt;"",Y28,CEILING((I28*(1+Параметры!$B$8*Параметры!$B$9)+K28)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))</f>
+        <f aca="false">IF(I28="","",CEILING((IF(Y28&lt;&gt;"",Y28,CEILING((I28*(1+Параметры!$B$9*Параметры!$B$10)+K28)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
         <v/>
       </c>
       <c r="N28" s="12"/>
@@ -4257,23 +4281,23 @@
         <v/>
       </c>
       <c r="P28" s="9" t="str">
-        <f aca="false">IF(M28="","",M28*Параметры!$B$6)</f>
+        <f aca="false">IF(M28="","",M28*Параметры!$B$7)</f>
         <v/>
       </c>
       <c r="Q28" s="9" t="str">
-        <f aca="false">IF(M28="","",M28*Параметры!$B$10)</f>
+        <f aca="false">IF(M28="","",M28*Параметры!$B$11)</f>
         <v/>
       </c>
       <c r="R28" s="9" t="str">
-        <f aca="false">IF(M28="","",Параметры!$B$7)</f>
+        <f aca="false">IF(M28="","",Параметры!$B$8)</f>
         <v/>
       </c>
       <c r="S28" s="9" t="str">
-        <f aca="false">IF(I28="","",I28*Параметры!$B$8)</f>
+        <f aca="false">IF(I28="","",I28*Параметры!$B$9)</f>
         <v/>
       </c>
       <c r="T28" s="9" t="str">
-        <f aca="false">IF(M28="","",Параметры!$B$18)</f>
+        <f aca="false">IF(M28="","",Параметры!$B$19)</f>
         <v/>
       </c>
       <c r="U28" s="11" t="str">
@@ -4281,7 +4305,7 @@
         <v/>
       </c>
       <c r="V28" s="11" t="str">
-        <f aca="false">IF(M28="","",M28-L28-Q28-R28-S28-T28-Параметры!$B$11)</f>
+        <f aca="false">IF(M28="","",M28-L28-Q28-R28-S28-T28-Параметры!$B$12)</f>
         <v/>
       </c>
       <c r="W28" s="13" t="str">
@@ -4338,16 +4362,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4366,7 +4391,9 @@
       <c r="D3" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -4374,21 +4401,25 @@
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="12" t="n">
-        <v>4490</v>
+        <v>4740</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>9990</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="8"/>
+        <v>10490</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>5290</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -4396,21 +4427,25 @@
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="12" t="n">
-        <v>3365</v>
+        <v>3365.09</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>7056.23</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="8"/>
+      <c r="D5" s="12" t="n">
+        <v>3624.6</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -4418,18 +4453,19 @@
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -4437,10 +4473,12 @@
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B7" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"ТО",Киты!$M:$M,"&gt;0"),"")</f>
@@ -4450,10 +4488,14 @@
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"ГРМ",Киты!$M:$M,"&gt;0"),"")</f>
         <v/>
       </c>
+      <c r="D7" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"Тормоза",Киты!$M:$M,"&gt;0"),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"ТО",Киты!$I:$I,"&gt;0"),"")</f>
@@ -4463,19 +4505,22 @@
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"ГРМ",Киты!$I:$I,"&gt;0"),"")</f>
         <v/>
       </c>
+      <c r="D8" s="9" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"Тормоза",Киты!$I:$I,"&gt;0"),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">(Параметры!$B$12+Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16)</f>
+        <f aca="false">(Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16+Параметры!$B$17)</f>
         <v>6783</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -4483,36 +4528,45 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B10" s="11" t="n">
-        <f aca="false">B4-(B5+Параметры!$B$3)-$B$6*B4*Параметры!$B$6-(1-$B$6)*(B4*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-B5*Параметры!$B$8</f>
-        <v>565.11</v>
+        <f aca="false">IF(B4="","",B4-(B5+Параметры!$B$3)-$B$6*B4*Параметры!$B$7-(1-$B$6)*(B4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-B5*Параметры!$B$9)</f>
+        <v>806.0155</v>
       </c>
       <c r="C10" s="11" t="n">
-        <f aca="false">C4-(C5+Параметры!$B$3)-$B$6*C4*Параметры!$B$6-(1-$B$6)*(C4*Параметры!$B$10+Параметры!$B$11)-Параметры!$B$7-C5*Параметры!$B$8</f>
-        <v>1991.3185</v>
+        <f aca="false">IF(C4="","",C4-(C5+Параметры!$B$3)-$B$6*C4*Параметры!$B$7-(1-$B$6)*(C4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-C5*Параметры!$B$9)</f>
+        <v>2473.3185</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <f aca="false">IF(D4="","",D4-(D5+Параметры!$B$3)-$B$6*D4*Параметры!$B$7-(1-$B$6)*(D4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-D5*Параметры!$B$9)</f>
+        <v>1063.73</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">IF(B10&lt;=0,"не окупается",ROUNDUP($B$9/B10,0))</f>
-        <v>13</v>
+        <f aca="false">IF(B10="","",IF(B10&lt;=0,"не окупается",ROUNDUP($B$9/B10,0)))</f>
+        <v>9</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">IF(C10&lt;=0,"не окупается",ROUNDUP($B$9/C10,0))</f>
-        <v>4</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="8"/>
+        <f aca="false">IF(C10="","",IF(C10&lt;=0,"не окупается",ROUNDUP($B$9/C10,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <f aca="false">IF(D10="","",IF(D10&lt;=0,"не окупается",ROUNDUP($B$9/D10,0)))</f>
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>175</v>
+      </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -4520,102 +4574,110 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="K13" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">B14*$B$4+C14*$C$4</f>
-        <v>49950</v>
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">B14*($B$5+Параметры!$B$3)+C14*($C$5+Параметры!$B$3)</f>
-        <v>35531.15</v>
+        <f aca="false">N(B14)*N($B$4)+N(C14)*N($C$4)+N(D14)*N($D$4)</f>
+        <v>94800</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">$B$6*D14*Параметры!$B$6</f>
-        <v>1623.375</v>
+        <f aca="false">N(B14)*(N($B$5)+Параметры!$B$3)+N(C14)*(N($C$5)+Параметры!$B$3)+N(D14)*(N($D$5)+Параметры!$B$3)</f>
+        <v>68301.8</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">(1-$B$6)*D14*Параметры!$B$10</f>
-        <v>174.825</v>
+        <f aca="false">$B$6*E14*Параметры!$B$7</f>
+        <v>3081</v>
       </c>
       <c r="H14" s="9" t="n">
-        <f aca="false">(B14+C14)*Параметры!$B$7</f>
-        <v>900</v>
+        <f aca="false">(1-$B$6)*E14*Параметры!$B$11</f>
+        <v>331.8</v>
       </c>
       <c r="I14" s="9" t="n">
-        <f aca="false">(B14*$B$5+C14*$C$5)*Параметры!$B$8</f>
-        <v>1764.0575</v>
+        <f aca="false">(B14+C14+D14)*Параметры!$B$8</f>
+        <v>3600</v>
       </c>
       <c r="J14" s="9" t="n">
-        <f aca="false">(B14+C14)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
+        <f aca="false">(N(B14)*N($B$5)+N(C14)*N($C$5)+N(D14)*N($D$5))*Параметры!$B$9</f>
+        <v>3365.09</v>
       </c>
       <c r="K14" s="9" t="n">
+        <f aca="false">(B14+C14+D14)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L14" s="11" t="n">
-        <f aca="false">D14-SUM(E14:K14)</f>
-        <v>3173.59250000001</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <f aca="false">IF(B14+C14=0,"",L14/(B14+C14))</f>
-        <v>634.718500000001</v>
+      <c r="M14" s="11" t="n">
+        <f aca="false">E14-SUM(F14:L14)</f>
+        <v>9337.31</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <f aca="false">IF((B14+C14+D14)=0,"",M14/(B14+C14+D14))</f>
+        <v>466.8655</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>0</v>
@@ -4623,470 +4685,335 @@
       <c r="C15" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">B15*$B$4+C15*$C$4</f>
-        <v>99900</v>
+      <c r="D15" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">B15*($B$5+Параметры!$B$3)+C15*($C$5+Параметры!$B$3)</f>
+        <f aca="false">N(B15)*N($B$4)+N(C15)*N($C$4)+N(D15)*N($D$4)</f>
+        <v>104900</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <f aca="false">N(B15)*(N($B$5)+Параметры!$B$3)+N(C15)*(N($C$5)+Параметры!$B$3)+N(D15)*(N($D$5)+Параметры!$B$3)</f>
         <v>71062.3</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <f aca="false">$B$6*D15*Параметры!$B$6</f>
-        <v>3246.75</v>
-      </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">(1-$B$6)*D15*Параметры!$B$10</f>
-        <v>349.65</v>
+        <f aca="false">$B$6*E15*Параметры!$B$7</f>
+        <v>3409.25</v>
       </c>
       <c r="H15" s="9" t="n">
-        <f aca="false">(B15+C15)*Параметры!$B$7</f>
+        <f aca="false">(1-$B$6)*E15*Параметры!$B$11</f>
+        <v>367.15</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <f aca="false">(B15+C15+D15)*Параметры!$B$8</f>
         <v>1800</v>
       </c>
-      <c r="I15" s="9" t="n">
-        <f aca="false">(B15*$B$5+C15*$C$5)*Параметры!$B$8</f>
+      <c r="J15" s="9" t="n">
+        <f aca="false">(N(B15)*N($B$5)+N(C15)*N($C$5)+N(D15)*N($D$5))*Параметры!$B$9</f>
         <v>3528.115</v>
       </c>
-      <c r="J15" s="9" t="n">
-        <f aca="false">(B15+C15)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
       <c r="K15" s="9" t="n">
+        <f aca="false">(B15+C15+D15)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L15" s="11" t="n">
-        <f aca="false">D15-SUM(E15:K15)</f>
-        <v>13130.185</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <f aca="false">IF(B15+C15=0,"",L15/(B15+C15))</f>
-        <v>1313.0185</v>
+      <c r="M15" s="11" t="n">
+        <f aca="false">E15-SUM(F15:L15)</f>
+        <v>17950.185</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <f aca="false">IF((B15+C15+D15)=0,"",M15/(B15+C15+D15))</f>
+        <v>1795.0185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">B16*$B$4+C16*$C$4</f>
-        <v>149850</v>
+        <v>0</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>10</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">B16*($B$5+Параметры!$B$3)+C16*($C$5+Параметры!$B$3)</f>
-        <v>106593.45</v>
+        <f aca="false">N(B16)*N($B$4)+N(C16)*N($C$4)+N(D16)*N($D$4)</f>
+        <v>52900</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">$B$6*D16*Параметры!$B$6</f>
-        <v>4870.125</v>
+        <f aca="false">N(B16)*(N($B$5)+Параметры!$B$3)+N(C16)*(N($C$5)+Параметры!$B$3)+N(D16)*(N($D$5)+Параметры!$B$3)</f>
+        <v>36746</v>
       </c>
       <c r="G16" s="9" t="n">
-        <f aca="false">(1-$B$6)*D16*Параметры!$B$10</f>
-        <v>524.475</v>
+        <f aca="false">$B$6*E16*Параметры!$B$7</f>
+        <v>1719.25</v>
       </c>
       <c r="H16" s="9" t="n">
-        <f aca="false">(B16+C16)*Параметры!$B$7</f>
-        <v>2700</v>
+        <f aca="false">(1-$B$6)*E16*Параметры!$B$11</f>
+        <v>185.15</v>
       </c>
       <c r="I16" s="9" t="n">
-        <f aca="false">(B16*$B$5+C16*$C$5)*Параметры!$B$8</f>
-        <v>5292.1725</v>
+        <f aca="false">(B16+C16+D16)*Параметры!$B$8</f>
+        <v>1800</v>
       </c>
       <c r="J16" s="9" t="n">
-        <f aca="false">(B16+C16)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
+        <f aca="false">(N(B16)*N($B$5)+N(C16)*N($C$5)+N(D16)*N($D$5))*Параметры!$B$9</f>
+        <v>1812.3</v>
       </c>
       <c r="K16" s="9" t="n">
+        <f aca="false">(B16+C16+D16)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L16" s="11" t="n">
-        <f aca="false">D16-SUM(E16:K16)</f>
-        <v>23086.7775</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <f aca="false">IF(B16+C16=0,"",L16/(B16+C16))</f>
-        <v>1539.1185</v>
+      <c r="M16" s="11" t="n">
+        <f aca="false">E16-SUM(F16:L16)</f>
+        <v>3854.3</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <f aca="false">IF((B16+C16+D16)=0,"",M16/(B16+C16+D16))</f>
+        <v>385.43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">B17*$B$4+C17*$C$4</f>
-        <v>199800</v>
+        <v>5</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">B17*($B$5+Параметры!$B$3)+C17*($C$5+Параметры!$B$3)</f>
-        <v>142124.6</v>
+        <f aca="false">N(B17)*N($B$4)+N(C17)*N($C$4)+N(D17)*N($D$4)</f>
+        <v>126300</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">$B$6*D17*Параметры!$B$6</f>
-        <v>6493.5</v>
+        <f aca="false">N(B17)*(N($B$5)+Параметры!$B$3)+N(C17)*(N($C$5)+Параметры!$B$3)+N(D17)*(N($D$5)+Параметры!$B$3)</f>
+        <v>88055.05</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">(1-$B$6)*D17*Параметры!$B$10</f>
-        <v>699.3</v>
+        <f aca="false">$B$6*E17*Параметры!$B$7</f>
+        <v>4104.75</v>
       </c>
       <c r="H17" s="9" t="n">
-        <f aca="false">(B17+C17)*Параметры!$B$7</f>
+        <f aca="false">(1-$B$6)*E17*Параметры!$B$11</f>
+        <v>442.05</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <f aca="false">(B17+C17+D17)*Параметры!$B$8</f>
         <v>3600</v>
       </c>
-      <c r="I17" s="9" t="n">
-        <f aca="false">(B17*$B$5+C17*$C$5)*Параметры!$B$8</f>
-        <v>7056.23</v>
-      </c>
       <c r="J17" s="9" t="n">
-        <f aca="false">(B17+C17)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
+        <f aca="false">(N(B17)*N($B$5)+N(C17)*N($C$5)+N(D17)*N($D$5))*Параметры!$B$9</f>
+        <v>4352.7525</v>
       </c>
       <c r="K17" s="9" t="n">
+        <f aca="false">(B17+C17+D17)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L17" s="11" t="n">
-        <f aca="false">D17-SUM(E17:K17)</f>
-        <v>33043.37</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <f aca="false">IF(B17+C17=0,"",L17/(B17+C17))</f>
-        <v>1652.1685</v>
+      <c r="M17" s="11" t="n">
+        <f aca="false">E17-SUM(F17:L17)</f>
+        <v>18962.3975</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <f aca="false">IF((B17+C17+D17)=0,"",M17/(B17+C17+D17))</f>
+        <v>948.119875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <f aca="false">B18*$B$4+C18*$C$4</f>
-        <v>299700</v>
+        <v>10</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>10</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">B18*($B$5+Параметры!$B$3)+C18*($C$5+Параметры!$B$3)</f>
-        <v>213186.9</v>
+        <f aca="false">N(B18)*N($B$4)+N(C18)*N($C$4)+N(D18)*N($D$4)</f>
+        <v>252600</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">$B$6*D18*Параметры!$B$6</f>
-        <v>9740.25</v>
+        <f aca="false">N(B18)*(N($B$5)+Параметры!$B$3)+N(C18)*(N($C$5)+Параметры!$B$3)+N(D18)*(N($D$5)+Параметры!$B$3)</f>
+        <v>176110.1</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">(1-$B$6)*D18*Параметры!$B$10</f>
-        <v>1048.95</v>
+        <f aca="false">$B$6*E18*Параметры!$B$7</f>
+        <v>8209.5</v>
       </c>
       <c r="H18" s="9" t="n">
-        <f aca="false">(B18+C18)*Параметры!$B$7</f>
-        <v>5400</v>
+        <f aca="false">(1-$B$6)*E18*Параметры!$B$11</f>
+        <v>884.1</v>
       </c>
       <c r="I18" s="9" t="n">
-        <f aca="false">(B18*$B$5+C18*$C$5)*Параметры!$B$8</f>
-        <v>10584.345</v>
+        <f aca="false">(B18+C18+D18)*Параметры!$B$8</f>
+        <v>7200</v>
       </c>
       <c r="J18" s="9" t="n">
-        <f aca="false">(B18+C18)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
+        <f aca="false">(N(B18)*N($B$5)+N(C18)*N($C$5)+N(D18)*N($D$5))*Параметры!$B$9</f>
+        <v>8705.505</v>
       </c>
       <c r="K18" s="9" t="n">
+        <f aca="false">(B18+C18+D18)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L18" s="11" t="n">
-        <f aca="false">D18-SUM(E18:K18)</f>
-        <v>52956.555</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <f aca="false">IF(B18+C18=0,"",L18/(B18+C18))</f>
-        <v>1765.2185</v>
+      <c r="M18" s="11" t="n">
+        <f aca="false">E18-SUM(F18:L18)</f>
+        <v>44707.795</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <f aca="false">IF((B18+C18+D18)=0,"",M18/(B18+C18+D18))</f>
+        <v>1117.694875</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B19" s="16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <f aca="false">B19*$B$4+C19*$C$4</f>
-        <v>89800</v>
+        <v>15</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>15</v>
       </c>
       <c r="E19" s="9" t="n">
-        <f aca="false">B19*($B$5+Параметры!$B$3)+C19*($C$5+Параметры!$B$3)</f>
-        <v>68300</v>
+        <f aca="false">N(B19)*N($B$4)+N(C19)*N($C$4)+N(D19)*N($D$4)</f>
+        <v>378900</v>
       </c>
       <c r="F19" s="9" t="n">
-        <f aca="false">$B$6*D19*Параметры!$B$6</f>
-        <v>2918.5</v>
+        <f aca="false">N(B19)*(N($B$5)+Параметры!$B$3)+N(C19)*(N($C$5)+Параметры!$B$3)+N(D19)*(N($D$5)+Параметры!$B$3)</f>
+        <v>264165.15</v>
       </c>
       <c r="G19" s="9" t="n">
-        <f aca="false">(1-$B$6)*D19*Параметры!$B$10</f>
-        <v>314.3</v>
+        <f aca="false">$B$6*E19*Параметры!$B$7</f>
+        <v>12314.25</v>
       </c>
       <c r="H19" s="9" t="n">
-        <f aca="false">(B19+C19)*Параметры!$B$7</f>
-        <v>3600</v>
+        <f aca="false">(1-$B$6)*E19*Параметры!$B$11</f>
+        <v>1326.15</v>
       </c>
       <c r="I19" s="9" t="n">
-        <f aca="false">(B19*$B$5+C19*$C$5)*Параметры!$B$8</f>
-        <v>3365</v>
+        <f aca="false">(B19+C19+D19)*Параметры!$B$8</f>
+        <v>10800</v>
       </c>
       <c r="J19" s="9" t="n">
-        <f aca="false">(B19+C19)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
+        <f aca="false">(N(B19)*N($B$5)+N(C19)*N($C$5)+N(D19)*N($D$5))*Параметры!$B$9</f>
+        <v>13058.2575</v>
       </c>
       <c r="K19" s="9" t="n">
+        <f aca="false">(B19+C19+D19)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L19" s="11" t="n">
-        <f aca="false">D19-SUM(E19:K19)</f>
-        <v>4519.2</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <f aca="false">IF(B19+C19=0,"",L19/(B19+C19))</f>
-        <v>225.96</v>
+      <c r="M19" s="11" t="n">
+        <f aca="false">E19-SUM(F19:L19)</f>
+        <v>70453.1925</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <f aca="false">IF((B19+C19+D19)=0,"",M19/(B19+C19+D19))</f>
+        <v>1174.219875</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B20" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">B20*$B$4+C20*$C$4</f>
-        <v>139750</v>
+      <c r="D20" s="16" t="n">
+        <v>20</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">B20*($B$5+Параметры!$B$3)+C20*($C$5+Параметры!$B$3)</f>
-        <v>103831.15</v>
+        <f aca="false">N(B20)*N($B$4)+N(C20)*N($C$4)+N(D20)*N($D$4)</f>
+        <v>552600</v>
       </c>
       <c r="F20" s="9" t="n">
-        <f aca="false">$B$6*D20*Параметры!$B$6</f>
-        <v>4541.875</v>
+        <f aca="false">N(B20)*(N($B$5)+Параметры!$B$3)+N(C20)*(N($C$5)+Параметры!$B$3)+N(D20)*(N($D$5)+Параметры!$B$3)</f>
+        <v>386371.1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <f aca="false">(1-$B$6)*D20*Параметры!$B$10</f>
-        <v>489.125</v>
+        <f aca="false">$B$6*E20*Параметры!$B$7</f>
+        <v>17959.5</v>
       </c>
       <c r="H20" s="9" t="n">
-        <f aca="false">(B20+C20)*Параметры!$B$7</f>
-        <v>4500</v>
+        <f aca="false">(1-$B$6)*E20*Параметры!$B$11</f>
+        <v>1934.1</v>
       </c>
       <c r="I20" s="9" t="n">
-        <f aca="false">(B20*$B$5+C20*$C$5)*Параметры!$B$8</f>
-        <v>5129.0575</v>
+        <f aca="false">(B20+C20+D20)*Параметры!$B$8</f>
+        <v>16200</v>
       </c>
       <c r="J20" s="9" t="n">
-        <f aca="false">(B20+C20)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
+        <f aca="false">(N(B20)*N($B$5)+N(C20)*N($C$5)+N(D20)*N($D$5))*Параметры!$B$9</f>
+        <v>19093.555</v>
       </c>
       <c r="K20" s="9" t="n">
+        <f aca="false">(B20+C20+D20)*(1-$B$6)*Параметры!$B$12</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="n">
         <f aca="false">$B$9</f>
         <v>6783</v>
       </c>
-      <c r="L20" s="11" t="n">
-        <f aca="false">D20-SUM(E20:K20)</f>
-        <v>14475.7925</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <f aca="false">IF(B20+C20=0,"",L20/(B20+C20))</f>
-        <v>579.031700000001</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <f aca="false">B21*$B$4+C21*$C$4</f>
-        <v>189700</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <f aca="false">B21*($B$5+Параметры!$B$3)+C21*($C$5+Параметры!$B$3)</f>
-        <v>139362.3</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <f aca="false">$B$6*D21*Параметры!$B$6</f>
-        <v>6165.25</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <f aca="false">(1-$B$6)*D21*Параметры!$B$10</f>
-        <v>663.95</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <f aca="false">(B21+C21)*Параметры!$B$7</f>
-        <v>5400</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <f aca="false">(B21*$B$5+C21*$C$5)*Параметры!$B$8</f>
-        <v>6893.115</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <f aca="false">(B21+C21)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <f aca="false">$B$9</f>
-        <v>6783</v>
-      </c>
-      <c r="L21" s="11" t="n">
-        <f aca="false">D21-SUM(E21:K21)</f>
-        <v>24432.385</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <f aca="false">IF(B21+C21=0,"",L21/(B21+C21))</f>
-        <v>814.412833333334</v>
+      <c r="M20" s="11" t="n">
+        <f aca="false">E20-SUM(F20:L20)</f>
+        <v>104258.745</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <f aca="false">IF((B20+C20+D20)=0,"",M20/(B20+C20+D20))</f>
+        <v>1158.4305</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <f aca="false">B22*$B$4+C22*$C$4</f>
-        <v>284550</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <f aca="false">B22*($B$5+Параметры!$B$3)+C22*($C$5+Параметры!$B$3)</f>
-        <v>209043.45</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <f aca="false">$B$6*D22*Параметры!$B$6</f>
-        <v>9247.875</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <f aca="false">(1-$B$6)*D22*Параметры!$B$10</f>
-        <v>995.925</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <f aca="false">(B22+C22)*Параметры!$B$7</f>
-        <v>8100</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <f aca="false">(B22*$B$5+C22*$C$5)*Параметры!$B$8</f>
-        <v>10339.6725</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <f aca="false">(B22+C22)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <f aca="false">$B$9</f>
-        <v>6783</v>
-      </c>
-      <c r="L22" s="11" t="n">
-        <f aca="false">D22-SUM(E22:K22)</f>
-        <v>40040.0775</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <f aca="false">IF(B22+C22=0,"",L22/(B22+C22))</f>
-        <v>889.7795</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <f aca="false">B23*$B$4+C23*$C$4</f>
-        <v>424300</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <f aca="false">B23*($B$5+Параметры!$B$3)+C23*($C$5+Параметры!$B$3)</f>
-        <v>312874.6</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <f aca="false">$B$6*D23*Параметры!$B$6</f>
-        <v>13789.75</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <f aca="false">(1-$B$6)*D23*Параметры!$B$10</f>
-        <v>1485.05</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <f aca="false">(B23+C23)*Параметры!$B$7</f>
-        <v>12600</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <f aca="false">(B23*$B$5+C23*$C$5)*Параметры!$B$8</f>
-        <v>15468.73</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <f aca="false">(B23+C23)*(1-$B$6)*Параметры!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <f aca="false">$B$9</f>
-        <v>6783</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <f aca="false">D23-SUM(E23:K23)</f>
-        <v>61298.87</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <f aca="false">IF(B23+C23=0,"",L23/(B23+C23))</f>
-        <v>875.698142857143</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>187</v>
+      <c r="A22" s="17" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="D5:L5"/>
-    <mergeCell ref="D6:L6"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="E4:N4"/>
+    <mergeCell ref="E5:N5"/>
+    <mergeCell ref="E6:N6"/>
+    <mergeCell ref="E9:N9"/>
+    <mergeCell ref="E11:N11"/>
   </mergeCells>
-  <conditionalFormatting sqref="L14:L23">
+  <conditionalFormatting sqref="M14:M20">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -5106,7 +5033,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -5116,206 +5043,217 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B6" s="18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="18" t="n">
         <v>0.065</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="C7" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>0.05</v>
-      </c>
       <c r="C8" s="8" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="19" t="n">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>0.05</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="18" t="n">
+        <v>213</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <v>0.007</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="C11" s="8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B12" s="12" t="n">
-        <v>4783</v>
+        <v>0</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1500</v>
+        <v>4783</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B14" s="12" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B17" s="19" t="n">
+        <v>227</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="11" t="n">
-        <f aca="false">($B$12+$B$13+$B$14+$B$15+$B$16)/MAX(1,$B$17)</f>
+      <c r="C18" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B19" s="11" t="n">
+        <f aca="false">($B$13+$B$14+$B$15+$B$16+$B$17)/MAX(1,$B$18)</f>
         <v>339.15</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>225</v>
+      <c r="C19" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -5358,75 +5296,75 @@
         <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G2" s="23" t="n">
         <v>460</v>
@@ -5458,7 +5396,7 @@
         <v>430</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5470,7 +5408,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -5499,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5511,7 +5449,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -5550,7 +5488,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -5589,7 +5527,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -5628,7 +5566,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -5667,7 +5605,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -5696,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5708,7 +5646,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -5747,7 +5685,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -5786,7 +5724,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -5825,7 +5763,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -5864,7 +5802,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -5893,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5905,7 +5843,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -5944,7 +5882,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -5983,7 +5921,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -6022,7 +5960,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -6061,7 +5999,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -6090,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6102,7 +6040,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -6141,7 +6079,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -6180,7 +6118,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -6219,7 +6157,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -6258,7 +6196,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -6287,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6299,7 +6237,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -6338,7 +6276,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -6377,7 +6315,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -6416,7 +6354,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -6455,7 +6393,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -6484,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6496,7 +6434,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -6535,7 +6473,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -6574,7 +6512,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -6613,7 +6551,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -6652,7 +6590,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -6681,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6693,7 +6631,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -6722,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6734,7 +6672,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -6773,7 +6711,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -6812,7 +6750,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -6851,7 +6789,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -6890,7 +6828,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -6919,7 +6857,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6931,7 +6869,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -6960,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6972,7 +6910,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -7011,7 +6949,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -7050,7 +6988,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -7089,7 +7027,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -7128,7 +7066,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -7157,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7169,7 +7107,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -7198,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7210,7 +7148,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -7249,7 +7187,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -7288,7 +7226,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -7327,7 +7265,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -7366,7 +7304,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -7395,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7407,7 +7345,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -7436,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7448,7 +7386,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -7487,7 +7425,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -7526,7 +7464,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -7565,7 +7503,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -7604,7 +7542,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -7633,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7645,7 +7583,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -7674,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7686,7 +7624,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -7725,7 +7663,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -7764,7 +7702,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -7803,7 +7741,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -7842,7 +7780,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -7871,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7883,7 +7821,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -7912,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7924,7 +7862,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -7963,7 +7901,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -8002,7 +7940,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -8041,7 +7979,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -8080,13 +8018,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -8111,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8123,13 +8061,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -8154,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8166,13 +8104,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -8197,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8209,13 +8147,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -8240,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8252,13 +8190,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -8283,7 +8221,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8295,13 +8233,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -8326,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8338,13 +8276,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -8369,7 +8307,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8381,13 +8319,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -8412,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8424,7 +8362,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -8453,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8465,7 +8403,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -8504,7 +8442,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -8543,7 +8481,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -8572,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8584,7 +8522,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -8613,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8625,7 +8563,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -8654,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8666,7 +8604,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -8705,7 +8643,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -8744,7 +8682,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -8773,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8785,7 +8723,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -8814,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8826,7 +8764,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -8855,7 +8793,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8867,7 +8805,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -8906,7 +8844,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -8945,7 +8883,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -8974,7 +8912,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8986,7 +8924,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -9015,7 +8953,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9027,7 +8965,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -9056,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9068,7 +9006,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -9107,7 +9045,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -9146,7 +9084,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -9175,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9187,7 +9125,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -9216,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9228,7 +9166,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -9257,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9269,7 +9207,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -9308,7 +9246,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -9347,7 +9285,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -9376,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9388,7 +9326,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -9417,7 +9355,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9429,7 +9367,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -9468,7 +9406,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -9497,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9509,7 +9447,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -9538,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9550,7 +9488,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -9579,7 +9517,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9591,7 +9529,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -9630,7 +9568,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -9669,7 +9607,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -9698,7 +9636,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9710,7 +9648,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -9739,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9751,7 +9689,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -9780,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9792,7 +9730,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -9831,7 +9769,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -9870,7 +9808,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -9899,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9911,7 +9849,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -9940,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9952,7 +9890,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -9981,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9993,7 +9931,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -10032,7 +9970,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -10071,7 +10009,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -10100,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10112,7 +10050,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -10141,7 +10079,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10153,7 +10091,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -10182,7 +10120,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10194,7 +10132,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -10233,7 +10171,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -10272,7 +10210,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -10301,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10313,7 +10251,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -10342,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10354,16 +10292,16 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
@@ -10387,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10399,7 +10337,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -10428,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10440,7 +10378,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -10469,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10481,7 +10419,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -10510,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10522,16 +10460,16 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D129" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G129" s="12"/>
       <c r="H129" s="12"/>
@@ -10555,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="8" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10567,16 +10505,16 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D130" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F130" s="14" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="G130" s="12"/>
       <c r="H130" s="12"/>
@@ -10600,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="S130" s="8" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10612,7 +10550,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D131" s="14" t="n">
         <v>1</v>
@@ -10641,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="S131" s="8" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10653,16 +10591,16 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D132" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F132" s="14" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G132" s="12"/>
       <c r="H132" s="12"/>
@@ -10686,7 +10624,7 @@
         <v>0</v>
       </c>
       <c r="S132" s="8" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10698,16 +10636,16 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D133" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F133" s="14" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="G133" s="12"/>
       <c r="H133" s="12"/>
@@ -10731,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="8" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10743,7 +10681,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D134" s="14" t="n">
         <v>1</v>
@@ -10772,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="8" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -10809,80 +10747,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -10896,10 +10834,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -10913,10 +10851,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -10930,10 +10868,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -10947,10 +10885,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
@@ -10964,10 +10902,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -10981,10 +10919,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
@@ -10998,10 +10936,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -11015,10 +10953,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -11069,7 +11007,7 @@
         <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>17</v>
@@ -11078,197 +11016,197 @@
         <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -636,7 +636,7 @@
     <t xml:space="preserve">Сумма, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Оплата</t>
+    <t xml:space="preserve">Оплата и получение</t>
   </si>
   <si>
     <t xml:space="preserve">Причина отказа</t>
@@ -10501,7 +10501,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K3:K302" type="list">
-      <formula1>"Авито Доставка,перевод"</formula1>
+      <formula1>"Авито Доставка,перевод + СДЭК,перевод + самовывоз"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L3:L302" type="list">

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="414">
   <si>
     <t xml:space="preserve">ZAPKIT — таблица закупки и цен</t>
   </si>
@@ -165,7 +165,7 @@
     <t xml:space="preserve">6. «Моторы» — справка: где цепь, где ремень, что входит в ГРМ-кит, источники.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. «Заявки» — каждое обращение на Авито: VIN, статус, следующий шаг. Справа считается воронка. Как вести — docs/avito/client-loop.md.</t>
+    <t xml:space="preserve">7. «Заявки» — каждое обращение на Авито от первого сообщения до отзыва: VIN, статус, следующий шаг, трек, напоминание о ТО. Справа считается воронка. Как вести — docs/avito/client-loop.md и docs/avito/order-loop.md.</t>
   </si>
   <si>
     <t xml:space="preserve">Обозначения:</t>
@@ -648,6 +648,18 @@
     <t xml:space="preserve">Когда</t>
   </si>
   <si>
+    <t xml:space="preserve">Трек-номер / встреча</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Получен (дата)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пробег в месяц, км</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напомнить о ТО</t>
+  </si>
+  <si>
     <t xml:space="preserve">Комментарий</t>
   </si>
   <si>
@@ -672,52 +684,76 @@
     <t xml:space="preserve">Z94C…</t>
   </si>
   <si>
+    <t xml:space="preserve">12. Закрыт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Авито Доставка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СДЭК 10…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">образец заполнения — строку можно удалить</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Всего обращений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Новый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Ждём VIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Подбор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Предложение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Думает</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Ждём оплату</t>
+  </si>
+  <si>
     <t xml:space="preserve">7. В обработке</t>
   </si>
   <si>
-    <t xml:space="preserve">Авито Доставка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказать у поставщика до отсечки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">образец заполнения — строку можно удалить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Всего обращений</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Новый</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Ждём VIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Подбор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Предложение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Думает</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Ждём оплату</t>
+    <t xml:space="preserve">8. Детали у нас</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Собран</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Отправлен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Получен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проблема</t>
   </si>
   <si>
     <t xml:space="preserve">Отказ</t>
   </si>
   <si>
-    <t xml:space="preserve">Доля заказов (в обработке ÷ всего)</t>
+    <t xml:space="preserve">Заказов (статусы 7–12 и «Проблема»)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля заказов (заказы ÷ всего)</t>
   </si>
   <si>
     <t xml:space="preserve">Среднее время первого ответа, мин</t>
   </si>
   <si>
-    <t xml:space="preserve">Выручка по заказам в обработке, ₽</t>
+    <t xml:space="preserve">Выручка по заказам, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Повторных обращений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пора напомнить о ТО (жёлтые строки)</t>
   </si>
   <si>
     <t xml:space="preserve">Причины отказов</t>
@@ -967,6 +1003,12 @@
   </si>
   <si>
     <t xml:space="preserve">На сколько заказов делятся постоянные расходы. Больше заказов — меньше расходов на один кит.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Интервал ТО для напоминания, км</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лист «Заявки»: напомнить о ТО = дата получения + (этот пробег ÷ пробег клиента в месяц), минус 2 недели. Не позже чем через год; если пробег клиента неизвестен — через 6 месяцев.</t>
   </si>
   <si>
     <t xml:space="preserve">Постоянные расходы на 1 кит, ₽</t>
@@ -1339,14 +1381,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;;\-#,##0&quot; ₽&quot;;\-"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="dd\.mm"/>
-    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="dd\.mm\.yy"/>
     <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1506,7 +1549,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1575,11 +1618,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1587,7 +1650,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1640,7 +1703,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -1664,6 +1727,20 @@
         <b val="1"/>
         <color rgb="FFC00000"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -1702,12 +1779,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2183,7 +2260,7 @@
         <v/>
       </c>
       <c r="T2" s="9" t="str">
-        <f aca="false">IF(M2="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M2="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U2" s="11" t="str">
@@ -2270,7 +2347,7 @@
         <v/>
       </c>
       <c r="T3" s="9" t="str">
-        <f aca="false">IF(M3="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M3="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U3" s="11" t="str">
@@ -2357,7 +2434,7 @@
         <v/>
       </c>
       <c r="T4" s="9" t="str">
-        <f aca="false">IF(M4="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M4="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U4" s="11" t="str">
@@ -2444,7 +2521,7 @@
         <v/>
       </c>
       <c r="T5" s="9" t="str">
-        <f aca="false">IF(M5="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M5="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U5" s="11" t="str">
@@ -2531,7 +2608,7 @@
         <v/>
       </c>
       <c r="T6" s="9" t="str">
-        <f aca="false">IF(M6="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M6="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U6" s="11" t="str">
@@ -2618,7 +2695,7 @@
         <v/>
       </c>
       <c r="T7" s="9" t="str">
-        <f aca="false">IF(M7="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M7="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U7" s="11" t="str">
@@ -2705,7 +2782,7 @@
         <v/>
       </c>
       <c r="T8" s="9" t="str">
-        <f aca="false">IF(M8="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M8="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U8" s="11" t="str">
@@ -2792,7 +2869,7 @@
         <v/>
       </c>
       <c r="T9" s="9" t="str">
-        <f aca="false">IF(M9="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M9="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U9" s="11" t="str">
@@ -2879,7 +2956,7 @@
         <v/>
       </c>
       <c r="T10" s="9" t="str">
-        <f aca="false">IF(M10="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M10="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U10" s="11" t="str">
@@ -2966,7 +3043,7 @@
         <v/>
       </c>
       <c r="T11" s="9" t="str">
-        <f aca="false">IF(M11="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M11="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U11" s="11" t="str">
@@ -3053,7 +3130,7 @@
         <v/>
       </c>
       <c r="T12" s="9" t="str">
-        <f aca="false">IF(M12="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M12="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U12" s="11" t="str">
@@ -3140,7 +3217,7 @@
         <v/>
       </c>
       <c r="T13" s="9" t="str">
-        <f aca="false">IF(M13="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M13="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U13" s="11" t="str">
@@ -3227,7 +3304,7 @@
         <v/>
       </c>
       <c r="T14" s="9" t="str">
-        <f aca="false">IF(M14="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M14="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U14" s="11" t="str">
@@ -3314,7 +3391,7 @@
         <v/>
       </c>
       <c r="T15" s="9" t="str">
-        <f aca="false">IF(M15="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M15="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U15" s="11" t="str">
@@ -3401,7 +3478,7 @@
         <v/>
       </c>
       <c r="T16" s="9" t="str">
-        <f aca="false">IF(M16="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M16="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U16" s="11" t="str">
@@ -3488,7 +3565,7 @@
         <v/>
       </c>
       <c r="T17" s="9" t="str">
-        <f aca="false">IF(M17="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M17="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U17" s="11" t="str">
@@ -3575,7 +3652,7 @@
         <v/>
       </c>
       <c r="T18" s="9" t="str">
-        <f aca="false">IF(M18="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M18="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U18" s="11" t="str">
@@ -3662,7 +3739,7 @@
         <v/>
       </c>
       <c r="T19" s="9" t="str">
-        <f aca="false">IF(M19="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M19="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U19" s="11" t="str">
@@ -3749,7 +3826,7 @@
         <v/>
       </c>
       <c r="T20" s="9" t="str">
-        <f aca="false">IF(M20="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M20="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U20" s="11" t="str">
@@ -3836,7 +3913,7 @@
         <v/>
       </c>
       <c r="T21" s="9" t="str">
-        <f aca="false">IF(M21="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M21="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U21" s="11" t="str">
@@ -3923,7 +4000,7 @@
         <v/>
       </c>
       <c r="T22" s="9" t="str">
-        <f aca="false">IF(M22="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M22="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U22" s="11" t="str">
@@ -4010,7 +4087,7 @@
         <v/>
       </c>
       <c r="T23" s="9" t="str">
-        <f aca="false">IF(M23="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M23="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U23" s="11" t="str">
@@ -4097,7 +4174,7 @@
         <v/>
       </c>
       <c r="T24" s="9" t="str">
-        <f aca="false">IF(M24="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M24="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U24" s="11" t="str">
@@ -4184,7 +4261,7 @@
         <v/>
       </c>
       <c r="T25" s="9" t="str">
-        <f aca="false">IF(M25="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M25="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U25" s="11" t="str">
@@ -4271,7 +4348,7 @@
         <v/>
       </c>
       <c r="T26" s="9" t="str">
-        <f aca="false">IF(M26="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M26="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U26" s="11" t="str">
@@ -4360,7 +4437,7 @@
         <v/>
       </c>
       <c r="T27" s="9" t="str">
-        <f aca="false">IF(M27="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M27="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U27" s="11" t="str">
@@ -4449,7 +4526,7 @@
         <v/>
       </c>
       <c r="T28" s="9" t="str">
-        <f aca="false">IF(M28="","",Параметры!$B$19)</f>
+        <f aca="false">IF(M28="","",Параметры!$B$20)</f>
         <v/>
       </c>
       <c r="U28" s="11" t="str">
@@ -4514,25 +4591,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R302"/>
+  <dimension ref="A1:V302"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4581,58 +4663,81 @@
       <c r="O1" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>172</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I2" s="15" t="n">
         <v>4</v>
       </c>
       <c r="J2" s="16" t="n">
-        <v>5290</v>
+        <v>4990</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L2" s="15"/>
       <c r="M2" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N2" s="17"/>
       <c r="O2" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="R2" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="P2" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="Q2" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R2" s="18" t="n">
+        <f aca="false">IF(P2="","",P2+IF(N(Q2)&gt;0,MIN(ROUND(Параметры!$B$19/Q2*30,0),365),180)-14)</f>
+        <v>46402</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="V2" s="6" t="n">
         <f aca="false">COUNTA(H3:H302)</f>
         <v>0</v>
       </c>
@@ -4653,12 +4758,19 @@
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
-      <c r="N3" s="17"/>
+      <c r="N3" s="19"/>
       <c r="O3" s="14"/>
-      <c r="Q3" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="R3" s="7" t="n">
+      <c r="P3" s="20"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="21" t="str">
+        <f aca="false">IF(P3="","",P3+IF(N(Q3)&gt;0,MIN(ROUND(Параметры!$B$19/Q3*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S3" s="14"/>
+      <c r="U3" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="V3" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"1. Новый")</f>
         <v>0</v>
       </c>
@@ -4679,12 +4791,19 @@
       <c r="K4" s="14"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="17"/>
+      <c r="N4" s="19"/>
       <c r="O4" s="14"/>
-      <c r="Q4" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="R4" s="7" t="n">
+      <c r="P4" s="20"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="21" t="str">
+        <f aca="false">IF(P4="","",P4+IF(N(Q4)&gt;0,MIN(ROUND(Параметры!$B$19/Q4*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S4" s="14"/>
+      <c r="U4" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="V4" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"2. Ждём VIN")</f>
         <v>0</v>
       </c>
@@ -4705,12 +4824,19 @@
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="17"/>
+      <c r="N5" s="19"/>
       <c r="O5" s="14"/>
-      <c r="Q5" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="R5" s="7" t="n">
+      <c r="P5" s="20"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="21" t="str">
+        <f aca="false">IF(P5="","",P5+IF(N(Q5)&gt;0,MIN(ROUND(Параметры!$B$19/Q5*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S5" s="14"/>
+      <c r="U5" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="V5" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"3. Подбор")</f>
         <v>0</v>
       </c>
@@ -4731,12 +4857,19 @@
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
-      <c r="N6" s="17"/>
+      <c r="N6" s="19"/>
       <c r="O6" s="14"/>
-      <c r="Q6" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="R6" s="7" t="n">
+      <c r="P6" s="20"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="21" t="str">
+        <f aca="false">IF(P6="","",P6+IF(N(Q6)&gt;0,MIN(ROUND(Параметры!$B$19/Q6*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S6" s="14"/>
+      <c r="U6" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="V6" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"4. Предложение")</f>
         <v>0</v>
       </c>
@@ -4757,12 +4890,19 @@
       <c r="K7" s="14"/>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
-      <c r="N7" s="17"/>
+      <c r="N7" s="19"/>
       <c r="O7" s="14"/>
-      <c r="Q7" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="R7" s="7" t="n">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="21" t="str">
+        <f aca="false">IF(P7="","",P7+IF(N(Q7)&gt;0,MIN(ROUND(Параметры!$B$19/Q7*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S7" s="14"/>
+      <c r="U7" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="V7" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"5. Думает")</f>
         <v>0</v>
       </c>
@@ -4783,12 +4923,19 @@
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
-      <c r="N8" s="17"/>
+      <c r="N8" s="19"/>
       <c r="O8" s="14"/>
-      <c r="Q8" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="R8" s="7" t="n">
+      <c r="P8" s="20"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="21" t="str">
+        <f aca="false">IF(P8="","",P8+IF(N(Q8)&gt;0,MIN(ROUND(Параметры!$B$19/Q8*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S8" s="14"/>
+      <c r="U8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="V8" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"6. Ждём оплату")</f>
         <v>0</v>
       </c>
@@ -4809,12 +4956,19 @@
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
-      <c r="N9" s="17"/>
+      <c r="N9" s="19"/>
       <c r="O9" s="14"/>
-      <c r="Q9" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="R9" s="7" t="n">
+      <c r="P9" s="20"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="21" t="str">
+        <f aca="false">IF(P9="","",P9+IF(N(Q9)&gt;0,MIN(ROUND(Параметры!$B$19/Q9*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S9" s="14"/>
+      <c r="U9" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="V9" s="7" t="n">
         <f aca="false">COUNTIF(H3:H302,"7. В обработке")</f>
         <v>0</v>
       </c>
@@ -4835,13 +4989,20 @@
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
-      <c r="N10" s="17"/>
+      <c r="N10" s="19"/>
       <c r="O10" s="14"/>
-      <c r="Q10" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="R10" s="7" t="n">
-        <f aca="false">COUNTIF(H3:H302,"Отказ")</f>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="21" t="str">
+        <f aca="false">IF(P10="","",P10+IF(N(Q10)&gt;0,MIN(ROUND(Параметры!$B$19/Q10*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S10" s="14"/>
+      <c r="U10" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"8. Детали у нас")</f>
         <v>0</v>
       </c>
     </row>
@@ -4861,14 +5022,21 @@
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
-      <c r="N11" s="17"/>
+      <c r="N11" s="19"/>
       <c r="O11" s="14"/>
-      <c r="Q11" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="R11" s="18" t="str">
-        <f aca="false">IF(R2=0,"",COUNTIF(H3:H302,"7. В обработке")/R2)</f>
-        <v/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="21" t="str">
+        <f aca="false">IF(P11="","",P11+IF(N(Q11)&gt;0,MIN(ROUND(Параметры!$B$19/Q11*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S11" s="14"/>
+      <c r="U11" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="V11" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"9. Собран")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4887,14 +5055,21 @@
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
-      <c r="N12" s="17"/>
+      <c r="N12" s="19"/>
       <c r="O12" s="14"/>
-      <c r="Q12" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="R12" s="19" t="str">
-        <f aca="false">IFERROR(AVERAGE(I3:I302),"")</f>
-        <v/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="21" t="str">
+        <f aca="false">IF(P12="","",P12+IF(N(Q12)&gt;0,MIN(ROUND(Параметры!$B$19/Q12*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S12" s="14"/>
+      <c r="U12" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"10. Отправлен")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4913,13 +5088,20 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="14"/>
-      <c r="Q13" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="R13" s="9" t="n">
-        <f aca="false">SUMIF(H3:H302,"7. В обработке",J3:J302)</f>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="21" t="str">
+        <f aca="false">IF(P13="","",P13+IF(N(Q13)&gt;0,MIN(ROUND(Параметры!$B$19/Q13*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S13" s="14"/>
+      <c r="U13" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="V13" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"11. Получен")</f>
         <v>0</v>
       </c>
     </row>
@@ -4939,8 +5121,22 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
-      <c r="N14" s="17"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="14"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="21" t="str">
+        <f aca="false">IF(P14="","",P14+IF(N(Q14)&gt;0,MIN(ROUND(Параметры!$B$19/Q14*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="14"/>
+      <c r="U14" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"12. Закрыт")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
@@ -4958,10 +5154,21 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
-      <c r="N15" s="17"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="14"/>
-      <c r="Q15" s="6" t="s">
-        <v>195</v>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="21" t="str">
+        <f aca="false">IF(P15="","",P15+IF(N(Q15)&gt;0,MIN(ROUND(Параметры!$B$19/Q15*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="14"/>
+      <c r="U15" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="V15" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"Проблема")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4980,13 +5187,20 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="14"/>
-      <c r="N16" s="17"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="14"/>
-      <c r="Q16" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="R16" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"не ответил")</f>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="21" t="str">
+        <f aca="false">IF(P16="","",P16+IF(N(Q16)&gt;0,MIN(ROUND(Параметры!$B$19/Q16*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S16" s="14"/>
+      <c r="U16" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <f aca="false">COUNTIF(H3:H302,"Отказ")</f>
         <v>0</v>
       </c>
     </row>
@@ -5006,13 +5220,20 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="14"/>
-      <c r="Q17" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="R17" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"дорого")</f>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="21" t="str">
+        <f aca="false">IF(P17="","",P17+IF(N(Q17)&gt;0,MIN(ROUND(Параметры!$B$19/Q17*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S17" s="14"/>
+      <c r="U17" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="V17" s="22" t="n">
+        <f aca="false">COUNTIF(H3:H302,"7. В обработке")+COUNTIF(H3:H302,"8. Детали у нас")+COUNTIF(H3:H302,"9. Собран")+COUNTIF(H3:H302,"10. Отправлен")+COUNTIF(H3:H302,"11. Получен")+COUNTIF(H3:H302,"12. Закрыт")+COUNTIF(H3:H302,"Проблема")</f>
         <v>0</v>
       </c>
     </row>
@@ -5032,14 +5253,21 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="19"/>
       <c r="O18" s="14"/>
-      <c r="Q18" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="R18" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"не подошло")</f>
-        <v>0</v>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="21" t="str">
+        <f aca="false">IF(P18="","",P18+IF(N(Q18)&gt;0,MIN(ROUND(Параметры!$B$19/Q18*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S18" s="14"/>
+      <c r="U18" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="V18" s="23" t="str">
+        <f aca="false">IF(V2=0,"",V17/V2)</f>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5058,14 +5286,21 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="17"/>
+      <c r="N19" s="19"/>
       <c r="O19" s="14"/>
-      <c r="Q19" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"нет в наличии")</f>
-        <v>0</v>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="21" t="str">
+        <f aca="false">IF(P19="","",P19+IF(N(Q19)&gt;0,MIN(ROUND(Параметры!$B$19/Q19*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S19" s="14"/>
+      <c r="U19" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="V19" s="24" t="str">
+        <f aca="false">IFERROR(AVERAGE(I3:I302),"")</f>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5084,13 +5319,20 @@
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
-      <c r="N20" s="17"/>
+      <c r="N20" s="19"/>
       <c r="O20" s="14"/>
-      <c r="Q20" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"долго ждать")</f>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="21" t="str">
+        <f aca="false">IF(P20="","",P20+IF(N(Q20)&gt;0,MIN(ROUND(Параметры!$B$19/Q20*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S20" s="14"/>
+      <c r="U20" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="V20" s="9" t="n">
+        <f aca="false">SUMIF(H3:H302,"7. В обработке",J3:J302)+SUMIF(H3:H302,"8. Детали у нас",J3:J302)+SUMIF(H3:H302,"9. Собран",J3:J302)+SUMIF(H3:H302,"10. Отправлен",J3:J302)+SUMIF(H3:H302,"11. Получен",J3:J302)+SUMIF(H3:H302,"12. Закрыт",J3:J302)+SUMIF(H3:H302,"Проблема",J3:J302)</f>
         <v>0</v>
       </c>
     </row>
@@ -5110,13 +5352,20 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
-      <c r="N21" s="17"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="14"/>
-      <c r="Q21" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"купил в другом месте")</f>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="21" t="str">
+        <f aca="false">IF(P21="","",P21+IF(N(Q21)&gt;0,MIN(ROUND(Параметры!$B$19/Q21*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S21" s="14"/>
+      <c r="U21" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="V21" s="24" t="n">
+        <f aca="false">COUNTIF(D3:D302,"повторный")</f>
         <v>0</v>
       </c>
     </row>
@@ -5136,13 +5385,20 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
-      <c r="N22" s="17"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="14"/>
-      <c r="Q22" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="R22" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"мы отказали")</f>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="21" t="str">
+        <f aca="false">IF(P22="","",P22+IF(N(Q22)&gt;0,MIN(ROUND(Параметры!$B$19/Q22*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S22" s="14"/>
+      <c r="U22" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="V22" s="22" t="n">
+        <f aca="true">COUNTIFS(R3:R302,"&gt;="&amp;(TODAY()-14),R3:R302,"&lt;="&amp;(TODAY()+7))</f>
         <v>0</v>
       </c>
     </row>
@@ -5162,15 +5418,15 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
-      <c r="N23" s="17"/>
+      <c r="N23" s="19"/>
       <c r="O23" s="14"/>
-      <c r="Q23" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="R23" s="7" t="n">
-        <f aca="false">COUNTIF(L3:L302,"другое")</f>
-        <v>0</v>
-      </c>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="21" t="str">
+        <f aca="false">IF(P23="","",P23+IF(N(Q23)&gt;0,MIN(ROUND(Параметры!$B$19/Q23*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
@@ -5188,14 +5444,17 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="17"/>
+      <c r="N24" s="19"/>
       <c r="O24" s="14"/>
-      <c r="Q24" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="R24" s="6" t="str">
-        <f aca="false">IF(SUM(R16:R23)=0,"",INDEX(Q16:Q23,MATCH(MAX(R16:R23),R16:R23,0)))</f>
-        <v/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="21" t="str">
+        <f aca="false">IF(P24="","",P24+IF(N(Q24)&gt;0,MIN(ROUND(Параметры!$B$19/Q24*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S24" s="14"/>
+      <c r="U24" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5214,8 +5473,22 @@
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
       <c r="M25" s="14"/>
-      <c r="N25" s="17"/>
+      <c r="N25" s="19"/>
       <c r="O25" s="14"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="21" t="str">
+        <f aca="false">IF(P25="","",P25+IF(N(Q25)&gt;0,MIN(ROUND(Параметры!$B$19/Q25*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S25" s="14"/>
+      <c r="U25" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="V25" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"не ответил")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
@@ -5233,8 +5506,22 @@
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
       <c r="M26" s="14"/>
-      <c r="N26" s="17"/>
+      <c r="N26" s="19"/>
       <c r="O26" s="14"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="21" t="str">
+        <f aca="false">IF(P26="","",P26+IF(N(Q26)&gt;0,MIN(ROUND(Параметры!$B$19/Q26*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S26" s="14"/>
+      <c r="U26" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="V26" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"дорого")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
@@ -5252,8 +5539,22 @@
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
-      <c r="N27" s="17"/>
+      <c r="N27" s="19"/>
       <c r="O27" s="14"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="21" t="str">
+        <f aca="false">IF(P27="","",P27+IF(N(Q27)&gt;0,MIN(ROUND(Параметры!$B$19/Q27*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S27" s="14"/>
+      <c r="U27" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="V27" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"не подошло")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
@@ -5271,8 +5572,22 @@
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
-      <c r="N28" s="17"/>
+      <c r="N28" s="19"/>
       <c r="O28" s="14"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="21" t="str">
+        <f aca="false">IF(P28="","",P28+IF(N(Q28)&gt;0,MIN(ROUND(Параметры!$B$19/Q28*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S28" s="14"/>
+      <c r="U28" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="V28" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"нет в наличии")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
@@ -5290,8 +5605,22 @@
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
-      <c r="N29" s="17"/>
+      <c r="N29" s="19"/>
       <c r="O29" s="14"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="21" t="str">
+        <f aca="false">IF(P29="","",P29+IF(N(Q29)&gt;0,MIN(ROUND(Параметры!$B$19/Q29*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S29" s="14"/>
+      <c r="U29" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="V29" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"долго ждать")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
@@ -5309,8 +5638,22 @@
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
-      <c r="N30" s="17"/>
+      <c r="N30" s="19"/>
       <c r="O30" s="14"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="21" t="str">
+        <f aca="false">IF(P30="","",P30+IF(N(Q30)&gt;0,MIN(ROUND(Параметры!$B$19/Q30*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S30" s="14"/>
+      <c r="U30" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="V30" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"купил в другом месте")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
@@ -5328,8 +5671,22 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
-      <c r="N31" s="17"/>
+      <c r="N31" s="19"/>
       <c r="O31" s="14"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="21" t="str">
+        <f aca="false">IF(P31="","",P31+IF(N(Q31)&gt;0,MIN(ROUND(Параметры!$B$19/Q31*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S31" s="14"/>
+      <c r="U31" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="V31" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"мы отказали")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
@@ -5347,8 +5704,22 @@
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
-      <c r="N32" s="17"/>
+      <c r="N32" s="19"/>
       <c r="O32" s="14"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="21" t="str">
+        <f aca="false">IF(P32="","",P32+IF(N(Q32)&gt;0,MIN(ROUND(Параметры!$B$19/Q32*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S32" s="14"/>
+      <c r="U32" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <f aca="false">COUNTIF(L3:L302,"другое")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
@@ -5366,8 +5737,22 @@
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
-      <c r="N33" s="17"/>
+      <c r="N33" s="19"/>
       <c r="O33" s="14"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="21" t="str">
+        <f aca="false">IF(P33="","",P33+IF(N(Q33)&gt;0,MIN(ROUND(Параметры!$B$19/Q33*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S33" s="14"/>
+      <c r="U33" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="V33" s="6" t="str">
+        <f aca="false">IF(SUM(V25:V32)=0,"",INDEX(U25:U32,MATCH(MAX(V25:V32),V25:V32,0)))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
@@ -5385,8 +5770,15 @@
       <c r="K34" s="14"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
-      <c r="N34" s="17"/>
+      <c r="N34" s="19"/>
       <c r="O34" s="14"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="21" t="str">
+        <f aca="false">IF(P34="","",P34+IF(N(Q34)&gt;0,MIN(ROUND(Параметры!$B$19/Q34*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S34" s="14"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
@@ -5404,8 +5796,15 @@
       <c r="K35" s="14"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
-      <c r="N35" s="17"/>
+      <c r="N35" s="19"/>
       <c r="O35" s="14"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="21" t="str">
+        <f aca="false">IF(P35="","",P35+IF(N(Q35)&gt;0,MIN(ROUND(Параметры!$B$19/Q35*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
@@ -5423,8 +5822,15 @@
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
-      <c r="N36" s="17"/>
+      <c r="N36" s="19"/>
       <c r="O36" s="14"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="21" t="str">
+        <f aca="false">IF(P36="","",P36+IF(N(Q36)&gt;0,MIN(ROUND(Параметры!$B$19/Q36*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
@@ -5442,8 +5848,15 @@
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="14"/>
-      <c r="N37" s="17"/>
+      <c r="N37" s="19"/>
       <c r="O37" s="14"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="21" t="str">
+        <f aca="false">IF(P37="","",P37+IF(N(Q37)&gt;0,MIN(ROUND(Параметры!$B$19/Q37*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
@@ -5461,8 +5874,15 @@
       <c r="K38" s="14"/>
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
-      <c r="N38" s="17"/>
+      <c r="N38" s="19"/>
       <c r="O38" s="14"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="21" t="str">
+        <f aca="false">IF(P38="","",P38+IF(N(Q38)&gt;0,MIN(ROUND(Параметры!$B$19/Q38*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S38" s="14"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
@@ -5480,8 +5900,15 @@
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
       <c r="M39" s="14"/>
-      <c r="N39" s="17"/>
+      <c r="N39" s="19"/>
       <c r="O39" s="14"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="14"/>
+      <c r="R39" s="21" t="str">
+        <f aca="false">IF(P39="","",P39+IF(N(Q39)&gt;0,MIN(ROUND(Параметры!$B$19/Q39*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
@@ -5499,8 +5926,15 @@
       <c r="K40" s="14"/>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
-      <c r="N40" s="17"/>
+      <c r="N40" s="19"/>
       <c r="O40" s="14"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="21" t="str">
+        <f aca="false">IF(P40="","",P40+IF(N(Q40)&gt;0,MIN(ROUND(Параметры!$B$19/Q40*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S40" s="14"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
@@ -5518,8 +5952,15 @@
       <c r="K41" s="14"/>
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
-      <c r="N41" s="17"/>
+      <c r="N41" s="19"/>
       <c r="O41" s="14"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="21" t="str">
+        <f aca="false">IF(P41="","",P41+IF(N(Q41)&gt;0,MIN(ROUND(Параметры!$B$19/Q41*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S41" s="14"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
@@ -5537,8 +5978,15 @@
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
-      <c r="N42" s="17"/>
+      <c r="N42" s="19"/>
       <c r="O42" s="14"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="21" t="str">
+        <f aca="false">IF(P42="","",P42+IF(N(Q42)&gt;0,MIN(ROUND(Параметры!$B$19/Q42*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S42" s="14"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
@@ -5556,8 +6004,15 @@
       <c r="K43" s="14"/>
       <c r="L43" s="14"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="17"/>
+      <c r="N43" s="19"/>
       <c r="O43" s="14"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="21" t="str">
+        <f aca="false">IF(P43="","",P43+IF(N(Q43)&gt;0,MIN(ROUND(Параметры!$B$19/Q43*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S43" s="14"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
@@ -5575,8 +6030,15 @@
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="17"/>
+      <c r="N44" s="19"/>
       <c r="O44" s="14"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="21" t="str">
+        <f aca="false">IF(P44="","",P44+IF(N(Q44)&gt;0,MIN(ROUND(Параметры!$B$19/Q44*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
@@ -5594,8 +6056,15 @@
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="17"/>
+      <c r="N45" s="19"/>
       <c r="O45" s="14"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="14"/>
+      <c r="R45" s="21" t="str">
+        <f aca="false">IF(P45="","",P45+IF(N(Q45)&gt;0,MIN(ROUND(Параметры!$B$19/Q45*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S45" s="14"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
@@ -5613,8 +6082,15 @@
       <c r="K46" s="14"/>
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
-      <c r="N46" s="17"/>
+      <c r="N46" s="19"/>
       <c r="O46" s="14"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="14"/>
+      <c r="R46" s="21" t="str">
+        <f aca="false">IF(P46="","",P46+IF(N(Q46)&gt;0,MIN(ROUND(Параметры!$B$19/Q46*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S46" s="14"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
@@ -5632,8 +6108,15 @@
       <c r="K47" s="14"/>
       <c r="L47" s="14"/>
       <c r="M47" s="14"/>
-      <c r="N47" s="17"/>
+      <c r="N47" s="19"/>
       <c r="O47" s="14"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="21" t="str">
+        <f aca="false">IF(P47="","",P47+IF(N(Q47)&gt;0,MIN(ROUND(Параметры!$B$19/Q47*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S47" s="14"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
@@ -5651,8 +6134,15 @@
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
-      <c r="N48" s="17"/>
+      <c r="N48" s="19"/>
       <c r="O48" s="14"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="14"/>
+      <c r="R48" s="21" t="str">
+        <f aca="false">IF(P48="","",P48+IF(N(Q48)&gt;0,MIN(ROUND(Параметры!$B$19/Q48*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S48" s="14"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
@@ -5670,8 +6160,15 @@
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
-      <c r="N49" s="17"/>
+      <c r="N49" s="19"/>
       <c r="O49" s="14"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="14"/>
+      <c r="R49" s="21" t="str">
+        <f aca="false">IF(P49="","",P49+IF(N(Q49)&gt;0,MIN(ROUND(Параметры!$B$19/Q49*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
@@ -5689,8 +6186,15 @@
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
       <c r="M50" s="14"/>
-      <c r="N50" s="17"/>
+      <c r="N50" s="19"/>
       <c r="O50" s="14"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="14"/>
+      <c r="R50" s="21" t="str">
+        <f aca="false">IF(P50="","",P50+IF(N(Q50)&gt;0,MIN(ROUND(Параметры!$B$19/Q50*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S50" s="14"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
@@ -5708,8 +6212,15 @@
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="17"/>
+      <c r="N51" s="19"/>
       <c r="O51" s="14"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="14"/>
+      <c r="R51" s="21" t="str">
+        <f aca="false">IF(P51="","",P51+IF(N(Q51)&gt;0,MIN(ROUND(Параметры!$B$19/Q51*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S51" s="14"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
@@ -5727,8 +6238,15 @@
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="17"/>
+      <c r="N52" s="19"/>
       <c r="O52" s="14"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="14"/>
+      <c r="R52" s="21" t="str">
+        <f aca="false">IF(P52="","",P52+IF(N(Q52)&gt;0,MIN(ROUND(Параметры!$B$19/Q52*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S52" s="14"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
@@ -5746,8 +6264,15 @@
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
-      <c r="N53" s="17"/>
+      <c r="N53" s="19"/>
       <c r="O53" s="14"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="14"/>
+      <c r="R53" s="21" t="str">
+        <f aca="false">IF(P53="","",P53+IF(N(Q53)&gt;0,MIN(ROUND(Параметры!$B$19/Q53*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S53" s="14"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
@@ -5765,8 +6290,15 @@
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
-      <c r="N54" s="17"/>
+      <c r="N54" s="19"/>
       <c r="O54" s="14"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="14"/>
+      <c r="R54" s="21" t="str">
+        <f aca="false">IF(P54="","",P54+IF(N(Q54)&gt;0,MIN(ROUND(Параметры!$B$19/Q54*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S54" s="14"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
@@ -5784,8 +6316,15 @@
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
-      <c r="N55" s="17"/>
+      <c r="N55" s="19"/>
       <c r="O55" s="14"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="14"/>
+      <c r="R55" s="21" t="str">
+        <f aca="false">IF(P55="","",P55+IF(N(Q55)&gt;0,MIN(ROUND(Параметры!$B$19/Q55*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
@@ -5803,8 +6342,15 @@
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
       <c r="M56" s="14"/>
-      <c r="N56" s="17"/>
+      <c r="N56" s="19"/>
       <c r="O56" s="14"/>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="21" t="str">
+        <f aca="false">IF(P56="","",P56+IF(N(Q56)&gt;0,MIN(ROUND(Параметры!$B$19/Q56*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S56" s="14"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
@@ -5822,8 +6368,15 @@
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
-      <c r="N57" s="17"/>
+      <c r="N57" s="19"/>
       <c r="O57" s="14"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="21" t="str">
+        <f aca="false">IF(P57="","",P57+IF(N(Q57)&gt;0,MIN(ROUND(Параметры!$B$19/Q57*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S57" s="14"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
@@ -5841,8 +6394,15 @@
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
-      <c r="N58" s="17"/>
+      <c r="N58" s="19"/>
       <c r="O58" s="14"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="14"/>
+      <c r="R58" s="21" t="str">
+        <f aca="false">IF(P58="","",P58+IF(N(Q58)&gt;0,MIN(ROUND(Параметры!$B$19/Q58*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S58" s="14"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
@@ -5860,8 +6420,15 @@
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
-      <c r="N59" s="17"/>
+      <c r="N59" s="19"/>
       <c r="O59" s="14"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="21" t="str">
+        <f aca="false">IF(P59="","",P59+IF(N(Q59)&gt;0,MIN(ROUND(Параметры!$B$19/Q59*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S59" s="14"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
@@ -5879,8 +6446,15 @@
       <c r="K60" s="14"/>
       <c r="L60" s="14"/>
       <c r="M60" s="14"/>
-      <c r="N60" s="17"/>
+      <c r="N60" s="19"/>
       <c r="O60" s="14"/>
+      <c r="P60" s="20"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="21" t="str">
+        <f aca="false">IF(P60="","",P60+IF(N(Q60)&gt;0,MIN(ROUND(Параметры!$B$19/Q60*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S60" s="14"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
@@ -5898,8 +6472,15 @@
       <c r="K61" s="14"/>
       <c r="L61" s="14"/>
       <c r="M61" s="14"/>
-      <c r="N61" s="17"/>
+      <c r="N61" s="19"/>
       <c r="O61" s="14"/>
+      <c r="P61" s="20"/>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="21" t="str">
+        <f aca="false">IF(P61="","",P61+IF(N(Q61)&gt;0,MIN(ROUND(Параметры!$B$19/Q61*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S61" s="14"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
@@ -5917,8 +6498,15 @@
       <c r="K62" s="14"/>
       <c r="L62" s="14"/>
       <c r="M62" s="14"/>
-      <c r="N62" s="17"/>
+      <c r="N62" s="19"/>
       <c r="O62" s="14"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="14"/>
+      <c r="R62" s="21" t="str">
+        <f aca="false">IF(P62="","",P62+IF(N(Q62)&gt;0,MIN(ROUND(Параметры!$B$19/Q62*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S62" s="14"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
@@ -5936,8 +6524,15 @@
       <c r="K63" s="14"/>
       <c r="L63" s="14"/>
       <c r="M63" s="14"/>
-      <c r="N63" s="17"/>
+      <c r="N63" s="19"/>
       <c r="O63" s="14"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="21" t="str">
+        <f aca="false">IF(P63="","",P63+IF(N(Q63)&gt;0,MIN(ROUND(Параметры!$B$19/Q63*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S63" s="14"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
@@ -5955,8 +6550,15 @@
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
-      <c r="N64" s="17"/>
+      <c r="N64" s="19"/>
       <c r="O64" s="14"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="14"/>
+      <c r="R64" s="21" t="str">
+        <f aca="false">IF(P64="","",P64+IF(N(Q64)&gt;0,MIN(ROUND(Параметры!$B$19/Q64*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S64" s="14"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
@@ -5974,8 +6576,15 @@
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
       <c r="M65" s="14"/>
-      <c r="N65" s="17"/>
+      <c r="N65" s="19"/>
       <c r="O65" s="14"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="14"/>
+      <c r="R65" s="21" t="str">
+        <f aca="false">IF(P65="","",P65+IF(N(Q65)&gt;0,MIN(ROUND(Параметры!$B$19/Q65*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S65" s="14"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
@@ -5993,8 +6602,15 @@
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
-      <c r="N66" s="17"/>
+      <c r="N66" s="19"/>
       <c r="O66" s="14"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="14"/>
+      <c r="R66" s="21" t="str">
+        <f aca="false">IF(P66="","",P66+IF(N(Q66)&gt;0,MIN(ROUND(Параметры!$B$19/Q66*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S66" s="14"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
@@ -6012,8 +6628,15 @@
       <c r="K67" s="14"/>
       <c r="L67" s="14"/>
       <c r="M67" s="14"/>
-      <c r="N67" s="17"/>
+      <c r="N67" s="19"/>
       <c r="O67" s="14"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="14"/>
+      <c r="R67" s="21" t="str">
+        <f aca="false">IF(P67="","",P67+IF(N(Q67)&gt;0,MIN(ROUND(Параметры!$B$19/Q67*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S67" s="14"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
@@ -6031,8 +6654,15 @@
       <c r="K68" s="14"/>
       <c r="L68" s="14"/>
       <c r="M68" s="14"/>
-      <c r="N68" s="17"/>
+      <c r="N68" s="19"/>
       <c r="O68" s="14"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="14"/>
+      <c r="R68" s="21" t="str">
+        <f aca="false">IF(P68="","",P68+IF(N(Q68)&gt;0,MIN(ROUND(Параметры!$B$19/Q68*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S68" s="14"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
@@ -6050,8 +6680,15 @@
       <c r="K69" s="14"/>
       <c r="L69" s="14"/>
       <c r="M69" s="14"/>
-      <c r="N69" s="17"/>
+      <c r="N69" s="19"/>
       <c r="O69" s="14"/>
+      <c r="P69" s="20"/>
+      <c r="Q69" s="14"/>
+      <c r="R69" s="21" t="str">
+        <f aca="false">IF(P69="","",P69+IF(N(Q69)&gt;0,MIN(ROUND(Параметры!$B$19/Q69*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S69" s="14"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
@@ -6069,8 +6706,15 @@
       <c r="K70" s="14"/>
       <c r="L70" s="14"/>
       <c r="M70" s="14"/>
-      <c r="N70" s="17"/>
+      <c r="N70" s="19"/>
       <c r="O70" s="14"/>
+      <c r="P70" s="20"/>
+      <c r="Q70" s="14"/>
+      <c r="R70" s="21" t="str">
+        <f aca="false">IF(P70="","",P70+IF(N(Q70)&gt;0,MIN(ROUND(Параметры!$B$19/Q70*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S70" s="14"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
@@ -6088,8 +6732,15 @@
       <c r="K71" s="14"/>
       <c r="L71" s="14"/>
       <c r="M71" s="14"/>
-      <c r="N71" s="17"/>
+      <c r="N71" s="19"/>
       <c r="O71" s="14"/>
+      <c r="P71" s="20"/>
+      <c r="Q71" s="14"/>
+      <c r="R71" s="21" t="str">
+        <f aca="false">IF(P71="","",P71+IF(N(Q71)&gt;0,MIN(ROUND(Параметры!$B$19/Q71*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S71" s="14"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
@@ -6107,8 +6758,15 @@
       <c r="K72" s="14"/>
       <c r="L72" s="14"/>
       <c r="M72" s="14"/>
-      <c r="N72" s="17"/>
+      <c r="N72" s="19"/>
       <c r="O72" s="14"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="14"/>
+      <c r="R72" s="21" t="str">
+        <f aca="false">IF(P72="","",P72+IF(N(Q72)&gt;0,MIN(ROUND(Параметры!$B$19/Q72*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S72" s="14"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
@@ -6126,8 +6784,15 @@
       <c r="K73" s="14"/>
       <c r="L73" s="14"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="17"/>
+      <c r="N73" s="19"/>
       <c r="O73" s="14"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="14"/>
+      <c r="R73" s="21" t="str">
+        <f aca="false">IF(P73="","",P73+IF(N(Q73)&gt;0,MIN(ROUND(Параметры!$B$19/Q73*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S73" s="14"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
@@ -6145,8 +6810,15 @@
       <c r="K74" s="14"/>
       <c r="L74" s="14"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="17"/>
+      <c r="N74" s="19"/>
       <c r="O74" s="14"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="14"/>
+      <c r="R74" s="21" t="str">
+        <f aca="false">IF(P74="","",P74+IF(N(Q74)&gt;0,MIN(ROUND(Параметры!$B$19/Q74*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S74" s="14"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
@@ -6164,8 +6836,15 @@
       <c r="K75" s="14"/>
       <c r="L75" s="14"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="17"/>
+      <c r="N75" s="19"/>
       <c r="O75" s="14"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="14"/>
+      <c r="R75" s="21" t="str">
+        <f aca="false">IF(P75="","",P75+IF(N(Q75)&gt;0,MIN(ROUND(Параметры!$B$19/Q75*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S75" s="14"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
@@ -6183,8 +6862,15 @@
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
       <c r="M76" s="14"/>
-      <c r="N76" s="17"/>
+      <c r="N76" s="19"/>
       <c r="O76" s="14"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="14"/>
+      <c r="R76" s="21" t="str">
+        <f aca="false">IF(P76="","",P76+IF(N(Q76)&gt;0,MIN(ROUND(Параметры!$B$19/Q76*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S76" s="14"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
@@ -6202,8 +6888,15 @@
       <c r="K77" s="14"/>
       <c r="L77" s="14"/>
       <c r="M77" s="14"/>
-      <c r="N77" s="17"/>
+      <c r="N77" s="19"/>
       <c r="O77" s="14"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="14"/>
+      <c r="R77" s="21" t="str">
+        <f aca="false">IF(P77="","",P77+IF(N(Q77)&gt;0,MIN(ROUND(Параметры!$B$19/Q77*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S77" s="14"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
@@ -6221,8 +6914,15 @@
       <c r="K78" s="14"/>
       <c r="L78" s="14"/>
       <c r="M78" s="14"/>
-      <c r="N78" s="17"/>
+      <c r="N78" s="19"/>
       <c r="O78" s="14"/>
+      <c r="P78" s="20"/>
+      <c r="Q78" s="14"/>
+      <c r="R78" s="21" t="str">
+        <f aca="false">IF(P78="","",P78+IF(N(Q78)&gt;0,MIN(ROUND(Параметры!$B$19/Q78*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S78" s="14"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
@@ -6240,8 +6940,15 @@
       <c r="K79" s="14"/>
       <c r="L79" s="14"/>
       <c r="M79" s="14"/>
-      <c r="N79" s="17"/>
+      <c r="N79" s="19"/>
       <c r="O79" s="14"/>
+      <c r="P79" s="20"/>
+      <c r="Q79" s="14"/>
+      <c r="R79" s="21" t="str">
+        <f aca="false">IF(P79="","",P79+IF(N(Q79)&gt;0,MIN(ROUND(Параметры!$B$19/Q79*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S79" s="14"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
@@ -6259,8 +6966,15 @@
       <c r="K80" s="14"/>
       <c r="L80" s="14"/>
       <c r="M80" s="14"/>
-      <c r="N80" s="17"/>
+      <c r="N80" s="19"/>
       <c r="O80" s="14"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="14"/>
+      <c r="R80" s="21" t="str">
+        <f aca="false">IF(P80="","",P80+IF(N(Q80)&gt;0,MIN(ROUND(Параметры!$B$19/Q80*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S80" s="14"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
@@ -6278,8 +6992,15 @@
       <c r="K81" s="14"/>
       <c r="L81" s="14"/>
       <c r="M81" s="14"/>
-      <c r="N81" s="17"/>
+      <c r="N81" s="19"/>
       <c r="O81" s="14"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="14"/>
+      <c r="R81" s="21" t="str">
+        <f aca="false">IF(P81="","",P81+IF(N(Q81)&gt;0,MIN(ROUND(Параметры!$B$19/Q81*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S81" s="14"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
@@ -6297,8 +7018,15 @@
       <c r="K82" s="14"/>
       <c r="L82" s="14"/>
       <c r="M82" s="14"/>
-      <c r="N82" s="17"/>
+      <c r="N82" s="19"/>
       <c r="O82" s="14"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="14"/>
+      <c r="R82" s="21" t="str">
+        <f aca="false">IF(P82="","",P82+IF(N(Q82)&gt;0,MIN(ROUND(Параметры!$B$19/Q82*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S82" s="14"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
@@ -6316,8 +7044,15 @@
       <c r="K83" s="14"/>
       <c r="L83" s="14"/>
       <c r="M83" s="14"/>
-      <c r="N83" s="17"/>
+      <c r="N83" s="19"/>
       <c r="O83" s="14"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="14"/>
+      <c r="R83" s="21" t="str">
+        <f aca="false">IF(P83="","",P83+IF(N(Q83)&gt;0,MIN(ROUND(Параметры!$B$19/Q83*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S83" s="14"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
@@ -6335,8 +7070,15 @@
       <c r="K84" s="14"/>
       <c r="L84" s="14"/>
       <c r="M84" s="14"/>
-      <c r="N84" s="17"/>
+      <c r="N84" s="19"/>
       <c r="O84" s="14"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="14"/>
+      <c r="R84" s="21" t="str">
+        <f aca="false">IF(P84="","",P84+IF(N(Q84)&gt;0,MIN(ROUND(Параметры!$B$19/Q84*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S84" s="14"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
@@ -6354,8 +7096,15 @@
       <c r="K85" s="14"/>
       <c r="L85" s="14"/>
       <c r="M85" s="14"/>
-      <c r="N85" s="17"/>
+      <c r="N85" s="19"/>
       <c r="O85" s="14"/>
+      <c r="P85" s="20"/>
+      <c r="Q85" s="14"/>
+      <c r="R85" s="21" t="str">
+        <f aca="false">IF(P85="","",P85+IF(N(Q85)&gt;0,MIN(ROUND(Параметры!$B$19/Q85*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S85" s="14"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
@@ -6373,8 +7122,15 @@
       <c r="K86" s="14"/>
       <c r="L86" s="14"/>
       <c r="M86" s="14"/>
-      <c r="N86" s="17"/>
+      <c r="N86" s="19"/>
       <c r="O86" s="14"/>
+      <c r="P86" s="20"/>
+      <c r="Q86" s="14"/>
+      <c r="R86" s="21" t="str">
+        <f aca="false">IF(P86="","",P86+IF(N(Q86)&gt;0,MIN(ROUND(Параметры!$B$19/Q86*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S86" s="14"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
@@ -6392,8 +7148,15 @@
       <c r="K87" s="14"/>
       <c r="L87" s="14"/>
       <c r="M87" s="14"/>
-      <c r="N87" s="17"/>
+      <c r="N87" s="19"/>
       <c r="O87" s="14"/>
+      <c r="P87" s="20"/>
+      <c r="Q87" s="14"/>
+      <c r="R87" s="21" t="str">
+        <f aca="false">IF(P87="","",P87+IF(N(Q87)&gt;0,MIN(ROUND(Параметры!$B$19/Q87*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S87" s="14"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
@@ -6411,8 +7174,15 @@
       <c r="K88" s="14"/>
       <c r="L88" s="14"/>
       <c r="M88" s="14"/>
-      <c r="N88" s="17"/>
+      <c r="N88" s="19"/>
       <c r="O88" s="14"/>
+      <c r="P88" s="20"/>
+      <c r="Q88" s="14"/>
+      <c r="R88" s="21" t="str">
+        <f aca="false">IF(P88="","",P88+IF(N(Q88)&gt;0,MIN(ROUND(Параметры!$B$19/Q88*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S88" s="14"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
@@ -6430,8 +7200,15 @@
       <c r="K89" s="14"/>
       <c r="L89" s="14"/>
       <c r="M89" s="14"/>
-      <c r="N89" s="17"/>
+      <c r="N89" s="19"/>
       <c r="O89" s="14"/>
+      <c r="P89" s="20"/>
+      <c r="Q89" s="14"/>
+      <c r="R89" s="21" t="str">
+        <f aca="false">IF(P89="","",P89+IF(N(Q89)&gt;0,MIN(ROUND(Параметры!$B$19/Q89*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S89" s="14"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
@@ -6449,8 +7226,15 @@
       <c r="K90" s="14"/>
       <c r="L90" s="14"/>
       <c r="M90" s="14"/>
-      <c r="N90" s="17"/>
+      <c r="N90" s="19"/>
       <c r="O90" s="14"/>
+      <c r="P90" s="20"/>
+      <c r="Q90" s="14"/>
+      <c r="R90" s="21" t="str">
+        <f aca="false">IF(P90="","",P90+IF(N(Q90)&gt;0,MIN(ROUND(Параметры!$B$19/Q90*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S90" s="14"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
@@ -6468,8 +7252,15 @@
       <c r="K91" s="14"/>
       <c r="L91" s="14"/>
       <c r="M91" s="14"/>
-      <c r="N91" s="17"/>
+      <c r="N91" s="19"/>
       <c r="O91" s="14"/>
+      <c r="P91" s="20"/>
+      <c r="Q91" s="14"/>
+      <c r="R91" s="21" t="str">
+        <f aca="false">IF(P91="","",P91+IF(N(Q91)&gt;0,MIN(ROUND(Параметры!$B$19/Q91*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S91" s="14"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
@@ -6487,8 +7278,15 @@
       <c r="K92" s="14"/>
       <c r="L92" s="14"/>
       <c r="M92" s="14"/>
-      <c r="N92" s="17"/>
+      <c r="N92" s="19"/>
       <c r="O92" s="14"/>
+      <c r="P92" s="20"/>
+      <c r="Q92" s="14"/>
+      <c r="R92" s="21" t="str">
+        <f aca="false">IF(P92="","",P92+IF(N(Q92)&gt;0,MIN(ROUND(Параметры!$B$19/Q92*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S92" s="14"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
@@ -6506,8 +7304,15 @@
       <c r="K93" s="14"/>
       <c r="L93" s="14"/>
       <c r="M93" s="14"/>
-      <c r="N93" s="17"/>
+      <c r="N93" s="19"/>
       <c r="O93" s="14"/>
+      <c r="P93" s="20"/>
+      <c r="Q93" s="14"/>
+      <c r="R93" s="21" t="str">
+        <f aca="false">IF(P93="","",P93+IF(N(Q93)&gt;0,MIN(ROUND(Параметры!$B$19/Q93*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S93" s="14"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
@@ -6525,8 +7330,15 @@
       <c r="K94" s="14"/>
       <c r="L94" s="14"/>
       <c r="M94" s="14"/>
-      <c r="N94" s="17"/>
+      <c r="N94" s="19"/>
       <c r="O94" s="14"/>
+      <c r="P94" s="20"/>
+      <c r="Q94" s="14"/>
+      <c r="R94" s="21" t="str">
+        <f aca="false">IF(P94="","",P94+IF(N(Q94)&gt;0,MIN(ROUND(Параметры!$B$19/Q94*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S94" s="14"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
@@ -6544,8 +7356,15 @@
       <c r="K95" s="14"/>
       <c r="L95" s="14"/>
       <c r="M95" s="14"/>
-      <c r="N95" s="17"/>
+      <c r="N95" s="19"/>
       <c r="O95" s="14"/>
+      <c r="P95" s="20"/>
+      <c r="Q95" s="14"/>
+      <c r="R95" s="21" t="str">
+        <f aca="false">IF(P95="","",P95+IF(N(Q95)&gt;0,MIN(ROUND(Параметры!$B$19/Q95*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S95" s="14"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
@@ -6563,8 +7382,15 @@
       <c r="K96" s="14"/>
       <c r="L96" s="14"/>
       <c r="M96" s="14"/>
-      <c r="N96" s="17"/>
+      <c r="N96" s="19"/>
       <c r="O96" s="14"/>
+      <c r="P96" s="20"/>
+      <c r="Q96" s="14"/>
+      <c r="R96" s="21" t="str">
+        <f aca="false">IF(P96="","",P96+IF(N(Q96)&gt;0,MIN(ROUND(Параметры!$B$19/Q96*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S96" s="14"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
@@ -6582,8 +7408,15 @@
       <c r="K97" s="14"/>
       <c r="L97" s="14"/>
       <c r="M97" s="14"/>
-      <c r="N97" s="17"/>
+      <c r="N97" s="19"/>
       <c r="O97" s="14"/>
+      <c r="P97" s="20"/>
+      <c r="Q97" s="14"/>
+      <c r="R97" s="21" t="str">
+        <f aca="false">IF(P97="","",P97+IF(N(Q97)&gt;0,MIN(ROUND(Параметры!$B$19/Q97*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S97" s="14"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
@@ -6601,8 +7434,15 @@
       <c r="K98" s="14"/>
       <c r="L98" s="14"/>
       <c r="M98" s="14"/>
-      <c r="N98" s="17"/>
+      <c r="N98" s="19"/>
       <c r="O98" s="14"/>
+      <c r="P98" s="20"/>
+      <c r="Q98" s="14"/>
+      <c r="R98" s="21" t="str">
+        <f aca="false">IF(P98="","",P98+IF(N(Q98)&gt;0,MIN(ROUND(Параметры!$B$19/Q98*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S98" s="14"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
@@ -6620,8 +7460,15 @@
       <c r="K99" s="14"/>
       <c r="L99" s="14"/>
       <c r="M99" s="14"/>
-      <c r="N99" s="17"/>
+      <c r="N99" s="19"/>
       <c r="O99" s="14"/>
+      <c r="P99" s="20"/>
+      <c r="Q99" s="14"/>
+      <c r="R99" s="21" t="str">
+        <f aca="false">IF(P99="","",P99+IF(N(Q99)&gt;0,MIN(ROUND(Параметры!$B$19/Q99*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S99" s="14"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
@@ -6639,8 +7486,15 @@
       <c r="K100" s="14"/>
       <c r="L100" s="14"/>
       <c r="M100" s="14"/>
-      <c r="N100" s="17"/>
+      <c r="N100" s="19"/>
       <c r="O100" s="14"/>
+      <c r="P100" s="20"/>
+      <c r="Q100" s="14"/>
+      <c r="R100" s="21" t="str">
+        <f aca="false">IF(P100="","",P100+IF(N(Q100)&gt;0,MIN(ROUND(Параметры!$B$19/Q100*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S100" s="14"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
@@ -6658,8 +7512,15 @@
       <c r="K101" s="14"/>
       <c r="L101" s="14"/>
       <c r="M101" s="14"/>
-      <c r="N101" s="17"/>
+      <c r="N101" s="19"/>
       <c r="O101" s="14"/>
+      <c r="P101" s="20"/>
+      <c r="Q101" s="14"/>
+      <c r="R101" s="21" t="str">
+        <f aca="false">IF(P101="","",P101+IF(N(Q101)&gt;0,MIN(ROUND(Параметры!$B$19/Q101*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S101" s="14"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
@@ -6677,8 +7538,15 @@
       <c r="K102" s="14"/>
       <c r="L102" s="14"/>
       <c r="M102" s="14"/>
-      <c r="N102" s="17"/>
+      <c r="N102" s="19"/>
       <c r="O102" s="14"/>
+      <c r="P102" s="20"/>
+      <c r="Q102" s="14"/>
+      <c r="R102" s="21" t="str">
+        <f aca="false">IF(P102="","",P102+IF(N(Q102)&gt;0,MIN(ROUND(Параметры!$B$19/Q102*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S102" s="14"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
@@ -6696,8 +7564,15 @@
       <c r="K103" s="14"/>
       <c r="L103" s="14"/>
       <c r="M103" s="14"/>
-      <c r="N103" s="17"/>
+      <c r="N103" s="19"/>
       <c r="O103" s="14"/>
+      <c r="P103" s="20"/>
+      <c r="Q103" s="14"/>
+      <c r="R103" s="21" t="str">
+        <f aca="false">IF(P103="","",P103+IF(N(Q103)&gt;0,MIN(ROUND(Параметры!$B$19/Q103*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S103" s="14"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
@@ -6715,8 +7590,15 @@
       <c r="K104" s="14"/>
       <c r="L104" s="14"/>
       <c r="M104" s="14"/>
-      <c r="N104" s="17"/>
+      <c r="N104" s="19"/>
       <c r="O104" s="14"/>
+      <c r="P104" s="20"/>
+      <c r="Q104" s="14"/>
+      <c r="R104" s="21" t="str">
+        <f aca="false">IF(P104="","",P104+IF(N(Q104)&gt;0,MIN(ROUND(Параметры!$B$19/Q104*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S104" s="14"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="n">
@@ -6734,8 +7616,15 @@
       <c r="K105" s="14"/>
       <c r="L105" s="14"/>
       <c r="M105" s="14"/>
-      <c r="N105" s="17"/>
+      <c r="N105" s="19"/>
       <c r="O105" s="14"/>
+      <c r="P105" s="20"/>
+      <c r="Q105" s="14"/>
+      <c r="R105" s="21" t="str">
+        <f aca="false">IF(P105="","",P105+IF(N(Q105)&gt;0,MIN(ROUND(Параметры!$B$19/Q105*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S105" s="14"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="n">
@@ -6753,8 +7642,15 @@
       <c r="K106" s="14"/>
       <c r="L106" s="14"/>
       <c r="M106" s="14"/>
-      <c r="N106" s="17"/>
+      <c r="N106" s="19"/>
       <c r="O106" s="14"/>
+      <c r="P106" s="20"/>
+      <c r="Q106" s="14"/>
+      <c r="R106" s="21" t="str">
+        <f aca="false">IF(P106="","",P106+IF(N(Q106)&gt;0,MIN(ROUND(Параметры!$B$19/Q106*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S106" s="14"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="n">
@@ -6772,8 +7668,15 @@
       <c r="K107" s="14"/>
       <c r="L107" s="14"/>
       <c r="M107" s="14"/>
-      <c r="N107" s="17"/>
+      <c r="N107" s="19"/>
       <c r="O107" s="14"/>
+      <c r="P107" s="20"/>
+      <c r="Q107" s="14"/>
+      <c r="R107" s="21" t="str">
+        <f aca="false">IF(P107="","",P107+IF(N(Q107)&gt;0,MIN(ROUND(Параметры!$B$19/Q107*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S107" s="14"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="n">
@@ -6791,8 +7694,15 @@
       <c r="K108" s="14"/>
       <c r="L108" s="14"/>
       <c r="M108" s="14"/>
-      <c r="N108" s="17"/>
+      <c r="N108" s="19"/>
       <c r="O108" s="14"/>
+      <c r="P108" s="20"/>
+      <c r="Q108" s="14"/>
+      <c r="R108" s="21" t="str">
+        <f aca="false">IF(P108="","",P108+IF(N(Q108)&gt;0,MIN(ROUND(Параметры!$B$19/Q108*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S108" s="14"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="n">
@@ -6810,8 +7720,15 @@
       <c r="K109" s="14"/>
       <c r="L109" s="14"/>
       <c r="M109" s="14"/>
-      <c r="N109" s="17"/>
+      <c r="N109" s="19"/>
       <c r="O109" s="14"/>
+      <c r="P109" s="20"/>
+      <c r="Q109" s="14"/>
+      <c r="R109" s="21" t="str">
+        <f aca="false">IF(P109="","",P109+IF(N(Q109)&gt;0,MIN(ROUND(Параметры!$B$19/Q109*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S109" s="14"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="n">
@@ -6829,8 +7746,15 @@
       <c r="K110" s="14"/>
       <c r="L110" s="14"/>
       <c r="M110" s="14"/>
-      <c r="N110" s="17"/>
+      <c r="N110" s="19"/>
       <c r="O110" s="14"/>
+      <c r="P110" s="20"/>
+      <c r="Q110" s="14"/>
+      <c r="R110" s="21" t="str">
+        <f aca="false">IF(P110="","",P110+IF(N(Q110)&gt;0,MIN(ROUND(Параметры!$B$19/Q110*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S110" s="14"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="n">
@@ -6848,8 +7772,15 @@
       <c r="K111" s="14"/>
       <c r="L111" s="14"/>
       <c r="M111" s="14"/>
-      <c r="N111" s="17"/>
+      <c r="N111" s="19"/>
       <c r="O111" s="14"/>
+      <c r="P111" s="20"/>
+      <c r="Q111" s="14"/>
+      <c r="R111" s="21" t="str">
+        <f aca="false">IF(P111="","",P111+IF(N(Q111)&gt;0,MIN(ROUND(Параметры!$B$19/Q111*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S111" s="14"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="n">
@@ -6867,8 +7798,15 @@
       <c r="K112" s="14"/>
       <c r="L112" s="14"/>
       <c r="M112" s="14"/>
-      <c r="N112" s="17"/>
+      <c r="N112" s="19"/>
       <c r="O112" s="14"/>
+      <c r="P112" s="20"/>
+      <c r="Q112" s="14"/>
+      <c r="R112" s="21" t="str">
+        <f aca="false">IF(P112="","",P112+IF(N(Q112)&gt;0,MIN(ROUND(Параметры!$B$19/Q112*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S112" s="14"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="n">
@@ -6886,8 +7824,15 @@
       <c r="K113" s="14"/>
       <c r="L113" s="14"/>
       <c r="M113" s="14"/>
-      <c r="N113" s="17"/>
+      <c r="N113" s="19"/>
       <c r="O113" s="14"/>
+      <c r="P113" s="20"/>
+      <c r="Q113" s="14"/>
+      <c r="R113" s="21" t="str">
+        <f aca="false">IF(P113="","",P113+IF(N(Q113)&gt;0,MIN(ROUND(Параметры!$B$19/Q113*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S113" s="14"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="n">
@@ -6905,8 +7850,15 @@
       <c r="K114" s="14"/>
       <c r="L114" s="14"/>
       <c r="M114" s="14"/>
-      <c r="N114" s="17"/>
+      <c r="N114" s="19"/>
       <c r="O114" s="14"/>
+      <c r="P114" s="20"/>
+      <c r="Q114" s="14"/>
+      <c r="R114" s="21" t="str">
+        <f aca="false">IF(P114="","",P114+IF(N(Q114)&gt;0,MIN(ROUND(Параметры!$B$19/Q114*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S114" s="14"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="n">
@@ -6924,8 +7876,15 @@
       <c r="K115" s="14"/>
       <c r="L115" s="14"/>
       <c r="M115" s="14"/>
-      <c r="N115" s="17"/>
+      <c r="N115" s="19"/>
       <c r="O115" s="14"/>
+      <c r="P115" s="20"/>
+      <c r="Q115" s="14"/>
+      <c r="R115" s="21" t="str">
+        <f aca="false">IF(P115="","",P115+IF(N(Q115)&gt;0,MIN(ROUND(Параметры!$B$19/Q115*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S115" s="14"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="n">
@@ -6943,8 +7902,15 @@
       <c r="K116" s="14"/>
       <c r="L116" s="14"/>
       <c r="M116" s="14"/>
-      <c r="N116" s="17"/>
+      <c r="N116" s="19"/>
       <c r="O116" s="14"/>
+      <c r="P116" s="20"/>
+      <c r="Q116" s="14"/>
+      <c r="R116" s="21" t="str">
+        <f aca="false">IF(P116="","",P116+IF(N(Q116)&gt;0,MIN(ROUND(Параметры!$B$19/Q116*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S116" s="14"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="n">
@@ -6962,8 +7928,15 @@
       <c r="K117" s="14"/>
       <c r="L117" s="14"/>
       <c r="M117" s="14"/>
-      <c r="N117" s="17"/>
+      <c r="N117" s="19"/>
       <c r="O117" s="14"/>
+      <c r="P117" s="20"/>
+      <c r="Q117" s="14"/>
+      <c r="R117" s="21" t="str">
+        <f aca="false">IF(P117="","",P117+IF(N(Q117)&gt;0,MIN(ROUND(Параметры!$B$19/Q117*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S117" s="14"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="n">
@@ -6981,8 +7954,15 @@
       <c r="K118" s="14"/>
       <c r="L118" s="14"/>
       <c r="M118" s="14"/>
-      <c r="N118" s="17"/>
+      <c r="N118" s="19"/>
       <c r="O118" s="14"/>
+      <c r="P118" s="20"/>
+      <c r="Q118" s="14"/>
+      <c r="R118" s="21" t="str">
+        <f aca="false">IF(P118="","",P118+IF(N(Q118)&gt;0,MIN(ROUND(Параметры!$B$19/Q118*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S118" s="14"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="n">
@@ -7000,8 +7980,15 @@
       <c r="K119" s="14"/>
       <c r="L119" s="14"/>
       <c r="M119" s="14"/>
-      <c r="N119" s="17"/>
+      <c r="N119" s="19"/>
       <c r="O119" s="14"/>
+      <c r="P119" s="20"/>
+      <c r="Q119" s="14"/>
+      <c r="R119" s="21" t="str">
+        <f aca="false">IF(P119="","",P119+IF(N(Q119)&gt;0,MIN(ROUND(Параметры!$B$19/Q119*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S119" s="14"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="n">
@@ -7019,8 +8006,15 @@
       <c r="K120" s="14"/>
       <c r="L120" s="14"/>
       <c r="M120" s="14"/>
-      <c r="N120" s="17"/>
+      <c r="N120" s="19"/>
       <c r="O120" s="14"/>
+      <c r="P120" s="20"/>
+      <c r="Q120" s="14"/>
+      <c r="R120" s="21" t="str">
+        <f aca="false">IF(P120="","",P120+IF(N(Q120)&gt;0,MIN(ROUND(Параметры!$B$19/Q120*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S120" s="14"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="n">
@@ -7038,8 +8032,15 @@
       <c r="K121" s="14"/>
       <c r="L121" s="14"/>
       <c r="M121" s="14"/>
-      <c r="N121" s="17"/>
+      <c r="N121" s="19"/>
       <c r="O121" s="14"/>
+      <c r="P121" s="20"/>
+      <c r="Q121" s="14"/>
+      <c r="R121" s="21" t="str">
+        <f aca="false">IF(P121="","",P121+IF(N(Q121)&gt;0,MIN(ROUND(Параметры!$B$19/Q121*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S121" s="14"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="n">
@@ -7057,8 +8058,15 @@
       <c r="K122" s="14"/>
       <c r="L122" s="14"/>
       <c r="M122" s="14"/>
-      <c r="N122" s="17"/>
+      <c r="N122" s="19"/>
       <c r="O122" s="14"/>
+      <c r="P122" s="20"/>
+      <c r="Q122" s="14"/>
+      <c r="R122" s="21" t="str">
+        <f aca="false">IF(P122="","",P122+IF(N(Q122)&gt;0,MIN(ROUND(Параметры!$B$19/Q122*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S122" s="14"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="n">
@@ -7076,8 +8084,15 @@
       <c r="K123" s="14"/>
       <c r="L123" s="14"/>
       <c r="M123" s="14"/>
-      <c r="N123" s="17"/>
+      <c r="N123" s="19"/>
       <c r="O123" s="14"/>
+      <c r="P123" s="20"/>
+      <c r="Q123" s="14"/>
+      <c r="R123" s="21" t="str">
+        <f aca="false">IF(P123="","",P123+IF(N(Q123)&gt;0,MIN(ROUND(Параметры!$B$19/Q123*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S123" s="14"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="n">
@@ -7095,8 +8110,15 @@
       <c r="K124" s="14"/>
       <c r="L124" s="14"/>
       <c r="M124" s="14"/>
-      <c r="N124" s="17"/>
+      <c r="N124" s="19"/>
       <c r="O124" s="14"/>
+      <c r="P124" s="20"/>
+      <c r="Q124" s="14"/>
+      <c r="R124" s="21" t="str">
+        <f aca="false">IF(P124="","",P124+IF(N(Q124)&gt;0,MIN(ROUND(Параметры!$B$19/Q124*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S124" s="14"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="n">
@@ -7114,8 +8136,15 @@
       <c r="K125" s="14"/>
       <c r="L125" s="14"/>
       <c r="M125" s="14"/>
-      <c r="N125" s="17"/>
+      <c r="N125" s="19"/>
       <c r="O125" s="14"/>
+      <c r="P125" s="20"/>
+      <c r="Q125" s="14"/>
+      <c r="R125" s="21" t="str">
+        <f aca="false">IF(P125="","",P125+IF(N(Q125)&gt;0,MIN(ROUND(Параметры!$B$19/Q125*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S125" s="14"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="n">
@@ -7133,8 +8162,15 @@
       <c r="K126" s="14"/>
       <c r="L126" s="14"/>
       <c r="M126" s="14"/>
-      <c r="N126" s="17"/>
+      <c r="N126" s="19"/>
       <c r="O126" s="14"/>
+      <c r="P126" s="20"/>
+      <c r="Q126" s="14"/>
+      <c r="R126" s="21" t="str">
+        <f aca="false">IF(P126="","",P126+IF(N(Q126)&gt;0,MIN(ROUND(Параметры!$B$19/Q126*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S126" s="14"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="n">
@@ -7152,8 +8188,15 @@
       <c r="K127" s="14"/>
       <c r="L127" s="14"/>
       <c r="M127" s="14"/>
-      <c r="N127" s="17"/>
+      <c r="N127" s="19"/>
       <c r="O127" s="14"/>
+      <c r="P127" s="20"/>
+      <c r="Q127" s="14"/>
+      <c r="R127" s="21" t="str">
+        <f aca="false">IF(P127="","",P127+IF(N(Q127)&gt;0,MIN(ROUND(Параметры!$B$19/Q127*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S127" s="14"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="n">
@@ -7171,8 +8214,15 @@
       <c r="K128" s="14"/>
       <c r="L128" s="14"/>
       <c r="M128" s="14"/>
-      <c r="N128" s="17"/>
+      <c r="N128" s="19"/>
       <c r="O128" s="14"/>
+      <c r="P128" s="20"/>
+      <c r="Q128" s="14"/>
+      <c r="R128" s="21" t="str">
+        <f aca="false">IF(P128="","",P128+IF(N(Q128)&gt;0,MIN(ROUND(Параметры!$B$19/Q128*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S128" s="14"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="n">
@@ -7190,8 +8240,15 @@
       <c r="K129" s="14"/>
       <c r="L129" s="14"/>
       <c r="M129" s="14"/>
-      <c r="N129" s="17"/>
+      <c r="N129" s="19"/>
       <c r="O129" s="14"/>
+      <c r="P129" s="20"/>
+      <c r="Q129" s="14"/>
+      <c r="R129" s="21" t="str">
+        <f aca="false">IF(P129="","",P129+IF(N(Q129)&gt;0,MIN(ROUND(Параметры!$B$19/Q129*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S129" s="14"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="n">
@@ -7209,8 +8266,15 @@
       <c r="K130" s="14"/>
       <c r="L130" s="14"/>
       <c r="M130" s="14"/>
-      <c r="N130" s="17"/>
+      <c r="N130" s="19"/>
       <c r="O130" s="14"/>
+      <c r="P130" s="20"/>
+      <c r="Q130" s="14"/>
+      <c r="R130" s="21" t="str">
+        <f aca="false">IF(P130="","",P130+IF(N(Q130)&gt;0,MIN(ROUND(Параметры!$B$19/Q130*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S130" s="14"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="n">
@@ -7228,8 +8292,15 @@
       <c r="K131" s="14"/>
       <c r="L131" s="14"/>
       <c r="M131" s="14"/>
-      <c r="N131" s="17"/>
+      <c r="N131" s="19"/>
       <c r="O131" s="14"/>
+      <c r="P131" s="20"/>
+      <c r="Q131" s="14"/>
+      <c r="R131" s="21" t="str">
+        <f aca="false">IF(P131="","",P131+IF(N(Q131)&gt;0,MIN(ROUND(Параметры!$B$19/Q131*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S131" s="14"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="n">
@@ -7247,8 +8318,15 @@
       <c r="K132" s="14"/>
       <c r="L132" s="14"/>
       <c r="M132" s="14"/>
-      <c r="N132" s="17"/>
+      <c r="N132" s="19"/>
       <c r="O132" s="14"/>
+      <c r="P132" s="20"/>
+      <c r="Q132" s="14"/>
+      <c r="R132" s="21" t="str">
+        <f aca="false">IF(P132="","",P132+IF(N(Q132)&gt;0,MIN(ROUND(Параметры!$B$19/Q132*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S132" s="14"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="n">
@@ -7266,8 +8344,15 @@
       <c r="K133" s="14"/>
       <c r="L133" s="14"/>
       <c r="M133" s="14"/>
-      <c r="N133" s="17"/>
+      <c r="N133" s="19"/>
       <c r="O133" s="14"/>
+      <c r="P133" s="20"/>
+      <c r="Q133" s="14"/>
+      <c r="R133" s="21" t="str">
+        <f aca="false">IF(P133="","",P133+IF(N(Q133)&gt;0,MIN(ROUND(Параметры!$B$19/Q133*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S133" s="14"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="n">
@@ -7285,8 +8370,15 @@
       <c r="K134" s="14"/>
       <c r="L134" s="14"/>
       <c r="M134" s="14"/>
-      <c r="N134" s="17"/>
+      <c r="N134" s="19"/>
       <c r="O134" s="14"/>
+      <c r="P134" s="20"/>
+      <c r="Q134" s="14"/>
+      <c r="R134" s="21" t="str">
+        <f aca="false">IF(P134="","",P134+IF(N(Q134)&gt;0,MIN(ROUND(Параметры!$B$19/Q134*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S134" s="14"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="n">
@@ -7304,8 +8396,15 @@
       <c r="K135" s="14"/>
       <c r="L135" s="14"/>
       <c r="M135" s="14"/>
-      <c r="N135" s="17"/>
+      <c r="N135" s="19"/>
       <c r="O135" s="14"/>
+      <c r="P135" s="20"/>
+      <c r="Q135" s="14"/>
+      <c r="R135" s="21" t="str">
+        <f aca="false">IF(P135="","",P135+IF(N(Q135)&gt;0,MIN(ROUND(Параметры!$B$19/Q135*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S135" s="14"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="n">
@@ -7323,8 +8422,15 @@
       <c r="K136" s="14"/>
       <c r="L136" s="14"/>
       <c r="M136" s="14"/>
-      <c r="N136" s="17"/>
+      <c r="N136" s="19"/>
       <c r="O136" s="14"/>
+      <c r="P136" s="20"/>
+      <c r="Q136" s="14"/>
+      <c r="R136" s="21" t="str">
+        <f aca="false">IF(P136="","",P136+IF(N(Q136)&gt;0,MIN(ROUND(Параметры!$B$19/Q136*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S136" s="14"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="n">
@@ -7342,8 +8448,15 @@
       <c r="K137" s="14"/>
       <c r="L137" s="14"/>
       <c r="M137" s="14"/>
-      <c r="N137" s="17"/>
+      <c r="N137" s="19"/>
       <c r="O137" s="14"/>
+      <c r="P137" s="20"/>
+      <c r="Q137" s="14"/>
+      <c r="R137" s="21" t="str">
+        <f aca="false">IF(P137="","",P137+IF(N(Q137)&gt;0,MIN(ROUND(Параметры!$B$19/Q137*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S137" s="14"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="n">
@@ -7361,8 +8474,15 @@
       <c r="K138" s="14"/>
       <c r="L138" s="14"/>
       <c r="M138" s="14"/>
-      <c r="N138" s="17"/>
+      <c r="N138" s="19"/>
       <c r="O138" s="14"/>
+      <c r="P138" s="20"/>
+      <c r="Q138" s="14"/>
+      <c r="R138" s="21" t="str">
+        <f aca="false">IF(P138="","",P138+IF(N(Q138)&gt;0,MIN(ROUND(Параметры!$B$19/Q138*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S138" s="14"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="n">
@@ -7380,8 +8500,15 @@
       <c r="K139" s="14"/>
       <c r="L139" s="14"/>
       <c r="M139" s="14"/>
-      <c r="N139" s="17"/>
+      <c r="N139" s="19"/>
       <c r="O139" s="14"/>
+      <c r="P139" s="20"/>
+      <c r="Q139" s="14"/>
+      <c r="R139" s="21" t="str">
+        <f aca="false">IF(P139="","",P139+IF(N(Q139)&gt;0,MIN(ROUND(Параметры!$B$19/Q139*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S139" s="14"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="n">
@@ -7399,8 +8526,15 @@
       <c r="K140" s="14"/>
       <c r="L140" s="14"/>
       <c r="M140" s="14"/>
-      <c r="N140" s="17"/>
+      <c r="N140" s="19"/>
       <c r="O140" s="14"/>
+      <c r="P140" s="20"/>
+      <c r="Q140" s="14"/>
+      <c r="R140" s="21" t="str">
+        <f aca="false">IF(P140="","",P140+IF(N(Q140)&gt;0,MIN(ROUND(Параметры!$B$19/Q140*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S140" s="14"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="n">
@@ -7418,8 +8552,15 @@
       <c r="K141" s="14"/>
       <c r="L141" s="14"/>
       <c r="M141" s="14"/>
-      <c r="N141" s="17"/>
+      <c r="N141" s="19"/>
       <c r="O141" s="14"/>
+      <c r="P141" s="20"/>
+      <c r="Q141" s="14"/>
+      <c r="R141" s="21" t="str">
+        <f aca="false">IF(P141="","",P141+IF(N(Q141)&gt;0,MIN(ROUND(Параметры!$B$19/Q141*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S141" s="14"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="n">
@@ -7437,8 +8578,15 @@
       <c r="K142" s="14"/>
       <c r="L142" s="14"/>
       <c r="M142" s="14"/>
-      <c r="N142" s="17"/>
+      <c r="N142" s="19"/>
       <c r="O142" s="14"/>
+      <c r="P142" s="20"/>
+      <c r="Q142" s="14"/>
+      <c r="R142" s="21" t="str">
+        <f aca="false">IF(P142="","",P142+IF(N(Q142)&gt;0,MIN(ROUND(Параметры!$B$19/Q142*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S142" s="14"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="n">
@@ -7456,8 +8604,15 @@
       <c r="K143" s="14"/>
       <c r="L143" s="14"/>
       <c r="M143" s="14"/>
-      <c r="N143" s="17"/>
+      <c r="N143" s="19"/>
       <c r="O143" s="14"/>
+      <c r="P143" s="20"/>
+      <c r="Q143" s="14"/>
+      <c r="R143" s="21" t="str">
+        <f aca="false">IF(P143="","",P143+IF(N(Q143)&gt;0,MIN(ROUND(Параметры!$B$19/Q143*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S143" s="14"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="n">
@@ -7475,8 +8630,15 @@
       <c r="K144" s="14"/>
       <c r="L144" s="14"/>
       <c r="M144" s="14"/>
-      <c r="N144" s="17"/>
+      <c r="N144" s="19"/>
       <c r="O144" s="14"/>
+      <c r="P144" s="20"/>
+      <c r="Q144" s="14"/>
+      <c r="R144" s="21" t="str">
+        <f aca="false">IF(P144="","",P144+IF(N(Q144)&gt;0,MIN(ROUND(Параметры!$B$19/Q144*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S144" s="14"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="n">
@@ -7494,8 +8656,15 @@
       <c r="K145" s="14"/>
       <c r="L145" s="14"/>
       <c r="M145" s="14"/>
-      <c r="N145" s="17"/>
+      <c r="N145" s="19"/>
       <c r="O145" s="14"/>
+      <c r="P145" s="20"/>
+      <c r="Q145" s="14"/>
+      <c r="R145" s="21" t="str">
+        <f aca="false">IF(P145="","",P145+IF(N(Q145)&gt;0,MIN(ROUND(Параметры!$B$19/Q145*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S145" s="14"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="n">
@@ -7513,8 +8682,15 @@
       <c r="K146" s="14"/>
       <c r="L146" s="14"/>
       <c r="M146" s="14"/>
-      <c r="N146" s="17"/>
+      <c r="N146" s="19"/>
       <c r="O146" s="14"/>
+      <c r="P146" s="20"/>
+      <c r="Q146" s="14"/>
+      <c r="R146" s="21" t="str">
+        <f aca="false">IF(P146="","",P146+IF(N(Q146)&gt;0,MIN(ROUND(Параметры!$B$19/Q146*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S146" s="14"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="n">
@@ -7532,8 +8708,15 @@
       <c r="K147" s="14"/>
       <c r="L147" s="14"/>
       <c r="M147" s="14"/>
-      <c r="N147" s="17"/>
+      <c r="N147" s="19"/>
       <c r="O147" s="14"/>
+      <c r="P147" s="20"/>
+      <c r="Q147" s="14"/>
+      <c r="R147" s="21" t="str">
+        <f aca="false">IF(P147="","",P147+IF(N(Q147)&gt;0,MIN(ROUND(Параметры!$B$19/Q147*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S147" s="14"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="n">
@@ -7551,8 +8734,15 @@
       <c r="K148" s="14"/>
       <c r="L148" s="14"/>
       <c r="M148" s="14"/>
-      <c r="N148" s="17"/>
+      <c r="N148" s="19"/>
       <c r="O148" s="14"/>
+      <c r="P148" s="20"/>
+      <c r="Q148" s="14"/>
+      <c r="R148" s="21" t="str">
+        <f aca="false">IF(P148="","",P148+IF(N(Q148)&gt;0,MIN(ROUND(Параметры!$B$19/Q148*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S148" s="14"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="n">
@@ -7570,8 +8760,15 @@
       <c r="K149" s="14"/>
       <c r="L149" s="14"/>
       <c r="M149" s="14"/>
-      <c r="N149" s="17"/>
+      <c r="N149" s="19"/>
       <c r="O149" s="14"/>
+      <c r="P149" s="20"/>
+      <c r="Q149" s="14"/>
+      <c r="R149" s="21" t="str">
+        <f aca="false">IF(P149="","",P149+IF(N(Q149)&gt;0,MIN(ROUND(Параметры!$B$19/Q149*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S149" s="14"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="n">
@@ -7589,8 +8786,15 @@
       <c r="K150" s="14"/>
       <c r="L150" s="14"/>
       <c r="M150" s="14"/>
-      <c r="N150" s="17"/>
+      <c r="N150" s="19"/>
       <c r="O150" s="14"/>
+      <c r="P150" s="20"/>
+      <c r="Q150" s="14"/>
+      <c r="R150" s="21" t="str">
+        <f aca="false">IF(P150="","",P150+IF(N(Q150)&gt;0,MIN(ROUND(Параметры!$B$19/Q150*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S150" s="14"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="n">
@@ -7608,8 +8812,15 @@
       <c r="K151" s="14"/>
       <c r="L151" s="14"/>
       <c r="M151" s="14"/>
-      <c r="N151" s="17"/>
+      <c r="N151" s="19"/>
       <c r="O151" s="14"/>
+      <c r="P151" s="20"/>
+      <c r="Q151" s="14"/>
+      <c r="R151" s="21" t="str">
+        <f aca="false">IF(P151="","",P151+IF(N(Q151)&gt;0,MIN(ROUND(Параметры!$B$19/Q151*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S151" s="14"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="n">
@@ -7627,8 +8838,15 @@
       <c r="K152" s="14"/>
       <c r="L152" s="14"/>
       <c r="M152" s="14"/>
-      <c r="N152" s="17"/>
+      <c r="N152" s="19"/>
       <c r="O152" s="14"/>
+      <c r="P152" s="20"/>
+      <c r="Q152" s="14"/>
+      <c r="R152" s="21" t="str">
+        <f aca="false">IF(P152="","",P152+IF(N(Q152)&gt;0,MIN(ROUND(Параметры!$B$19/Q152*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S152" s="14"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="n">
@@ -7646,8 +8864,15 @@
       <c r="K153" s="14"/>
       <c r="L153" s="14"/>
       <c r="M153" s="14"/>
-      <c r="N153" s="17"/>
+      <c r="N153" s="19"/>
       <c r="O153" s="14"/>
+      <c r="P153" s="20"/>
+      <c r="Q153" s="14"/>
+      <c r="R153" s="21" t="str">
+        <f aca="false">IF(P153="","",P153+IF(N(Q153)&gt;0,MIN(ROUND(Параметры!$B$19/Q153*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S153" s="14"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="n">
@@ -7665,8 +8890,15 @@
       <c r="K154" s="14"/>
       <c r="L154" s="14"/>
       <c r="M154" s="14"/>
-      <c r="N154" s="17"/>
+      <c r="N154" s="19"/>
       <c r="O154" s="14"/>
+      <c r="P154" s="20"/>
+      <c r="Q154" s="14"/>
+      <c r="R154" s="21" t="str">
+        <f aca="false">IF(P154="","",P154+IF(N(Q154)&gt;0,MIN(ROUND(Параметры!$B$19/Q154*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S154" s="14"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="n">
@@ -7684,8 +8916,15 @@
       <c r="K155" s="14"/>
       <c r="L155" s="14"/>
       <c r="M155" s="14"/>
-      <c r="N155" s="17"/>
+      <c r="N155" s="19"/>
       <c r="O155" s="14"/>
+      <c r="P155" s="20"/>
+      <c r="Q155" s="14"/>
+      <c r="R155" s="21" t="str">
+        <f aca="false">IF(P155="","",P155+IF(N(Q155)&gt;0,MIN(ROUND(Параметры!$B$19/Q155*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S155" s="14"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="n">
@@ -7703,8 +8942,15 @@
       <c r="K156" s="14"/>
       <c r="L156" s="14"/>
       <c r="M156" s="14"/>
-      <c r="N156" s="17"/>
+      <c r="N156" s="19"/>
       <c r="O156" s="14"/>
+      <c r="P156" s="20"/>
+      <c r="Q156" s="14"/>
+      <c r="R156" s="21" t="str">
+        <f aca="false">IF(P156="","",P156+IF(N(Q156)&gt;0,MIN(ROUND(Параметры!$B$19/Q156*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S156" s="14"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="n">
@@ -7722,8 +8968,15 @@
       <c r="K157" s="14"/>
       <c r="L157" s="14"/>
       <c r="M157" s="14"/>
-      <c r="N157" s="17"/>
+      <c r="N157" s="19"/>
       <c r="O157" s="14"/>
+      <c r="P157" s="20"/>
+      <c r="Q157" s="14"/>
+      <c r="R157" s="21" t="str">
+        <f aca="false">IF(P157="","",P157+IF(N(Q157)&gt;0,MIN(ROUND(Параметры!$B$19/Q157*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S157" s="14"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="n">
@@ -7741,8 +8994,15 @@
       <c r="K158" s="14"/>
       <c r="L158" s="14"/>
       <c r="M158" s="14"/>
-      <c r="N158" s="17"/>
+      <c r="N158" s="19"/>
       <c r="O158" s="14"/>
+      <c r="P158" s="20"/>
+      <c r="Q158" s="14"/>
+      <c r="R158" s="21" t="str">
+        <f aca="false">IF(P158="","",P158+IF(N(Q158)&gt;0,MIN(ROUND(Параметры!$B$19/Q158*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S158" s="14"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="n">
@@ -7760,8 +9020,15 @@
       <c r="K159" s="14"/>
       <c r="L159" s="14"/>
       <c r="M159" s="14"/>
-      <c r="N159" s="17"/>
+      <c r="N159" s="19"/>
       <c r="O159" s="14"/>
+      <c r="P159" s="20"/>
+      <c r="Q159" s="14"/>
+      <c r="R159" s="21" t="str">
+        <f aca="false">IF(P159="","",P159+IF(N(Q159)&gt;0,MIN(ROUND(Параметры!$B$19/Q159*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S159" s="14"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="n">
@@ -7779,8 +9046,15 @@
       <c r="K160" s="14"/>
       <c r="L160" s="14"/>
       <c r="M160" s="14"/>
-      <c r="N160" s="17"/>
+      <c r="N160" s="19"/>
       <c r="O160" s="14"/>
+      <c r="P160" s="20"/>
+      <c r="Q160" s="14"/>
+      <c r="R160" s="21" t="str">
+        <f aca="false">IF(P160="","",P160+IF(N(Q160)&gt;0,MIN(ROUND(Параметры!$B$19/Q160*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S160" s="14"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="n">
@@ -7798,8 +9072,15 @@
       <c r="K161" s="14"/>
       <c r="L161" s="14"/>
       <c r="M161" s="14"/>
-      <c r="N161" s="17"/>
+      <c r="N161" s="19"/>
       <c r="O161" s="14"/>
+      <c r="P161" s="20"/>
+      <c r="Q161" s="14"/>
+      <c r="R161" s="21" t="str">
+        <f aca="false">IF(P161="","",P161+IF(N(Q161)&gt;0,MIN(ROUND(Параметры!$B$19/Q161*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S161" s="14"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="n">
@@ -7817,8 +9098,15 @@
       <c r="K162" s="14"/>
       <c r="L162" s="14"/>
       <c r="M162" s="14"/>
-      <c r="N162" s="17"/>
+      <c r="N162" s="19"/>
       <c r="O162" s="14"/>
+      <c r="P162" s="20"/>
+      <c r="Q162" s="14"/>
+      <c r="R162" s="21" t="str">
+        <f aca="false">IF(P162="","",P162+IF(N(Q162)&gt;0,MIN(ROUND(Параметры!$B$19/Q162*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S162" s="14"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="n">
@@ -7836,8 +9124,15 @@
       <c r="K163" s="14"/>
       <c r="L163" s="14"/>
       <c r="M163" s="14"/>
-      <c r="N163" s="17"/>
+      <c r="N163" s="19"/>
       <c r="O163" s="14"/>
+      <c r="P163" s="20"/>
+      <c r="Q163" s="14"/>
+      <c r="R163" s="21" t="str">
+        <f aca="false">IF(P163="","",P163+IF(N(Q163)&gt;0,MIN(ROUND(Параметры!$B$19/Q163*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S163" s="14"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="n">
@@ -7855,8 +9150,15 @@
       <c r="K164" s="14"/>
       <c r="L164" s="14"/>
       <c r="M164" s="14"/>
-      <c r="N164" s="17"/>
+      <c r="N164" s="19"/>
       <c r="O164" s="14"/>
+      <c r="P164" s="20"/>
+      <c r="Q164" s="14"/>
+      <c r="R164" s="21" t="str">
+        <f aca="false">IF(P164="","",P164+IF(N(Q164)&gt;0,MIN(ROUND(Параметры!$B$19/Q164*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S164" s="14"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="n">
@@ -7874,8 +9176,15 @@
       <c r="K165" s="14"/>
       <c r="L165" s="14"/>
       <c r="M165" s="14"/>
-      <c r="N165" s="17"/>
+      <c r="N165" s="19"/>
       <c r="O165" s="14"/>
+      <c r="P165" s="20"/>
+      <c r="Q165" s="14"/>
+      <c r="R165" s="21" t="str">
+        <f aca="false">IF(P165="","",P165+IF(N(Q165)&gt;0,MIN(ROUND(Параметры!$B$19/Q165*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S165" s="14"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="n">
@@ -7893,8 +9202,15 @@
       <c r="K166" s="14"/>
       <c r="L166" s="14"/>
       <c r="M166" s="14"/>
-      <c r="N166" s="17"/>
+      <c r="N166" s="19"/>
       <c r="O166" s="14"/>
+      <c r="P166" s="20"/>
+      <c r="Q166" s="14"/>
+      <c r="R166" s="21" t="str">
+        <f aca="false">IF(P166="","",P166+IF(N(Q166)&gt;0,MIN(ROUND(Параметры!$B$19/Q166*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S166" s="14"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="n">
@@ -7912,8 +9228,15 @@
       <c r="K167" s="14"/>
       <c r="L167" s="14"/>
       <c r="M167" s="14"/>
-      <c r="N167" s="17"/>
+      <c r="N167" s="19"/>
       <c r="O167" s="14"/>
+      <c r="P167" s="20"/>
+      <c r="Q167" s="14"/>
+      <c r="R167" s="21" t="str">
+        <f aca="false">IF(P167="","",P167+IF(N(Q167)&gt;0,MIN(ROUND(Параметры!$B$19/Q167*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S167" s="14"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="n">
@@ -7931,8 +9254,15 @@
       <c r="K168" s="14"/>
       <c r="L168" s="14"/>
       <c r="M168" s="14"/>
-      <c r="N168" s="17"/>
+      <c r="N168" s="19"/>
       <c r="O168" s="14"/>
+      <c r="P168" s="20"/>
+      <c r="Q168" s="14"/>
+      <c r="R168" s="21" t="str">
+        <f aca="false">IF(P168="","",P168+IF(N(Q168)&gt;0,MIN(ROUND(Параметры!$B$19/Q168*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S168" s="14"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="n">
@@ -7950,8 +9280,15 @@
       <c r="K169" s="14"/>
       <c r="L169" s="14"/>
       <c r="M169" s="14"/>
-      <c r="N169" s="17"/>
+      <c r="N169" s="19"/>
       <c r="O169" s="14"/>
+      <c r="P169" s="20"/>
+      <c r="Q169" s="14"/>
+      <c r="R169" s="21" t="str">
+        <f aca="false">IF(P169="","",P169+IF(N(Q169)&gt;0,MIN(ROUND(Параметры!$B$19/Q169*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S169" s="14"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="n">
@@ -7969,8 +9306,15 @@
       <c r="K170" s="14"/>
       <c r="L170" s="14"/>
       <c r="M170" s="14"/>
-      <c r="N170" s="17"/>
+      <c r="N170" s="19"/>
       <c r="O170" s="14"/>
+      <c r="P170" s="20"/>
+      <c r="Q170" s="14"/>
+      <c r="R170" s="21" t="str">
+        <f aca="false">IF(P170="","",P170+IF(N(Q170)&gt;0,MIN(ROUND(Параметры!$B$19/Q170*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S170" s="14"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="n">
@@ -7988,8 +9332,15 @@
       <c r="K171" s="14"/>
       <c r="L171" s="14"/>
       <c r="M171" s="14"/>
-      <c r="N171" s="17"/>
+      <c r="N171" s="19"/>
       <c r="O171" s="14"/>
+      <c r="P171" s="20"/>
+      <c r="Q171" s="14"/>
+      <c r="R171" s="21" t="str">
+        <f aca="false">IF(P171="","",P171+IF(N(Q171)&gt;0,MIN(ROUND(Параметры!$B$19/Q171*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S171" s="14"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="n">
@@ -8007,8 +9358,15 @@
       <c r="K172" s="14"/>
       <c r="L172" s="14"/>
       <c r="M172" s="14"/>
-      <c r="N172" s="17"/>
+      <c r="N172" s="19"/>
       <c r="O172" s="14"/>
+      <c r="P172" s="20"/>
+      <c r="Q172" s="14"/>
+      <c r="R172" s="21" t="str">
+        <f aca="false">IF(P172="","",P172+IF(N(Q172)&gt;0,MIN(ROUND(Параметры!$B$19/Q172*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S172" s="14"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="n">
@@ -8026,8 +9384,15 @@
       <c r="K173" s="14"/>
       <c r="L173" s="14"/>
       <c r="M173" s="14"/>
-      <c r="N173" s="17"/>
+      <c r="N173" s="19"/>
       <c r="O173" s="14"/>
+      <c r="P173" s="20"/>
+      <c r="Q173" s="14"/>
+      <c r="R173" s="21" t="str">
+        <f aca="false">IF(P173="","",P173+IF(N(Q173)&gt;0,MIN(ROUND(Параметры!$B$19/Q173*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S173" s="14"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="n">
@@ -8045,8 +9410,15 @@
       <c r="K174" s="14"/>
       <c r="L174" s="14"/>
       <c r="M174" s="14"/>
-      <c r="N174" s="17"/>
+      <c r="N174" s="19"/>
       <c r="O174" s="14"/>
+      <c r="P174" s="20"/>
+      <c r="Q174" s="14"/>
+      <c r="R174" s="21" t="str">
+        <f aca="false">IF(P174="","",P174+IF(N(Q174)&gt;0,MIN(ROUND(Параметры!$B$19/Q174*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S174" s="14"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="n">
@@ -8064,8 +9436,15 @@
       <c r="K175" s="14"/>
       <c r="L175" s="14"/>
       <c r="M175" s="14"/>
-      <c r="N175" s="17"/>
+      <c r="N175" s="19"/>
       <c r="O175" s="14"/>
+      <c r="P175" s="20"/>
+      <c r="Q175" s="14"/>
+      <c r="R175" s="21" t="str">
+        <f aca="false">IF(P175="","",P175+IF(N(Q175)&gt;0,MIN(ROUND(Параметры!$B$19/Q175*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S175" s="14"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="n">
@@ -8083,8 +9462,15 @@
       <c r="K176" s="14"/>
       <c r="L176" s="14"/>
       <c r="M176" s="14"/>
-      <c r="N176" s="17"/>
+      <c r="N176" s="19"/>
       <c r="O176" s="14"/>
+      <c r="P176" s="20"/>
+      <c r="Q176" s="14"/>
+      <c r="R176" s="21" t="str">
+        <f aca="false">IF(P176="","",P176+IF(N(Q176)&gt;0,MIN(ROUND(Параметры!$B$19/Q176*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S176" s="14"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="n">
@@ -8102,8 +9488,15 @@
       <c r="K177" s="14"/>
       <c r="L177" s="14"/>
       <c r="M177" s="14"/>
-      <c r="N177" s="17"/>
+      <c r="N177" s="19"/>
       <c r="O177" s="14"/>
+      <c r="P177" s="20"/>
+      <c r="Q177" s="14"/>
+      <c r="R177" s="21" t="str">
+        <f aca="false">IF(P177="","",P177+IF(N(Q177)&gt;0,MIN(ROUND(Параметры!$B$19/Q177*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S177" s="14"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="n">
@@ -8121,8 +9514,15 @@
       <c r="K178" s="14"/>
       <c r="L178" s="14"/>
       <c r="M178" s="14"/>
-      <c r="N178" s="17"/>
+      <c r="N178" s="19"/>
       <c r="O178" s="14"/>
+      <c r="P178" s="20"/>
+      <c r="Q178" s="14"/>
+      <c r="R178" s="21" t="str">
+        <f aca="false">IF(P178="","",P178+IF(N(Q178)&gt;0,MIN(ROUND(Параметры!$B$19/Q178*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S178" s="14"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="n">
@@ -8140,8 +9540,15 @@
       <c r="K179" s="14"/>
       <c r="L179" s="14"/>
       <c r="M179" s="14"/>
-      <c r="N179" s="17"/>
+      <c r="N179" s="19"/>
       <c r="O179" s="14"/>
+      <c r="P179" s="20"/>
+      <c r="Q179" s="14"/>
+      <c r="R179" s="21" t="str">
+        <f aca="false">IF(P179="","",P179+IF(N(Q179)&gt;0,MIN(ROUND(Параметры!$B$19/Q179*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S179" s="14"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="n">
@@ -8159,8 +9566,15 @@
       <c r="K180" s="14"/>
       <c r="L180" s="14"/>
       <c r="M180" s="14"/>
-      <c r="N180" s="17"/>
+      <c r="N180" s="19"/>
       <c r="O180" s="14"/>
+      <c r="P180" s="20"/>
+      <c r="Q180" s="14"/>
+      <c r="R180" s="21" t="str">
+        <f aca="false">IF(P180="","",P180+IF(N(Q180)&gt;0,MIN(ROUND(Параметры!$B$19/Q180*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S180" s="14"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="n">
@@ -8178,8 +9592,15 @@
       <c r="K181" s="14"/>
       <c r="L181" s="14"/>
       <c r="M181" s="14"/>
-      <c r="N181" s="17"/>
+      <c r="N181" s="19"/>
       <c r="O181" s="14"/>
+      <c r="P181" s="20"/>
+      <c r="Q181" s="14"/>
+      <c r="R181" s="21" t="str">
+        <f aca="false">IF(P181="","",P181+IF(N(Q181)&gt;0,MIN(ROUND(Параметры!$B$19/Q181*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S181" s="14"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="n">
@@ -8197,8 +9618,15 @@
       <c r="K182" s="14"/>
       <c r="L182" s="14"/>
       <c r="M182" s="14"/>
-      <c r="N182" s="17"/>
+      <c r="N182" s="19"/>
       <c r="O182" s="14"/>
+      <c r="P182" s="20"/>
+      <c r="Q182" s="14"/>
+      <c r="R182" s="21" t="str">
+        <f aca="false">IF(P182="","",P182+IF(N(Q182)&gt;0,MIN(ROUND(Параметры!$B$19/Q182*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S182" s="14"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="n">
@@ -8216,8 +9644,15 @@
       <c r="K183" s="14"/>
       <c r="L183" s="14"/>
       <c r="M183" s="14"/>
-      <c r="N183" s="17"/>
+      <c r="N183" s="19"/>
       <c r="O183" s="14"/>
+      <c r="P183" s="20"/>
+      <c r="Q183" s="14"/>
+      <c r="R183" s="21" t="str">
+        <f aca="false">IF(P183="","",P183+IF(N(Q183)&gt;0,MIN(ROUND(Параметры!$B$19/Q183*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S183" s="14"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="n">
@@ -8235,8 +9670,15 @@
       <c r="K184" s="14"/>
       <c r="L184" s="14"/>
       <c r="M184" s="14"/>
-      <c r="N184" s="17"/>
+      <c r="N184" s="19"/>
       <c r="O184" s="14"/>
+      <c r="P184" s="20"/>
+      <c r="Q184" s="14"/>
+      <c r="R184" s="21" t="str">
+        <f aca="false">IF(P184="","",P184+IF(N(Q184)&gt;0,MIN(ROUND(Параметры!$B$19/Q184*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S184" s="14"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="n">
@@ -8254,8 +9696,15 @@
       <c r="K185" s="14"/>
       <c r="L185" s="14"/>
       <c r="M185" s="14"/>
-      <c r="N185" s="17"/>
+      <c r="N185" s="19"/>
       <c r="O185" s="14"/>
+      <c r="P185" s="20"/>
+      <c r="Q185" s="14"/>
+      <c r="R185" s="21" t="str">
+        <f aca="false">IF(P185="","",P185+IF(N(Q185)&gt;0,MIN(ROUND(Параметры!$B$19/Q185*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S185" s="14"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="n">
@@ -8273,8 +9722,15 @@
       <c r="K186" s="14"/>
       <c r="L186" s="14"/>
       <c r="M186" s="14"/>
-      <c r="N186" s="17"/>
+      <c r="N186" s="19"/>
       <c r="O186" s="14"/>
+      <c r="P186" s="20"/>
+      <c r="Q186" s="14"/>
+      <c r="R186" s="21" t="str">
+        <f aca="false">IF(P186="","",P186+IF(N(Q186)&gt;0,MIN(ROUND(Параметры!$B$19/Q186*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S186" s="14"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="n">
@@ -8292,8 +9748,15 @@
       <c r="K187" s="14"/>
       <c r="L187" s="14"/>
       <c r="M187" s="14"/>
-      <c r="N187" s="17"/>
+      <c r="N187" s="19"/>
       <c r="O187" s="14"/>
+      <c r="P187" s="20"/>
+      <c r="Q187" s="14"/>
+      <c r="R187" s="21" t="str">
+        <f aca="false">IF(P187="","",P187+IF(N(Q187)&gt;0,MIN(ROUND(Параметры!$B$19/Q187*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S187" s="14"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="n">
@@ -8311,8 +9774,15 @@
       <c r="K188" s="14"/>
       <c r="L188" s="14"/>
       <c r="M188" s="14"/>
-      <c r="N188" s="17"/>
+      <c r="N188" s="19"/>
       <c r="O188" s="14"/>
+      <c r="P188" s="20"/>
+      <c r="Q188" s="14"/>
+      <c r="R188" s="21" t="str">
+        <f aca="false">IF(P188="","",P188+IF(N(Q188)&gt;0,MIN(ROUND(Параметры!$B$19/Q188*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S188" s="14"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="n">
@@ -8330,8 +9800,15 @@
       <c r="K189" s="14"/>
       <c r="L189" s="14"/>
       <c r="M189" s="14"/>
-      <c r="N189" s="17"/>
+      <c r="N189" s="19"/>
       <c r="O189" s="14"/>
+      <c r="P189" s="20"/>
+      <c r="Q189" s="14"/>
+      <c r="R189" s="21" t="str">
+        <f aca="false">IF(P189="","",P189+IF(N(Q189)&gt;0,MIN(ROUND(Параметры!$B$19/Q189*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S189" s="14"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="n">
@@ -8349,8 +9826,15 @@
       <c r="K190" s="14"/>
       <c r="L190" s="14"/>
       <c r="M190" s="14"/>
-      <c r="N190" s="17"/>
+      <c r="N190" s="19"/>
       <c r="O190" s="14"/>
+      <c r="P190" s="20"/>
+      <c r="Q190" s="14"/>
+      <c r="R190" s="21" t="str">
+        <f aca="false">IF(P190="","",P190+IF(N(Q190)&gt;0,MIN(ROUND(Параметры!$B$19/Q190*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S190" s="14"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="n">
@@ -8368,8 +9852,15 @@
       <c r="K191" s="14"/>
       <c r="L191" s="14"/>
       <c r="M191" s="14"/>
-      <c r="N191" s="17"/>
+      <c r="N191" s="19"/>
       <c r="O191" s="14"/>
+      <c r="P191" s="20"/>
+      <c r="Q191" s="14"/>
+      <c r="R191" s="21" t="str">
+        <f aca="false">IF(P191="","",P191+IF(N(Q191)&gt;0,MIN(ROUND(Параметры!$B$19/Q191*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S191" s="14"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="n">
@@ -8387,8 +9878,15 @@
       <c r="K192" s="14"/>
       <c r="L192" s="14"/>
       <c r="M192" s="14"/>
-      <c r="N192" s="17"/>
+      <c r="N192" s="19"/>
       <c r="O192" s="14"/>
+      <c r="P192" s="20"/>
+      <c r="Q192" s="14"/>
+      <c r="R192" s="21" t="str">
+        <f aca="false">IF(P192="","",P192+IF(N(Q192)&gt;0,MIN(ROUND(Параметры!$B$19/Q192*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S192" s="14"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="n">
@@ -8406,8 +9904,15 @@
       <c r="K193" s="14"/>
       <c r="L193" s="14"/>
       <c r="M193" s="14"/>
-      <c r="N193" s="17"/>
+      <c r="N193" s="19"/>
       <c r="O193" s="14"/>
+      <c r="P193" s="20"/>
+      <c r="Q193" s="14"/>
+      <c r="R193" s="21" t="str">
+        <f aca="false">IF(P193="","",P193+IF(N(Q193)&gt;0,MIN(ROUND(Параметры!$B$19/Q193*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S193" s="14"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="n">
@@ -8425,8 +9930,15 @@
       <c r="K194" s="14"/>
       <c r="L194" s="14"/>
       <c r="M194" s="14"/>
-      <c r="N194" s="17"/>
+      <c r="N194" s="19"/>
       <c r="O194" s="14"/>
+      <c r="P194" s="20"/>
+      <c r="Q194" s="14"/>
+      <c r="R194" s="21" t="str">
+        <f aca="false">IF(P194="","",P194+IF(N(Q194)&gt;0,MIN(ROUND(Параметры!$B$19/Q194*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S194" s="14"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="n">
@@ -8444,8 +9956,15 @@
       <c r="K195" s="14"/>
       <c r="L195" s="14"/>
       <c r="M195" s="14"/>
-      <c r="N195" s="17"/>
+      <c r="N195" s="19"/>
       <c r="O195" s="14"/>
+      <c r="P195" s="20"/>
+      <c r="Q195" s="14"/>
+      <c r="R195" s="21" t="str">
+        <f aca="false">IF(P195="","",P195+IF(N(Q195)&gt;0,MIN(ROUND(Параметры!$B$19/Q195*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S195" s="14"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="n">
@@ -8463,8 +9982,15 @@
       <c r="K196" s="14"/>
       <c r="L196" s="14"/>
       <c r="M196" s="14"/>
-      <c r="N196" s="17"/>
+      <c r="N196" s="19"/>
       <c r="O196" s="14"/>
+      <c r="P196" s="20"/>
+      <c r="Q196" s="14"/>
+      <c r="R196" s="21" t="str">
+        <f aca="false">IF(P196="","",P196+IF(N(Q196)&gt;0,MIN(ROUND(Параметры!$B$19/Q196*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S196" s="14"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="n">
@@ -8482,8 +10008,15 @@
       <c r="K197" s="14"/>
       <c r="L197" s="14"/>
       <c r="M197" s="14"/>
-      <c r="N197" s="17"/>
+      <c r="N197" s="19"/>
       <c r="O197" s="14"/>
+      <c r="P197" s="20"/>
+      <c r="Q197" s="14"/>
+      <c r="R197" s="21" t="str">
+        <f aca="false">IF(P197="","",P197+IF(N(Q197)&gt;0,MIN(ROUND(Параметры!$B$19/Q197*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S197" s="14"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="n">
@@ -8501,8 +10034,15 @@
       <c r="K198" s="14"/>
       <c r="L198" s="14"/>
       <c r="M198" s="14"/>
-      <c r="N198" s="17"/>
+      <c r="N198" s="19"/>
       <c r="O198" s="14"/>
+      <c r="P198" s="20"/>
+      <c r="Q198" s="14"/>
+      <c r="R198" s="21" t="str">
+        <f aca="false">IF(P198="","",P198+IF(N(Q198)&gt;0,MIN(ROUND(Параметры!$B$19/Q198*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S198" s="14"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="n">
@@ -8520,8 +10060,15 @@
       <c r="K199" s="14"/>
       <c r="L199" s="14"/>
       <c r="M199" s="14"/>
-      <c r="N199" s="17"/>
+      <c r="N199" s="19"/>
       <c r="O199" s="14"/>
+      <c r="P199" s="20"/>
+      <c r="Q199" s="14"/>
+      <c r="R199" s="21" t="str">
+        <f aca="false">IF(P199="","",P199+IF(N(Q199)&gt;0,MIN(ROUND(Параметры!$B$19/Q199*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S199" s="14"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="n">
@@ -8539,8 +10086,15 @@
       <c r="K200" s="14"/>
       <c r="L200" s="14"/>
       <c r="M200" s="14"/>
-      <c r="N200" s="17"/>
+      <c r="N200" s="19"/>
       <c r="O200" s="14"/>
+      <c r="P200" s="20"/>
+      <c r="Q200" s="14"/>
+      <c r="R200" s="21" t="str">
+        <f aca="false">IF(P200="","",P200+IF(N(Q200)&gt;0,MIN(ROUND(Параметры!$B$19/Q200*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S200" s="14"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="n">
@@ -8558,8 +10112,15 @@
       <c r="K201" s="14"/>
       <c r="L201" s="14"/>
       <c r="M201" s="14"/>
-      <c r="N201" s="17"/>
+      <c r="N201" s="19"/>
       <c r="O201" s="14"/>
+      <c r="P201" s="20"/>
+      <c r="Q201" s="14"/>
+      <c r="R201" s="21" t="str">
+        <f aca="false">IF(P201="","",P201+IF(N(Q201)&gt;0,MIN(ROUND(Параметры!$B$19/Q201*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S201" s="14"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="n">
@@ -8577,8 +10138,15 @@
       <c r="K202" s="14"/>
       <c r="L202" s="14"/>
       <c r="M202" s="14"/>
-      <c r="N202" s="17"/>
+      <c r="N202" s="19"/>
       <c r="O202" s="14"/>
+      <c r="P202" s="20"/>
+      <c r="Q202" s="14"/>
+      <c r="R202" s="21" t="str">
+        <f aca="false">IF(P202="","",P202+IF(N(Q202)&gt;0,MIN(ROUND(Параметры!$B$19/Q202*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S202" s="14"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="n">
@@ -8596,8 +10164,15 @@
       <c r="K203" s="14"/>
       <c r="L203" s="14"/>
       <c r="M203" s="14"/>
-      <c r="N203" s="17"/>
+      <c r="N203" s="19"/>
       <c r="O203" s="14"/>
+      <c r="P203" s="20"/>
+      <c r="Q203" s="14"/>
+      <c r="R203" s="21" t="str">
+        <f aca="false">IF(P203="","",P203+IF(N(Q203)&gt;0,MIN(ROUND(Параметры!$B$19/Q203*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S203" s="14"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="n">
@@ -8615,8 +10190,15 @@
       <c r="K204" s="14"/>
       <c r="L204" s="14"/>
       <c r="M204" s="14"/>
-      <c r="N204" s="17"/>
+      <c r="N204" s="19"/>
       <c r="O204" s="14"/>
+      <c r="P204" s="20"/>
+      <c r="Q204" s="14"/>
+      <c r="R204" s="21" t="str">
+        <f aca="false">IF(P204="","",P204+IF(N(Q204)&gt;0,MIN(ROUND(Параметры!$B$19/Q204*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S204" s="14"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="n">
@@ -8634,8 +10216,15 @@
       <c r="K205" s="14"/>
       <c r="L205" s="14"/>
       <c r="M205" s="14"/>
-      <c r="N205" s="17"/>
+      <c r="N205" s="19"/>
       <c r="O205" s="14"/>
+      <c r="P205" s="20"/>
+      <c r="Q205" s="14"/>
+      <c r="R205" s="21" t="str">
+        <f aca="false">IF(P205="","",P205+IF(N(Q205)&gt;0,MIN(ROUND(Параметры!$B$19/Q205*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S205" s="14"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="n">
@@ -8653,8 +10242,15 @@
       <c r="K206" s="14"/>
       <c r="L206" s="14"/>
       <c r="M206" s="14"/>
-      <c r="N206" s="17"/>
+      <c r="N206" s="19"/>
       <c r="O206" s="14"/>
+      <c r="P206" s="20"/>
+      <c r="Q206" s="14"/>
+      <c r="R206" s="21" t="str">
+        <f aca="false">IF(P206="","",P206+IF(N(Q206)&gt;0,MIN(ROUND(Параметры!$B$19/Q206*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S206" s="14"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="n">
@@ -8672,8 +10268,15 @@
       <c r="K207" s="14"/>
       <c r="L207" s="14"/>
       <c r="M207" s="14"/>
-      <c r="N207" s="17"/>
+      <c r="N207" s="19"/>
       <c r="O207" s="14"/>
+      <c r="P207" s="20"/>
+      <c r="Q207" s="14"/>
+      <c r="R207" s="21" t="str">
+        <f aca="false">IF(P207="","",P207+IF(N(Q207)&gt;0,MIN(ROUND(Параметры!$B$19/Q207*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S207" s="14"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="n">
@@ -8691,8 +10294,15 @@
       <c r="K208" s="14"/>
       <c r="L208" s="14"/>
       <c r="M208" s="14"/>
-      <c r="N208" s="17"/>
+      <c r="N208" s="19"/>
       <c r="O208" s="14"/>
+      <c r="P208" s="20"/>
+      <c r="Q208" s="14"/>
+      <c r="R208" s="21" t="str">
+        <f aca="false">IF(P208="","",P208+IF(N(Q208)&gt;0,MIN(ROUND(Параметры!$B$19/Q208*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S208" s="14"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="n">
@@ -8710,8 +10320,15 @@
       <c r="K209" s="14"/>
       <c r="L209" s="14"/>
       <c r="M209" s="14"/>
-      <c r="N209" s="17"/>
+      <c r="N209" s="19"/>
       <c r="O209" s="14"/>
+      <c r="P209" s="20"/>
+      <c r="Q209" s="14"/>
+      <c r="R209" s="21" t="str">
+        <f aca="false">IF(P209="","",P209+IF(N(Q209)&gt;0,MIN(ROUND(Параметры!$B$19/Q209*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S209" s="14"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="n">
@@ -8729,8 +10346,15 @@
       <c r="K210" s="14"/>
       <c r="L210" s="14"/>
       <c r="M210" s="14"/>
-      <c r="N210" s="17"/>
+      <c r="N210" s="19"/>
       <c r="O210" s="14"/>
+      <c r="P210" s="20"/>
+      <c r="Q210" s="14"/>
+      <c r="R210" s="21" t="str">
+        <f aca="false">IF(P210="","",P210+IF(N(Q210)&gt;0,MIN(ROUND(Параметры!$B$19/Q210*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S210" s="14"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="n">
@@ -8748,8 +10372,15 @@
       <c r="K211" s="14"/>
       <c r="L211" s="14"/>
       <c r="M211" s="14"/>
-      <c r="N211" s="17"/>
+      <c r="N211" s="19"/>
       <c r="O211" s="14"/>
+      <c r="P211" s="20"/>
+      <c r="Q211" s="14"/>
+      <c r="R211" s="21" t="str">
+        <f aca="false">IF(P211="","",P211+IF(N(Q211)&gt;0,MIN(ROUND(Параметры!$B$19/Q211*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S211" s="14"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="n">
@@ -8767,8 +10398,15 @@
       <c r="K212" s="14"/>
       <c r="L212" s="14"/>
       <c r="M212" s="14"/>
-      <c r="N212" s="17"/>
+      <c r="N212" s="19"/>
       <c r="O212" s="14"/>
+      <c r="P212" s="20"/>
+      <c r="Q212" s="14"/>
+      <c r="R212" s="21" t="str">
+        <f aca="false">IF(P212="","",P212+IF(N(Q212)&gt;0,MIN(ROUND(Параметры!$B$19/Q212*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S212" s="14"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="n">
@@ -8786,8 +10424,15 @@
       <c r="K213" s="14"/>
       <c r="L213" s="14"/>
       <c r="M213" s="14"/>
-      <c r="N213" s="17"/>
+      <c r="N213" s="19"/>
       <c r="O213" s="14"/>
+      <c r="P213" s="20"/>
+      <c r="Q213" s="14"/>
+      <c r="R213" s="21" t="str">
+        <f aca="false">IF(P213="","",P213+IF(N(Q213)&gt;0,MIN(ROUND(Параметры!$B$19/Q213*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S213" s="14"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="n">
@@ -8805,8 +10450,15 @@
       <c r="K214" s="14"/>
       <c r="L214" s="14"/>
       <c r="M214" s="14"/>
-      <c r="N214" s="17"/>
+      <c r="N214" s="19"/>
       <c r="O214" s="14"/>
+      <c r="P214" s="20"/>
+      <c r="Q214" s="14"/>
+      <c r="R214" s="21" t="str">
+        <f aca="false">IF(P214="","",P214+IF(N(Q214)&gt;0,MIN(ROUND(Параметры!$B$19/Q214*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S214" s="14"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="n">
@@ -8824,8 +10476,15 @@
       <c r="K215" s="14"/>
       <c r="L215" s="14"/>
       <c r="M215" s="14"/>
-      <c r="N215" s="17"/>
+      <c r="N215" s="19"/>
       <c r="O215" s="14"/>
+      <c r="P215" s="20"/>
+      <c r="Q215" s="14"/>
+      <c r="R215" s="21" t="str">
+        <f aca="false">IF(P215="","",P215+IF(N(Q215)&gt;0,MIN(ROUND(Параметры!$B$19/Q215*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S215" s="14"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="n">
@@ -8843,8 +10502,15 @@
       <c r="K216" s="14"/>
       <c r="L216" s="14"/>
       <c r="M216" s="14"/>
-      <c r="N216" s="17"/>
+      <c r="N216" s="19"/>
       <c r="O216" s="14"/>
+      <c r="P216" s="20"/>
+      <c r="Q216" s="14"/>
+      <c r="R216" s="21" t="str">
+        <f aca="false">IF(P216="","",P216+IF(N(Q216)&gt;0,MIN(ROUND(Параметры!$B$19/Q216*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S216" s="14"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="n">
@@ -8862,8 +10528,15 @@
       <c r="K217" s="14"/>
       <c r="L217" s="14"/>
       <c r="M217" s="14"/>
-      <c r="N217" s="17"/>
+      <c r="N217" s="19"/>
       <c r="O217" s="14"/>
+      <c r="P217" s="20"/>
+      <c r="Q217" s="14"/>
+      <c r="R217" s="21" t="str">
+        <f aca="false">IF(P217="","",P217+IF(N(Q217)&gt;0,MIN(ROUND(Параметры!$B$19/Q217*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S217" s="14"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="n">
@@ -8881,8 +10554,15 @@
       <c r="K218" s="14"/>
       <c r="L218" s="14"/>
       <c r="M218" s="14"/>
-      <c r="N218" s="17"/>
+      <c r="N218" s="19"/>
       <c r="O218" s="14"/>
+      <c r="P218" s="20"/>
+      <c r="Q218" s="14"/>
+      <c r="R218" s="21" t="str">
+        <f aca="false">IF(P218="","",P218+IF(N(Q218)&gt;0,MIN(ROUND(Параметры!$B$19/Q218*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S218" s="14"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="n">
@@ -8900,8 +10580,15 @@
       <c r="K219" s="14"/>
       <c r="L219" s="14"/>
       <c r="M219" s="14"/>
-      <c r="N219" s="17"/>
+      <c r="N219" s="19"/>
       <c r="O219" s="14"/>
+      <c r="P219" s="20"/>
+      <c r="Q219" s="14"/>
+      <c r="R219" s="21" t="str">
+        <f aca="false">IF(P219="","",P219+IF(N(Q219)&gt;0,MIN(ROUND(Параметры!$B$19/Q219*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S219" s="14"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="n">
@@ -8919,8 +10606,15 @@
       <c r="K220" s="14"/>
       <c r="L220" s="14"/>
       <c r="M220" s="14"/>
-      <c r="N220" s="17"/>
+      <c r="N220" s="19"/>
       <c r="O220" s="14"/>
+      <c r="P220" s="20"/>
+      <c r="Q220" s="14"/>
+      <c r="R220" s="21" t="str">
+        <f aca="false">IF(P220="","",P220+IF(N(Q220)&gt;0,MIN(ROUND(Параметры!$B$19/Q220*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S220" s="14"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="n">
@@ -8938,8 +10632,15 @@
       <c r="K221" s="14"/>
       <c r="L221" s="14"/>
       <c r="M221" s="14"/>
-      <c r="N221" s="17"/>
+      <c r="N221" s="19"/>
       <c r="O221" s="14"/>
+      <c r="P221" s="20"/>
+      <c r="Q221" s="14"/>
+      <c r="R221" s="21" t="str">
+        <f aca="false">IF(P221="","",P221+IF(N(Q221)&gt;0,MIN(ROUND(Параметры!$B$19/Q221*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S221" s="14"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="n">
@@ -8957,8 +10658,15 @@
       <c r="K222" s="14"/>
       <c r="L222" s="14"/>
       <c r="M222" s="14"/>
-      <c r="N222" s="17"/>
+      <c r="N222" s="19"/>
       <c r="O222" s="14"/>
+      <c r="P222" s="20"/>
+      <c r="Q222" s="14"/>
+      <c r="R222" s="21" t="str">
+        <f aca="false">IF(P222="","",P222+IF(N(Q222)&gt;0,MIN(ROUND(Параметры!$B$19/Q222*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S222" s="14"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="n">
@@ -8976,8 +10684,15 @@
       <c r="K223" s="14"/>
       <c r="L223" s="14"/>
       <c r="M223" s="14"/>
-      <c r="N223" s="17"/>
+      <c r="N223" s="19"/>
       <c r="O223" s="14"/>
+      <c r="P223" s="20"/>
+      <c r="Q223" s="14"/>
+      <c r="R223" s="21" t="str">
+        <f aca="false">IF(P223="","",P223+IF(N(Q223)&gt;0,MIN(ROUND(Параметры!$B$19/Q223*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S223" s="14"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="n">
@@ -8995,8 +10710,15 @@
       <c r="K224" s="14"/>
       <c r="L224" s="14"/>
       <c r="M224" s="14"/>
-      <c r="N224" s="17"/>
+      <c r="N224" s="19"/>
       <c r="O224" s="14"/>
+      <c r="P224" s="20"/>
+      <c r="Q224" s="14"/>
+      <c r="R224" s="21" t="str">
+        <f aca="false">IF(P224="","",P224+IF(N(Q224)&gt;0,MIN(ROUND(Параметры!$B$19/Q224*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S224" s="14"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="n">
@@ -9014,8 +10736,15 @@
       <c r="K225" s="14"/>
       <c r="L225" s="14"/>
       <c r="M225" s="14"/>
-      <c r="N225" s="17"/>
+      <c r="N225" s="19"/>
       <c r="O225" s="14"/>
+      <c r="P225" s="20"/>
+      <c r="Q225" s="14"/>
+      <c r="R225" s="21" t="str">
+        <f aca="false">IF(P225="","",P225+IF(N(Q225)&gt;0,MIN(ROUND(Параметры!$B$19/Q225*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S225" s="14"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="n">
@@ -9033,8 +10762,15 @@
       <c r="K226" s="14"/>
       <c r="L226" s="14"/>
       <c r="M226" s="14"/>
-      <c r="N226" s="17"/>
+      <c r="N226" s="19"/>
       <c r="O226" s="14"/>
+      <c r="P226" s="20"/>
+      <c r="Q226" s="14"/>
+      <c r="R226" s="21" t="str">
+        <f aca="false">IF(P226="","",P226+IF(N(Q226)&gt;0,MIN(ROUND(Параметры!$B$19/Q226*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S226" s="14"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="n">
@@ -9052,8 +10788,15 @@
       <c r="K227" s="14"/>
       <c r="L227" s="14"/>
       <c r="M227" s="14"/>
-      <c r="N227" s="17"/>
+      <c r="N227" s="19"/>
       <c r="O227" s="14"/>
+      <c r="P227" s="20"/>
+      <c r="Q227" s="14"/>
+      <c r="R227" s="21" t="str">
+        <f aca="false">IF(P227="","",P227+IF(N(Q227)&gt;0,MIN(ROUND(Параметры!$B$19/Q227*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S227" s="14"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="n">
@@ -9071,8 +10814,15 @@
       <c r="K228" s="14"/>
       <c r="L228" s="14"/>
       <c r="M228" s="14"/>
-      <c r="N228" s="17"/>
+      <c r="N228" s="19"/>
       <c r="O228" s="14"/>
+      <c r="P228" s="20"/>
+      <c r="Q228" s="14"/>
+      <c r="R228" s="21" t="str">
+        <f aca="false">IF(P228="","",P228+IF(N(Q228)&gt;0,MIN(ROUND(Параметры!$B$19/Q228*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S228" s="14"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="n">
@@ -9090,8 +10840,15 @@
       <c r="K229" s="14"/>
       <c r="L229" s="14"/>
       <c r="M229" s="14"/>
-      <c r="N229" s="17"/>
+      <c r="N229" s="19"/>
       <c r="O229" s="14"/>
+      <c r="P229" s="20"/>
+      <c r="Q229" s="14"/>
+      <c r="R229" s="21" t="str">
+        <f aca="false">IF(P229="","",P229+IF(N(Q229)&gt;0,MIN(ROUND(Параметры!$B$19/Q229*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S229" s="14"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="n">
@@ -9109,8 +10866,15 @@
       <c r="K230" s="14"/>
       <c r="L230" s="14"/>
       <c r="M230" s="14"/>
-      <c r="N230" s="17"/>
+      <c r="N230" s="19"/>
       <c r="O230" s="14"/>
+      <c r="P230" s="20"/>
+      <c r="Q230" s="14"/>
+      <c r="R230" s="21" t="str">
+        <f aca="false">IF(P230="","",P230+IF(N(Q230)&gt;0,MIN(ROUND(Параметры!$B$19/Q230*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S230" s="14"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="n">
@@ -9128,8 +10892,15 @@
       <c r="K231" s="14"/>
       <c r="L231" s="14"/>
       <c r="M231" s="14"/>
-      <c r="N231" s="17"/>
+      <c r="N231" s="19"/>
       <c r="O231" s="14"/>
+      <c r="P231" s="20"/>
+      <c r="Q231" s="14"/>
+      <c r="R231" s="21" t="str">
+        <f aca="false">IF(P231="","",P231+IF(N(Q231)&gt;0,MIN(ROUND(Параметры!$B$19/Q231*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S231" s="14"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="n">
@@ -9147,8 +10918,15 @@
       <c r="K232" s="14"/>
       <c r="L232" s="14"/>
       <c r="M232" s="14"/>
-      <c r="N232" s="17"/>
+      <c r="N232" s="19"/>
       <c r="O232" s="14"/>
+      <c r="P232" s="20"/>
+      <c r="Q232" s="14"/>
+      <c r="R232" s="21" t="str">
+        <f aca="false">IF(P232="","",P232+IF(N(Q232)&gt;0,MIN(ROUND(Параметры!$B$19/Q232*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S232" s="14"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="n">
@@ -9166,8 +10944,15 @@
       <c r="K233" s="14"/>
       <c r="L233" s="14"/>
       <c r="M233" s="14"/>
-      <c r="N233" s="17"/>
+      <c r="N233" s="19"/>
       <c r="O233" s="14"/>
+      <c r="P233" s="20"/>
+      <c r="Q233" s="14"/>
+      <c r="R233" s="21" t="str">
+        <f aca="false">IF(P233="","",P233+IF(N(Q233)&gt;0,MIN(ROUND(Параметры!$B$19/Q233*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S233" s="14"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="n">
@@ -9185,8 +10970,15 @@
       <c r="K234" s="14"/>
       <c r="L234" s="14"/>
       <c r="M234" s="14"/>
-      <c r="N234" s="17"/>
+      <c r="N234" s="19"/>
       <c r="O234" s="14"/>
+      <c r="P234" s="20"/>
+      <c r="Q234" s="14"/>
+      <c r="R234" s="21" t="str">
+        <f aca="false">IF(P234="","",P234+IF(N(Q234)&gt;0,MIN(ROUND(Параметры!$B$19/Q234*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S234" s="14"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="n">
@@ -9204,8 +10996,15 @@
       <c r="K235" s="14"/>
       <c r="L235" s="14"/>
       <c r="M235" s="14"/>
-      <c r="N235" s="17"/>
+      <c r="N235" s="19"/>
       <c r="O235" s="14"/>
+      <c r="P235" s="20"/>
+      <c r="Q235" s="14"/>
+      <c r="R235" s="21" t="str">
+        <f aca="false">IF(P235="","",P235+IF(N(Q235)&gt;0,MIN(ROUND(Параметры!$B$19/Q235*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S235" s="14"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="n">
@@ -9223,8 +11022,15 @@
       <c r="K236" s="14"/>
       <c r="L236" s="14"/>
       <c r="M236" s="14"/>
-      <c r="N236" s="17"/>
+      <c r="N236" s="19"/>
       <c r="O236" s="14"/>
+      <c r="P236" s="20"/>
+      <c r="Q236" s="14"/>
+      <c r="R236" s="21" t="str">
+        <f aca="false">IF(P236="","",P236+IF(N(Q236)&gt;0,MIN(ROUND(Параметры!$B$19/Q236*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S236" s="14"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="n">
@@ -9242,8 +11048,15 @@
       <c r="K237" s="14"/>
       <c r="L237" s="14"/>
       <c r="M237" s="14"/>
-      <c r="N237" s="17"/>
+      <c r="N237" s="19"/>
       <c r="O237" s="14"/>
+      <c r="P237" s="20"/>
+      <c r="Q237" s="14"/>
+      <c r="R237" s="21" t="str">
+        <f aca="false">IF(P237="","",P237+IF(N(Q237)&gt;0,MIN(ROUND(Параметры!$B$19/Q237*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S237" s="14"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="n">
@@ -9261,8 +11074,15 @@
       <c r="K238" s="14"/>
       <c r="L238" s="14"/>
       <c r="M238" s="14"/>
-      <c r="N238" s="17"/>
+      <c r="N238" s="19"/>
       <c r="O238" s="14"/>
+      <c r="P238" s="20"/>
+      <c r="Q238" s="14"/>
+      <c r="R238" s="21" t="str">
+        <f aca="false">IF(P238="","",P238+IF(N(Q238)&gt;0,MIN(ROUND(Параметры!$B$19/Q238*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S238" s="14"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="7" t="n">
@@ -9280,8 +11100,15 @@
       <c r="K239" s="14"/>
       <c r="L239" s="14"/>
       <c r="M239" s="14"/>
-      <c r="N239" s="17"/>
+      <c r="N239" s="19"/>
       <c r="O239" s="14"/>
+      <c r="P239" s="20"/>
+      <c r="Q239" s="14"/>
+      <c r="R239" s="21" t="str">
+        <f aca="false">IF(P239="","",P239+IF(N(Q239)&gt;0,MIN(ROUND(Параметры!$B$19/Q239*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S239" s="14"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="n">
@@ -9299,8 +11126,15 @@
       <c r="K240" s="14"/>
       <c r="L240" s="14"/>
       <c r="M240" s="14"/>
-      <c r="N240" s="17"/>
+      <c r="N240" s="19"/>
       <c r="O240" s="14"/>
+      <c r="P240" s="20"/>
+      <c r="Q240" s="14"/>
+      <c r="R240" s="21" t="str">
+        <f aca="false">IF(P240="","",P240+IF(N(Q240)&gt;0,MIN(ROUND(Параметры!$B$19/Q240*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S240" s="14"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="n">
@@ -9318,8 +11152,15 @@
       <c r="K241" s="14"/>
       <c r="L241" s="14"/>
       <c r="M241" s="14"/>
-      <c r="N241" s="17"/>
+      <c r="N241" s="19"/>
       <c r="O241" s="14"/>
+      <c r="P241" s="20"/>
+      <c r="Q241" s="14"/>
+      <c r="R241" s="21" t="str">
+        <f aca="false">IF(P241="","",P241+IF(N(Q241)&gt;0,MIN(ROUND(Параметры!$B$19/Q241*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S241" s="14"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="n">
@@ -9337,8 +11178,15 @@
       <c r="K242" s="14"/>
       <c r="L242" s="14"/>
       <c r="M242" s="14"/>
-      <c r="N242" s="17"/>
+      <c r="N242" s="19"/>
       <c r="O242" s="14"/>
+      <c r="P242" s="20"/>
+      <c r="Q242" s="14"/>
+      <c r="R242" s="21" t="str">
+        <f aca="false">IF(P242="","",P242+IF(N(Q242)&gt;0,MIN(ROUND(Параметры!$B$19/Q242*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S242" s="14"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="n">
@@ -9356,8 +11204,15 @@
       <c r="K243" s="14"/>
       <c r="L243" s="14"/>
       <c r="M243" s="14"/>
-      <c r="N243" s="17"/>
+      <c r="N243" s="19"/>
       <c r="O243" s="14"/>
+      <c r="P243" s="20"/>
+      <c r="Q243" s="14"/>
+      <c r="R243" s="21" t="str">
+        <f aca="false">IF(P243="","",P243+IF(N(Q243)&gt;0,MIN(ROUND(Параметры!$B$19/Q243*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S243" s="14"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="n">
@@ -9375,8 +11230,15 @@
       <c r="K244" s="14"/>
       <c r="L244" s="14"/>
       <c r="M244" s="14"/>
-      <c r="N244" s="17"/>
+      <c r="N244" s="19"/>
       <c r="O244" s="14"/>
+      <c r="P244" s="20"/>
+      <c r="Q244" s="14"/>
+      <c r="R244" s="21" t="str">
+        <f aca="false">IF(P244="","",P244+IF(N(Q244)&gt;0,MIN(ROUND(Параметры!$B$19/Q244*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S244" s="14"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="n">
@@ -9394,8 +11256,15 @@
       <c r="K245" s="14"/>
       <c r="L245" s="14"/>
       <c r="M245" s="14"/>
-      <c r="N245" s="17"/>
+      <c r="N245" s="19"/>
       <c r="O245" s="14"/>
+      <c r="P245" s="20"/>
+      <c r="Q245" s="14"/>
+      <c r="R245" s="21" t="str">
+        <f aca="false">IF(P245="","",P245+IF(N(Q245)&gt;0,MIN(ROUND(Параметры!$B$19/Q245*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S245" s="14"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="n">
@@ -9413,8 +11282,15 @@
       <c r="K246" s="14"/>
       <c r="L246" s="14"/>
       <c r="M246" s="14"/>
-      <c r="N246" s="17"/>
+      <c r="N246" s="19"/>
       <c r="O246" s="14"/>
+      <c r="P246" s="20"/>
+      <c r="Q246" s="14"/>
+      <c r="R246" s="21" t="str">
+        <f aca="false">IF(P246="","",P246+IF(N(Q246)&gt;0,MIN(ROUND(Параметры!$B$19/Q246*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S246" s="14"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="n">
@@ -9432,8 +11308,15 @@
       <c r="K247" s="14"/>
       <c r="L247" s="14"/>
       <c r="M247" s="14"/>
-      <c r="N247" s="17"/>
+      <c r="N247" s="19"/>
       <c r="O247" s="14"/>
+      <c r="P247" s="20"/>
+      <c r="Q247" s="14"/>
+      <c r="R247" s="21" t="str">
+        <f aca="false">IF(P247="","",P247+IF(N(Q247)&gt;0,MIN(ROUND(Параметры!$B$19/Q247*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S247" s="14"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="n">
@@ -9451,8 +11334,15 @@
       <c r="K248" s="14"/>
       <c r="L248" s="14"/>
       <c r="M248" s="14"/>
-      <c r="N248" s="17"/>
+      <c r="N248" s="19"/>
       <c r="O248" s="14"/>
+      <c r="P248" s="20"/>
+      <c r="Q248" s="14"/>
+      <c r="R248" s="21" t="str">
+        <f aca="false">IF(P248="","",P248+IF(N(Q248)&gt;0,MIN(ROUND(Параметры!$B$19/Q248*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S248" s="14"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="n">
@@ -9470,8 +11360,15 @@
       <c r="K249" s="14"/>
       <c r="L249" s="14"/>
       <c r="M249" s="14"/>
-      <c r="N249" s="17"/>
+      <c r="N249" s="19"/>
       <c r="O249" s="14"/>
+      <c r="P249" s="20"/>
+      <c r="Q249" s="14"/>
+      <c r="R249" s="21" t="str">
+        <f aca="false">IF(P249="","",P249+IF(N(Q249)&gt;0,MIN(ROUND(Параметры!$B$19/Q249*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S249" s="14"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="n">
@@ -9489,8 +11386,15 @@
       <c r="K250" s="14"/>
       <c r="L250" s="14"/>
       <c r="M250" s="14"/>
-      <c r="N250" s="17"/>
+      <c r="N250" s="19"/>
       <c r="O250" s="14"/>
+      <c r="P250" s="20"/>
+      <c r="Q250" s="14"/>
+      <c r="R250" s="21" t="str">
+        <f aca="false">IF(P250="","",P250+IF(N(Q250)&gt;0,MIN(ROUND(Параметры!$B$19/Q250*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S250" s="14"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="n">
@@ -9508,8 +11412,15 @@
       <c r="K251" s="14"/>
       <c r="L251" s="14"/>
       <c r="M251" s="14"/>
-      <c r="N251" s="17"/>
+      <c r="N251" s="19"/>
       <c r="O251" s="14"/>
+      <c r="P251" s="20"/>
+      <c r="Q251" s="14"/>
+      <c r="R251" s="21" t="str">
+        <f aca="false">IF(P251="","",P251+IF(N(Q251)&gt;0,MIN(ROUND(Параметры!$B$19/Q251*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S251" s="14"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="n">
@@ -9527,8 +11438,15 @@
       <c r="K252" s="14"/>
       <c r="L252" s="14"/>
       <c r="M252" s="14"/>
-      <c r="N252" s="17"/>
+      <c r="N252" s="19"/>
       <c r="O252" s="14"/>
+      <c r="P252" s="20"/>
+      <c r="Q252" s="14"/>
+      <c r="R252" s="21" t="str">
+        <f aca="false">IF(P252="","",P252+IF(N(Q252)&gt;0,MIN(ROUND(Параметры!$B$19/Q252*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S252" s="14"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="n">
@@ -9546,8 +11464,15 @@
       <c r="K253" s="14"/>
       <c r="L253" s="14"/>
       <c r="M253" s="14"/>
-      <c r="N253" s="17"/>
+      <c r="N253" s="19"/>
       <c r="O253" s="14"/>
+      <c r="P253" s="20"/>
+      <c r="Q253" s="14"/>
+      <c r="R253" s="21" t="str">
+        <f aca="false">IF(P253="","",P253+IF(N(Q253)&gt;0,MIN(ROUND(Параметры!$B$19/Q253*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S253" s="14"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="n">
@@ -9565,8 +11490,15 @@
       <c r="K254" s="14"/>
       <c r="L254" s="14"/>
       <c r="M254" s="14"/>
-      <c r="N254" s="17"/>
+      <c r="N254" s="19"/>
       <c r="O254" s="14"/>
+      <c r="P254" s="20"/>
+      <c r="Q254" s="14"/>
+      <c r="R254" s="21" t="str">
+        <f aca="false">IF(P254="","",P254+IF(N(Q254)&gt;0,MIN(ROUND(Параметры!$B$19/Q254*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S254" s="14"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="n">
@@ -9584,8 +11516,15 @@
       <c r="K255" s="14"/>
       <c r="L255" s="14"/>
       <c r="M255" s="14"/>
-      <c r="N255" s="17"/>
+      <c r="N255" s="19"/>
       <c r="O255" s="14"/>
+      <c r="P255" s="20"/>
+      <c r="Q255" s="14"/>
+      <c r="R255" s="21" t="str">
+        <f aca="false">IF(P255="","",P255+IF(N(Q255)&gt;0,MIN(ROUND(Параметры!$B$19/Q255*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S255" s="14"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="n">
@@ -9603,8 +11542,15 @@
       <c r="K256" s="14"/>
       <c r="L256" s="14"/>
       <c r="M256" s="14"/>
-      <c r="N256" s="17"/>
+      <c r="N256" s="19"/>
       <c r="O256" s="14"/>
+      <c r="P256" s="20"/>
+      <c r="Q256" s="14"/>
+      <c r="R256" s="21" t="str">
+        <f aca="false">IF(P256="","",P256+IF(N(Q256)&gt;0,MIN(ROUND(Параметры!$B$19/Q256*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S256" s="14"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="n">
@@ -9622,8 +11568,15 @@
       <c r="K257" s="14"/>
       <c r="L257" s="14"/>
       <c r="M257" s="14"/>
-      <c r="N257" s="17"/>
+      <c r="N257" s="19"/>
       <c r="O257" s="14"/>
+      <c r="P257" s="20"/>
+      <c r="Q257" s="14"/>
+      <c r="R257" s="21" t="str">
+        <f aca="false">IF(P257="","",P257+IF(N(Q257)&gt;0,MIN(ROUND(Параметры!$B$19/Q257*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S257" s="14"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="n">
@@ -9641,8 +11594,15 @@
       <c r="K258" s="14"/>
       <c r="L258" s="14"/>
       <c r="M258" s="14"/>
-      <c r="N258" s="17"/>
+      <c r="N258" s="19"/>
       <c r="O258" s="14"/>
+      <c r="P258" s="20"/>
+      <c r="Q258" s="14"/>
+      <c r="R258" s="21" t="str">
+        <f aca="false">IF(P258="","",P258+IF(N(Q258)&gt;0,MIN(ROUND(Параметры!$B$19/Q258*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S258" s="14"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="n">
@@ -9660,8 +11620,15 @@
       <c r="K259" s="14"/>
       <c r="L259" s="14"/>
       <c r="M259" s="14"/>
-      <c r="N259" s="17"/>
+      <c r="N259" s="19"/>
       <c r="O259" s="14"/>
+      <c r="P259" s="20"/>
+      <c r="Q259" s="14"/>
+      <c r="R259" s="21" t="str">
+        <f aca="false">IF(P259="","",P259+IF(N(Q259)&gt;0,MIN(ROUND(Параметры!$B$19/Q259*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S259" s="14"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="n">
@@ -9679,8 +11646,15 @@
       <c r="K260" s="14"/>
       <c r="L260" s="14"/>
       <c r="M260" s="14"/>
-      <c r="N260" s="17"/>
+      <c r="N260" s="19"/>
       <c r="O260" s="14"/>
+      <c r="P260" s="20"/>
+      <c r="Q260" s="14"/>
+      <c r="R260" s="21" t="str">
+        <f aca="false">IF(P260="","",P260+IF(N(Q260)&gt;0,MIN(ROUND(Параметры!$B$19/Q260*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S260" s="14"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="n">
@@ -9698,8 +11672,15 @@
       <c r="K261" s="14"/>
       <c r="L261" s="14"/>
       <c r="M261" s="14"/>
-      <c r="N261" s="17"/>
+      <c r="N261" s="19"/>
       <c r="O261" s="14"/>
+      <c r="P261" s="20"/>
+      <c r="Q261" s="14"/>
+      <c r="R261" s="21" t="str">
+        <f aca="false">IF(P261="","",P261+IF(N(Q261)&gt;0,MIN(ROUND(Параметры!$B$19/Q261*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S261" s="14"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="n">
@@ -9717,8 +11698,15 @@
       <c r="K262" s="14"/>
       <c r="L262" s="14"/>
       <c r="M262" s="14"/>
-      <c r="N262" s="17"/>
+      <c r="N262" s="19"/>
       <c r="O262" s="14"/>
+      <c r="P262" s="20"/>
+      <c r="Q262" s="14"/>
+      <c r="R262" s="21" t="str">
+        <f aca="false">IF(P262="","",P262+IF(N(Q262)&gt;0,MIN(ROUND(Параметры!$B$19/Q262*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S262" s="14"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="n">
@@ -9736,8 +11724,15 @@
       <c r="K263" s="14"/>
       <c r="L263" s="14"/>
       <c r="M263" s="14"/>
-      <c r="N263" s="17"/>
+      <c r="N263" s="19"/>
       <c r="O263" s="14"/>
+      <c r="P263" s="20"/>
+      <c r="Q263" s="14"/>
+      <c r="R263" s="21" t="str">
+        <f aca="false">IF(P263="","",P263+IF(N(Q263)&gt;0,MIN(ROUND(Параметры!$B$19/Q263*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S263" s="14"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="n">
@@ -9755,8 +11750,15 @@
       <c r="K264" s="14"/>
       <c r="L264" s="14"/>
       <c r="M264" s="14"/>
-      <c r="N264" s="17"/>
+      <c r="N264" s="19"/>
       <c r="O264" s="14"/>
+      <c r="P264" s="20"/>
+      <c r="Q264" s="14"/>
+      <c r="R264" s="21" t="str">
+        <f aca="false">IF(P264="","",P264+IF(N(Q264)&gt;0,MIN(ROUND(Параметры!$B$19/Q264*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S264" s="14"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="n">
@@ -9774,8 +11776,15 @@
       <c r="K265" s="14"/>
       <c r="L265" s="14"/>
       <c r="M265" s="14"/>
-      <c r="N265" s="17"/>
+      <c r="N265" s="19"/>
       <c r="O265" s="14"/>
+      <c r="P265" s="20"/>
+      <c r="Q265" s="14"/>
+      <c r="R265" s="21" t="str">
+        <f aca="false">IF(P265="","",P265+IF(N(Q265)&gt;0,MIN(ROUND(Параметры!$B$19/Q265*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S265" s="14"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="n">
@@ -9793,8 +11802,15 @@
       <c r="K266" s="14"/>
       <c r="L266" s="14"/>
       <c r="M266" s="14"/>
-      <c r="N266" s="17"/>
+      <c r="N266" s="19"/>
       <c r="O266" s="14"/>
+      <c r="P266" s="20"/>
+      <c r="Q266" s="14"/>
+      <c r="R266" s="21" t="str">
+        <f aca="false">IF(P266="","",P266+IF(N(Q266)&gt;0,MIN(ROUND(Параметры!$B$19/Q266*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S266" s="14"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="n">
@@ -9812,8 +11828,15 @@
       <c r="K267" s="14"/>
       <c r="L267" s="14"/>
       <c r="M267" s="14"/>
-      <c r="N267" s="17"/>
+      <c r="N267" s="19"/>
       <c r="O267" s="14"/>
+      <c r="P267" s="20"/>
+      <c r="Q267" s="14"/>
+      <c r="R267" s="21" t="str">
+        <f aca="false">IF(P267="","",P267+IF(N(Q267)&gt;0,MIN(ROUND(Параметры!$B$19/Q267*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S267" s="14"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="n">
@@ -9831,8 +11854,15 @@
       <c r="K268" s="14"/>
       <c r="L268" s="14"/>
       <c r="M268" s="14"/>
-      <c r="N268" s="17"/>
+      <c r="N268" s="19"/>
       <c r="O268" s="14"/>
+      <c r="P268" s="20"/>
+      <c r="Q268" s="14"/>
+      <c r="R268" s="21" t="str">
+        <f aca="false">IF(P268="","",P268+IF(N(Q268)&gt;0,MIN(ROUND(Параметры!$B$19/Q268*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S268" s="14"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="7" t="n">
@@ -9850,8 +11880,15 @@
       <c r="K269" s="14"/>
       <c r="L269" s="14"/>
       <c r="M269" s="14"/>
-      <c r="N269" s="17"/>
+      <c r="N269" s="19"/>
       <c r="O269" s="14"/>
+      <c r="P269" s="20"/>
+      <c r="Q269" s="14"/>
+      <c r="R269" s="21" t="str">
+        <f aca="false">IF(P269="","",P269+IF(N(Q269)&gt;0,MIN(ROUND(Параметры!$B$19/Q269*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S269" s="14"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="7" t="n">
@@ -9869,8 +11906,15 @@
       <c r="K270" s="14"/>
       <c r="L270" s="14"/>
       <c r="M270" s="14"/>
-      <c r="N270" s="17"/>
+      <c r="N270" s="19"/>
       <c r="O270" s="14"/>
+      <c r="P270" s="20"/>
+      <c r="Q270" s="14"/>
+      <c r="R270" s="21" t="str">
+        <f aca="false">IF(P270="","",P270+IF(N(Q270)&gt;0,MIN(ROUND(Параметры!$B$19/Q270*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S270" s="14"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="7" t="n">
@@ -9888,8 +11932,15 @@
       <c r="K271" s="14"/>
       <c r="L271" s="14"/>
       <c r="M271" s="14"/>
-      <c r="N271" s="17"/>
+      <c r="N271" s="19"/>
       <c r="O271" s="14"/>
+      <c r="P271" s="20"/>
+      <c r="Q271" s="14"/>
+      <c r="R271" s="21" t="str">
+        <f aca="false">IF(P271="","",P271+IF(N(Q271)&gt;0,MIN(ROUND(Параметры!$B$19/Q271*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S271" s="14"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="7" t="n">
@@ -9907,8 +11958,15 @@
       <c r="K272" s="14"/>
       <c r="L272" s="14"/>
       <c r="M272" s="14"/>
-      <c r="N272" s="17"/>
+      <c r="N272" s="19"/>
       <c r="O272" s="14"/>
+      <c r="P272" s="20"/>
+      <c r="Q272" s="14"/>
+      <c r="R272" s="21" t="str">
+        <f aca="false">IF(P272="","",P272+IF(N(Q272)&gt;0,MIN(ROUND(Параметры!$B$19/Q272*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S272" s="14"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="7" t="n">
@@ -9926,8 +11984,15 @@
       <c r="K273" s="14"/>
       <c r="L273" s="14"/>
       <c r="M273" s="14"/>
-      <c r="N273" s="17"/>
+      <c r="N273" s="19"/>
       <c r="O273" s="14"/>
+      <c r="P273" s="20"/>
+      <c r="Q273" s="14"/>
+      <c r="R273" s="21" t="str">
+        <f aca="false">IF(P273="","",P273+IF(N(Q273)&gt;0,MIN(ROUND(Параметры!$B$19/Q273*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S273" s="14"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="7" t="n">
@@ -9945,8 +12010,15 @@
       <c r="K274" s="14"/>
       <c r="L274" s="14"/>
       <c r="M274" s="14"/>
-      <c r="N274" s="17"/>
+      <c r="N274" s="19"/>
       <c r="O274" s="14"/>
+      <c r="P274" s="20"/>
+      <c r="Q274" s="14"/>
+      <c r="R274" s="21" t="str">
+        <f aca="false">IF(P274="","",P274+IF(N(Q274)&gt;0,MIN(ROUND(Параметры!$B$19/Q274*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S274" s="14"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="7" t="n">
@@ -9964,8 +12036,15 @@
       <c r="K275" s="14"/>
       <c r="L275" s="14"/>
       <c r="M275" s="14"/>
-      <c r="N275" s="17"/>
+      <c r="N275" s="19"/>
       <c r="O275" s="14"/>
+      <c r="P275" s="20"/>
+      <c r="Q275" s="14"/>
+      <c r="R275" s="21" t="str">
+        <f aca="false">IF(P275="","",P275+IF(N(Q275)&gt;0,MIN(ROUND(Параметры!$B$19/Q275*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S275" s="14"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="7" t="n">
@@ -9983,8 +12062,15 @@
       <c r="K276" s="14"/>
       <c r="L276" s="14"/>
       <c r="M276" s="14"/>
-      <c r="N276" s="17"/>
+      <c r="N276" s="19"/>
       <c r="O276" s="14"/>
+      <c r="P276" s="20"/>
+      <c r="Q276" s="14"/>
+      <c r="R276" s="21" t="str">
+        <f aca="false">IF(P276="","",P276+IF(N(Q276)&gt;0,MIN(ROUND(Параметры!$B$19/Q276*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S276" s="14"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="7" t="n">
@@ -10002,8 +12088,15 @@
       <c r="K277" s="14"/>
       <c r="L277" s="14"/>
       <c r="M277" s="14"/>
-      <c r="N277" s="17"/>
+      <c r="N277" s="19"/>
       <c r="O277" s="14"/>
+      <c r="P277" s="20"/>
+      <c r="Q277" s="14"/>
+      <c r="R277" s="21" t="str">
+        <f aca="false">IF(P277="","",P277+IF(N(Q277)&gt;0,MIN(ROUND(Параметры!$B$19/Q277*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S277" s="14"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="7" t="n">
@@ -10021,8 +12114,15 @@
       <c r="K278" s="14"/>
       <c r="L278" s="14"/>
       <c r="M278" s="14"/>
-      <c r="N278" s="17"/>
+      <c r="N278" s="19"/>
       <c r="O278" s="14"/>
+      <c r="P278" s="20"/>
+      <c r="Q278" s="14"/>
+      <c r="R278" s="21" t="str">
+        <f aca="false">IF(P278="","",P278+IF(N(Q278)&gt;0,MIN(ROUND(Параметры!$B$19/Q278*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S278" s="14"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="7" t="n">
@@ -10040,8 +12140,15 @@
       <c r="K279" s="14"/>
       <c r="L279" s="14"/>
       <c r="M279" s="14"/>
-      <c r="N279" s="17"/>
+      <c r="N279" s="19"/>
       <c r="O279" s="14"/>
+      <c r="P279" s="20"/>
+      <c r="Q279" s="14"/>
+      <c r="R279" s="21" t="str">
+        <f aca="false">IF(P279="","",P279+IF(N(Q279)&gt;0,MIN(ROUND(Параметры!$B$19/Q279*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S279" s="14"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="7" t="n">
@@ -10059,8 +12166,15 @@
       <c r="K280" s="14"/>
       <c r="L280" s="14"/>
       <c r="M280" s="14"/>
-      <c r="N280" s="17"/>
+      <c r="N280" s="19"/>
       <c r="O280" s="14"/>
+      <c r="P280" s="20"/>
+      <c r="Q280" s="14"/>
+      <c r="R280" s="21" t="str">
+        <f aca="false">IF(P280="","",P280+IF(N(Q280)&gt;0,MIN(ROUND(Параметры!$B$19/Q280*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S280" s="14"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="7" t="n">
@@ -10078,8 +12192,15 @@
       <c r="K281" s="14"/>
       <c r="L281" s="14"/>
       <c r="M281" s="14"/>
-      <c r="N281" s="17"/>
+      <c r="N281" s="19"/>
       <c r="O281" s="14"/>
+      <c r="P281" s="20"/>
+      <c r="Q281" s="14"/>
+      <c r="R281" s="21" t="str">
+        <f aca="false">IF(P281="","",P281+IF(N(Q281)&gt;0,MIN(ROUND(Параметры!$B$19/Q281*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S281" s="14"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="7" t="n">
@@ -10097,8 +12218,15 @@
       <c r="K282" s="14"/>
       <c r="L282" s="14"/>
       <c r="M282" s="14"/>
-      <c r="N282" s="17"/>
+      <c r="N282" s="19"/>
       <c r="O282" s="14"/>
+      <c r="P282" s="20"/>
+      <c r="Q282" s="14"/>
+      <c r="R282" s="21" t="str">
+        <f aca="false">IF(P282="","",P282+IF(N(Q282)&gt;0,MIN(ROUND(Параметры!$B$19/Q282*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S282" s="14"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="7" t="n">
@@ -10116,8 +12244,15 @@
       <c r="K283" s="14"/>
       <c r="L283" s="14"/>
       <c r="M283" s="14"/>
-      <c r="N283" s="17"/>
+      <c r="N283" s="19"/>
       <c r="O283" s="14"/>
+      <c r="P283" s="20"/>
+      <c r="Q283" s="14"/>
+      <c r="R283" s="21" t="str">
+        <f aca="false">IF(P283="","",P283+IF(N(Q283)&gt;0,MIN(ROUND(Параметры!$B$19/Q283*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S283" s="14"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="7" t="n">
@@ -10135,8 +12270,15 @@
       <c r="K284" s="14"/>
       <c r="L284" s="14"/>
       <c r="M284" s="14"/>
-      <c r="N284" s="17"/>
+      <c r="N284" s="19"/>
       <c r="O284" s="14"/>
+      <c r="P284" s="20"/>
+      <c r="Q284" s="14"/>
+      <c r="R284" s="21" t="str">
+        <f aca="false">IF(P284="","",P284+IF(N(Q284)&gt;0,MIN(ROUND(Параметры!$B$19/Q284*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S284" s="14"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="7" t="n">
@@ -10154,8 +12296,15 @@
       <c r="K285" s="14"/>
       <c r="L285" s="14"/>
       <c r="M285" s="14"/>
-      <c r="N285" s="17"/>
+      <c r="N285" s="19"/>
       <c r="O285" s="14"/>
+      <c r="P285" s="20"/>
+      <c r="Q285" s="14"/>
+      <c r="R285" s="21" t="str">
+        <f aca="false">IF(P285="","",P285+IF(N(Q285)&gt;0,MIN(ROUND(Параметры!$B$19/Q285*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S285" s="14"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="7" t="n">
@@ -10173,8 +12322,15 @@
       <c r="K286" s="14"/>
       <c r="L286" s="14"/>
       <c r="M286" s="14"/>
-      <c r="N286" s="17"/>
+      <c r="N286" s="19"/>
       <c r="O286" s="14"/>
+      <c r="P286" s="20"/>
+      <c r="Q286" s="14"/>
+      <c r="R286" s="21" t="str">
+        <f aca="false">IF(P286="","",P286+IF(N(Q286)&gt;0,MIN(ROUND(Параметры!$B$19/Q286*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S286" s="14"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="7" t="n">
@@ -10192,8 +12348,15 @@
       <c r="K287" s="14"/>
       <c r="L287" s="14"/>
       <c r="M287" s="14"/>
-      <c r="N287" s="17"/>
+      <c r="N287" s="19"/>
       <c r="O287" s="14"/>
+      <c r="P287" s="20"/>
+      <c r="Q287" s="14"/>
+      <c r="R287" s="21" t="str">
+        <f aca="false">IF(P287="","",P287+IF(N(Q287)&gt;0,MIN(ROUND(Параметры!$B$19/Q287*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S287" s="14"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="7" t="n">
@@ -10211,8 +12374,15 @@
       <c r="K288" s="14"/>
       <c r="L288" s="14"/>
       <c r="M288" s="14"/>
-      <c r="N288" s="17"/>
+      <c r="N288" s="19"/>
       <c r="O288" s="14"/>
+      <c r="P288" s="20"/>
+      <c r="Q288" s="14"/>
+      <c r="R288" s="21" t="str">
+        <f aca="false">IF(P288="","",P288+IF(N(Q288)&gt;0,MIN(ROUND(Параметры!$B$19/Q288*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S288" s="14"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="7" t="n">
@@ -10230,8 +12400,15 @@
       <c r="K289" s="14"/>
       <c r="L289" s="14"/>
       <c r="M289" s="14"/>
-      <c r="N289" s="17"/>
+      <c r="N289" s="19"/>
       <c r="O289" s="14"/>
+      <c r="P289" s="20"/>
+      <c r="Q289" s="14"/>
+      <c r="R289" s="21" t="str">
+        <f aca="false">IF(P289="","",P289+IF(N(Q289)&gt;0,MIN(ROUND(Параметры!$B$19/Q289*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S289" s="14"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="7" t="n">
@@ -10249,8 +12426,15 @@
       <c r="K290" s="14"/>
       <c r="L290" s="14"/>
       <c r="M290" s="14"/>
-      <c r="N290" s="17"/>
+      <c r="N290" s="19"/>
       <c r="O290" s="14"/>
+      <c r="P290" s="20"/>
+      <c r="Q290" s="14"/>
+      <c r="R290" s="21" t="str">
+        <f aca="false">IF(P290="","",P290+IF(N(Q290)&gt;0,MIN(ROUND(Параметры!$B$19/Q290*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S290" s="14"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="7" t="n">
@@ -10268,8 +12452,15 @@
       <c r="K291" s="14"/>
       <c r="L291" s="14"/>
       <c r="M291" s="14"/>
-      <c r="N291" s="17"/>
+      <c r="N291" s="19"/>
       <c r="O291" s="14"/>
+      <c r="P291" s="20"/>
+      <c r="Q291" s="14"/>
+      <c r="R291" s="21" t="str">
+        <f aca="false">IF(P291="","",P291+IF(N(Q291)&gt;0,MIN(ROUND(Параметры!$B$19/Q291*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S291" s="14"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="7" t="n">
@@ -10287,8 +12478,15 @@
       <c r="K292" s="14"/>
       <c r="L292" s="14"/>
       <c r="M292" s="14"/>
-      <c r="N292" s="17"/>
+      <c r="N292" s="19"/>
       <c r="O292" s="14"/>
+      <c r="P292" s="20"/>
+      <c r="Q292" s="14"/>
+      <c r="R292" s="21" t="str">
+        <f aca="false">IF(P292="","",P292+IF(N(Q292)&gt;0,MIN(ROUND(Параметры!$B$19/Q292*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S292" s="14"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="7" t="n">
@@ -10306,8 +12504,15 @@
       <c r="K293" s="14"/>
       <c r="L293" s="14"/>
       <c r="M293" s="14"/>
-      <c r="N293" s="17"/>
+      <c r="N293" s="19"/>
       <c r="O293" s="14"/>
+      <c r="P293" s="20"/>
+      <c r="Q293" s="14"/>
+      <c r="R293" s="21" t="str">
+        <f aca="false">IF(P293="","",P293+IF(N(Q293)&gt;0,MIN(ROUND(Параметры!$B$19/Q293*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S293" s="14"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="7" t="n">
@@ -10325,8 +12530,15 @@
       <c r="K294" s="14"/>
       <c r="L294" s="14"/>
       <c r="M294" s="14"/>
-      <c r="N294" s="17"/>
+      <c r="N294" s="19"/>
       <c r="O294" s="14"/>
+      <c r="P294" s="20"/>
+      <c r="Q294" s="14"/>
+      <c r="R294" s="21" t="str">
+        <f aca="false">IF(P294="","",P294+IF(N(Q294)&gt;0,MIN(ROUND(Параметры!$B$19/Q294*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S294" s="14"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="7" t="n">
@@ -10344,8 +12556,15 @@
       <c r="K295" s="14"/>
       <c r="L295" s="14"/>
       <c r="M295" s="14"/>
-      <c r="N295" s="17"/>
+      <c r="N295" s="19"/>
       <c r="O295" s="14"/>
+      <c r="P295" s="20"/>
+      <c r="Q295" s="14"/>
+      <c r="R295" s="21" t="str">
+        <f aca="false">IF(P295="","",P295+IF(N(Q295)&gt;0,MIN(ROUND(Параметры!$B$19/Q295*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S295" s="14"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="7" t="n">
@@ -10363,8 +12582,15 @@
       <c r="K296" s="14"/>
       <c r="L296" s="14"/>
       <c r="M296" s="14"/>
-      <c r="N296" s="17"/>
+      <c r="N296" s="19"/>
       <c r="O296" s="14"/>
+      <c r="P296" s="20"/>
+      <c r="Q296" s="14"/>
+      <c r="R296" s="21" t="str">
+        <f aca="false">IF(P296="","",P296+IF(N(Q296)&gt;0,MIN(ROUND(Параметры!$B$19/Q296*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S296" s="14"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="7" t="n">
@@ -10382,8 +12608,15 @@
       <c r="K297" s="14"/>
       <c r="L297" s="14"/>
       <c r="M297" s="14"/>
-      <c r="N297" s="17"/>
+      <c r="N297" s="19"/>
       <c r="O297" s="14"/>
+      <c r="P297" s="20"/>
+      <c r="Q297" s="14"/>
+      <c r="R297" s="21" t="str">
+        <f aca="false">IF(P297="","",P297+IF(N(Q297)&gt;0,MIN(ROUND(Параметры!$B$19/Q297*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S297" s="14"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="7" t="n">
@@ -10401,8 +12634,15 @@
       <c r="K298" s="14"/>
       <c r="L298" s="14"/>
       <c r="M298" s="14"/>
-      <c r="N298" s="17"/>
+      <c r="N298" s="19"/>
       <c r="O298" s="14"/>
+      <c r="P298" s="20"/>
+      <c r="Q298" s="14"/>
+      <c r="R298" s="21" t="str">
+        <f aca="false">IF(P298="","",P298+IF(N(Q298)&gt;0,MIN(ROUND(Параметры!$B$19/Q298*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S298" s="14"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="7" t="n">
@@ -10420,8 +12660,15 @@
       <c r="K299" s="14"/>
       <c r="L299" s="14"/>
       <c r="M299" s="14"/>
-      <c r="N299" s="17"/>
+      <c r="N299" s="19"/>
       <c r="O299" s="14"/>
+      <c r="P299" s="20"/>
+      <c r="Q299" s="14"/>
+      <c r="R299" s="21" t="str">
+        <f aca="false">IF(P299="","",P299+IF(N(Q299)&gt;0,MIN(ROUND(Параметры!$B$19/Q299*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S299" s="14"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="7" t="n">
@@ -10439,8 +12686,15 @@
       <c r="K300" s="14"/>
       <c r="L300" s="14"/>
       <c r="M300" s="14"/>
-      <c r="N300" s="17"/>
+      <c r="N300" s="19"/>
       <c r="O300" s="14"/>
+      <c r="P300" s="20"/>
+      <c r="Q300" s="14"/>
+      <c r="R300" s="21" t="str">
+        <f aca="false">IF(P300="","",P300+IF(N(Q300)&gt;0,MIN(ROUND(Параметры!$B$19/Q300*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S300" s="14"/>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="7" t="n">
@@ -10458,8 +12712,15 @@
       <c r="K301" s="14"/>
       <c r="L301" s="14"/>
       <c r="M301" s="14"/>
-      <c r="N301" s="17"/>
+      <c r="N301" s="19"/>
       <c r="O301" s="14"/>
+      <c r="P301" s="20"/>
+      <c r="Q301" s="14"/>
+      <c r="R301" s="21" t="str">
+        <f aca="false">IF(P301="","",P301+IF(N(Q301)&gt;0,MIN(ROUND(Параметры!$B$19/Q301*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S301" s="14"/>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="7" t="n">
@@ -10477,27 +12738,44 @@
       <c r="K302" s="14"/>
       <c r="L302" s="14"/>
       <c r="M302" s="14"/>
-      <c r="N302" s="17"/>
+      <c r="N302" s="19"/>
       <c r="O302" s="14"/>
+      <c r="P302" s="20"/>
+      <c r="Q302" s="14"/>
+      <c r="R302" s="21" t="str">
+        <f aca="false">IF(P302="","",P302+IF(N(Q302)&gt;0,MIN(ROUND(Параметры!$B$19/Q302*30,0),365),180)-14)</f>
+        <v/>
+      </c>
+      <c r="S302" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="M3:N302">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND($N3&lt;&gt;"",$N3&lt;=TODAY(),$H3&lt;&gt;"7. В обработке",$H3&lt;&gt;"Отказ")</formula>
+      <formula>AND($N3&lt;&gt;"",$N3&lt;=TODAY(),$H3&lt;&gt;"12. Закрыт",$H3&lt;&gt;"Отказ")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H302">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>"Проблема"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I302">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R302">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>AND(ISNUMBER($R3),$R3&gt;=TODAY()-14,$R3&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D3:D302" type="list">
-      <formula1>"чат,купил сразу,звонок"</formula1>
+      <formula1>"чат,купил сразу,звонок,повторный"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H3:H302" type="list">
-      <formula1>"1. Новый,2. Ждём VIN,3. Подбор,4. Предложение,5. Думает,6. Ждём оплату,7. В обработке,Отказ"</formula1>
+      <formula1>"1. Новый,2. Ждём VIN,3. Подбор,4. Предложение,5. Думает,6. Ждём оплату,7. В обработке,8. Детали у нас,9. Собран,10. Отправлен,11. Получен,12. Закрыт,Проблема,Отказ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K3:K302" type="list">
@@ -10539,22 +12817,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -10568,7 +12846,7 @@
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>4740</v>
@@ -10580,7 +12858,7 @@
         <v>5290</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -10594,7 +12872,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>3365.09</v>
@@ -10606,7 +12884,7 @@
         <v>3624.6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -10620,13 +12898,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" s="20" t="n">
+        <v>226</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -10640,7 +12918,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B7" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$M:$M,Киты!$B:$B,"ТО",Киты!$M:$M,"&gt;0"),"")</f>
@@ -10657,7 +12935,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B8" s="9" t="str">
         <f aca="false">IFERROR(AVERAGEIFS(Киты!$I:$I,Киты!$B:$B,"ТО",Киты!$I:$I,"&gt;0"),"")</f>
@@ -10674,14 +12952,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">(Параметры!$B$13+Параметры!$B$14+Параметры!$B$15+Параметры!$B$16+Параметры!$B$17)</f>
         <v>12783</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -10695,7 +12973,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">IF(B4="","",B4-(B5+Параметры!$B$3)-$B$6*B4*Параметры!$B$7-(1-$B$6)*(B4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-B5*Параметры!$B$9)</f>
@@ -10712,7 +12990,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">IF(B10="","",IF(B10&lt;=0,"не окупается",ROUNDUP($B$9/B10,0)))</f>
@@ -10727,7 +13005,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -10741,22 +13019,22 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>30</v>
@@ -10771,29 +13049,29 @@
         <v>33</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="21" t="n">
+        <v>245</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="C14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="21" t="n">
+      <c r="C14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="9" t="n">
@@ -10839,15 +13117,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="21" t="n">
+        <v>246</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
@@ -10893,15 +13171,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="21" t="n">
+        <v>247</v>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="26" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="9" t="n">
@@ -10947,15 +13225,15 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" s="21" t="n">
+        <v>248</v>
+      </c>
+      <c r="B17" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="26" t="n">
         <v>5</v>
       </c>
       <c r="E17" s="9" t="n">
@@ -11001,15 +13279,15 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B18" s="21" t="n">
+        <v>249</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="26" t="n">
         <v>10</v>
       </c>
       <c r="E18" s="9" t="n">
@@ -11055,15 +13333,15 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B19" s="21" t="n">
+        <v>250</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <v>30</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="26" t="n">
         <v>15</v>
       </c>
       <c r="E19" s="9" t="n">
@@ -11109,15 +13387,15 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="21" t="n">
+        <v>251</v>
+      </c>
+      <c r="B20" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="26" t="n">
         <v>20</v>
       </c>
       <c r="E20" s="9" t="n">
@@ -11162,8 +13440,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>240</v>
+      <c r="A22" s="27" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -11195,7 +13473,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -11205,217 +13483,228 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="23" t="n">
+        <v>256</v>
+      </c>
+      <c r="B2" s="28" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>264</v>
+      </c>
+      <c r="B6" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>266</v>
+      </c>
+      <c r="B7" s="28" t="n">
         <v>0.065</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>270</v>
+      </c>
+      <c r="B9" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B10" s="24" t="n">
+        <v>272</v>
+      </c>
+      <c r="B10" s="29" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B11" s="23" t="n">
+        <v>274</v>
+      </c>
+      <c r="B11" s="28" t="n">
         <v>0.007</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>4783</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>1500</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>6000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>500</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B18" s="24" t="n">
+        <v>288</v>
+      </c>
+      <c r="B18" s="29" t="n">
         <v>20</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="11" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="11" t="n">
         <f aca="false">($B$13+$B$14+$B$15+$B$16+$B$17)/MAX(1,$B$18)</f>
         <v>639.15</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
-        <v>280</v>
+      <c r="C20" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="27" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -11458,107 +13747,107 @@
         <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>166</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="D2" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G2" s="27" t="n">
+      <c r="E2" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="G2" s="32" t="n">
         <v>460</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27" t="n">
+      <c r="H2" s="32"/>
+      <c r="I2" s="32" t="n">
         <v>445</v>
       </c>
-      <c r="J2" s="27" t="n">
+      <c r="J2" s="32" t="n">
         <v>430</v>
       </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27" t="n">
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32" t="n">
         <v>470</v>
       </c>
-      <c r="O2" s="27"/>
-      <c r="P2" s="28" t="n">
+      <c r="O2" s="32"/>
+      <c r="P2" s="33" t="n">
         <f aca="false">IF(COUNT(G2:O2)=0,"",MIN(G2:O2))</f>
         <v>430</v>
       </c>
-      <c r="Q2" s="25" t="str">
+      <c r="Q2" s="30" t="str">
         <f aca="false">IF(P2="","",INDEX($G$1:$O$1,MATCH(P2,G2:O2,0)))</f>
         <v>Росско</v>
       </c>
-      <c r="R2" s="28" t="n">
+      <c r="R2" s="33" t="n">
         <f aca="false">IF(P2="",0,P2*D2)</f>
         <v>430</v>
       </c>
-      <c r="S2" s="29" t="s">
-        <v>299</v>
+      <c r="S2" s="34" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11570,7 +13859,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>1</v>
@@ -11599,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11611,7 +13900,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -11650,7 +13939,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1</v>
@@ -11689,7 +13978,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
@@ -11728,7 +14017,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
@@ -11767,7 +14056,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
@@ -11796,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11808,7 +14097,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
@@ -11847,7 +14136,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
@@ -11886,7 +14175,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
@@ -11925,7 +14214,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>1</v>
@@ -11964,7 +14253,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>1</v>
@@ -11993,7 +14282,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12005,7 +14294,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>1</v>
@@ -12044,7 +14333,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>1</v>
@@ -12083,7 +14372,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>1</v>
@@ -12122,7 +14411,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>1</v>
@@ -12161,7 +14450,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
@@ -12190,7 +14479,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12202,7 +14491,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -12241,7 +14530,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -12280,7 +14569,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>1</v>
@@ -12319,7 +14608,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
@@ -12358,7 +14647,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>1</v>
@@ -12387,7 +14676,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12399,7 +14688,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
@@ -12438,7 +14727,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>1</v>
@@ -12477,7 +14766,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>1</v>
@@ -12516,7 +14805,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>1</v>
@@ -12555,7 +14844,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
@@ -12584,7 +14873,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12596,7 +14885,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>1</v>
@@ -12635,7 +14924,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>1</v>
@@ -12674,7 +14963,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>1</v>
@@ -12713,7 +15002,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
@@ -12752,7 +15041,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>1</v>
@@ -12781,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12793,7 +15082,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
@@ -12822,7 +15111,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12834,7 +15123,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>1</v>
@@ -12873,7 +15162,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
@@ -12912,7 +15201,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>1</v>
@@ -12951,7 +15240,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>1</v>
@@ -12990,7 +15279,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>1</v>
@@ -13019,7 +15308,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13031,7 +15320,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
@@ -13060,7 +15349,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13072,7 +15361,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>1</v>
@@ -13111,7 +15400,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
@@ -13150,7 +15439,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>1</v>
@@ -13189,7 +15478,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>1</v>
@@ -13228,7 +15517,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>1</v>
@@ -13257,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13269,7 +15558,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
@@ -13298,7 +15587,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13310,7 +15599,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>1</v>
@@ -13349,7 +15638,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>1</v>
@@ -13388,7 +15677,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>1</v>
@@ -13427,7 +15716,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>1</v>
@@ -13466,7 +15755,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>1</v>
@@ -13495,7 +15784,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13507,7 +15796,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
@@ -13536,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13548,7 +15837,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>
@@ -13587,7 +15876,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>1</v>
@@ -13626,7 +15915,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1</v>
@@ -13665,7 +15954,7 @@
         <v>Chery Tiggo 7 Pro 1.5T</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>1</v>
@@ -13704,7 +15993,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>1</v>
@@ -13733,7 +16022,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13745,7 +16034,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
@@ -13774,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13786,7 +16075,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>1</v>
@@ -13825,7 +16114,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>1</v>
@@ -13864,7 +16153,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>1</v>
@@ -13903,7 +16192,7 @@
         <v>Chery Tiggo 4 Pro 1.5T</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>1</v>
@@ -13942,7 +16231,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>1</v>
@@ -13971,7 +16260,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13983,7 +16272,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
@@ -14012,7 +16301,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14024,7 +16313,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>1</v>
@@ -14063,7 +16352,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>1</v>
@@ -14102,7 +16391,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>1</v>
@@ -14141,7 +16430,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>1</v>
@@ -14180,13 +16469,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="12"/>
@@ -14211,7 +16500,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="8" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14223,13 +16512,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="12"/>
@@ -14254,7 +16543,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14266,13 +16555,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="12"/>
@@ -14297,7 +16586,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14309,13 +16598,13 @@
         <v>Kia Picanto 1.0 / 1.2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="12"/>
@@ -14340,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14352,13 +16641,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="12"/>
@@ -14383,7 +16672,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14395,13 +16684,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F74" s="14"/>
       <c r="G74" s="12"/>
@@ -14426,7 +16715,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="8" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14438,13 +16727,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="F75" s="14"/>
       <c r="G75" s="12"/>
@@ -14469,7 +16758,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14481,13 +16770,13 @@
         <v>VW Jetta</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="F76" s="14"/>
       <c r="G76" s="12"/>
@@ -14512,7 +16801,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14524,7 +16813,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>1</v>
@@ -14553,7 +16842,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14565,7 +16854,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>1</v>
@@ -14604,7 +16893,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>1</v>
@@ -14643,7 +16932,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
@@ -14672,7 +16961,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14684,7 +16973,7 @@
         <v>Hyundai Solaris 2010–2017</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -14713,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14725,7 +17014,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>1</v>
@@ -14754,7 +17043,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14766,7 +17055,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>1</v>
@@ -14805,7 +17094,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>1</v>
@@ -14844,7 +17133,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -14873,7 +17162,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14885,7 +17174,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -14914,7 +17203,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14926,7 +17215,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>1</v>
@@ -14955,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14967,7 +17256,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>1</v>
@@ -15006,7 +17295,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>1</v>
@@ -15045,7 +17334,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -15074,7 +17363,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15086,7 +17375,7 @@
         <v>Kia Rio 2011–2017</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -15115,7 +17404,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15127,7 +17416,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>1</v>
@@ -15156,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15168,7 +17457,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>1</v>
@@ -15207,7 +17496,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>1</v>
@@ -15246,7 +17535,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -15275,7 +17564,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15287,7 +17576,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -15316,7 +17605,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15328,7 +17617,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>1</v>
@@ -15357,7 +17646,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15369,7 +17658,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>1</v>
@@ -15408,7 +17697,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>1</v>
@@ -15447,7 +17736,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0</v>
@@ -15476,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15488,7 +17777,7 @@
         <v>VW Polo 1.6 CFNA</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0</v>
@@ -15517,7 +17806,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15529,7 +17818,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>1</v>
@@ -15568,7 +17857,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0</v>
@@ -15597,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15609,7 +17898,7 @@
         <v>VW Polo 1.6 CWVA</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0</v>
@@ -15638,7 +17927,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15650,7 +17939,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>1</v>
@@ -15679,7 +17968,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15691,7 +17980,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>1</v>
@@ -15730,7 +18019,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>1</v>
@@ -15769,7 +18058,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0</v>
@@ -15798,7 +18087,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15810,7 +18099,7 @@
         <v>Haval Jolion 1.5T</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0</v>
@@ -15839,7 +18128,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15851,7 +18140,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>1</v>
@@ -15880,7 +18169,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15892,7 +18181,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>1</v>
@@ -15931,7 +18220,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>1</v>
@@ -15970,7 +18259,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0</v>
@@ -15999,7 +18288,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16011,7 +18300,7 @@
         <v>Haval F7 / F7x 1.5T</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0</v>
@@ -16040,7 +18329,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16052,7 +18341,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>1</v>
@@ -16081,7 +18370,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16093,7 +18382,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>1</v>
@@ -16132,7 +18421,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>1</v>
@@ -16171,7 +18460,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0</v>
@@ -16200,7 +18489,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16212,7 +18501,7 @@
         <v>Haval F7 / F7x 2.0T</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0</v>
@@ -16241,7 +18530,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16253,7 +18542,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>1</v>
@@ -16282,7 +18571,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16294,7 +18583,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>1</v>
@@ -16333,7 +18622,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>1</v>
@@ -16372,7 +18661,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0</v>
@@ -16401,7 +18690,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16413,7 +18702,7 @@
         <v>Chery Tiggo 7 Pro / 4 Pro 1.5T</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0</v>
@@ -16442,7 +18731,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16454,16 +18743,16 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
@@ -16487,7 +18776,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16499,7 +18788,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>1</v>
@@ -16528,7 +18817,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16540,7 +18829,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0</v>
@@ -16569,7 +18858,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16581,7 +18870,7 @@
         <v>Geely Coolray 1.5T</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0</v>
@@ -16610,7 +18899,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16622,16 +18911,16 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D129" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="G129" s="12"/>
       <c r="H129" s="12"/>
@@ -16655,7 +18944,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="8" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16667,16 +18956,16 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D130" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F130" s="14" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G130" s="12"/>
       <c r="H130" s="12"/>
@@ -16700,7 +18989,7 @@
         <v>0</v>
       </c>
       <c r="S130" s="8" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16712,7 +19001,7 @@
         <v>Kia Rio 2017–2021</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D131" s="14" t="n">
         <v>1</v>
@@ -16741,7 +19030,7 @@
         <v>0</v>
       </c>
       <c r="S131" s="8" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16753,16 +19042,16 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D132" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F132" s="14" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="G132" s="12"/>
       <c r="H132" s="12"/>
@@ -16786,7 +19075,7 @@
         <v>0</v>
       </c>
       <c r="S132" s="8" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16798,16 +19087,16 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D133" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F133" s="14" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G133" s="12"/>
       <c r="H133" s="12"/>
@@ -16831,7 +19120,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="8" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16843,7 +19132,7 @@
         <v>Hyundai Solaris 2017–2022</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D134" s="14" t="n">
         <v>1</v>
@@ -16872,7 +19161,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="8" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -16909,226 +19198,226 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
+        <v>374</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
+        <v>366</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -17169,7 +19458,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -17178,197 +19467,197 @@
         <v>19</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/avito/zapkit-zakupka.xlsx
+++ b/avito/zapkit-zakupka.xlsx
@@ -52,7 +52,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">База — по наценке с листа «Параметры» или цена по рынку из колонки Y, если она есть. Сверху — «Повышение цен» с листа «Параметры», затем округление до …90.</t>
+          <t xml:space="preserve">Если в колонке Y есть цена по рынку — берётся она. Иначе — наценка и повышение цен с листа «Параметры», округление до …90.</t>
         </r>
       </text>
     </comment>
@@ -88,7 +88,31 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Для китов, где цену ставим по рынку, а не по наценке: впишите цену, по которой конечный покупатель берёт то же самое на маркетплейсах. Повышение цен добавится сверху. Пусто — цена по наценке.</t>
+          <t xml:space="preserve">Цена впритык к рынку: сложите типичные розничные цены тех же деталей у других продавцов и округлите вниз до …90. Это и есть цена кита. Пусто — цена по наценке.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Впритык к рынку (сентябрь 2026): масло Hyundai/Kia 5W-30 4 л в рознице 2 187–3 109 ₽ (≈2 650), фильтры AMD масляный ≈300, AMD воздушный ≈700, салонный ≈450 (оценка по похожим позициям). Итого по отдельности ≈4 100 ₽ → 4 090 ₽.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Впритык к рынку (сентябрь 2026): масло Teboil Diamond Multi 5W-40 4 л в рознице 3 290–3 950 ₽ (≈3 675), масляный фильтр AMD ≈350 (309–422), воздушный BRAVE ≈500 и салонный BRAVE ≈450 (оценка, от 410 ₽). Итого по отдельности ≈4 975 ₽ → 4 990 ₽.</t>
         </r>
       </text>
     </comment>
@@ -100,7 +124,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Рыночная база (сентябрь 2026): Gates K0120529 отдельно — 7 290–10 526 ₽ в рознице, ремень помпы — 740–1 679 ₽. Итоговая цена — база плюс повышение с листа «Параметры»; даже с ним кит дешевле, чем Gates и ремень помпы по отдельности на Яндекс Маркете.</t>
+          <t xml:space="preserve">Впритык к рынку (сентябрь 2026): Gates K0120529 в рознице 7 290–14 130 ₽ (типично ≈9 610), ремень помпы 740–1 679 ₽ (≈1 200). Итого по отдельности ≈10 810 ₽ → 10 790 ₽.</t>
         </r>
       </text>
     </comment>
@@ -112,7 +136,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Рыночная база (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000). Итоговая цена — база плюс повышение с листа «Параметры».</t>
+          <t xml:space="preserve">Впритык к рынку (сентябрь 2026): диск AMD ≈1 700–2 300 ₽ за штуку (≈2 000 × 2), колодки AMDBF453 806–1 289 ₽ (≈1 020), смазка ≈100–150 ₽. Итого по отдельности ≈5 145 ₽ → 5 090 ₽.</t>
         </r>
       </text>
     </comment>
@@ -124,7 +148,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Рыночная база (сентябрь 2026): диск AMD в рознице ≈1 700–2 300 ₽ за штуку, колодки AMDBF453 — 806–1 289 ₽ (обычно ≈1 020), смазка ≈100–150 ₽. По отдельности покупатель отдаст ≈5 150 ₽ (от 4 300 до 6 000). Итоговая цена — база плюс повышение с листа «Параметры».</t>
+          <t xml:space="preserve">Впритык к рынку (сентябрь 2026): диск AMD ≈1 700–2 300 ₽ за штуку (≈2 000 × 2), колодки AMDBF453 806–1 289 ₽ (≈1 020), смазка ≈100–150 ₽. Итого по отдельности ≈5 145 ₽ → 5 090 ₽.</t>
         </r>
       </text>
     </comment>
@@ -153,7 +177,7 @@
     <t xml:space="preserve">3. «Киты» — сами посчитаются закупка, цена на Авито и прибыль до налога в двух вариантах: оплата через Авито Доставку и прямым переводом.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком. Колонка Y «Цена по рынку (база)» — если цену кита ставим по рынку, а не по наценке.</t>
+    <t xml:space="preserve">    Впишите минимальную цену конкурентов — появится сравнение с рынком. Колонка Y «Цена по рынку» — цена впритык к рынку; если она есть, наценка не применяется.</t>
   </si>
   <si>
     <t xml:space="preserve">4. «Параметры» — наценка, повышение цен (+5%), комиссии, резерв на товар, постоянные расходы и план заказов. Поменяете там — пересчитается всё.</t>
@@ -252,7 +276,7 @@
     <t xml:space="preserve">Статус</t>
   </si>
   <si>
-    <t xml:space="preserve">Цена по рынку (база), ₽</t>
+    <t xml:space="preserve">Цена по рынку, ₽</t>
   </si>
   <si>
     <t xml:space="preserve">TO-01</t>
@@ -804,7 +828,7 @@
     <t xml:space="preserve">Средний чек кита, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Среднее по собранным китам, уже с повышением цен: ТО-кит: Kia Picanto 1.0 / 1.2 (4 390 ₽), VW Jetta (5 090 ₽); ГРМ-кит: Geely Coolray 1.5T (10 490 ₽); Тормоз-кит: Kia Rio 2017–2021 (5 290 ₽), Hyundai Solaris 2017–2022 (5 290 ₽). Замените, когда соберёте больше китов.</t>
+    <t xml:space="preserve">Среднее по собранным китам, уже с повышением цен: ТО-кит: Kia Picanto 1.0 / 1.2 (4 090 ₽), VW Jetta (4 990 ₽); ГРМ-кит: Geely Coolray 1.5T (10 790 ₽); Тормоз-кит: Kia Rio 2017–2021 (5 090 ₽), Hyundai Solaris 2017–2022 (5 090 ₽). Замените, когда соберёте больше китов.</t>
   </si>
   <si>
     <t xml:space="preserve">Средняя стоимость деталей, ₽</t>
@@ -927,10 +951,10 @@
     <t xml:space="preserve">Чтобы цена заканчивалась на …90 (4 700 → 4 690).</t>
   </si>
   <si>
-    <t xml:space="preserve">Повышение цен ко всем китам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ваше решение: +5% сверху ко всем китам — и к цене по наценке, и к цене по рынку (колонка Y на листе «Киты»). Затем снова округление до …90. Поставьте 0%, чтобы убрать.</t>
+    <t xml:space="preserve">Повышение цен (для китов без цены по рынку)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5% сверху к цене по наценке, затем округление до …90. Киты с ценой по рынку (колонка Y на листе «Киты») стоят впритык к рынку, повышение к ним не добавляется.</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссия Авито Доставки</t>
@@ -2235,7 +2259,7 @@
         <v/>
       </c>
       <c r="M2" s="11" t="str">
-        <f aca="false">IF(I2="","",CEILING((IF(Y2&lt;&gt;"",Y2,CEILING((I2*(1+Параметры!$B$9*Параметры!$B$10)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I2="","",IF(Y2&lt;&gt;"",Y2,CEILING((CEILING((I2*(1+Параметры!$B$9*Параметры!$B$10)+K2)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N2" s="12"/>
@@ -2322,7 +2346,7 @@
         <v/>
       </c>
       <c r="M3" s="11" t="str">
-        <f aca="false">IF(I3="","",CEILING((IF(Y3&lt;&gt;"",Y3,CEILING((I3*(1+Параметры!$B$9*Параметры!$B$10)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I3="","",IF(Y3&lt;&gt;"",Y3,CEILING((CEILING((I3*(1+Параметры!$B$9*Параметры!$B$10)+K3)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N3" s="12"/>
@@ -2409,7 +2433,7 @@
         <v/>
       </c>
       <c r="M4" s="11" t="str">
-        <f aca="false">IF(I4="","",CEILING((IF(Y4&lt;&gt;"",Y4,CEILING((I4*(1+Параметры!$B$9*Параметры!$B$10)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I4="","",IF(Y4&lt;&gt;"",Y4,CEILING((CEILING((I4*(1+Параметры!$B$9*Параметры!$B$10)+K4)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N4" s="12"/>
@@ -2496,7 +2520,7 @@
         <v/>
       </c>
       <c r="M5" s="11" t="str">
-        <f aca="false">IF(I5="","",CEILING((IF(Y5&lt;&gt;"",Y5,CEILING((I5*(1+Параметры!$B$9*Параметры!$B$10)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I5="","",IF(Y5&lt;&gt;"",Y5,CEILING((CEILING((I5*(1+Параметры!$B$9*Параметры!$B$10)+K5)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N5" s="12"/>
@@ -2583,7 +2607,7 @@
         <v/>
       </c>
       <c r="M6" s="11" t="str">
-        <f aca="false">IF(I6="","",CEILING((IF(Y6&lt;&gt;"",Y6,CEILING((I6*(1+Параметры!$B$9*Параметры!$B$10)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I6="","",IF(Y6&lt;&gt;"",Y6,CEILING((CEILING((I6*(1+Параметры!$B$9*Параметры!$B$10)+K6)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N6" s="12"/>
@@ -2670,7 +2694,7 @@
         <v/>
       </c>
       <c r="M7" s="11" t="str">
-        <f aca="false">IF(I7="","",CEILING((IF(Y7&lt;&gt;"",Y7,CEILING((I7*(1+Параметры!$B$9*Параметры!$B$10)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I7="","",IF(Y7&lt;&gt;"",Y7,CEILING((CEILING((I7*(1+Параметры!$B$9*Параметры!$B$10)+K7)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N7" s="12"/>
@@ -2757,7 +2781,7 @@
         <v/>
       </c>
       <c r="M8" s="11" t="str">
-        <f aca="false">IF(I8="","",CEILING((IF(Y8&lt;&gt;"",Y8,CEILING((I8*(1+Параметры!$B$9*Параметры!$B$10)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I8="","",IF(Y8&lt;&gt;"",Y8,CEILING((CEILING((I8*(1+Параметры!$B$9*Параметры!$B$10)+K8)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N8" s="12"/>
@@ -2844,7 +2868,7 @@
         <v/>
       </c>
       <c r="M9" s="11" t="str">
-        <f aca="false">IF(I9="","",CEILING((IF(Y9&lt;&gt;"",Y9,CEILING((I9*(1+Параметры!$B$9*Параметры!$B$10)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I9="","",IF(Y9&lt;&gt;"",Y9,CEILING((CEILING((I9*(1+Параметры!$B$9*Параметры!$B$10)+K9)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N9" s="12"/>
@@ -2931,7 +2955,7 @@
         <v/>
       </c>
       <c r="M10" s="11" t="str">
-        <f aca="false">IF(I10="","",CEILING((IF(Y10&lt;&gt;"",Y10,CEILING((I10*(1+Параметры!$B$9*Параметры!$B$10)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I10="","",IF(Y10&lt;&gt;"",Y10,CEILING((CEILING((I10*(1+Параметры!$B$9*Параметры!$B$10)+K10)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N10" s="12"/>
@@ -3018,7 +3042,7 @@
         <v/>
       </c>
       <c r="M11" s="11" t="str">
-        <f aca="false">IF(I11="","",CEILING((IF(Y11&lt;&gt;"",Y11,CEILING((I11*(1+Параметры!$B$9*Параметры!$B$10)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I11="","",IF(Y11&lt;&gt;"",Y11,CEILING((CEILING((I11*(1+Параметры!$B$9*Параметры!$B$10)+K11)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N11" s="12"/>
@@ -3105,7 +3129,7 @@
         <v/>
       </c>
       <c r="M12" s="11" t="str">
-        <f aca="false">IF(I12="","",CEILING((IF(Y12&lt;&gt;"",Y12,CEILING((I12*(1+Параметры!$B$9*Параметры!$B$10)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I12="","",IF(Y12&lt;&gt;"",Y12,CEILING((CEILING((I12*(1+Параметры!$B$9*Параметры!$B$10)+K12)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N12" s="12"/>
@@ -3192,7 +3216,7 @@
         <v/>
       </c>
       <c r="M13" s="11" t="str">
-        <f aca="false">IF(I13="","",CEILING((IF(Y13&lt;&gt;"",Y13,CEILING((I13*(1+Параметры!$B$9*Параметры!$B$10)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I13="","",IF(Y13&lt;&gt;"",Y13,CEILING((CEILING((I13*(1+Параметры!$B$9*Параметры!$B$10)+K13)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N13" s="12"/>
@@ -3279,7 +3303,7 @@
         <v/>
       </c>
       <c r="M14" s="11" t="str">
-        <f aca="false">IF(I14="","",CEILING((IF(Y14&lt;&gt;"",Y14,CEILING((I14*(1+Параметры!$B$9*Параметры!$B$10)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I14="","",IF(Y14&lt;&gt;"",Y14,CEILING((CEILING((I14*(1+Параметры!$B$9*Параметры!$B$10)+K14)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N14" s="12"/>
@@ -3322,7 +3346,9 @@
       <c r="X14" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Y14" s="12"/>
+      <c r="Y14" s="12" t="n">
+        <v>4090</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
@@ -3366,7 +3392,7 @@
         <v/>
       </c>
       <c r="M15" s="11" t="str">
-        <f aca="false">IF(I15="","",CEILING((IF(Y15&lt;&gt;"",Y15,CEILING((I15*(1+Параметры!$B$9*Параметры!$B$10)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I15="","",IF(Y15&lt;&gt;"",Y15,CEILING((CEILING((I15*(1+Параметры!$B$9*Параметры!$B$10)+K15)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N15" s="12"/>
@@ -3409,7 +3435,9 @@
       <c r="X15" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Y15" s="12"/>
+      <c r="Y15" s="12" t="n">
+        <v>4990</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
@@ -3453,7 +3481,7 @@
         <v/>
       </c>
       <c r="M16" s="11" t="str">
-        <f aca="false">IF(I16="","",CEILING((IF(Y16&lt;&gt;"",Y16,CEILING((I16*(1+Параметры!$B$9*Параметры!$B$10)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I16="","",IF(Y16&lt;&gt;"",Y16,CEILING((CEILING((I16*(1+Параметры!$B$9*Параметры!$B$10)+K16)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N16" s="12"/>
@@ -3540,7 +3568,7 @@
         <v/>
       </c>
       <c r="M17" s="11" t="str">
-        <f aca="false">IF(I17="","",CEILING((IF(Y17&lt;&gt;"",Y17,CEILING((I17*(1+Параметры!$B$9*Параметры!$B$10)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I17="","",IF(Y17&lt;&gt;"",Y17,CEILING((CEILING((I17*(1+Параметры!$B$9*Параметры!$B$10)+K17)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N17" s="12"/>
@@ -3627,7 +3655,7 @@
         <v/>
       </c>
       <c r="M18" s="11" t="str">
-        <f aca="false">IF(I18="","",CEILING((IF(Y18&lt;&gt;"",Y18,CEILING((I18*(1+Параметры!$B$9*Параметры!$B$10)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I18="","",IF(Y18&lt;&gt;"",Y18,CEILING((CEILING((I18*(1+Параметры!$B$9*Параметры!$B$10)+K18)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N18" s="12"/>
@@ -3714,7 +3742,7 @@
         <v/>
       </c>
       <c r="M19" s="11" t="str">
-        <f aca="false">IF(I19="","",CEILING((IF(Y19&lt;&gt;"",Y19,CEILING((I19*(1+Параметры!$B$9*Параметры!$B$10)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I19="","",IF(Y19&lt;&gt;"",Y19,CEILING((CEILING((I19*(1+Параметры!$B$9*Параметры!$B$10)+K19)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N19" s="12"/>
@@ -3801,7 +3829,7 @@
         <v/>
       </c>
       <c r="M20" s="11" t="str">
-        <f aca="false">IF(I20="","",CEILING((IF(Y20&lt;&gt;"",Y20,CEILING((I20*(1+Параметры!$B$9*Параметры!$B$10)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I20="","",IF(Y20&lt;&gt;"",Y20,CEILING((CEILING((I20*(1+Параметры!$B$9*Параметры!$B$10)+K20)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N20" s="12"/>
@@ -3888,7 +3916,7 @@
         <v/>
       </c>
       <c r="M21" s="11" t="str">
-        <f aca="false">IF(I21="","",CEILING((IF(Y21&lt;&gt;"",Y21,CEILING((I21*(1+Параметры!$B$9*Параметры!$B$10)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I21="","",IF(Y21&lt;&gt;"",Y21,CEILING((CEILING((I21*(1+Параметры!$B$9*Параметры!$B$10)+K21)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N21" s="12"/>
@@ -3975,7 +4003,7 @@
         <v/>
       </c>
       <c r="M22" s="11" t="str">
-        <f aca="false">IF(I22="","",CEILING((IF(Y22&lt;&gt;"",Y22,CEILING((I22*(1+Параметры!$B$9*Параметры!$B$10)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I22="","",IF(Y22&lt;&gt;"",Y22,CEILING((CEILING((I22*(1+Параметры!$B$9*Параметры!$B$10)+K22)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N22" s="12"/>
@@ -4062,7 +4090,7 @@
         <v/>
       </c>
       <c r="M23" s="11" t="str">
-        <f aca="false">IF(I23="","",CEILING((IF(Y23&lt;&gt;"",Y23,CEILING((I23*(1+Параметры!$B$9*Параметры!$B$10)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I23="","",IF(Y23&lt;&gt;"",Y23,CEILING((CEILING((I23*(1+Параметры!$B$9*Параметры!$B$10)+K23)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N23" s="12"/>
@@ -4149,7 +4177,7 @@
         <v/>
       </c>
       <c r="M24" s="11" t="str">
-        <f aca="false">IF(I24="","",CEILING((IF(Y24&lt;&gt;"",Y24,CEILING((I24*(1+Параметры!$B$9*Параметры!$B$10)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I24="","",IF(Y24&lt;&gt;"",Y24,CEILING((CEILING((I24*(1+Параметры!$B$9*Параметры!$B$10)+K24)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N24" s="12"/>
@@ -4236,7 +4264,7 @@
         <v/>
       </c>
       <c r="M25" s="11" t="str">
-        <f aca="false">IF(I25="","",CEILING((IF(Y25&lt;&gt;"",Y25,CEILING((I25*(1+Параметры!$B$9*Параметры!$B$10)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I25="","",IF(Y25&lt;&gt;"",Y25,CEILING((CEILING((I25*(1+Параметры!$B$9*Параметры!$B$10)+K25)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N25" s="12"/>
@@ -4323,7 +4351,7 @@
         <v/>
       </c>
       <c r="M26" s="11" t="str">
-        <f aca="false">IF(I26="","",CEILING((IF(Y26&lt;&gt;"",Y26,CEILING((I26*(1+Параметры!$B$9*Параметры!$B$10)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I26="","",IF(Y26&lt;&gt;"",Y26,CEILING((CEILING((I26*(1+Параметры!$B$9*Параметры!$B$10)+K26)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N26" s="12"/>
@@ -4367,7 +4395,7 @@
         <v>48</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>9990</v>
+        <v>10790</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4412,7 +4440,7 @@
         <v/>
       </c>
       <c r="M27" s="11" t="str">
-        <f aca="false">IF(I27="","",CEILING((IF(Y27&lt;&gt;"",Y27,CEILING((I27*(1+Параметры!$B$9*Параметры!$B$10)+K27)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I27="","",IF(Y27&lt;&gt;"",Y27,CEILING((CEILING((I27*(1+Параметры!$B$9*Параметры!$B$10)+K27)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N27" s="12"/>
@@ -4456,7 +4484,7 @@
         <v>48</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>4990</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4501,7 +4529,7 @@
         <v/>
       </c>
       <c r="M28" s="11" t="str">
-        <f aca="false">IF(I28="","",CEILING((IF(Y28&lt;&gt;"",Y28,CEILING((I28*(1+Параметры!$B$9*Параметры!$B$10)+K28)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5))*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5)</f>
+        <f aca="false">IF(I28="","",IF(Y28&lt;&gt;"",Y28,CEILING((CEILING((I28*(1+Параметры!$B$9*Параметры!$B$10)+K28)*(1+Параметры!$B$2),Параметры!$B$4)-Параметры!$B$5)*(1+Параметры!$B$6),Параметры!$B$4)-Параметры!$B$5))</f>
         <v/>
       </c>
       <c r="N28" s="12"/>
@@ -4545,7 +4573,7 @@
         <v>48</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>4990</v>
+        <v>5090</v>
       </c>
     </row>
   </sheetData>
@@ -12849,13 +12877,13 @@
         <v>222</v>
       </c>
       <c r="B4" s="12" t="n">
-        <v>4740</v>
+        <v>4540</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>10490</v>
+        <v>10790</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>5290</v>
+        <v>5090</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>223</v>
@@ -12977,15 +13005,15 @@
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">IF(B4="","",B4-(B5+Параметры!$B$3)-$B$6*B4*Параметры!$B$7-(1-$B$6)*(B4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-B5*Параметры!$B$9)</f>
-        <v>806.0155</v>
+        <v>613.2155</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">IF(C4="","",C4-(C5+Параметры!$B$3)-$B$6*C4*Параметры!$B$7-(1-$B$6)*(C4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-C5*Параметры!$B$9)</f>
-        <v>2473.3185</v>
+        <v>2762.5185</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">IF(D4="","",D4-(D5+Параметры!$B$3)-$B$6*D4*Параметры!$B$7-(1-$B$6)*(D4*Параметры!$B$11+Параметры!$B$12)-Параметры!$B$8-D5*Параметры!$B$9)</f>
-        <v>1063.73</v>
+        <v>870.93</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12994,15 +13022,15 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">IF(B10="","",IF(B10&lt;=0,"не окупается",ROUNDUP($B$9/B10,0)))</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">IF(C10="","",IF(C10&lt;=0,"не окупается",ROUNDUP($B$9/C10,0)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">IF(D10="","",IF(D10&lt;=0,"не окупается",ROUNDUP($B$9/D10,0)))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>234</v>
@@ -13076,7 +13104,7 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">N(B14)*N($B$4)+N(C14)*N($C$4)+N(D14)*N($D$4)</f>
-        <v>94800</v>
+        <v>90800</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">N(B14)*(N($B$5)+Параметры!$B$3)+N(C14)*(N($C$5)+Параметры!$B$3)+N(D14)*(N($D$5)+Параметры!$B$3)</f>
@@ -13084,11 +13112,11 @@
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">$B$6*E14*Параметры!$B$7</f>
-        <v>3081</v>
+        <v>2951</v>
       </c>
       <c r="H14" s="9" t="n">
         <f aca="false">(1-$B$6)*E14*Параметры!$B$11</f>
-        <v>331.8</v>
+        <v>317.8</v>
       </c>
       <c r="I14" s="9" t="n">
         <f aca="false">(B14+C14+D14)*Параметры!$B$8</f>
@@ -13108,11 +13136,11 @@
       </c>
       <c r="M14" s="11" t="n">
         <f aca="false">E14-SUM(F14:L14)</f>
-        <v>3337.31</v>
+        <v>-518.690000000002</v>
       </c>
       <c r="N14" s="9" t="n">
         <f aca="false">IF((B14+C14+D14)=0,"",M14/(B14+C14+D14))</f>
-        <v>166.8655</v>
+        <v>-25.9345000000001</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13130,7 +13158,7 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">N(B15)*N($B$4)+N(C15)*N($C$4)+N(D15)*N($D$4)</f>
-        <v>104900</v>
+        <v>107900</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">N(B15)*(N($B$5)+Параметры!$B$3)+N(C15)*(N($C$5)+Параметры!$B$3)+N(D15)*(N($D$5)+Параметры!$B$3)</f>
@@ -13138,11 +13166,11 @@
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">$B$6*E15*Параметры!$B$7</f>
-        <v>3409.25</v>
+        <v>3506.75</v>
       </c>
       <c r="H15" s="9" t="n">
         <f aca="false">(1-$B$6)*E15*Параметры!$B$11</f>
-        <v>367.15</v>
+        <v>377.65</v>
       </c>
       <c r="I15" s="9" t="n">
         <f aca="false">(B15+C15+D15)*Параметры!$B$8</f>
@@ -13162,11 +13190,11 @@
       </c>
       <c r="M15" s="11" t="n">
         <f aca="false">E15-SUM(F15:L15)</f>
-        <v>11950.185</v>
+        <v>14842.185</v>
       </c>
       <c r="N15" s="9" t="n">
         <f aca="false">IF((B15+C15+D15)=0,"",M15/(B15+C15+D15))</f>
-        <v>1195.0185</v>
+        <v>1484.2185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13184,7 +13212,7 @@
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">N(B16)*N($B$4)+N(C16)*N($C$4)+N(D16)*N($D$4)</f>
-        <v>52900</v>
+        <v>50900</v>
       </c>
       <c r="F16" s="9" t="n">
         <f aca="false">N(B16)*(N($B$5)+Параметры!$B$3)+N(C16)*(N($C$5)+Параметры!$B$3)+N(D16)*(N($D$5)+Параметры!$B$3)</f>
@@ -13192,11 +13220,11 @@
       </c>
       <c r="G16" s="9" t="n">
         <f aca="false">$B$6*E16*Параметры!$B$7</f>
-        <v>1719.25</v>
+        <v>1654.25</v>
       </c>
       <c r="H16" s="9" t="n">
         <f aca="false">(1-$B$6)*E16*Параметры!$B$11</f>
-        <v>185.15</v>
+        <v>178.15</v>
       </c>
       <c r="I16" s="9" t="n">
         <f aca="false">(B16+C16+D16)*Параметры!$B$8</f>
@@ -13216,11 +13244,11 @@
       </c>
       <c r="M16" s="11" t="n">
         <f aca="false">E16-SUM(F16:L16)</f>
-        <v>-2145.7</v>
+        <v>-4073.7</v>
       </c>
       <c r="N16" s="9" t="n">
         <f aca="false">IF((B16+C16+D16)=0,"",M16/(B16+C16+D16))</f>
-        <v>-214.57</v>
+        <v>-407.37</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13238,7 +13266,7 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">N(B17)*N($B$4)+N(C17)*N($C$4)+N(D17)*N($D$4)</f>
-        <v>126300</v>
+        <v>124800</v>
       </c>
       <c r="F17" s="9" t="n">
         <f aca="false">N(B17)*(N($B$5)+Параметры!$B$3)+N(C17)*(N($C$5)+Параметры!$B$3)+N(D17)*(N($D$5)+Параметры!$B$3)</f>
@@ -13246,11 +13274,11 @@
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">$B$6*E17*Параметры!$B$7</f>
-        <v>4104.75</v>
+        <v>4056</v>
       </c>
       <c r="H17" s="9" t="n">
         <f aca="false">(1-$B$6)*E17*Параметры!$B$11</f>
-        <v>442.05</v>
+        <v>436.8</v>
       </c>
       <c r="I17" s="9" t="n">
         <f aca="false">(B17+C17+D17)*Параметры!$B$8</f>
@@ -13270,11 +13298,11 @@
       </c>
       <c r="M17" s="11" t="n">
         <f aca="false">E17-SUM(F17:L17)</f>
-        <v>12962.3975</v>
+        <v>11516.3975</v>
       </c>
       <c r="N17" s="9" t="n">
         <f aca="false">IF((B17+C17+D17)=0,"",M17/(B17+C17+D17))</f>
-        <v>648.119875</v>
+        <v>575.819875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13292,7 +13320,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">N(B18)*N($B$4)+N(C18)*N($C$4)+N(D18)*N($D$4)</f>
-        <v>252600</v>
+        <v>249600</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">N(B18)*(N($B$5)+Параметры!$B$3)+N(C18)*(N($C$5)+Параметры!$B$3)+N(D18)*(N($D$5)+Параметры!$B$3)</f>
@@ -13300,11 +13328,11 @@
       </c>
       <c r="G18" s="9" t="n">
         <f aca="false">$B$6*E18*Параметры!$B$7</f>
-        <v>8209.5</v>
+        <v>8112</v>
       </c>
       <c r="H18" s="9" t="n">
         <f aca="false">(1-$B$6)*E18*Параметры!$B$11</f>
-        <v>884.1</v>
+        <v>873.6</v>
       </c>
       <c r="I18" s="9" t="n">
         <f aca="false">(B18+C18+D18)*Параметры!$B$8</f>
@@ -13324,11 +13352,11 @@
       </c>
       <c r="M18" s="11" t="n">
         <f aca="false">E18-SUM(F18:L18)</f>
-        <v>38707.795</v>
+        <v>35815.795</v>
       </c>
       <c r="N18" s="9" t="n">
         <f aca="false">IF((B18+C18+D18)=0,"",M18/(B18+C18+D18))</f>
-        <v>967.694875</v>
+        <v>895.394875</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13346,7 +13374,7 @@
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">N(B19)*N($B$4)+N(C19)*N($C$4)+N(D19)*N($D$4)</f>
-        <v>378900</v>
+        <v>374400</v>
       </c>
       <c r="F19" s="9" t="n">
         <f aca="false">N(B19)*(N($B$5)+Параметры!$B$3)+N(C19)*(N($C$5)+Параметры!$B$3)+N(D19)*(N($D$5)+Параметры!$B$3)</f>
@@ -13354,11 +13382,11 @@
       </c>
       <c r="G19" s="9" t="n">
         <f aca="false">$B$6*E19*Параметры!$B$7</f>
-        <v>12314.25</v>
+        <v>12168</v>
       </c>
       <c r="H19" s="9" t="n">
         <f aca="false">(1-$B$6)*E19*Параметры!$B$11</f>
-        <v>1326.15</v>
+        <v>1310.4</v>
       </c>
       <c r="I19" s="9" t="n">
         <f aca="false">(B19+C19+D19)*Параметры!$B$8</f>
@@ -13378,11 +13406,11 @@
       </c>
       <c r="M19" s="11" t="n">
         <f aca="false">E19-SUM(F19:L19)</f>
-        <v>64453.1925</v>
+        <v>60115.1925</v>
       </c>
       <c r="N19" s="9" t="n">
         <f aca="false">IF((B19+C19+D19)=0,"",M19/(B19+C19+D19))</f>
-        <v>1074.219875</v>
+        <v>1001.919875</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13400,7 +13428,7 @@
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">N(B20)*N($B$4)+N(C20)*N($C$4)+N(D20)*N($D$4)</f>
-        <v>552600</v>
+        <v>544600</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">N(B20)*(N($B$5)+Параметры!$B$3)+N(C20)*(N($C$5)+Параметры!$B$3)+N(D20)*(N($D$5)+Параметры!$B$3)</f>
@@ -13408,11 +13436,11 @@
       </c>
       <c r="G20" s="9" t="n">
         <f aca="false">$B$6*E20*Параметры!$B$7</f>
-        <v>17959.5</v>
+        <v>17699.5</v>
       </c>
       <c r="H20" s="9" t="n">
         <f aca="false">(1-$B$6)*E20*Параметры!$B$11</f>
-        <v>1934.1</v>
+        <v>1906.1</v>
       </c>
       <c r="I20" s="9" t="n">
         <f aca="false">(B20+C20+D20)*Параметры!$B$8</f>
@@ -13432,11 +13460,11 @@
       </c>
       <c r="M20" s="11" t="n">
         <f aca="false">E20-SUM(F20:L20)</f>
-        <v>98258.745</v>
+        <v>90546.745</v>
       </c>
       <c r="N20" s="9" t="n">
         <f aca="false">IF((B20+C20+D20)=0,"",M20/(B20+C20+D20))</f>
-        <v>1091.76383333333</v>
+        <v>1006.07494444444</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
